--- a/.cursor/scratch/tax_turbo_parts/Personal Income 2025 — like last year (EPGC+Art+GCM).xlsx
+++ b/.cursor/scratch/tax_turbo_parts/Personal Income 2025 — like last year (EPGC+Art+GCM).xlsx
@@ -175,7 +175,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -263,11 +263,16 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="10" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="10" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -280,7 +285,6 @@
     <xf numFmtId="0" fontId="14" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="8" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -290,7 +294,12 @@
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -2450,8 +2459,8 @@
       <c r="F54" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="G54" s="10" t="n">
-        <v>0</v>
+      <c r="G54" s="9" t="n">
+        <v>13595</v>
       </c>
       <c r="H54" s="10" t="n">
         <v>0</v>
@@ -3186,7 +3195,7 @@
     <row r="75">
       <c r="A75" s="14" t="inlineStr">
         <is>
-          <t>2025 Mercury unbundled 2026-09-20: Art Sales = MATCHED cash only (Berk $14,000 Jan + Berk $30,000 / mosaics $105,000 Feb = $149,000). Prior mixed Mercury dump removed. Consultant $0 until EOEB remainder $130,270.00 and L5 $87,396.32 are answered. Coinbase is Investments, not this tab. Newstar $23,581 is Art Sales COGS, not operating expense. 2024 leftover supplies/furniture/consultant-fee numbers on this 2025 block were zeroed. GCM 1099 is personal. Not tax advice.</t>
+          <t>2025 Mercury 2026-09-20: Art Sales = MATCHED cash only (Berk $14,000 Jan + Berk $30,000 / mosaics $105,000 Feb = $149,000). Consultant June $13,595 = David Aaron Limited LOCKED (user: consultant fee, not a sale). EOEB remainder $130,270.00 and L5 $87,396.32 still ASK — not on Consultant. Koziol/Ariadne $150,000 LOCKED pass-through — not P&amp;L. Coinbase is Investments, not this tab. Newstar $23,581 is Art Sales COGS, not operating expense. 2024 leftover supplies/furniture/consultant-fee numbers on this 2025 block were zeroed. GCM 1099 is personal. Not tax advice.</t>
         </is>
       </c>
     </row>
@@ -5897,7 +5906,7 @@
     <row r="78">
       <c r="A78" s="39" t="inlineStr">
         <is>
-          <t>Mercury 8291 MATCHED: Berk $14,000 (1/10 seals) + $30,000 (2/7 lots). EOEB $105,000 (2/21 mosaics). Fortuna $13,000 (1/8 seals Cost). Plutus $50,000 of mosaics $90,000 Cost — $40,000 of Cost not on 8291 (ASK). Newstar $23,581 is jewelry fabrication COGS, parked below — not in sold-lot Cost (Berk gem/scarab lots already sold in February). Not tax advice.</t>
+          <t>Mercury 8291 MATCHED: Berk $14,000 (1/10 seals) + $30,000 (2/7 lots). EOEB $105,000 (2/21 mosaics). Fortuna $13,000 (1/8 seals Cost). Plutus $50,000 of mosaics $90,000 Cost — $40,000 of Cost not on 8291 (ASK). Newstar $23,581 is jewelry fabrication COGS, parked below — not in sold-lot Cost (Berk gem/scarab lots already sold in February). David Aaron $13,595 (6/24) is LOCKED consultant fee — not a sale (EPGC Consultant June). Not tax advice.</t>
         </is>
       </c>
     </row>
@@ -6534,69 +6543,58 @@
     </row>
     <row r="118"/>
     <row r="119">
-      <c r="A119" s="41" t="inlineStr">
-        <is>
-          <t>2025 Mercury 8291 — proposed sale / ASK cash (not in EPGC Art Sales until confirmed)</t>
+      <c r="A119" s="43" t="inlineStr">
+        <is>
+          <t>2025 Mercury 8291 — David Aaron Limited is LOCKED consultant fee (not Art Sales)</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="43" t="inlineStr">
-        <is>
-          <t>Proposed: object TBD (David Aaron Limited invoice)</t>
-        </is>
-      </c>
-      <c r="B120" s="43" t="inlineStr">
+      <c r="A120" s="44" t="inlineStr">
+        <is>
+          <t>NOT a 2025 art sale — David Aaron Limited consultant fee (EPGC Consultant June)</t>
+        </is>
+      </c>
+      <c r="B120" s="44" t="inlineStr">
         <is>
           <t>David Aaron Limited</t>
         </is>
       </c>
-      <c r="E120" s="43" t="inlineStr">
-        <is>
-          <t>David Aaron Limited (London)</t>
-        </is>
-      </c>
-      <c r="F120" s="42" t="n">
-        <v>13595</v>
-      </c>
-      <c r="G120" s="32" t="inlineStr">
-        <is>
-          <t>2025-06-24</t>
-        </is>
-      </c>
-      <c r="H120" s="32">
-        <f>IF(OR(F120="",C120=""),"",F120-C120)</f>
-        <v/>
-      </c>
-      <c r="I120" s="43" t="inlineStr">
-        <is>
-          <t>PROPOSED art sale — confirm object. Mercury Request or Invoice Payment.</t>
+      <c r="C120" s="44" t="n"/>
+      <c r="D120" s="44" t="n"/>
+      <c r="E120" s="44" t="n"/>
+      <c r="F120" s="45" t="n"/>
+      <c r="G120" s="46" t="n"/>
+      <c r="H120" s="46" t="n"/>
+      <c r="I120" s="44" t="inlineStr">
+        <is>
+          <t>LOCKED 2026-09-20: consultant fee, not a sale. $13,595 is on EPGC Consultant June. Not tax advice.</t>
         </is>
       </c>
     </row>
     <row r="121"/>
     <row r="122">
-      <c r="A122" s="44" t="inlineStr">
+      <c r="A122" s="43" t="inlineStr">
         <is>
           <t>2025 Mercury COGS — Newstar Jewelers (LOCKED jewelry fabrication)</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="45" t="inlineStr">
+      <c r="A123" s="47" t="inlineStr">
         <is>
           <t>Newstar Jewelers — jewelry from intaglios / engraved gems / scarabs</t>
         </is>
       </c>
-      <c r="B123" s="45" t="inlineStr">
+      <c r="B123" s="47" t="inlineStr">
         <is>
           <t>Mercury 8291</t>
         </is>
       </c>
-      <c r="C123" s="46" t="n">
+      <c r="C123" s="48" t="n">
         <v>8000</v>
       </c>
-      <c r="D123" s="45" t="inlineStr">
+      <c r="D123" s="47" t="inlineStr">
         <is>
           <t>2025-10-14</t>
         </is>
@@ -6608,20 +6606,20 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="45" t="inlineStr">
+      <c r="A124" s="47" t="inlineStr">
         <is>
           <t>Newstar Jewelers — jewelry from intaglios / engraved gems / scarabs</t>
         </is>
       </c>
-      <c r="B124" s="45" t="inlineStr">
+      <c r="B124" s="47" t="inlineStr">
         <is>
           <t>Mercury 8291</t>
         </is>
       </c>
-      <c r="C124" s="46" t="n">
+      <c r="C124" s="48" t="n">
         <v>8000</v>
       </c>
-      <c r="D124" s="45" t="inlineStr">
+      <c r="D124" s="47" t="inlineStr">
         <is>
           <t>2025-11-12</t>
         </is>
@@ -6633,20 +6631,20 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="45" t="inlineStr">
+      <c r="A125" s="47" t="inlineStr">
         <is>
           <t>Newstar Jewelers — jewelry from intaglios / engraved gems / scarabs (3 of 3)</t>
         </is>
       </c>
-      <c r="B125" s="45" t="inlineStr">
+      <c r="B125" s="47" t="inlineStr">
         <is>
           <t>Mercury 8291</t>
         </is>
       </c>
-      <c r="C125" s="46" t="n">
+      <c r="C125" s="48" t="n">
         <v>7581</v>
       </c>
-      <c r="D125" s="45" t="inlineStr">
+      <c r="D125" s="47" t="inlineStr">
         <is>
           <t>2025-12-24</t>
         </is>
@@ -6663,26 +6661,26 @@
           <t>Newstar 2025 total</t>
         </is>
       </c>
-      <c r="C126" s="46">
+      <c r="C126" s="48">
         <f>SUM(C123:C125)</f>
         <v/>
       </c>
     </row>
     <row r="127"/>
     <row r="128">
-      <c r="A128" s="47" t="inlineStr">
+      <c r="A128" s="49" t="inlineStr">
         <is>
           <t>2025 Mercury ASK — Fortuna inventory remaining (not in Cost total until object is named)</t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="43" t="inlineStr">
+      <c r="A129" s="50" t="inlineStr">
         <is>
           <t>Fortuna / Erdal Dere — object TBD</t>
         </is>
       </c>
-      <c r="B129" s="43" t="inlineStr">
+      <c r="B129" s="50" t="inlineStr">
         <is>
           <t>Mercury 8291</t>
         </is>
@@ -6690,7 +6688,7 @@
       <c r="C129" s="42" t="n">
         <v>20000</v>
       </c>
-      <c r="D129" s="43" t="inlineStr">
+      <c r="D129" s="50" t="inlineStr">
         <is>
           <t>2025-05-09</t>
         </is>
@@ -6702,12 +6700,12 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="43" t="inlineStr">
+      <c r="A130" s="50" t="inlineStr">
         <is>
           <t>Fortuna / Erdal Dere — object TBD</t>
         </is>
       </c>
-      <c r="B130" s="43" t="inlineStr">
+      <c r="B130" s="50" t="inlineStr">
         <is>
           <t>Mercury 8291</t>
         </is>
@@ -6715,7 +6713,7 @@
       <c r="C130" s="42" t="n">
         <v>45000</v>
       </c>
-      <c r="D130" s="43" t="inlineStr">
+      <c r="D130" s="50" t="inlineStr">
         <is>
           <t>2025-07-21</t>
         </is>
@@ -6727,12 +6725,12 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="43" t="inlineStr">
+      <c r="A131" s="50" t="inlineStr">
         <is>
           <t>Fortuna / Erdal Dere — object TBD</t>
         </is>
       </c>
-      <c r="B131" s="43" t="inlineStr">
+      <c r="B131" s="50" t="inlineStr">
         <is>
           <t>Mercury 8291</t>
         </is>
@@ -6740,7 +6738,7 @@
       <c r="C131" s="42" t="n">
         <v>20000</v>
       </c>
-      <c r="D131" s="43" t="inlineStr">
+      <c r="D131" s="50" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
@@ -6785,15 +6783,15 @@
   <sheetData>
     <row r="1"/>
     <row r="2">
-      <c r="A2" s="48" t="inlineStr">
+      <c r="A2" s="51" t="inlineStr">
         <is>
           <t>GCM Boards 2022</t>
         </is>
       </c>
-      <c r="B2" s="49" t="n"/>
-      <c r="C2" s="49" t="n"/>
-      <c r="D2" s="49" t="n"/>
-      <c r="E2" s="49" t="n"/>
+      <c r="B2" s="52" t="n"/>
+      <c r="C2" s="52" t="n"/>
+      <c r="D2" s="52" t="n"/>
+      <c r="E2" s="52" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -6896,15 +6894,15 @@
     </row>
     <row r="8"/>
     <row r="9">
-      <c r="A9" s="48" t="inlineStr">
+      <c r="A9" s="51" t="inlineStr">
         <is>
           <t>GCM Boards 2023</t>
         </is>
       </c>
-      <c r="B9" s="49" t="n"/>
-      <c r="C9" s="49" t="n"/>
-      <c r="D9" s="49" t="n"/>
-      <c r="E9" s="49" t="n"/>
+      <c r="B9" s="52" t="n"/>
+      <c r="C9" s="52" t="n"/>
+      <c r="D9" s="52" t="n"/>
+      <c r="E9" s="52" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -6945,10 +6943,10 @@
       <c r="C11" s="5" t="n">
         <v>3675</v>
       </c>
-      <c r="D11" s="50" t="n">
+      <c r="D11" s="53" t="n">
         <v>3675</v>
       </c>
-      <c r="E11" s="50" t="n">
+      <c r="E11" s="53" t="n">
         <v>3675</v>
       </c>
     </row>
@@ -6990,15 +6988,15 @@
     </row>
     <row r="14"/>
     <row r="15">
-      <c r="A15" s="48" t="inlineStr">
+      <c r="A15" s="51" t="inlineStr">
         <is>
           <t>GCM Boards 2024</t>
         </is>
       </c>
-      <c r="B15" s="49" t="n"/>
-      <c r="C15" s="49" t="n"/>
-      <c r="D15" s="49" t="n"/>
-      <c r="E15" s="49" t="n"/>
+      <c r="B15" s="52" t="n"/>
+      <c r="C15" s="52" t="n"/>
+      <c r="D15" s="52" t="n"/>
+      <c r="E15" s="52" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -7039,10 +7037,10 @@
       <c r="C17" s="5" t="n">
         <v>4050</v>
       </c>
-      <c r="D17" s="50" t="n">
+      <c r="D17" s="53" t="n">
         <v>4050</v>
       </c>
-      <c r="E17" s="50" t="n">
+      <c r="E17" s="53" t="n">
         <v>4050</v>
       </c>
     </row>
@@ -7084,11 +7082,11 @@
     </row>
     <row r="20">
       <c r="A20" s="22" t="n"/>
-      <c r="B20" s="51" t="n"/>
+      <c r="B20" s="54" t="n"/>
     </row>
     <row r="21"/>
     <row r="22">
-      <c r="A22" s="52" t="inlineStr">
+      <c r="A22" s="55" t="inlineStr">
         <is>
           <t>GCM Boards 2025</t>
         </is>
@@ -7127,16 +7125,16 @@
           <t>GCM Board</t>
         </is>
       </c>
-      <c r="B24" s="53" t="n">
+      <c r="B24" s="56" t="n">
         <v>4100</v>
       </c>
-      <c r="C24" s="53" t="n">
+      <c r="C24" s="56" t="n">
         <v>9200</v>
       </c>
-      <c r="D24" s="53" t="n">
+      <c r="D24" s="56" t="n">
         <v>4100</v>
       </c>
-      <c r="E24" s="53" t="n">
+      <c r="E24" s="56" t="n">
         <v>4100</v>
       </c>
     </row>
@@ -7250,80 +7248,80 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="52" t="inlineStr">
+      <c r="A5" s="55" t="inlineStr">
         <is>
           <t>Coinbase (ACH from Mercury 8291)</t>
         </is>
       </c>
-      <c r="B5" s="54" t="inlineStr">
+      <c r="B5" s="57" t="inlineStr">
         <is>
           <t>Investment transfers — not EPGC Art Sales, not advisory. Distinct from Coinbase 6108 card.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="55" t="inlineStr"/>
-      <c r="B6" s="55" t="inlineStr">
+      <c r="A6" s="58" t="inlineStr"/>
+      <c r="B6" s="58" t="inlineStr">
         <is>
           <t>JAN</t>
         </is>
       </c>
-      <c r="C6" s="55" t="inlineStr">
+      <c r="C6" s="58" t="inlineStr">
         <is>
           <t>FEB</t>
         </is>
       </c>
-      <c r="D6" s="55" t="inlineStr">
+      <c r="D6" s="58" t="inlineStr">
         <is>
           <t>MAR</t>
         </is>
       </c>
-      <c r="E6" s="55" t="inlineStr">
+      <c r="E6" s="58" t="inlineStr">
         <is>
           <t>APR</t>
         </is>
       </c>
-      <c r="F6" s="55" t="inlineStr">
+      <c r="F6" s="58" t="inlineStr">
         <is>
           <t>MAY</t>
         </is>
       </c>
-      <c r="G6" s="55" t="inlineStr">
+      <c r="G6" s="58" t="inlineStr">
         <is>
           <t>JUN</t>
         </is>
       </c>
-      <c r="H6" s="55" t="inlineStr">
+      <c r="H6" s="58" t="inlineStr">
         <is>
           <t>JUL</t>
         </is>
       </c>
-      <c r="I6" s="55" t="inlineStr">
+      <c r="I6" s="58" t="inlineStr">
         <is>
           <t>AUG</t>
         </is>
       </c>
-      <c r="J6" s="55" t="inlineStr">
+      <c r="J6" s="58" t="inlineStr">
         <is>
           <t>SEP</t>
         </is>
       </c>
-      <c r="K6" s="55" t="inlineStr">
+      <c r="K6" s="58" t="inlineStr">
         <is>
           <t>OCT</t>
         </is>
       </c>
-      <c r="L6" s="55" t="inlineStr">
+      <c r="L6" s="58" t="inlineStr">
         <is>
           <t>NOV</t>
         </is>
       </c>
-      <c r="M6" s="55" t="inlineStr">
+      <c r="M6" s="58" t="inlineStr">
         <is>
           <t>DEC</t>
         </is>
       </c>
-      <c r="N6" s="55" t="inlineStr">
+      <c r="N6" s="58" t="inlineStr">
         <is>
           <t>2025 NET</t>
         </is>
@@ -7359,19 +7357,19 @@
       <c r="I7" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="J7" s="56" t="n">
+      <c r="J7" s="59" t="n">
         <v>-9000</v>
       </c>
-      <c r="K7" s="56" t="n">
+      <c r="K7" s="59" t="n">
         <v>-10000</v>
       </c>
-      <c r="L7" s="56" t="n">
+      <c r="L7" s="59" t="n">
         <v>-35000</v>
       </c>
-      <c r="M7" s="56" t="n">
+      <c r="M7" s="59" t="n">
         <v>-5000</v>
       </c>
-      <c r="N7" s="57">
+      <c r="N7" s="60">
         <f>SUM(B7:M7)</f>
         <v/>
       </c>
@@ -7415,10 +7413,10 @@
       <c r="L8" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="M8" s="56" t="n">
+      <c r="M8" s="59" t="n">
         <v>8000</v>
       </c>
-      <c r="N8" s="57">
+      <c r="N8" s="60">
         <f>SUM(B8:M8)</f>
         <v/>
       </c>
@@ -7453,26 +7451,26 @@
       <c r="I9" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="J9" s="58" t="n">
+      <c r="J9" s="45" t="n">
         <v>-9000</v>
       </c>
-      <c r="K9" s="58" t="n">
+      <c r="K9" s="45" t="n">
         <v>-10000</v>
       </c>
-      <c r="L9" s="58" t="n">
+      <c r="L9" s="45" t="n">
         <v>-35000</v>
       </c>
-      <c r="M9" s="58" t="n">
+      <c r="M9" s="45" t="n">
         <v>3000</v>
       </c>
-      <c r="N9" s="57">
+      <c r="N9" s="60">
         <f>SUM(B9:M9)</f>
         <v/>
       </c>
     </row>
     <row r="10"/>
     <row r="11">
-      <c r="A11" s="59" t="inlineStr">
+      <c r="A11" s="61" t="inlineStr">
         <is>
           <t>2025: funded $59,000.00 / returned $8,000.00 / net $-51,000.00 off the EPGC operating account. Not income, not an expense. Not tax advice.</t>
         </is>
@@ -7489,7 +7487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -7500,138 +7498,138 @@
     <row r="1">
       <c r="A1" s="41" t="inlineStr">
         <is>
-          <t>ASK — Mercury 8291 (answer these so EPGC Consultant / remaining sales can be booked). Not tax advice.</t>
+          <t>ASK — remaining Mercury 8291 questions. Q6 David Aaron consultant fee and Q8 Koziol/Ariadne pass-through LOCKED 2026-09-20. Not tax advice.</t>
         </is>
       </c>
     </row>
     <row r="2"/>
     <row r="3">
-      <c r="A3" s="55" t="inlineStr">
+      <c r="A3" s="58" t="inlineStr">
         <is>
           <t>Question</t>
         </is>
       </c>
-      <c r="B3" s="55" t="inlineStr">
+      <c r="B3" s="58" t="inlineStr">
         <is>
           <t>What I need</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="60" t="inlineStr">
+      <c r="A4" s="62" t="inlineStr">
         <is>
           <t>1. EOEB LLC remainder after mosaics</t>
         </is>
       </c>
-      <c r="B4" s="61" t="inlineStr">
+      <c r="B4" s="63" t="inlineStr">
         <is>
           <t>$130,270.00 of EOEB IN is not the $105,000 mosaics sale and not the $565.75 Wise reimbursement. Invoice / MAKE A PAYMENT pattern. Book as art advisory (EPGC Consultant) or as more art sales? Jan 16 $1,000 might be the Canosan horse (sold to Erdal $1,000 on Art Sales) — yes/no?</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="60" t="inlineStr">
+      <c r="A5" s="62" t="inlineStr">
         <is>
           <t>2. L5 (all seven invoices)</t>
         </is>
       </c>
-      <c r="B5" s="61" t="inlineStr">
+      <c r="B5" s="63" t="inlineStr">
         <is>
           <t>$87,396.32. Same Auto-Routing Request or Invoice Payment pattern as EOEB. Advisory fees, art sales, or mixed? The 7/15 $50,000 lands the same week as Aysel $50k and Fortuna $45k.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="60" t="inlineStr">
+      <c r="A6" s="62" t="inlineStr">
         <is>
           <t>3. Fortuna / Erdal Dere OUT after seals</t>
         </is>
       </c>
-      <c r="B6" s="61" t="inlineStr">
+      <c r="B6" s="63" t="inlineStr">
         <is>
           <t>$85,000.00 after the 1/8 $13,000 seals COGS (5/9 $20k, 7/21 $45k, 8/15 $20k). Inventory purchases (object names) or something else?</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="60" t="inlineStr">
+      <c r="A7" s="62" t="inlineStr">
         <is>
           <t>4. Erdal Dere IN</t>
         </is>
       </c>
-      <c r="B7" s="61" t="inlineStr">
+      <c r="B7" s="63" t="inlineStr">
         <is>
           <t>$57,000.00 (7/24 $26k, 10/9 $25k, 11/7 $6k ‘FORTUNA PAYMENT’). Sales to Erdal, refunds of Fortuna purchases, or other?</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="60" t="inlineStr">
+      <c r="A8" s="62" t="inlineStr">
         <is>
           <t>5. Aysel Dere $50,000 IN (7/18)</t>
         </is>
       </c>
-      <c r="B8" s="61" t="inlineStr">
+      <c r="B8" s="63" t="inlineStr">
         <is>
           <t>Sale, related-party transfer, or part of the mid-July Fortuna/L5 cluster?</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="60" t="inlineStr">
-        <is>
-          <t>6. David Aaron Limited $13,595 IN (6/24)</t>
-        </is>
-      </c>
-      <c r="B9" s="61" t="inlineStr">
-        <is>
-          <t>Proposed art sale (London antiquities dealer invoice). Confirm object. If it is a purchase you paid and they refunded, say so.</t>
+      <c r="A9" s="64" t="inlineStr">
+        <is>
+          <t>6. David Aaron Limited $13,595 IN (6/24) — LOCKED consultant fee</t>
+        </is>
+      </c>
+      <c r="B9" s="65" t="inlineStr">
+        <is>
+          <t>CONFIRMED 2026-09-20: consultant fee, not a sale. Booked EPGC Consultant June $13,595 (peach). Not Art Sales. Not Income I8.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="60" t="inlineStr">
+      <c r="A10" s="62" t="inlineStr">
         <is>
           <t>7. Wise $334.17 (7/9) and $658.63 (10/30)</t>
         </is>
       </c>
-      <c r="B10" s="61" t="inlineStr">
+      <c r="B10" s="63" t="inlineStr">
         <is>
           <t>Who / what? Dec $565.75 was reimbursed by EOEB (locked net $0). These two were not.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="60" t="inlineStr">
-        <is>
-          <t>8. Jack Koziol &amp; Tracy Hoffman $150,000 IN (10/20) / Ariadne Demirjian $150,000 OUT (10/21)</t>
-        </is>
-      </c>
-      <c r="B11" s="61" t="inlineStr">
-        <is>
-          <t>Proposed pass-through (not P&amp;L). If this was a real purchase/sale, name the object.</t>
+      <c r="A11" s="64" t="inlineStr">
+        <is>
+          <t>8. Jack Koziol &amp; Tracy Hoffman $150,000 IN (10/20) / Ariadne Demirjian $150,000 OUT (10/21) — LOCKED pass-through</t>
+        </is>
+      </c>
+      <c r="B11" s="65" t="inlineStr">
+        <is>
+          <t>CONFIRMED 2026-09-20: pass-through, not P&amp;L. Not a sale, not a purchase, not COGS, not Consultant.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="60" t="inlineStr">
+      <c r="A12" s="62" t="inlineStr">
         <is>
           <t>9. Aquinas Hobor $1,000 IN (2/4)</t>
         </is>
       </c>
-      <c r="B12" s="61" t="inlineStr">
+      <c r="B12" s="63" t="inlineStr">
         <is>
           <t>Sale, leftover, or other? Aquinas bought Saharan bracelets in 2022.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="60" t="inlineStr">
+      <c r="A13" s="62" t="inlineStr">
         <is>
           <t>10. Mosaics Cost $90,000 vs Mercury $50,000</t>
         </is>
       </c>
-      <c r="B13" s="61" t="inlineStr">
+      <c r="B13" s="63" t="inlineStr">
         <is>
           <t>Plutus &amp; Mnemosyne paid $50,000 in February. Where is the other $40,000 of Cost (other account / 2024 / still owed)?</t>
         </is>
@@ -7639,93 +7637,117 @@
     </row>
     <row r="14"/>
     <row r="15">
-      <c r="A15" s="55" t="inlineStr">
+      <c r="A15" s="58" t="inlineStr">
         <is>
           <t>LOCKED / MATCHED this pass (do not recast without saying so)</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="62" t="inlineStr">
+      <c r="A16" s="44" t="inlineStr">
         <is>
           <t>Coinbase ACH net</t>
         </is>
       </c>
-      <c r="B16" s="62" t="inlineStr">
+      <c r="B16" s="44" t="inlineStr">
         <is>
           <t>$-51,000.00  (OUT $-59,000.00 / IN $8,000.00) — Investments tab, not EPGC</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="62" t="inlineStr">
+      <c r="A17" s="44" t="inlineStr">
         <is>
           <t>Newstar Jewelers</t>
         </is>
       </c>
-      <c r="B17" s="62" t="inlineStr">
+      <c r="B17" s="44" t="inlineStr">
         <is>
           <t>$23,581.00 jewelry fabrication COGS (10/14 $8,000 + 11/12 $8,000 + 12/24 $7,581)</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="62" t="inlineStr">
+      <c r="A18" s="44" t="inlineStr">
         <is>
           <t>Berk sales</t>
         </is>
       </c>
-      <c r="B18" s="62" t="inlineStr">
+      <c r="B18" s="44" t="inlineStr">
         <is>
           <t>$14,000 seals (1/10) + $30,000 lots (2/7) = $44,000 Art Sales</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="62" t="inlineStr">
+      <c r="A19" s="44" t="inlineStr">
         <is>
           <t>Mosaics</t>
         </is>
       </c>
-      <c r="B19" s="62" t="inlineStr">
+      <c r="B19" s="44" t="inlineStr">
         <is>
           <t>EOEB $105,000 sale (2/21) / Plutus $50,000 of $90,000 Cost</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="62" t="inlineStr">
+      <c r="A20" s="44" t="inlineStr">
         <is>
           <t>BoA 9922 draws</t>
         </is>
       </c>
-      <c r="B20" s="62" t="inlineStr">
+      <c r="B20" s="44" t="inlineStr">
         <is>
           <t>$261,172.00 owner transfer — not P&amp;L</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="62" t="inlineStr">
+      <c r="A21" s="44" t="inlineStr">
         <is>
           <t>Wise/EOEB 12/2</t>
         </is>
       </c>
-      <c r="B21" s="62" t="inlineStr">
+      <c r="B21" s="44" t="inlineStr">
         <is>
           <t>$565.75 reimbursed — not income, not expense</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="62" t="inlineStr">
+      <c r="A22" s="44" t="inlineStr">
         <is>
           <t>$10 test wires</t>
         </is>
       </c>
-      <c r="B22" s="62" t="inlineStr">
+      <c r="B22" s="44" t="inlineStr">
         <is>
           <t>Jamal Rifai / EPGC / Plutus tests — not P&amp;L</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="44" t="inlineStr">
+        <is>
+          <t>David Aaron Limited</t>
+        </is>
+      </c>
+      <c r="B23" s="44" t="inlineStr">
+        <is>
+          <t>$13,595 (6/24) consultant fee → EPGC Consultant June. Not a sale.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="44" t="inlineStr">
+        <is>
+          <t>Koziol / Ariadne</t>
+        </is>
+      </c>
+      <c r="B24" s="44" t="inlineStr">
+        <is>
+          <t>$150,000 IN 10/20 + $150,000 OUT 10/21 LOCKED pass-through — not P&amp;L</t>
         </is>
       </c>
     </row>
@@ -7758,82 +7780,82 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="63" t="inlineStr">
-        <is>
-          <t>Mercury Checking 8291 — EPGC LLC (Choice Financial) 2025. 64 unique cash transactions. Coinbase ACH = investment. Newstar = jewelry COGS on intaglios/gems/scarabs. Do not treat BoA 9922 draws or Koziol/Ariadne $150k as P&amp;L until confirmed. Not tax advice.</t>
+      <c r="A1" s="66" t="inlineStr">
+        <is>
+          <t>Mercury Checking 8291 — EPGC LLC (Choice Financial) 2025. 64 unique cash transactions. Coinbase ACH = investment. Newstar = jewelry COGS on intaglios/gems/scarabs. BoA 9922 draws and Koziol/Ariadne $150k are LOCKED not-P&amp;L (pass-through / owner transfer). David Aaron $13,595 is LOCKED EPGC Consultant (June). Not tax advice.</t>
         </is>
       </c>
     </row>
     <row r="2"/>
     <row r="3">
-      <c r="A3" s="64" t="inlineStr">
+      <c r="A3" s="67" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B3" s="64" t="inlineStr">
+      <c r="B3" s="67" t="inlineStr">
         <is>
           <t>Counterparty</t>
         </is>
       </c>
-      <c r="C3" s="64" t="inlineStr">
+      <c r="C3" s="67" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="D3" s="64" t="inlineStr">
+      <c r="D3" s="67" t="inlineStr">
         <is>
           <t>Direction</t>
         </is>
       </c>
-      <c r="E3" s="64" t="inlineStr">
+      <c r="E3" s="67" t="inlineStr">
         <is>
           <t>Bucket</t>
         </is>
       </c>
-      <c r="F3" s="64" t="inlineStr">
+      <c r="F3" s="67" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G3" s="64" t="inlineStr">
+      <c r="G3" s="67" t="inlineStr">
         <is>
           <t>Deal / object</t>
         </is>
       </c>
-      <c r="H3" s="64" t="inlineStr">
+      <c r="H3" s="67" t="inlineStr">
         <is>
           <t>Hits EPGC Art Sales?</t>
         </is>
       </c>
-      <c r="I3" s="64" t="inlineStr">
+      <c r="I3" s="67" t="inlineStr">
         <is>
           <t>Hits EPGC Consultant?</t>
         </is>
       </c>
-      <c r="J3" s="64" t="inlineStr">
+      <c r="J3" s="67" t="inlineStr">
         <is>
           <t>Monarch category</t>
         </is>
       </c>
-      <c r="K3" s="64" t="inlineStr">
+      <c r="K3" s="67" t="inlineStr">
         <is>
           <t>Original statement</t>
         </is>
       </c>
-      <c r="L3" s="64" t="inlineStr">
+      <c r="L3" s="67" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="54" t="inlineStr">
+      <c r="A4" s="57" t="inlineStr">
         <is>
           <t>2025-01-08</t>
         </is>
       </c>
-      <c r="B4" s="54" t="inlineStr">
+      <c r="B4" s="57" t="inlineStr">
         <is>
           <t>Erdal Dere (Fortuna)</t>
         </is>
@@ -7841,42 +7863,42 @@
       <c r="C4" s="10" t="n">
         <v>-13000</v>
       </c>
-      <c r="D4" s="54" t="inlineStr">
+      <c r="D4" s="57" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E4" s="65" t="inlineStr">
+      <c r="E4" s="68" t="inlineStr">
         <is>
           <t>ART_PURCHASE</t>
         </is>
       </c>
-      <c r="F4" s="62" t="inlineStr">
+      <c r="F4" s="44" t="inlineStr">
         <is>
           <t>MATCHED</t>
         </is>
       </c>
-      <c r="G4" s="54" t="inlineStr">
+      <c r="G4" s="57" t="inlineStr">
         <is>
           <t>A Collection of Seals — COGS</t>
         </is>
       </c>
-      <c r="H4" s="54" t="inlineStr">
+      <c r="H4" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I4" s="54" t="inlineStr">
+      <c r="I4" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J4" s="54" t="inlineStr">
+      <c r="J4" s="57" t="inlineStr">
         <is>
           <t xml:space="preserve">Business Investment </t>
         </is>
       </c>
-      <c r="K4" s="54" t="inlineStr">
+      <c r="K4" s="57" t="inlineStr">
         <is>
           <t>Merchant name: Erdal Dere (Fortuna)</t>
         </is>
@@ -7888,55 +7910,55 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="54" t="inlineStr">
+      <c r="A5" s="57" t="inlineStr">
         <is>
           <t>2025-01-10</t>
         </is>
       </c>
-      <c r="B5" s="54" t="inlineStr">
+      <c r="B5" s="57" t="inlineStr">
         <is>
           <t>HARLAN J BERK LTD</t>
         </is>
       </c>
-      <c r="C5" s="58" t="n">
+      <c r="C5" s="45" t="n">
         <v>14000</v>
       </c>
-      <c r="D5" s="54" t="inlineStr">
+      <c r="D5" s="57" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E5" s="66" t="inlineStr">
+      <c r="E5" s="69" t="inlineStr">
         <is>
           <t>ART_SALE</t>
         </is>
       </c>
-      <c r="F5" s="62" t="inlineStr">
+      <c r="F5" s="44" t="inlineStr">
         <is>
           <t>MATCHED</t>
         </is>
       </c>
-      <c r="G5" s="54" t="inlineStr">
+      <c r="G5" s="57" t="inlineStr">
         <is>
           <t>A Collection of Seals — Sale Price</t>
         </is>
       </c>
-      <c r="H5" s="54" t="inlineStr">
+      <c r="H5" s="57" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="I5" s="54" t="inlineStr">
+      <c r="I5" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J5" s="54" t="inlineStr">
+      <c r="J5" s="57" t="inlineStr">
         <is>
           <t>Business Income</t>
         </is>
       </c>
-      <c r="K5" s="54" t="inlineStr">
+      <c r="K5" s="57" t="inlineStr">
         <is>
           <t>Incoming Wire; Merchant name: HARLAN J BERK LTD</t>
         </is>
@@ -7948,55 +7970,55 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="54" t="inlineStr">
+      <c r="A6" s="57" t="inlineStr">
         <is>
           <t>2025-01-16</t>
         </is>
       </c>
-      <c r="B6" s="54" t="inlineStr">
+      <c r="B6" s="57" t="inlineStr">
         <is>
           <t>EOEB LLC</t>
         </is>
       </c>
-      <c r="C6" s="67" t="n">
+      <c r="C6" s="70" t="n">
         <v>1000</v>
       </c>
-      <c r="D6" s="54" t="inlineStr">
+      <c r="D6" s="57" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E6" s="68" t="inlineStr">
+      <c r="E6" s="71" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="F6" s="68" t="inlineStr">
+      <c r="F6" s="71" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G6" s="54" t="inlineStr">
+      <c r="G6" s="57" t="inlineStr">
         <is>
           <t>EOEB $1,000 — Canosan horse vs advisory</t>
         </is>
       </c>
-      <c r="H6" s="54" t="inlineStr">
+      <c r="H6" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I6" s="54" t="inlineStr">
+      <c r="I6" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J6" s="54" t="inlineStr">
+      <c r="J6" s="57" t="inlineStr">
         <is>
           <t>Business Income</t>
         </is>
       </c>
-      <c r="K6" s="54" t="inlineStr">
+      <c r="K6" s="57" t="inlineStr">
         <is>
           <t>Incoming Wire; MAKE A PAYMENT; Merchant name: EOEB LLC</t>
         </is>
@@ -8008,12 +8030,12 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="54" t="inlineStr">
+      <c r="A7" s="57" t="inlineStr">
         <is>
           <t>2025-02-04</t>
         </is>
       </c>
-      <c r="B7" s="54" t="inlineStr">
+      <c r="B7" s="57" t="inlineStr">
         <is>
           <t>Bank of America - Checking ••9922</t>
         </is>
@@ -8021,42 +8043,42 @@
       <c r="C7" s="10" t="n">
         <v>-25000</v>
       </c>
-      <c r="D7" s="54" t="inlineStr">
+      <c r="D7" s="57" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E7" s="69" t="inlineStr">
+      <c r="E7" s="72" t="inlineStr">
         <is>
           <t>TRANSFER</t>
         </is>
       </c>
-      <c r="F7" s="62" t="inlineStr">
+      <c r="F7" s="44" t="inlineStr">
         <is>
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="G7" s="54" t="inlineStr">
+      <c r="G7" s="57" t="inlineStr">
         <is>
           <t>Owner transfer to BoA 9922</t>
         </is>
       </c>
-      <c r="H7" s="54" t="inlineStr">
+      <c r="H7" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I7" s="54" t="inlineStr">
+      <c r="I7" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J7" s="54" t="inlineStr">
+      <c r="J7" s="57" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K7" s="54" t="inlineStr">
+      <c r="K7" s="57" t="inlineStr">
         <is>
           <t>Transfer from Mercury to another bank account; Merchant name: Bank of America - Checking ••9922</t>
         </is>
@@ -8068,55 +8090,55 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="54" t="inlineStr">
+      <c r="A8" s="57" t="inlineStr">
         <is>
           <t>2025-02-04</t>
         </is>
       </c>
-      <c r="B8" s="54" t="inlineStr">
+      <c r="B8" s="57" t="inlineStr">
         <is>
           <t>AQUINAS HOBOR</t>
         </is>
       </c>
-      <c r="C8" s="67" t="n">
+      <c r="C8" s="70" t="n">
         <v>1000</v>
       </c>
-      <c r="D8" s="54" t="inlineStr">
+      <c r="D8" s="57" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E8" s="68" t="inlineStr">
+      <c r="E8" s="71" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="F8" s="68" t="inlineStr">
+      <c r="F8" s="71" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G8" s="54" t="inlineStr">
+      <c r="G8" s="57" t="inlineStr">
         <is>
           <t>Aquinas Hobor $1,000</t>
         </is>
       </c>
-      <c r="H8" s="54" t="inlineStr">
+      <c r="H8" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I8" s="54" t="inlineStr">
+      <c r="I8" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J8" s="54" t="inlineStr">
+      <c r="J8" s="57" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K8" s="54" t="inlineStr">
+      <c r="K8" s="57" t="inlineStr">
         <is>
           <t>AQUINAS HOBOR; SENDER; 770699534; Merchant name: AQUINAS HOBOR</t>
         </is>
@@ -8128,55 +8150,55 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="54" t="inlineStr">
+      <c r="A9" s="57" t="inlineStr">
         <is>
           <t>2025-02-07</t>
         </is>
       </c>
-      <c r="B9" s="54" t="inlineStr">
+      <c r="B9" s="57" t="inlineStr">
         <is>
           <t>HARLAN J BERK LTD</t>
         </is>
       </c>
-      <c r="C9" s="58" t="n">
+      <c r="C9" s="45" t="n">
         <v>30000</v>
       </c>
-      <c r="D9" s="54" t="inlineStr">
+      <c r="D9" s="57" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E9" s="66" t="inlineStr">
+      <c r="E9" s="69" t="inlineStr">
         <is>
           <t>ART_SALE</t>
         </is>
       </c>
-      <c r="F9" s="62" t="inlineStr">
+      <c r="F9" s="44" t="inlineStr">
         <is>
           <t>MATCHED</t>
         </is>
       </c>
-      <c r="G9" s="54" t="inlineStr">
+      <c r="G9" s="57" t="inlineStr">
         <is>
           <t>Berk lots lump Sale Price $30,000</t>
         </is>
       </c>
-      <c r="H9" s="54" t="inlineStr">
+      <c r="H9" s="57" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="I9" s="54" t="inlineStr">
+      <c r="I9" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J9" s="54" t="inlineStr">
+      <c r="J9" s="57" t="inlineStr">
         <is>
           <t>Business Income</t>
         </is>
       </c>
-      <c r="K9" s="54" t="inlineStr">
+      <c r="K9" s="57" t="inlineStr">
         <is>
           <t>Incoming Wire; PER ARB; Merchant name: HARLAN J BERK LTD</t>
         </is>
@@ -8188,12 +8210,12 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="54" t="inlineStr">
+      <c r="A10" s="57" t="inlineStr">
         <is>
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="B10" s="54" t="inlineStr">
+      <c r="B10" s="57" t="inlineStr">
         <is>
           <t>Jamal M Rifai</t>
         </is>
@@ -8201,42 +8223,42 @@
       <c r="C10" s="10" t="n">
         <v>-10</v>
       </c>
-      <c r="D10" s="54" t="inlineStr">
+      <c r="D10" s="57" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E10" s="69" t="inlineStr">
+      <c r="E10" s="72" t="inlineStr">
         <is>
           <t>TEST</t>
         </is>
       </c>
-      <c r="F10" s="62" t="inlineStr">
+      <c r="F10" s="44" t="inlineStr">
         <is>
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="G10" s="54" t="inlineStr">
+      <c r="G10" s="57" t="inlineStr">
         <is>
           <t>$10 test wire to Jamal M. Rifai</t>
         </is>
       </c>
-      <c r="H10" s="54" t="inlineStr">
+      <c r="H10" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I10" s="54" t="inlineStr">
+      <c r="I10" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J10" s="54" t="inlineStr">
+      <c r="J10" s="57" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K10" s="54" t="inlineStr">
+      <c r="K10" s="57" t="inlineStr">
         <is>
           <t>Merchant name: Jamal M Rifai</t>
         </is>
@@ -8248,12 +8270,12 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="54" t="inlineStr">
+      <c r="A11" s="57" t="inlineStr">
         <is>
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="B11" s="54" t="inlineStr">
+      <c r="B11" s="57" t="inlineStr">
         <is>
           <t>DDA/066196221</t>
         </is>
@@ -8261,42 +8283,42 @@
       <c r="C11" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="D11" s="54" t="inlineStr">
+      <c r="D11" s="57" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E11" s="69" t="inlineStr">
+      <c r="E11" s="72" t="inlineStr">
         <is>
           <t>TEST</t>
         </is>
       </c>
-      <c r="F11" s="62" t="inlineStr">
+      <c r="F11" s="44" t="inlineStr">
         <is>
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="G11" s="54" t="inlineStr">
+      <c r="G11" s="57" t="inlineStr">
         <is>
           <t>$10 test wire in</t>
         </is>
       </c>
-      <c r="H11" s="54" t="inlineStr">
+      <c r="H11" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I11" s="54" t="inlineStr">
+      <c r="I11" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J11" s="54" t="inlineStr">
+      <c r="J11" s="57" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K11" s="54" t="inlineStr">
+      <c r="K11" s="57" t="inlineStr">
         <is>
           <t>Incoming Wire; Merchant name: DDA/066196221</t>
         </is>
@@ -8308,55 +8330,55 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="54" t="inlineStr">
+      <c r="A12" s="57" t="inlineStr">
         <is>
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="B12" s="54" t="inlineStr">
+      <c r="B12" s="57" t="inlineStr">
         <is>
           <t>EOEB LLC</t>
         </is>
       </c>
-      <c r="C12" s="58" t="n">
+      <c r="C12" s="45" t="n">
         <v>105000</v>
       </c>
-      <c r="D12" s="54" t="inlineStr">
+      <c r="D12" s="57" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E12" s="66" t="inlineStr">
+      <c r="E12" s="69" t="inlineStr">
         <is>
           <t>ART_SALE</t>
         </is>
       </c>
-      <c r="F12" s="62" t="inlineStr">
+      <c r="F12" s="44" t="inlineStr">
         <is>
           <t>MATCHED</t>
         </is>
       </c>
-      <c r="G12" s="54" t="inlineStr">
+      <c r="G12" s="57" t="inlineStr">
         <is>
           <t>Three Ancient Mosaics — Sale Price</t>
         </is>
       </c>
-      <c r="H12" s="54" t="inlineStr">
+      <c r="H12" s="57" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="I12" s="54" t="inlineStr">
+      <c r="I12" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J12" s="54" t="inlineStr">
+      <c r="J12" s="57" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K12" s="54" t="inlineStr">
+      <c r="K12" s="57" t="inlineStr">
         <is>
           <t>Incoming Wire; MAKE A PAYMENT; Merchant name: EOEB LLC</t>
         </is>
@@ -8368,12 +8390,12 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="54" t="inlineStr">
+      <c r="A13" s="57" t="inlineStr">
         <is>
           <t>2025-02-24</t>
         </is>
       </c>
-      <c r="B13" s="54" t="inlineStr">
+      <c r="B13" s="57" t="inlineStr">
         <is>
           <t>Bank of America - Checking ••9922</t>
         </is>
@@ -8381,42 +8403,42 @@
       <c r="C13" s="10" t="n">
         <v>-90000</v>
       </c>
-      <c r="D13" s="54" t="inlineStr">
+      <c r="D13" s="57" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E13" s="69" t="inlineStr">
+      <c r="E13" s="72" t="inlineStr">
         <is>
           <t>TRANSFER</t>
         </is>
       </c>
-      <c r="F13" s="62" t="inlineStr">
+      <c r="F13" s="44" t="inlineStr">
         <is>
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="G13" s="54" t="inlineStr">
+      <c r="G13" s="57" t="inlineStr">
         <is>
           <t>Owner transfer to BoA 9922</t>
         </is>
       </c>
-      <c r="H13" s="54" t="inlineStr">
+      <c r="H13" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I13" s="54" t="inlineStr">
+      <c r="I13" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J13" s="54" t="inlineStr">
+      <c r="J13" s="57" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K13" s="54" t="inlineStr">
+      <c r="K13" s="57" t="inlineStr">
         <is>
           <t>Transfer from Mercury to another bank account; Merchant name: Bank of America - Checking ••9922</t>
         </is>
@@ -8428,12 +8450,12 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="54" t="inlineStr">
+      <c r="A14" s="57" t="inlineStr">
         <is>
           <t>2025-02-24</t>
         </is>
       </c>
-      <c r="B14" s="54" t="inlineStr">
+      <c r="B14" s="57" t="inlineStr">
         <is>
           <t>Jamal M Rifai</t>
         </is>
@@ -8441,42 +8463,42 @@
       <c r="C14" s="10" t="n">
         <v>-10</v>
       </c>
-      <c r="D14" s="54" t="inlineStr">
+      <c r="D14" s="57" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E14" s="69" t="inlineStr">
+      <c r="E14" s="72" t="inlineStr">
         <is>
           <t>TEST</t>
         </is>
       </c>
-      <c r="F14" s="62" t="inlineStr">
+      <c r="F14" s="44" t="inlineStr">
         <is>
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="G14" s="54" t="inlineStr">
+      <c r="G14" s="57" t="inlineStr">
         <is>
           <t>$10 test (Jamal or Plutus)</t>
         </is>
       </c>
-      <c r="H14" s="54" t="inlineStr">
+      <c r="H14" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I14" s="54" t="inlineStr">
+      <c r="I14" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J14" s="54" t="inlineStr">
+      <c r="J14" s="57" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K14" s="54" t="inlineStr">
+      <c r="K14" s="57" t="inlineStr">
         <is>
           <t>Merchant name: Jamal M Rifai</t>
         </is>
@@ -8488,12 +8510,12 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="54" t="inlineStr">
+      <c r="A15" s="57" t="inlineStr">
         <is>
           <t>2025-02-24</t>
         </is>
       </c>
-      <c r="B15" s="54" t="inlineStr">
+      <c r="B15" s="57" t="inlineStr">
         <is>
           <t>Plutus &amp; Mnemosyne, LLC</t>
         </is>
@@ -8501,42 +8523,42 @@
       <c r="C15" s="10" t="n">
         <v>-10</v>
       </c>
-      <c r="D15" s="54" t="inlineStr">
+      <c r="D15" s="57" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E15" s="69" t="inlineStr">
+      <c r="E15" s="72" t="inlineStr">
         <is>
           <t>TEST</t>
         </is>
       </c>
-      <c r="F15" s="62" t="inlineStr">
+      <c r="F15" s="44" t="inlineStr">
         <is>
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="G15" s="54" t="inlineStr">
+      <c r="G15" s="57" t="inlineStr">
         <is>
           <t>$10 test (Jamal or Plutus)</t>
         </is>
       </c>
-      <c r="H15" s="54" t="inlineStr">
+      <c r="H15" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I15" s="54" t="inlineStr">
+      <c r="I15" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J15" s="54" t="inlineStr">
+      <c r="J15" s="57" t="inlineStr">
         <is>
           <t xml:space="preserve">Business Investment </t>
         </is>
       </c>
-      <c r="K15" s="54" t="inlineStr">
+      <c r="K15" s="57" t="inlineStr">
         <is>
           <t>Merchant name: Plutus &amp; Mnemosyne, LLC</t>
         </is>
@@ -8548,12 +8570,12 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="54" t="inlineStr">
+      <c r="A16" s="57" t="inlineStr">
         <is>
           <t>2025-02-24</t>
         </is>
       </c>
-      <c r="B16" s="54" t="inlineStr">
+      <c r="B16" s="57" t="inlineStr">
         <is>
           <t>EPGC LLC</t>
         </is>
@@ -8561,42 +8583,42 @@
       <c r="C16" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="D16" s="54" t="inlineStr">
+      <c r="D16" s="57" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E16" s="69" t="inlineStr">
+      <c r="E16" s="72" t="inlineStr">
         <is>
           <t>TEST</t>
         </is>
       </c>
-      <c r="F16" s="62" t="inlineStr">
+      <c r="F16" s="44" t="inlineStr">
         <is>
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="G16" s="54" t="inlineStr">
+      <c r="G16" s="57" t="inlineStr">
         <is>
           <t>$10 test wire EPGC</t>
         </is>
       </c>
-      <c r="H16" s="54" t="inlineStr">
+      <c r="H16" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I16" s="54" t="inlineStr">
+      <c r="I16" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J16" s="54" t="inlineStr">
+      <c r="J16" s="57" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K16" s="54" t="inlineStr">
+      <c r="K16" s="57" t="inlineStr">
         <is>
           <t>Incoming Wire; Merchant name: EPGC LLC</t>
         </is>
@@ -8608,12 +8630,12 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="54" t="inlineStr">
+      <c r="A17" s="57" t="inlineStr">
         <is>
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="B17" s="54" t="inlineStr">
+      <c r="B17" s="57" t="inlineStr">
         <is>
           <t>Plutus &amp; Mnemosyne, LLC</t>
         </is>
@@ -8621,42 +8643,42 @@
       <c r="C17" s="10" t="n">
         <v>-49990</v>
       </c>
-      <c r="D17" s="54" t="inlineStr">
+      <c r="D17" s="57" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E17" s="65" t="inlineStr">
+      <c r="E17" s="68" t="inlineStr">
         <is>
           <t>ART_PURCHASE</t>
         </is>
       </c>
-      <c r="F17" s="62" t="inlineStr">
+      <c r="F17" s="44" t="inlineStr">
         <is>
           <t>MATCHED</t>
         </is>
       </c>
-      <c r="G17" s="54" t="inlineStr">
+      <c r="G17" s="57" t="inlineStr">
         <is>
           <t>Three Ancient Mosaics — partial COGS</t>
         </is>
       </c>
-      <c r="H17" s="54" t="inlineStr">
+      <c r="H17" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I17" s="54" t="inlineStr">
+      <c r="I17" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J17" s="54" t="inlineStr">
+      <c r="J17" s="57" t="inlineStr">
         <is>
           <t xml:space="preserve">Business Investment </t>
         </is>
       </c>
-      <c r="K17" s="54" t="inlineStr">
+      <c r="K17" s="57" t="inlineStr">
         <is>
           <t>Merchant name: Plutus &amp; Mnemosyne, LLC</t>
         </is>
@@ -8668,55 +8690,55 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="54" t="inlineStr">
+      <c r="A18" s="57" t="inlineStr">
         <is>
           <t>2025-03-10</t>
         </is>
       </c>
-      <c r="B18" s="54" t="inlineStr">
+      <c r="B18" s="57" t="inlineStr">
         <is>
           <t>EOEB LLC</t>
         </is>
       </c>
-      <c r="C18" s="67" t="n">
+      <c r="C18" s="70" t="n">
         <v>14000</v>
       </c>
-      <c r="D18" s="54" t="inlineStr">
+      <c r="D18" s="57" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E18" s="68" t="inlineStr">
+      <c r="E18" s="71" t="inlineStr">
         <is>
           <t>ADVISORY</t>
         </is>
       </c>
-      <c r="F18" s="68" t="inlineStr">
+      <c r="F18" s="71" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G18" s="54" t="inlineStr">
+      <c r="G18" s="57" t="inlineStr">
         <is>
           <t>EOEB — sale vs art advisory</t>
         </is>
       </c>
-      <c r="H18" s="54" t="inlineStr">
+      <c r="H18" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I18" s="54" t="inlineStr">
+      <c r="I18" s="57" t="inlineStr">
         <is>
           <t>no — ASK first</t>
         </is>
       </c>
-      <c r="J18" s="54" t="inlineStr">
+      <c r="J18" s="57" t="inlineStr">
         <is>
           <t>Business Income</t>
         </is>
       </c>
-      <c r="K18" s="54" t="inlineStr">
+      <c r="K18" s="57" t="inlineStr">
         <is>
           <t>Incoming Wire; MAKE A PAYMENT; Merchant name: EOEB LLC</t>
         </is>
@@ -8728,55 +8750,55 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="54" t="inlineStr">
+      <c r="A19" s="57" t="inlineStr">
         <is>
           <t>2025-05-01</t>
         </is>
       </c>
-      <c r="B19" s="54" t="inlineStr">
+      <c r="B19" s="57" t="inlineStr">
         <is>
           <t>EOEB LLC</t>
         </is>
       </c>
-      <c r="C19" s="67" t="n">
+      <c r="C19" s="70" t="n">
         <v>21000</v>
       </c>
-      <c r="D19" s="54" t="inlineStr">
+      <c r="D19" s="57" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E19" s="68" t="inlineStr">
+      <c r="E19" s="71" t="inlineStr">
         <is>
           <t>ADVISORY</t>
         </is>
       </c>
-      <c r="F19" s="68" t="inlineStr">
+      <c r="F19" s="71" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G19" s="54" t="inlineStr">
+      <c r="G19" s="57" t="inlineStr">
         <is>
           <t>EOEB — sale vs art advisory</t>
         </is>
       </c>
-      <c r="H19" s="54" t="inlineStr">
+      <c r="H19" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I19" s="54" t="inlineStr">
+      <c r="I19" s="57" t="inlineStr">
         <is>
           <t>no — ASK first</t>
         </is>
       </c>
-      <c r="J19" s="54" t="inlineStr">
+      <c r="J19" s="57" t="inlineStr">
         <is>
           <t>Business Income</t>
         </is>
       </c>
-      <c r="K19" s="54" t="inlineStr">
+      <c r="K19" s="57" t="inlineStr">
         <is>
           <t>Incoming Wire; MAKE A PAYMENT; Merchant name: EOEB LLC</t>
         </is>
@@ -8788,55 +8810,55 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="54" t="inlineStr">
+      <c r="A20" s="57" t="inlineStr">
         <is>
           <t>2025-05-09</t>
         </is>
       </c>
-      <c r="B20" s="54" t="inlineStr">
+      <c r="B20" s="57" t="inlineStr">
         <is>
           <t>Erdal Dere (Fortuna)</t>
         </is>
       </c>
-      <c r="C20" s="67" t="n">
+      <c r="C20" s="70" t="n">
         <v>-20000</v>
       </c>
-      <c r="D20" s="54" t="inlineStr">
+      <c r="D20" s="57" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E20" s="65" t="inlineStr">
+      <c r="E20" s="68" t="inlineStr">
         <is>
           <t>ART_PURCHASE</t>
         </is>
       </c>
-      <c r="F20" s="68" t="inlineStr">
+      <c r="F20" s="71" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G20" s="54" t="inlineStr">
+      <c r="G20" s="57" t="inlineStr">
         <is>
           <t>Fortuna / Erdal — inventory vs other</t>
         </is>
       </c>
-      <c r="H20" s="54" t="inlineStr">
+      <c r="H20" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I20" s="54" t="inlineStr">
+      <c r="I20" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J20" s="54" t="inlineStr">
+      <c r="J20" s="57" t="inlineStr">
         <is>
           <t xml:space="preserve">Business Investment </t>
         </is>
       </c>
-      <c r="K20" s="54" t="inlineStr">
+      <c r="K20" s="57" t="inlineStr">
         <is>
           <t>Merchant name: Erdal Dere (Fortuna)</t>
         </is>
@@ -8848,55 +8870,55 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="54" t="inlineStr">
+      <c r="A21" s="57" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="B21" s="54" t="inlineStr">
+      <c r="B21" s="57" t="inlineStr">
         <is>
           <t>EOEB LLC</t>
         </is>
       </c>
-      <c r="C21" s="67" t="n">
+      <c r="C21" s="70" t="n">
         <v>16200</v>
       </c>
-      <c r="D21" s="54" t="inlineStr">
+      <c r="D21" s="57" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E21" s="68" t="inlineStr">
+      <c r="E21" s="71" t="inlineStr">
         <is>
           <t>ADVISORY</t>
         </is>
       </c>
-      <c r="F21" s="68" t="inlineStr">
+      <c r="F21" s="71" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G21" s="54" t="inlineStr">
+      <c r="G21" s="57" t="inlineStr">
         <is>
           <t>EOEB — sale vs art advisory</t>
         </is>
       </c>
-      <c r="H21" s="54" t="inlineStr">
+      <c r="H21" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I21" s="54" t="inlineStr">
+      <c r="I21" s="57" t="inlineStr">
         <is>
           <t>no — ASK first</t>
         </is>
       </c>
-      <c r="J21" s="54" t="inlineStr">
+      <c r="J21" s="57" t="inlineStr">
         <is>
           <t>Business Income</t>
         </is>
       </c>
-      <c r="K21" s="54" t="inlineStr">
+      <c r="K21" s="57" t="inlineStr">
         <is>
           <t>Incoming Wire; MAKE A PAYMENT; Merchant name: EOEB LLC</t>
         </is>
@@ -8908,55 +8930,55 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="54" t="inlineStr">
+      <c r="A22" s="57" t="inlineStr">
         <is>
           <t>2025-06-12</t>
         </is>
       </c>
-      <c r="B22" s="54" t="inlineStr">
+      <c r="B22" s="57" t="inlineStr">
         <is>
           <t>EOEB LLC</t>
         </is>
       </c>
-      <c r="C22" s="67" t="n">
+      <c r="C22" s="70" t="n">
         <v>3300</v>
       </c>
-      <c r="D22" s="54" t="inlineStr">
+      <c r="D22" s="57" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E22" s="68" t="inlineStr">
+      <c r="E22" s="71" t="inlineStr">
         <is>
           <t>ADVISORY</t>
         </is>
       </c>
-      <c r="F22" s="68" t="inlineStr">
+      <c r="F22" s="71" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G22" s="54" t="inlineStr">
+      <c r="G22" s="57" t="inlineStr">
         <is>
           <t>EOEB — sale vs art advisory</t>
         </is>
       </c>
-      <c r="H22" s="54" t="inlineStr">
+      <c r="H22" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I22" s="54" t="inlineStr">
+      <c r="I22" s="57" t="inlineStr">
         <is>
           <t>no — ASK first</t>
         </is>
       </c>
-      <c r="J22" s="54" t="inlineStr">
+      <c r="J22" s="57" t="inlineStr">
         <is>
           <t>Business Income</t>
         </is>
       </c>
-      <c r="K22" s="54" t="inlineStr">
+      <c r="K22" s="57" t="inlineStr">
         <is>
           <t>Incoming Wire; MAKE A PAYMENT; Merchant name: EOEB LLC</t>
         </is>
@@ -8968,55 +8990,55 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="54" t="inlineStr">
+      <c r="A23" s="57" t="inlineStr">
         <is>
           <t>2025-06-12</t>
         </is>
       </c>
-      <c r="B23" s="54" t="inlineStr">
+      <c r="B23" s="57" t="inlineStr">
         <is>
           <t>EOEB LLC</t>
         </is>
       </c>
-      <c r="C23" s="67" t="n">
+      <c r="C23" s="70" t="n">
         <v>25000</v>
       </c>
-      <c r="D23" s="54" t="inlineStr">
+      <c r="D23" s="57" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E23" s="68" t="inlineStr">
+      <c r="E23" s="71" t="inlineStr">
         <is>
           <t>ADVISORY</t>
         </is>
       </c>
-      <c r="F23" s="68" t="inlineStr">
+      <c r="F23" s="71" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G23" s="54" t="inlineStr">
+      <c r="G23" s="57" t="inlineStr">
         <is>
           <t>EOEB — sale vs art advisory</t>
         </is>
       </c>
-      <c r="H23" s="54" t="inlineStr">
+      <c r="H23" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I23" s="54" t="inlineStr">
+      <c r="I23" s="57" t="inlineStr">
         <is>
           <t>no — ASK first</t>
         </is>
       </c>
-      <c r="J23" s="54" t="inlineStr">
+      <c r="J23" s="57" t="inlineStr">
         <is>
           <t>Business Income</t>
         </is>
       </c>
-      <c r="K23" s="54" t="inlineStr">
+      <c r="K23" s="57" t="inlineStr">
         <is>
           <t>Incoming Wire; MAKE A PAYMENT; Merchant name: EOEB LLC</t>
         </is>
@@ -9028,72 +9050,72 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="54" t="inlineStr">
+      <c r="A24" s="57" t="inlineStr">
         <is>
           <t>2025-06-24</t>
         </is>
       </c>
-      <c r="B24" s="54" t="inlineStr">
+      <c r="B24" s="57" t="inlineStr">
         <is>
           <t>DAVID AARON LIMITED</t>
         </is>
       </c>
-      <c r="C24" s="67" t="n">
+      <c r="C24" s="45" t="n">
         <v>13595</v>
       </c>
-      <c r="D24" s="54" t="inlineStr">
+      <c r="D24" s="57" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E24" s="66" t="inlineStr">
-        <is>
-          <t>ART_SALE</t>
-        </is>
-      </c>
-      <c r="F24" s="68" t="inlineStr">
-        <is>
-          <t>PROPOSED</t>
-        </is>
-      </c>
-      <c r="G24" s="54" t="inlineStr">
-        <is>
-          <t>David Aaron Limited — proposed art sale</t>
-        </is>
-      </c>
-      <c r="H24" s="54" t="inlineStr">
+      <c r="E24" s="44" t="inlineStr">
+        <is>
+          <t>ADVISORY</t>
+        </is>
+      </c>
+      <c r="F24" s="44" t="inlineStr">
+        <is>
+          <t>LOCKED</t>
+        </is>
+      </c>
+      <c r="G24" s="57" t="inlineStr">
+        <is>
+          <t>David Aaron Limited — consultant fee</t>
+        </is>
+      </c>
+      <c r="H24" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I24" s="54" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J24" s="54" t="inlineStr">
+      <c r="I24" s="57" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J24" s="57" t="inlineStr">
         <is>
           <t>Business Income</t>
         </is>
       </c>
-      <c r="K24" s="54" t="inlineStr">
+      <c r="K24" s="57" t="inlineStr">
         <is>
           <t>Auto-Routing transfer; Merchant name: DAVID AARON LIMITED</t>
         </is>
       </c>
       <c r="L24" s="14" t="inlineStr">
         <is>
-          <t>London antiquities dealer; Request or Invoice Payment $13,595. Booked as a proposed sale (yellow) — confirm object / whether this is a purchase refund.</t>
+          <t>User 2026-09-20: consultant fee, not a sale. Hits EPGC Consultant June $13,595. Not Art Sales.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="54" t="inlineStr">
+      <c r="A25" s="57" t="inlineStr">
         <is>
           <t>2025-07-03</t>
         </is>
       </c>
-      <c r="B25" s="54" t="inlineStr">
+      <c r="B25" s="57" t="inlineStr">
         <is>
           <t>Bank of America - Checking ••9922</t>
         </is>
@@ -9101,42 +9123,42 @@
       <c r="C25" s="10" t="n">
         <v>-40000</v>
       </c>
-      <c r="D25" s="54" t="inlineStr">
+      <c r="D25" s="57" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E25" s="69" t="inlineStr">
+      <c r="E25" s="72" t="inlineStr">
         <is>
           <t>TRANSFER</t>
         </is>
       </c>
-      <c r="F25" s="62" t="inlineStr">
+      <c r="F25" s="44" t="inlineStr">
         <is>
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="G25" s="54" t="inlineStr">
+      <c r="G25" s="57" t="inlineStr">
         <is>
           <t>Owner transfer to BoA 9922</t>
         </is>
       </c>
-      <c r="H25" s="54" t="inlineStr">
+      <c r="H25" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I25" s="54" t="inlineStr">
+      <c r="I25" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J25" s="54" t="inlineStr">
+      <c r="J25" s="57" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K25" s="54" t="inlineStr">
+      <c r="K25" s="57" t="inlineStr">
         <is>
           <t>Transfer from Mercury to another bank account; Merchant name: Bank of America - Checking ••9922</t>
         </is>
@@ -9148,55 +9170,55 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="54" t="inlineStr">
+      <c r="A26" s="57" t="inlineStr">
         <is>
           <t>2025-07-08</t>
         </is>
       </c>
-      <c r="B26" s="54" t="inlineStr">
+      <c r="B26" s="57" t="inlineStr">
         <is>
           <t>EOEB LLC</t>
         </is>
       </c>
-      <c r="C26" s="67" t="n">
+      <c r="C26" s="70" t="n">
         <v>2000</v>
       </c>
-      <c r="D26" s="54" t="inlineStr">
+      <c r="D26" s="57" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E26" s="68" t="inlineStr">
+      <c r="E26" s="71" t="inlineStr">
         <is>
           <t>ADVISORY</t>
         </is>
       </c>
-      <c r="F26" s="68" t="inlineStr">
+      <c r="F26" s="71" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G26" s="54" t="inlineStr">
+      <c r="G26" s="57" t="inlineStr">
         <is>
           <t>EOEB — sale vs art advisory</t>
         </is>
       </c>
-      <c r="H26" s="54" t="inlineStr">
+      <c r="H26" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I26" s="54" t="inlineStr">
+      <c r="I26" s="57" t="inlineStr">
         <is>
           <t>no — ASK first</t>
         </is>
       </c>
-      <c r="J26" s="54" t="inlineStr">
+      <c r="J26" s="57" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K26" s="54" t="inlineStr">
+      <c r="K26" s="57" t="inlineStr">
         <is>
           <t>Auto-Routing transfer; Merchant name: EOEB LLC</t>
         </is>
@@ -9208,55 +9230,55 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="54" t="inlineStr">
+      <c r="A27" s="57" t="inlineStr">
         <is>
           <t>2025-07-09</t>
         </is>
       </c>
-      <c r="B27" s="54" t="inlineStr">
+      <c r="B27" s="57" t="inlineStr">
         <is>
           <t>Wise Inc</t>
         </is>
       </c>
-      <c r="C27" s="67" t="n">
+      <c r="C27" s="70" t="n">
         <v>-334.17</v>
       </c>
-      <c r="D27" s="54" t="inlineStr">
+      <c r="D27" s="57" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E27" s="68" t="inlineStr">
+      <c r="E27" s="71" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="F27" s="68" t="inlineStr">
+      <c r="F27" s="71" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G27" s="54" t="inlineStr">
+      <c r="G27" s="57" t="inlineStr">
         <is>
           <t>Wise — vendor / COGS / other</t>
         </is>
       </c>
-      <c r="H27" s="54" t="inlineStr">
+      <c r="H27" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I27" s="54" t="inlineStr">
+      <c r="I27" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J27" s="54" t="inlineStr">
+      <c r="J27" s="57" t="inlineStr">
         <is>
           <t xml:space="preserve">Business Expense </t>
         </is>
       </c>
-      <c r="K27" s="54" t="inlineStr">
+      <c r="K27" s="57" t="inlineStr">
         <is>
           <t>Wise Inc; WISE; EPGC LLC; Merchant name: Wise Inc</t>
         </is>
@@ -9268,55 +9290,55 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="54" t="inlineStr">
+      <c r="A28" s="57" t="inlineStr">
         <is>
           <t>2025-07-11</t>
         </is>
       </c>
-      <c r="B28" s="54" t="inlineStr">
+      <c r="B28" s="57" t="inlineStr">
         <is>
           <t>L5</t>
         </is>
       </c>
-      <c r="C28" s="67" t="n">
+      <c r="C28" s="70" t="n">
         <v>8534.790000000001</v>
       </c>
-      <c r="D28" s="54" t="inlineStr">
+      <c r="D28" s="57" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E28" s="68" t="inlineStr">
+      <c r="E28" s="71" t="inlineStr">
         <is>
           <t>ADVISORY</t>
         </is>
       </c>
-      <c r="F28" s="68" t="inlineStr">
+      <c r="F28" s="71" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G28" s="54" t="inlineStr">
+      <c r="G28" s="57" t="inlineStr">
         <is>
           <t>L5 — sale vs art advisory</t>
         </is>
       </c>
-      <c r="H28" s="54" t="inlineStr">
+      <c r="H28" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I28" s="54" t="inlineStr">
+      <c r="I28" s="57" t="inlineStr">
         <is>
           <t>no — ASK first</t>
         </is>
       </c>
-      <c r="J28" s="54" t="inlineStr">
+      <c r="J28" s="57" t="inlineStr">
         <is>
           <t>Business Income</t>
         </is>
       </c>
-      <c r="K28" s="54" t="inlineStr">
+      <c r="K28" s="57" t="inlineStr">
         <is>
           <t>Auto-Routing transfer; Merchant name: L5</t>
         </is>
@@ -9328,55 +9350,55 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="54" t="inlineStr">
+      <c r="A29" s="57" t="inlineStr">
         <is>
           <t>2025-07-15</t>
         </is>
       </c>
-      <c r="B29" s="54" t="inlineStr">
+      <c r="B29" s="57" t="inlineStr">
         <is>
           <t>L5</t>
         </is>
       </c>
-      <c r="C29" s="67" t="n">
+      <c r="C29" s="70" t="n">
         <v>2500</v>
       </c>
-      <c r="D29" s="54" t="inlineStr">
+      <c r="D29" s="57" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E29" s="68" t="inlineStr">
+      <c r="E29" s="71" t="inlineStr">
         <is>
           <t>ADVISORY</t>
         </is>
       </c>
-      <c r="F29" s="68" t="inlineStr">
+      <c r="F29" s="71" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G29" s="54" t="inlineStr">
+      <c r="G29" s="57" t="inlineStr">
         <is>
           <t>L5 — sale vs art advisory</t>
         </is>
       </c>
-      <c r="H29" s="54" t="inlineStr">
+      <c r="H29" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I29" s="54" t="inlineStr">
+      <c r="I29" s="57" t="inlineStr">
         <is>
           <t>no — ASK first</t>
         </is>
       </c>
-      <c r="J29" s="54" t="inlineStr">
+      <c r="J29" s="57" t="inlineStr">
         <is>
           <t>Business Income</t>
         </is>
       </c>
-      <c r="K29" s="54" t="inlineStr">
+      <c r="K29" s="57" t="inlineStr">
         <is>
           <t>Auto-Routing transfer; Merchant name: L5</t>
         </is>
@@ -9388,55 +9410,55 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="54" t="inlineStr">
+      <c r="A30" s="57" t="inlineStr">
         <is>
           <t>2025-07-15</t>
         </is>
       </c>
-      <c r="B30" s="54" t="inlineStr">
+      <c r="B30" s="57" t="inlineStr">
         <is>
           <t>L5</t>
         </is>
       </c>
-      <c r="C30" s="67" t="n">
+      <c r="C30" s="70" t="n">
         <v>50000</v>
       </c>
-      <c r="D30" s="54" t="inlineStr">
+      <c r="D30" s="57" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E30" s="68" t="inlineStr">
+      <c r="E30" s="71" t="inlineStr">
         <is>
           <t>ADVISORY</t>
         </is>
       </c>
-      <c r="F30" s="68" t="inlineStr">
+      <c r="F30" s="71" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G30" s="54" t="inlineStr">
+      <c r="G30" s="57" t="inlineStr">
         <is>
           <t>L5 $50,000 — sale vs art advisory vs pass-through</t>
         </is>
       </c>
-      <c r="H30" s="54" t="inlineStr">
+      <c r="H30" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I30" s="54" t="inlineStr">
+      <c r="I30" s="57" t="inlineStr">
         <is>
           <t>no — ASK first</t>
         </is>
       </c>
-      <c r="J30" s="54" t="inlineStr">
+      <c r="J30" s="57" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K30" s="54" t="inlineStr">
+      <c r="K30" s="57" t="inlineStr">
         <is>
           <t>Auto-Routing transfer; Merchant name: L5</t>
         </is>
@@ -9448,55 +9470,55 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="54" t="inlineStr">
+      <c r="A31" s="57" t="inlineStr">
         <is>
           <t>2025-07-18</t>
         </is>
       </c>
-      <c r="B31" s="54" t="inlineStr">
+      <c r="B31" s="57" t="inlineStr">
         <is>
           <t>Aysel Dere</t>
         </is>
       </c>
-      <c r="C31" s="67" t="n">
+      <c r="C31" s="70" t="n">
         <v>50000</v>
       </c>
-      <c r="D31" s="54" t="inlineStr">
+      <c r="D31" s="57" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E31" s="68" t="inlineStr">
+      <c r="E31" s="71" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="F31" s="68" t="inlineStr">
+      <c r="F31" s="71" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G31" s="54" t="inlineStr">
+      <c r="G31" s="57" t="inlineStr">
         <is>
           <t>Aysel Dere $50,000 IN</t>
         </is>
       </c>
-      <c r="H31" s="54" t="inlineStr">
+      <c r="H31" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I31" s="54" t="inlineStr">
+      <c r="I31" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J31" s="54" t="inlineStr">
+      <c r="J31" s="57" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K31" s="54" t="inlineStr">
+      <c r="K31" s="57" t="inlineStr">
         <is>
           <t>Merchant name: Aysel Dere</t>
         </is>
@@ -9508,55 +9530,55 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="54" t="inlineStr">
+      <c r="A32" s="57" t="inlineStr">
         <is>
           <t>2025-07-21</t>
         </is>
       </c>
-      <c r="B32" s="54" t="inlineStr">
+      <c r="B32" s="57" t="inlineStr">
         <is>
           <t>Erdal Dere (Fortuna)</t>
         </is>
       </c>
-      <c r="C32" s="67" t="n">
+      <c r="C32" s="70" t="n">
         <v>-45000</v>
       </c>
-      <c r="D32" s="54" t="inlineStr">
+      <c r="D32" s="57" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E32" s="65" t="inlineStr">
+      <c r="E32" s="68" t="inlineStr">
         <is>
           <t>ART_PURCHASE</t>
         </is>
       </c>
-      <c r="F32" s="68" t="inlineStr">
+      <c r="F32" s="71" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G32" s="54" t="inlineStr">
+      <c r="G32" s="57" t="inlineStr">
         <is>
           <t>Fortuna / Erdal — inventory vs other</t>
         </is>
       </c>
-      <c r="H32" s="54" t="inlineStr">
+      <c r="H32" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I32" s="54" t="inlineStr">
+      <c r="I32" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J32" s="54" t="inlineStr">
+      <c r="J32" s="57" t="inlineStr">
         <is>
           <t xml:space="preserve">Business Investment </t>
         </is>
       </c>
-      <c r="K32" s="54" t="inlineStr">
+      <c r="K32" s="57" t="inlineStr">
         <is>
           <t>Merchant name: Erdal Dere (Fortuna)</t>
         </is>
@@ -9568,55 +9590,55 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="54" t="inlineStr">
+      <c r="A33" s="57" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="B33" s="54" t="inlineStr">
+      <c r="B33" s="57" t="inlineStr">
         <is>
           <t>ERDAL DERE</t>
         </is>
       </c>
-      <c r="C33" s="67" t="n">
+      <c r="C33" s="70" t="n">
         <v>26000</v>
       </c>
-      <c r="D33" s="54" t="inlineStr">
+      <c r="D33" s="57" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E33" s="66" t="inlineStr">
+      <c r="E33" s="69" t="inlineStr">
         <is>
           <t>ART_SALE</t>
         </is>
       </c>
-      <c r="F33" s="68" t="inlineStr">
+      <c r="F33" s="71" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G33" s="54" t="inlineStr">
+      <c r="G33" s="57" t="inlineStr">
         <is>
           <t>Erdal Dere $26,000 IN — sale vs other</t>
         </is>
       </c>
-      <c r="H33" s="54" t="inlineStr">
+      <c r="H33" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I33" s="54" t="inlineStr">
+      <c r="I33" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J33" s="54" t="inlineStr">
+      <c r="J33" s="57" t="inlineStr">
         <is>
           <t>Business Income</t>
         </is>
       </c>
-      <c r="K33" s="54" t="inlineStr">
+      <c r="K33" s="57" t="inlineStr">
         <is>
           <t>Incoming Wire; Merchant name: ERDAL DERE</t>
         </is>
@@ -9628,12 +9650,12 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="54" t="inlineStr">
+      <c r="A34" s="57" t="inlineStr">
         <is>
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="B34" s="54" t="inlineStr">
+      <c r="B34" s="57" t="inlineStr">
         <is>
           <t>Bank of America - Checking ••9922</t>
         </is>
@@ -9641,42 +9663,42 @@
       <c r="C34" s="10" t="n">
         <v>-60000</v>
       </c>
-      <c r="D34" s="54" t="inlineStr">
+      <c r="D34" s="57" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E34" s="69" t="inlineStr">
+      <c r="E34" s="72" t="inlineStr">
         <is>
           <t>TRANSFER</t>
         </is>
       </c>
-      <c r="F34" s="62" t="inlineStr">
+      <c r="F34" s="44" t="inlineStr">
         <is>
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="G34" s="54" t="inlineStr">
+      <c r="G34" s="57" t="inlineStr">
         <is>
           <t>Owner transfer to BoA 9922</t>
         </is>
       </c>
-      <c r="H34" s="54" t="inlineStr">
+      <c r="H34" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I34" s="54" t="inlineStr">
+      <c r="I34" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J34" s="54" t="inlineStr">
+      <c r="J34" s="57" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K34" s="54" t="inlineStr">
+      <c r="K34" s="57" t="inlineStr">
         <is>
           <t>Transfer from Mercury to another bank account; Merchant name: Bank of America - Checking ••9922</t>
         </is>
@@ -9688,55 +9710,55 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="54" t="inlineStr">
+      <c r="A35" s="57" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="B35" s="54" t="inlineStr">
+      <c r="B35" s="57" t="inlineStr">
         <is>
           <t>Erdal Dere (Fortuna)</t>
         </is>
       </c>
-      <c r="C35" s="67" t="n">
+      <c r="C35" s="70" t="n">
         <v>-20000</v>
       </c>
-      <c r="D35" s="54" t="inlineStr">
+      <c r="D35" s="57" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E35" s="65" t="inlineStr">
+      <c r="E35" s="68" t="inlineStr">
         <is>
           <t>ART_PURCHASE</t>
         </is>
       </c>
-      <c r="F35" s="68" t="inlineStr">
+      <c r="F35" s="71" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G35" s="54" t="inlineStr">
+      <c r="G35" s="57" t="inlineStr">
         <is>
           <t>Fortuna / Erdal — inventory vs other</t>
         </is>
       </c>
-      <c r="H35" s="54" t="inlineStr">
+      <c r="H35" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I35" s="54" t="inlineStr">
+      <c r="I35" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J35" s="54" t="inlineStr">
+      <c r="J35" s="57" t="inlineStr">
         <is>
           <t xml:space="preserve">Business Investment </t>
         </is>
       </c>
-      <c r="K35" s="54" t="inlineStr">
+      <c r="K35" s="57" t="inlineStr">
         <is>
           <t>Merchant name: Erdal Dere (Fortuna)</t>
         </is>
@@ -9748,55 +9770,55 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="54" t="inlineStr">
+      <c r="A36" s="57" t="inlineStr">
         <is>
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="B36" s="54" t="inlineStr">
+      <c r="B36" s="57" t="inlineStr">
         <is>
           <t>EOEB LLC</t>
         </is>
       </c>
-      <c r="C36" s="67" t="n">
+      <c r="C36" s="70" t="n">
         <v>10000</v>
       </c>
-      <c r="D36" s="54" t="inlineStr">
+      <c r="D36" s="57" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E36" s="68" t="inlineStr">
+      <c r="E36" s="71" t="inlineStr">
         <is>
           <t>ADVISORY</t>
         </is>
       </c>
-      <c r="F36" s="68" t="inlineStr">
+      <c r="F36" s="71" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G36" s="54" t="inlineStr">
+      <c r="G36" s="57" t="inlineStr">
         <is>
           <t>EOEB — sale vs art advisory</t>
         </is>
       </c>
-      <c r="H36" s="54" t="inlineStr">
+      <c r="H36" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I36" s="54" t="inlineStr">
+      <c r="I36" s="57" t="inlineStr">
         <is>
           <t>no — ASK first</t>
         </is>
       </c>
-      <c r="J36" s="54" t="inlineStr">
+      <c r="J36" s="57" t="inlineStr">
         <is>
           <t>Business Income</t>
         </is>
       </c>
-      <c r="K36" s="54" t="inlineStr">
+      <c r="K36" s="57" t="inlineStr">
         <is>
           <t>Auto-Routing transfer; Merchant name: EOEB LLC</t>
         </is>
@@ -9808,55 +9830,55 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="54" t="inlineStr">
+      <c r="A37" s="57" t="inlineStr">
         <is>
           <t>2025-09-02</t>
         </is>
       </c>
-      <c r="B37" s="54" t="inlineStr">
+      <c r="B37" s="57" t="inlineStr">
         <is>
           <t>L5</t>
         </is>
       </c>
-      <c r="C37" s="67" t="n">
+      <c r="C37" s="70" t="n">
         <v>5042</v>
       </c>
-      <c r="D37" s="54" t="inlineStr">
+      <c r="D37" s="57" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E37" s="68" t="inlineStr">
+      <c r="E37" s="71" t="inlineStr">
         <is>
           <t>ADVISORY</t>
         </is>
       </c>
-      <c r="F37" s="68" t="inlineStr">
+      <c r="F37" s="71" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G37" s="54" t="inlineStr">
+      <c r="G37" s="57" t="inlineStr">
         <is>
           <t>L5 — sale vs art advisory</t>
         </is>
       </c>
-      <c r="H37" s="54" t="inlineStr">
+      <c r="H37" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I37" s="54" t="inlineStr">
+      <c r="I37" s="57" t="inlineStr">
         <is>
           <t>no — ASK first</t>
         </is>
       </c>
-      <c r="J37" s="54" t="inlineStr">
+      <c r="J37" s="57" t="inlineStr">
         <is>
           <t>Business Income</t>
         </is>
       </c>
-      <c r="K37" s="54" t="inlineStr">
+      <c r="K37" s="57" t="inlineStr">
         <is>
           <t>Auto-Routing transfer; Merchant name: L5</t>
         </is>
@@ -9868,55 +9890,55 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="54" t="inlineStr">
+      <c r="A38" s="57" t="inlineStr">
         <is>
           <t>2025-09-04</t>
         </is>
       </c>
-      <c r="B38" s="54" t="inlineStr">
+      <c r="B38" s="57" t="inlineStr">
         <is>
           <t>COINBASE INC.</t>
         </is>
       </c>
-      <c r="C38" s="58" t="n">
+      <c r="C38" s="45" t="n">
         <v>-3000</v>
       </c>
-      <c r="D38" s="54" t="inlineStr">
+      <c r="D38" s="57" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E38" s="70" t="inlineStr">
+      <c r="E38" s="73" t="inlineStr">
         <is>
           <t>INVESTMENT</t>
         </is>
       </c>
-      <c r="F38" s="62" t="inlineStr">
+      <c r="F38" s="44" t="inlineStr">
         <is>
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="G38" s="54" t="inlineStr">
+      <c r="G38" s="57" t="inlineStr">
         <is>
           <t>Coinbase ACH funding</t>
         </is>
       </c>
-      <c r="H38" s="54" t="inlineStr">
+      <c r="H38" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I38" s="54" t="inlineStr">
+      <c r="I38" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J38" s="54" t="inlineStr">
+      <c r="J38" s="57" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K38" s="54" t="inlineStr">
+      <c r="K38" s="57" t="inlineStr">
         <is>
           <t>COINBASE INC.; 2A0875F9; JACOB COLEY; Merchant name: COINBASE INC.</t>
         </is>
@@ -9928,55 +9950,55 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="54" t="inlineStr">
+      <c r="A39" s="57" t="inlineStr">
         <is>
           <t>2025-09-19</t>
         </is>
       </c>
-      <c r="B39" s="54" t="inlineStr">
+      <c r="B39" s="57" t="inlineStr">
         <is>
           <t>EOEB LLC</t>
         </is>
       </c>
-      <c r="C39" s="67" t="n">
+      <c r="C39" s="70" t="n">
         <v>5000</v>
       </c>
-      <c r="D39" s="54" t="inlineStr">
+      <c r="D39" s="57" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E39" s="68" t="inlineStr">
+      <c r="E39" s="71" t="inlineStr">
         <is>
           <t>ADVISORY</t>
         </is>
       </c>
-      <c r="F39" s="68" t="inlineStr">
+      <c r="F39" s="71" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G39" s="54" t="inlineStr">
+      <c r="G39" s="57" t="inlineStr">
         <is>
           <t>EOEB — sale vs art advisory</t>
         </is>
       </c>
-      <c r="H39" s="54" t="inlineStr">
+      <c r="H39" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I39" s="54" t="inlineStr">
+      <c r="I39" s="57" t="inlineStr">
         <is>
           <t>no — ASK first</t>
         </is>
       </c>
-      <c r="J39" s="54" t="inlineStr">
+      <c r="J39" s="57" t="inlineStr">
         <is>
           <t>Business Income</t>
         </is>
       </c>
-      <c r="K39" s="54" t="inlineStr">
+      <c r="K39" s="57" t="inlineStr">
         <is>
           <t>Auto-Routing transfer; Merchant name: EOEB LLC</t>
         </is>
@@ -9988,55 +10010,55 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="54" t="inlineStr">
+      <c r="A40" s="57" t="inlineStr">
         <is>
           <t>2025-09-23</t>
         </is>
       </c>
-      <c r="B40" s="54" t="inlineStr">
+      <c r="B40" s="57" t="inlineStr">
         <is>
           <t>L5</t>
         </is>
       </c>
-      <c r="C40" s="67" t="n">
+      <c r="C40" s="70" t="n">
         <v>9119.27</v>
       </c>
-      <c r="D40" s="54" t="inlineStr">
+      <c r="D40" s="57" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E40" s="68" t="inlineStr">
+      <c r="E40" s="71" t="inlineStr">
         <is>
           <t>ADVISORY</t>
         </is>
       </c>
-      <c r="F40" s="68" t="inlineStr">
+      <c r="F40" s="71" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G40" s="54" t="inlineStr">
+      <c r="G40" s="57" t="inlineStr">
         <is>
           <t>L5 — sale vs art advisory</t>
         </is>
       </c>
-      <c r="H40" s="54" t="inlineStr">
+      <c r="H40" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I40" s="54" t="inlineStr">
+      <c r="I40" s="57" t="inlineStr">
         <is>
           <t>no — ASK first</t>
         </is>
       </c>
-      <c r="J40" s="54" t="inlineStr">
+      <c r="J40" s="57" t="inlineStr">
         <is>
           <t>Business Income</t>
         </is>
       </c>
-      <c r="K40" s="54" t="inlineStr">
+      <c r="K40" s="57" t="inlineStr">
         <is>
           <t>Auto-Routing transfer; Merchant name: L5</t>
         </is>
@@ -10048,12 +10070,12 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="54" t="inlineStr">
+      <c r="A41" s="57" t="inlineStr">
         <is>
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="B41" s="54" t="inlineStr">
+      <c r="B41" s="57" t="inlineStr">
         <is>
           <t>Bank of America - Checking ••9922</t>
         </is>
@@ -10061,42 +10083,42 @@
       <c r="C41" s="10" t="n">
         <v>-40000</v>
       </c>
-      <c r="D41" s="54" t="inlineStr">
+      <c r="D41" s="57" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E41" s="69" t="inlineStr">
+      <c r="E41" s="72" t="inlineStr">
         <is>
           <t>TRANSFER</t>
         </is>
       </c>
-      <c r="F41" s="62" t="inlineStr">
+      <c r="F41" s="44" t="inlineStr">
         <is>
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="G41" s="54" t="inlineStr">
+      <c r="G41" s="57" t="inlineStr">
         <is>
           <t>Owner transfer to BoA 9922</t>
         </is>
       </c>
-      <c r="H41" s="54" t="inlineStr">
+      <c r="H41" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I41" s="54" t="inlineStr">
+      <c r="I41" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J41" s="54" t="inlineStr">
+      <c r="J41" s="57" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K41" s="54" t="inlineStr">
+      <c r="K41" s="57" t="inlineStr">
         <is>
           <t>Transfer from Mercury to another bank account; Merchant name: Bank of America - Checking ••9922</t>
         </is>
@@ -10108,55 +10130,55 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="54" t="inlineStr">
+      <c r="A42" s="57" t="inlineStr">
         <is>
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="B42" s="54" t="inlineStr">
+      <c r="B42" s="57" t="inlineStr">
         <is>
           <t>EOEB LLC</t>
         </is>
       </c>
-      <c r="C42" s="67" t="n">
+      <c r="C42" s="70" t="n">
         <v>3100</v>
       </c>
-      <c r="D42" s="54" t="inlineStr">
+      <c r="D42" s="57" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E42" s="68" t="inlineStr">
+      <c r="E42" s="71" t="inlineStr">
         <is>
           <t>ADVISORY</t>
         </is>
       </c>
-      <c r="F42" s="68" t="inlineStr">
+      <c r="F42" s="71" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G42" s="54" t="inlineStr">
+      <c r="G42" s="57" t="inlineStr">
         <is>
           <t>EOEB — sale vs art advisory</t>
         </is>
       </c>
-      <c r="H42" s="54" t="inlineStr">
+      <c r="H42" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I42" s="54" t="inlineStr">
+      <c r="I42" s="57" t="inlineStr">
         <is>
           <t>no — ASK first</t>
         </is>
       </c>
-      <c r="J42" s="54" t="inlineStr">
+      <c r="J42" s="57" t="inlineStr">
         <is>
           <t>Business Income</t>
         </is>
       </c>
-      <c r="K42" s="54" t="inlineStr">
+      <c r="K42" s="57" t="inlineStr">
         <is>
           <t>Auto-Routing transfer; Merchant name: EOEB LLC</t>
         </is>
@@ -10168,55 +10190,55 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="54" t="inlineStr">
+      <c r="A43" s="57" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="B43" s="54" t="inlineStr">
+      <c r="B43" s="57" t="inlineStr">
         <is>
           <t>COINBASE INC.</t>
         </is>
       </c>
-      <c r="C43" s="58" t="n">
+      <c r="C43" s="45" t="n">
         <v>-6000</v>
       </c>
-      <c r="D43" s="54" t="inlineStr">
+      <c r="D43" s="57" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E43" s="70" t="inlineStr">
+      <c r="E43" s="73" t="inlineStr">
         <is>
           <t>INVESTMENT</t>
         </is>
       </c>
-      <c r="F43" s="62" t="inlineStr">
+      <c r="F43" s="44" t="inlineStr">
         <is>
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="G43" s="54" t="inlineStr">
+      <c r="G43" s="57" t="inlineStr">
         <is>
           <t>Coinbase ACH funding</t>
         </is>
       </c>
-      <c r="H43" s="54" t="inlineStr">
+      <c r="H43" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I43" s="54" t="inlineStr">
+      <c r="I43" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J43" s="54" t="inlineStr">
+      <c r="J43" s="57" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K43" s="54" t="inlineStr">
+      <c r="K43" s="57" t="inlineStr">
         <is>
           <t>COINBASE INC.; 27B17286; JACOB COLEY; Merchant name: COINBASE INC.</t>
         </is>
@@ -10228,55 +10250,55 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="54" t="inlineStr">
+      <c r="A44" s="57" t="inlineStr">
         <is>
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="B44" s="54" t="inlineStr">
+      <c r="B44" s="57" t="inlineStr">
         <is>
           <t>COINBASE INC.</t>
         </is>
       </c>
-      <c r="C44" s="58" t="n">
+      <c r="C44" s="45" t="n">
         <v>-10000</v>
       </c>
-      <c r="D44" s="54" t="inlineStr">
+      <c r="D44" s="57" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E44" s="70" t="inlineStr">
+      <c r="E44" s="73" t="inlineStr">
         <is>
           <t>INVESTMENT</t>
         </is>
       </c>
-      <c r="F44" s="62" t="inlineStr">
+      <c r="F44" s="44" t="inlineStr">
         <is>
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="G44" s="54" t="inlineStr">
+      <c r="G44" s="57" t="inlineStr">
         <is>
           <t>Coinbase ACH funding</t>
         </is>
       </c>
-      <c r="H44" s="54" t="inlineStr">
+      <c r="H44" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I44" s="54" t="inlineStr">
+      <c r="I44" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J44" s="54" t="inlineStr">
+      <c r="J44" s="57" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K44" s="54" t="inlineStr">
+      <c r="K44" s="57" t="inlineStr">
         <is>
           <t>COINBASE INC.; E2C52DA9; JACOB COLEY; Merchant name: COINBASE INC.</t>
         </is>
@@ -10288,55 +10310,55 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="54" t="inlineStr">
+      <c r="A45" s="57" t="inlineStr">
         <is>
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="B45" s="54" t="inlineStr">
+      <c r="B45" s="57" t="inlineStr">
         <is>
           <t>EOEB LLC</t>
         </is>
       </c>
-      <c r="C45" s="67" t="n">
+      <c r="C45" s="70" t="n">
         <v>10000</v>
       </c>
-      <c r="D45" s="54" t="inlineStr">
+      <c r="D45" s="57" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E45" s="68" t="inlineStr">
+      <c r="E45" s="71" t="inlineStr">
         <is>
           <t>ADVISORY</t>
         </is>
       </c>
-      <c r="F45" s="68" t="inlineStr">
+      <c r="F45" s="71" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G45" s="54" t="inlineStr">
+      <c r="G45" s="57" t="inlineStr">
         <is>
           <t>EOEB — sale vs art advisory</t>
         </is>
       </c>
-      <c r="H45" s="54" t="inlineStr">
+      <c r="H45" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I45" s="54" t="inlineStr">
+      <c r="I45" s="57" t="inlineStr">
         <is>
           <t>no — ASK first</t>
         </is>
       </c>
-      <c r="J45" s="54" t="inlineStr">
+      <c r="J45" s="57" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K45" s="54" t="inlineStr">
+      <c r="K45" s="57" t="inlineStr">
         <is>
           <t>Auto-Routing transfer; Merchant name: EOEB LLC</t>
         </is>
@@ -10348,12 +10370,12 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="54" t="inlineStr">
+      <c r="A46" s="57" t="inlineStr">
         <is>
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="B46" s="54" t="inlineStr">
+      <c r="B46" s="57" t="inlineStr">
         <is>
           <t>Bank of America - Checking ••9922</t>
         </is>
@@ -10361,42 +10383,42 @@
       <c r="C46" s="10" t="n">
         <v>-6172</v>
       </c>
-      <c r="D46" s="54" t="inlineStr">
+      <c r="D46" s="57" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E46" s="69" t="inlineStr">
+      <c r="E46" s="72" t="inlineStr">
         <is>
           <t>TRANSFER</t>
         </is>
       </c>
-      <c r="F46" s="62" t="inlineStr">
+      <c r="F46" s="44" t="inlineStr">
         <is>
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="G46" s="54" t="inlineStr">
+      <c r="G46" s="57" t="inlineStr">
         <is>
           <t>Owner transfer to BoA 9922</t>
         </is>
       </c>
-      <c r="H46" s="54" t="inlineStr">
+      <c r="H46" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I46" s="54" t="inlineStr">
+      <c r="I46" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J46" s="54" t="inlineStr">
+      <c r="J46" s="57" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K46" s="54" t="inlineStr">
+      <c r="K46" s="57" t="inlineStr">
         <is>
           <t>Transfer from Mercury to another bank account; Merchant name: Bank of America - Checking ••9922</t>
         </is>
@@ -10408,55 +10430,55 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="54" t="inlineStr">
+      <c r="A47" s="57" t="inlineStr">
         <is>
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="B47" s="54" t="inlineStr">
+      <c r="B47" s="57" t="inlineStr">
         <is>
           <t>ERDAL DERE</t>
         </is>
       </c>
-      <c r="C47" s="67" t="n">
+      <c r="C47" s="70" t="n">
         <v>25000</v>
       </c>
-      <c r="D47" s="54" t="inlineStr">
+      <c r="D47" s="57" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E47" s="66" t="inlineStr">
+      <c r="E47" s="69" t="inlineStr">
         <is>
           <t>ART_SALE</t>
         </is>
       </c>
-      <c r="F47" s="68" t="inlineStr">
+      <c r="F47" s="71" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G47" s="54" t="inlineStr">
+      <c r="G47" s="57" t="inlineStr">
         <is>
           <t>Erdal Dere $25,000 IN — sale vs other</t>
         </is>
       </c>
-      <c r="H47" s="54" t="inlineStr">
+      <c r="H47" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I47" s="54" t="inlineStr">
+      <c r="I47" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J47" s="54" t="inlineStr">
+      <c r="J47" s="57" t="inlineStr">
         <is>
           <t>Business Income</t>
         </is>
       </c>
-      <c r="K47" s="54" t="inlineStr">
+      <c r="K47" s="57" t="inlineStr">
         <is>
           <t>Incoming Wire; Merchant name: ERDAL DERE</t>
         </is>
@@ -10468,55 +10490,55 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="54" t="inlineStr">
+      <c r="A48" s="57" t="inlineStr">
         <is>
           <t>2025-10-14</t>
         </is>
       </c>
-      <c r="B48" s="54" t="inlineStr">
+      <c r="B48" s="57" t="inlineStr">
         <is>
           <t>Newstar Jewelers</t>
         </is>
       </c>
-      <c r="C48" s="58" t="n">
+      <c r="C48" s="45" t="n">
         <v>-8000</v>
       </c>
-      <c r="D48" s="54" t="inlineStr">
+      <c r="D48" s="57" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E48" s="65" t="inlineStr">
+      <c r="E48" s="68" t="inlineStr">
         <is>
           <t>COGS_JEWELRY</t>
         </is>
       </c>
-      <c r="F48" s="62" t="inlineStr">
+      <c r="F48" s="44" t="inlineStr">
         <is>
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="G48" s="54" t="inlineStr">
+      <c r="G48" s="57" t="inlineStr">
         <is>
           <t>Newstar Jewelers — jewelry fabrication</t>
         </is>
       </c>
-      <c r="H48" s="54" t="inlineStr">
+      <c r="H48" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I48" s="54" t="inlineStr">
+      <c r="I48" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J48" s="54" t="inlineStr">
+      <c r="J48" s="57" t="inlineStr">
         <is>
           <t xml:space="preserve">Business Expense </t>
         </is>
       </c>
-      <c r="K48" s="54" t="inlineStr">
+      <c r="K48" s="57" t="inlineStr">
         <is>
           <t>Merchant name: Newstar Jewelers</t>
         </is>
@@ -10528,55 +10550,55 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="54" t="inlineStr">
+      <c r="A49" s="57" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="B49" s="54" t="inlineStr">
+      <c r="B49" s="57" t="inlineStr">
         <is>
           <t>EOEB LLC</t>
         </is>
       </c>
-      <c r="C49" s="67" t="n">
+      <c r="C49" s="70" t="n">
         <v>16000</v>
       </c>
-      <c r="D49" s="54" t="inlineStr">
+      <c r="D49" s="57" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E49" s="68" t="inlineStr">
+      <c r="E49" s="71" t="inlineStr">
         <is>
           <t>ADVISORY</t>
         </is>
       </c>
-      <c r="F49" s="68" t="inlineStr">
+      <c r="F49" s="71" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G49" s="54" t="inlineStr">
+      <c r="G49" s="57" t="inlineStr">
         <is>
           <t>EOEB — sale vs art advisory</t>
         </is>
       </c>
-      <c r="H49" s="54" t="inlineStr">
+      <c r="H49" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I49" s="54" t="inlineStr">
+      <c r="I49" s="57" t="inlineStr">
         <is>
           <t>no — ASK first</t>
         </is>
       </c>
-      <c r="J49" s="54" t="inlineStr">
+      <c r="J49" s="57" t="inlineStr">
         <is>
           <t>Business Income</t>
         </is>
       </c>
-      <c r="K49" s="54" t="inlineStr">
+      <c r="K49" s="57" t="inlineStr">
         <is>
           <t>Auto-Routing transfer; Merchant name: EOEB LLC</t>
         </is>
@@ -10588,175 +10610,175 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="54" t="inlineStr">
+      <c r="A50" s="57" t="inlineStr">
         <is>
           <t>2025-10-20</t>
         </is>
       </c>
-      <c r="B50" s="54" t="inlineStr">
+      <c r="B50" s="57" t="inlineStr">
         <is>
           <t>JACK EDWARD KOZIOL &amp; TRACY HOFFMAN</t>
         </is>
       </c>
-      <c r="C50" s="67" t="n">
+      <c r="C50" s="10" t="n">
         <v>150000</v>
       </c>
-      <c r="D50" s="54" t="inlineStr">
+      <c r="D50" s="57" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E50" s="70" t="inlineStr">
+      <c r="E50" s="73" t="inlineStr">
         <is>
           <t>PASS_THROUGH</t>
         </is>
       </c>
-      <c r="F50" s="70" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="G50" s="54" t="inlineStr">
+      <c r="F50" s="44" t="inlineStr">
+        <is>
+          <t>LOCKED</t>
+        </is>
+      </c>
+      <c r="G50" s="57" t="inlineStr">
         <is>
           <t>Jack Koziol &amp; Tracy Hoffman $150,000 IN</t>
         </is>
       </c>
-      <c r="H50" s="54" t="inlineStr">
+      <c r="H50" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I50" s="54" t="inlineStr">
+      <c r="I50" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J50" s="54" t="inlineStr">
+      <c r="J50" s="57" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K50" s="54" t="inlineStr">
+      <c r="K50" s="57" t="inlineStr">
         <is>
           <t>Incoming Wire; /BNF/Per your request; Merchant name: JACK EDWARD KOZIOL &amp; TRACY HOFFMAN</t>
         </is>
       </c>
       <c r="L50" s="14" t="inlineStr">
         <is>
-          <t>Incoming wire /BNF/Per your request. Next-day $150,000 OUT to Ariadne Demirjian LLC. Proposed pass-through — not income unless you say it is a sale.</t>
+          <t>User 2026-09-20: pass-through, not a sale. Incoming wire /BNF/Per your request. Next-day $150,000 OUT to Ariadne Demirjian LLC. Not P&amp;L.</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="54" t="inlineStr">
+      <c r="A51" s="57" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="B51" s="54" t="inlineStr">
+      <c r="B51" s="57" t="inlineStr">
         <is>
           <t>Ariadne Demirjian LLC</t>
         </is>
       </c>
-      <c r="C51" s="67" t="n">
+      <c r="C51" s="10" t="n">
         <v>-150000</v>
       </c>
-      <c r="D51" s="54" t="inlineStr">
+      <c r="D51" s="57" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E51" s="70" t="inlineStr">
+      <c r="E51" s="73" t="inlineStr">
         <is>
           <t>PASS_THROUGH</t>
         </is>
       </c>
-      <c r="F51" s="70" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="G51" s="54" t="inlineStr">
+      <c r="F51" s="44" t="inlineStr">
+        <is>
+          <t>LOCKED</t>
+        </is>
+      </c>
+      <c r="G51" s="57" t="inlineStr">
         <is>
           <t>Ariadne Demirjian LLC $150,000 OUT</t>
         </is>
       </c>
-      <c r="H51" s="54" t="inlineStr">
+      <c r="H51" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I51" s="54" t="inlineStr">
+      <c r="I51" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J51" s="54" t="inlineStr">
+      <c r="J51" s="57" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K51" s="54" t="inlineStr">
+      <c r="K51" s="57" t="inlineStr">
         <is>
           <t>Merchant name: Ariadne Demirjian LLC</t>
         </is>
       </c>
       <c r="L51" s="14" t="inlineStr">
         <is>
-          <t>Same window as Koziol $150,000 IN. Proposed pass-through — not COGS/expense unless you say it is a purchase.</t>
+          <t>User 2026-09-20: pass-through, not a purchase. Same window as Koziol $150,000 IN. Not P&amp;L.</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="54" t="inlineStr">
+      <c r="A52" s="57" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="B52" s="54" t="inlineStr">
+      <c r="B52" s="57" t="inlineStr">
         <is>
           <t>L5</t>
         </is>
       </c>
-      <c r="C52" s="67" t="n">
+      <c r="C52" s="70" t="n">
         <v>7500</v>
       </c>
-      <c r="D52" s="54" t="inlineStr">
+      <c r="D52" s="57" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E52" s="68" t="inlineStr">
+      <c r="E52" s="71" t="inlineStr">
         <is>
           <t>ADVISORY</t>
         </is>
       </c>
-      <c r="F52" s="68" t="inlineStr">
+      <c r="F52" s="71" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G52" s="54" t="inlineStr">
+      <c r="G52" s="57" t="inlineStr">
         <is>
           <t>L5 — sale vs art advisory</t>
         </is>
       </c>
-      <c r="H52" s="54" t="inlineStr">
+      <c r="H52" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I52" s="54" t="inlineStr">
+      <c r="I52" s="57" t="inlineStr">
         <is>
           <t>no — ASK first</t>
         </is>
       </c>
-      <c r="J52" s="54" t="inlineStr">
+      <c r="J52" s="57" t="inlineStr">
         <is>
           <t>Business Income</t>
         </is>
       </c>
-      <c r="K52" s="54" t="inlineStr">
+      <c r="K52" s="57" t="inlineStr">
         <is>
           <t>Auto-Routing transfer; Merchant name: L5</t>
         </is>
@@ -10768,55 +10790,55 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="54" t="inlineStr">
+      <c r="A53" s="57" t="inlineStr">
         <is>
           <t>2025-10-24</t>
         </is>
       </c>
-      <c r="B53" s="54" t="inlineStr">
+      <c r="B53" s="57" t="inlineStr">
         <is>
           <t>EOEB LLC</t>
         </is>
       </c>
-      <c r="C53" s="67" t="n">
+      <c r="C53" s="70" t="n">
         <v>1500</v>
       </c>
-      <c r="D53" s="54" t="inlineStr">
+      <c r="D53" s="57" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E53" s="68" t="inlineStr">
+      <c r="E53" s="71" t="inlineStr">
         <is>
           <t>ADVISORY</t>
         </is>
       </c>
-      <c r="F53" s="68" t="inlineStr">
+      <c r="F53" s="71" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G53" s="54" t="inlineStr">
+      <c r="G53" s="57" t="inlineStr">
         <is>
           <t>EOEB — sale vs art advisory</t>
         </is>
       </c>
-      <c r="H53" s="54" t="inlineStr">
+      <c r="H53" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I53" s="54" t="inlineStr">
+      <c r="I53" s="57" t="inlineStr">
         <is>
           <t>no — ASK first</t>
         </is>
       </c>
-      <c r="J53" s="54" t="inlineStr">
+      <c r="J53" s="57" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K53" s="54" t="inlineStr">
+      <c r="K53" s="57" t="inlineStr">
         <is>
           <t>Auto-Routing transfer; Merchant name: EOEB LLC</t>
         </is>
@@ -10828,55 +10850,55 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="54" t="inlineStr">
+      <c r="A54" s="57" t="inlineStr">
         <is>
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="B54" s="54" t="inlineStr">
+      <c r="B54" s="57" t="inlineStr">
         <is>
           <t>Wise Inc</t>
         </is>
       </c>
-      <c r="C54" s="67" t="n">
+      <c r="C54" s="70" t="n">
         <v>-658.63</v>
       </c>
-      <c r="D54" s="54" t="inlineStr">
+      <c r="D54" s="57" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E54" s="68" t="inlineStr">
+      <c r="E54" s="71" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="F54" s="68" t="inlineStr">
+      <c r="F54" s="71" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G54" s="54" t="inlineStr">
+      <c r="G54" s="57" t="inlineStr">
         <is>
           <t>Wise — vendor / COGS / other</t>
         </is>
       </c>
-      <c r="H54" s="54" t="inlineStr">
+      <c r="H54" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I54" s="54" t="inlineStr">
+      <c r="I54" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J54" s="54" t="inlineStr">
+      <c r="J54" s="57" t="inlineStr">
         <is>
           <t xml:space="preserve">Business Expense </t>
         </is>
       </c>
-      <c r="K54" s="54" t="inlineStr">
+      <c r="K54" s="57" t="inlineStr">
         <is>
           <t>Wise Inc; WISE; EPGC LLC; Merchant name: Wise Inc</t>
         </is>
@@ -10888,55 +10910,55 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="54" t="inlineStr">
+      <c r="A55" s="57" t="inlineStr">
         <is>
           <t>2025-10-31</t>
         </is>
       </c>
-      <c r="B55" s="54" t="inlineStr">
+      <c r="B55" s="57" t="inlineStr">
         <is>
           <t>EOEB LLC</t>
         </is>
       </c>
-      <c r="C55" s="67" t="n">
+      <c r="C55" s="70" t="n">
         <v>2170</v>
       </c>
-      <c r="D55" s="54" t="inlineStr">
+      <c r="D55" s="57" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E55" s="68" t="inlineStr">
+      <c r="E55" s="71" t="inlineStr">
         <is>
           <t>ADVISORY</t>
         </is>
       </c>
-      <c r="F55" s="68" t="inlineStr">
+      <c r="F55" s="71" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G55" s="54" t="inlineStr">
+      <c r="G55" s="57" t="inlineStr">
         <is>
           <t>EOEB — sale vs art advisory</t>
         </is>
       </c>
-      <c r="H55" s="54" t="inlineStr">
+      <c r="H55" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I55" s="54" t="inlineStr">
+      <c r="I55" s="57" t="inlineStr">
         <is>
           <t>no — ASK first</t>
         </is>
       </c>
-      <c r="J55" s="54" t="inlineStr">
+      <c r="J55" s="57" t="inlineStr">
         <is>
           <t>Business Income</t>
         </is>
       </c>
-      <c r="K55" s="54" t="inlineStr">
+      <c r="K55" s="57" t="inlineStr">
         <is>
           <t>Auto-Routing transfer; Merchant name: EOEB LLC</t>
         </is>
@@ -10948,55 +10970,55 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="54" t="inlineStr">
+      <c r="A56" s="57" t="inlineStr">
         <is>
           <t>2025-11-06</t>
         </is>
       </c>
-      <c r="B56" s="54" t="inlineStr">
+      <c r="B56" s="57" t="inlineStr">
         <is>
           <t>COINBASE INC.</t>
         </is>
       </c>
-      <c r="C56" s="58" t="n">
+      <c r="C56" s="45" t="n">
         <v>-10000</v>
       </c>
-      <c r="D56" s="54" t="inlineStr">
+      <c r="D56" s="57" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E56" s="70" t="inlineStr">
+      <c r="E56" s="73" t="inlineStr">
         <is>
           <t>INVESTMENT</t>
         </is>
       </c>
-      <c r="F56" s="62" t="inlineStr">
+      <c r="F56" s="44" t="inlineStr">
         <is>
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="G56" s="54" t="inlineStr">
+      <c r="G56" s="57" t="inlineStr">
         <is>
           <t>Coinbase ACH funding</t>
         </is>
       </c>
-      <c r="H56" s="54" t="inlineStr">
+      <c r="H56" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I56" s="54" t="inlineStr">
+      <c r="I56" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J56" s="54" t="inlineStr">
+      <c r="J56" s="57" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K56" s="54" t="inlineStr">
+      <c r="K56" s="57" t="inlineStr">
         <is>
           <t>COINBASE INC.; 450310C7; JACOB COLEY; Merchant name: COINBASE INC.</t>
         </is>
@@ -11008,55 +11030,55 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="54" t="inlineStr">
+      <c r="A57" s="57" t="inlineStr">
         <is>
           <t>2025-11-07</t>
         </is>
       </c>
-      <c r="B57" s="54" t="inlineStr">
+      <c r="B57" s="57" t="inlineStr">
         <is>
           <t>ERDAL DERE</t>
         </is>
       </c>
-      <c r="C57" s="67" t="n">
+      <c r="C57" s="70" t="n">
         <v>6000</v>
       </c>
-      <c r="D57" s="54" t="inlineStr">
+      <c r="D57" s="57" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E57" s="66" t="inlineStr">
+      <c r="E57" s="69" t="inlineStr">
         <is>
           <t>ART_SALE</t>
         </is>
       </c>
-      <c r="F57" s="68" t="inlineStr">
+      <c r="F57" s="71" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G57" s="54" t="inlineStr">
+      <c r="G57" s="57" t="inlineStr">
         <is>
           <t>Erdal Dere Fortuna PAYMENT $6,000 IN</t>
         </is>
       </c>
-      <c r="H57" s="54" t="inlineStr">
+      <c r="H57" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I57" s="54" t="inlineStr">
+      <c r="I57" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J57" s="54" t="inlineStr">
+      <c r="J57" s="57" t="inlineStr">
         <is>
           <t>Business Income</t>
         </is>
       </c>
-      <c r="K57" s="54" t="inlineStr">
+      <c r="K57" s="57" t="inlineStr">
         <is>
           <t>Incoming Wire; ERDAL DERE FORTUNA PAYMENT; Merchant name: ERDAL DERE</t>
         </is>
@@ -11068,55 +11090,55 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="54" t="inlineStr">
+      <c r="A58" s="57" t="inlineStr">
         <is>
           <t>2025-11-12</t>
         </is>
       </c>
-      <c r="B58" s="54" t="inlineStr">
+      <c r="B58" s="57" t="inlineStr">
         <is>
           <t>Newstar Jewelers</t>
         </is>
       </c>
-      <c r="C58" s="58" t="n">
+      <c r="C58" s="45" t="n">
         <v>-8000</v>
       </c>
-      <c r="D58" s="54" t="inlineStr">
+      <c r="D58" s="57" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E58" s="65" t="inlineStr">
+      <c r="E58" s="68" t="inlineStr">
         <is>
           <t>COGS_JEWELRY</t>
         </is>
       </c>
-      <c r="F58" s="62" t="inlineStr">
+      <c r="F58" s="44" t="inlineStr">
         <is>
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="G58" s="54" t="inlineStr">
+      <c r="G58" s="57" t="inlineStr">
         <is>
           <t>Newstar Jewelers — jewelry fabrication</t>
         </is>
       </c>
-      <c r="H58" s="54" t="inlineStr">
+      <c r="H58" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I58" s="54" t="inlineStr">
+      <c r="I58" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J58" s="54" t="inlineStr">
+      <c r="J58" s="57" t="inlineStr">
         <is>
           <t xml:space="preserve">Business Expense </t>
         </is>
       </c>
-      <c r="K58" s="54" t="inlineStr">
+      <c r="K58" s="57" t="inlineStr">
         <is>
           <t>Merchant name: Newstar Jewelers</t>
         </is>
@@ -11128,55 +11150,55 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="54" t="inlineStr">
+      <c r="A59" s="57" t="inlineStr">
         <is>
           <t>2025-11-14</t>
         </is>
       </c>
-      <c r="B59" s="54" t="inlineStr">
+      <c r="B59" s="57" t="inlineStr">
         <is>
           <t>COINBASE INC.</t>
         </is>
       </c>
-      <c r="C59" s="58" t="n">
+      <c r="C59" s="45" t="n">
         <v>-10000</v>
       </c>
-      <c r="D59" s="54" t="inlineStr">
+      <c r="D59" s="57" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E59" s="70" t="inlineStr">
+      <c r="E59" s="73" t="inlineStr">
         <is>
           <t>INVESTMENT</t>
         </is>
       </c>
-      <c r="F59" s="62" t="inlineStr">
+      <c r="F59" s="44" t="inlineStr">
         <is>
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="G59" s="54" t="inlineStr">
+      <c r="G59" s="57" t="inlineStr">
         <is>
           <t>Coinbase ACH funding</t>
         </is>
       </c>
-      <c r="H59" s="54" t="inlineStr">
+      <c r="H59" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I59" s="54" t="inlineStr">
+      <c r="I59" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J59" s="54" t="inlineStr">
+      <c r="J59" s="57" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K59" s="54" t="inlineStr">
+      <c r="K59" s="57" t="inlineStr">
         <is>
           <t>COINBASE INC.; 8DF808EA; JACOB COLEY; Merchant name: COINBASE INC.</t>
         </is>
@@ -11188,55 +11210,55 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="54" t="inlineStr">
+      <c r="A60" s="57" t="inlineStr">
         <is>
           <t>2025-11-17</t>
         </is>
       </c>
-      <c r="B60" s="54" t="inlineStr">
+      <c r="B60" s="57" t="inlineStr">
         <is>
           <t>COINBASE INC.</t>
         </is>
       </c>
-      <c r="C60" s="58" t="n">
+      <c r="C60" s="45" t="n">
         <v>-10000</v>
       </c>
-      <c r="D60" s="54" t="inlineStr">
+      <c r="D60" s="57" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E60" s="70" t="inlineStr">
+      <c r="E60" s="73" t="inlineStr">
         <is>
           <t>INVESTMENT</t>
         </is>
       </c>
-      <c r="F60" s="62" t="inlineStr">
+      <c r="F60" s="44" t="inlineStr">
         <is>
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="G60" s="54" t="inlineStr">
+      <c r="G60" s="57" t="inlineStr">
         <is>
           <t>Coinbase ACH funding</t>
         </is>
       </c>
-      <c r="H60" s="54" t="inlineStr">
+      <c r="H60" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I60" s="54" t="inlineStr">
+      <c r="I60" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J60" s="54" t="inlineStr">
+      <c r="J60" s="57" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K60" s="54" t="inlineStr">
+      <c r="K60" s="57" t="inlineStr">
         <is>
           <t>COINBASE INC.; 6651A007; JACOB COLEY; Merchant name: COINBASE INC.</t>
         </is>
@@ -11248,55 +11270,55 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="54" t="inlineStr">
+      <c r="A61" s="57" t="inlineStr">
         <is>
           <t>2025-11-24</t>
         </is>
       </c>
-      <c r="B61" s="54" t="inlineStr">
+      <c r="B61" s="57" t="inlineStr">
         <is>
           <t>COINBASE INC.</t>
         </is>
       </c>
-      <c r="C61" s="58" t="n">
+      <c r="C61" s="45" t="n">
         <v>-5000</v>
       </c>
-      <c r="D61" s="54" t="inlineStr">
+      <c r="D61" s="57" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E61" s="70" t="inlineStr">
+      <c r="E61" s="73" t="inlineStr">
         <is>
           <t>INVESTMENT</t>
         </is>
       </c>
-      <c r="F61" s="62" t="inlineStr">
+      <c r="F61" s="44" t="inlineStr">
         <is>
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="G61" s="54" t="inlineStr">
+      <c r="G61" s="57" t="inlineStr">
         <is>
           <t>Coinbase ACH funding</t>
         </is>
       </c>
-      <c r="H61" s="54" t="inlineStr">
+      <c r="H61" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I61" s="54" t="inlineStr">
+      <c r="I61" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J61" s="54" t="inlineStr">
+      <c r="J61" s="57" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K61" s="54" t="inlineStr">
+      <c r="K61" s="57" t="inlineStr">
         <is>
           <t>COINBASE INC.; D5957FFE; JACOB COLEY; Merchant name: COINBASE INC.</t>
         </is>
@@ -11308,12 +11330,12 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="54" t="inlineStr">
+      <c r="A62" s="57" t="inlineStr">
         <is>
           <t>2025-12-02</t>
         </is>
       </c>
-      <c r="B62" s="54" t="inlineStr">
+      <c r="B62" s="57" t="inlineStr">
         <is>
           <t>Wise Inc</t>
         </is>
@@ -11321,42 +11343,42 @@
       <c r="C62" s="10" t="n">
         <v>-565.75</v>
       </c>
-      <c r="D62" s="54" t="inlineStr">
+      <c r="D62" s="57" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E62" s="69" t="inlineStr">
+      <c r="E62" s="72" t="inlineStr">
         <is>
           <t>REIMBURSE</t>
         </is>
       </c>
-      <c r="F62" s="62" t="inlineStr">
+      <c r="F62" s="44" t="inlineStr">
         <is>
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="G62" s="54" t="inlineStr">
+      <c r="G62" s="57" t="inlineStr">
         <is>
           <t>Wise $565.75 reimbursed by EOEB</t>
         </is>
       </c>
-      <c r="H62" s="54" t="inlineStr">
+      <c r="H62" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I62" s="54" t="inlineStr">
+      <c r="I62" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J62" s="54" t="inlineStr">
+      <c r="J62" s="57" t="inlineStr">
         <is>
           <t xml:space="preserve">Business Expense </t>
         </is>
       </c>
-      <c r="K62" s="54" t="inlineStr">
+      <c r="K62" s="57" t="inlineStr">
         <is>
           <t>Wise Inc; WISE; EPGC LLC; Merchant name: Wise Inc</t>
         </is>
@@ -11368,12 +11390,12 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="54" t="inlineStr">
+      <c r="A63" s="57" t="inlineStr">
         <is>
           <t>2025-12-02</t>
         </is>
       </c>
-      <c r="B63" s="54" t="inlineStr">
+      <c r="B63" s="57" t="inlineStr">
         <is>
           <t>EOEB LLC</t>
         </is>
@@ -11381,42 +11403,42 @@
       <c r="C63" s="10" t="n">
         <v>565.75</v>
       </c>
-      <c r="D63" s="54" t="inlineStr">
+      <c r="D63" s="57" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E63" s="69" t="inlineStr">
+      <c r="E63" s="72" t="inlineStr">
         <is>
           <t>REIMBURSE</t>
         </is>
       </c>
-      <c r="F63" s="62" t="inlineStr">
+      <c r="F63" s="44" t="inlineStr">
         <is>
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="G63" s="54" t="inlineStr">
+      <c r="G63" s="57" t="inlineStr">
         <is>
           <t>EOEB reimburses Wise $565.75</t>
         </is>
       </c>
-      <c r="H63" s="54" t="inlineStr">
+      <c r="H63" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I63" s="54" t="inlineStr">
+      <c r="I63" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J63" s="54" t="inlineStr">
+      <c r="J63" s="57" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K63" s="54" t="inlineStr">
+      <c r="K63" s="57" t="inlineStr">
         <is>
           <t>Auto-Routing transfer; Merchant name: EOEB LLC</t>
         </is>
@@ -11428,55 +11450,55 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="54" t="inlineStr">
+      <c r="A64" s="57" t="inlineStr">
         <is>
           <t>2025-12-04</t>
         </is>
       </c>
-      <c r="B64" s="54" t="inlineStr">
+      <c r="B64" s="57" t="inlineStr">
         <is>
           <t>L5</t>
         </is>
       </c>
-      <c r="C64" s="67" t="n">
+      <c r="C64" s="70" t="n">
         <v>4700.26</v>
       </c>
-      <c r="D64" s="54" t="inlineStr">
+      <c r="D64" s="57" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E64" s="68" t="inlineStr">
+      <c r="E64" s="71" t="inlineStr">
         <is>
           <t>ADVISORY</t>
         </is>
       </c>
-      <c r="F64" s="68" t="inlineStr">
+      <c r="F64" s="71" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G64" s="54" t="inlineStr">
+      <c r="G64" s="57" t="inlineStr">
         <is>
           <t>L5 — sale vs art advisory</t>
         </is>
       </c>
-      <c r="H64" s="54" t="inlineStr">
+      <c r="H64" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I64" s="54" t="inlineStr">
+      <c r="I64" s="57" t="inlineStr">
         <is>
           <t>no — ASK first</t>
         </is>
       </c>
-      <c r="J64" s="54" t="inlineStr">
+      <c r="J64" s="57" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K64" s="54" t="inlineStr">
+      <c r="K64" s="57" t="inlineStr">
         <is>
           <t>Auto-Routing transfer; Merchant name: L5</t>
         </is>
@@ -11488,55 +11510,55 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="54" t="inlineStr">
+      <c r="A65" s="57" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="B65" s="54" t="inlineStr">
+      <c r="B65" s="57" t="inlineStr">
         <is>
           <t>COINBASE INC.</t>
         </is>
       </c>
-      <c r="C65" s="58" t="n">
+      <c r="C65" s="45" t="n">
         <v>-5000</v>
       </c>
-      <c r="D65" s="54" t="inlineStr">
+      <c r="D65" s="57" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E65" s="70" t="inlineStr">
+      <c r="E65" s="73" t="inlineStr">
         <is>
           <t>INVESTMENT</t>
         </is>
       </c>
-      <c r="F65" s="62" t="inlineStr">
+      <c r="F65" s="44" t="inlineStr">
         <is>
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="G65" s="54" t="inlineStr">
+      <c r="G65" s="57" t="inlineStr">
         <is>
           <t>Coinbase ACH funding</t>
         </is>
       </c>
-      <c r="H65" s="54" t="inlineStr">
+      <c r="H65" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I65" s="54" t="inlineStr">
+      <c r="I65" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J65" s="54" t="inlineStr">
+      <c r="J65" s="57" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K65" s="54" t="inlineStr">
+      <c r="K65" s="57" t="inlineStr">
         <is>
           <t>COINBASE INC.; DFF8E6A8; JACOB COLEY; Merchant name: COINBASE INC.</t>
         </is>
@@ -11548,55 +11570,55 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="54" t="inlineStr">
+      <c r="A66" s="57" t="inlineStr">
         <is>
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="B66" s="54" t="inlineStr">
+      <c r="B66" s="57" t="inlineStr">
         <is>
           <t>COINBASE INC.</t>
         </is>
       </c>
-      <c r="C66" s="58" t="n">
+      <c r="C66" s="45" t="n">
         <v>8000</v>
       </c>
-      <c r="D66" s="54" t="inlineStr">
+      <c r="D66" s="57" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E66" s="70" t="inlineStr">
+      <c r="E66" s="73" t="inlineStr">
         <is>
           <t>INVESTMENT</t>
         </is>
       </c>
-      <c r="F66" s="62" t="inlineStr">
+      <c r="F66" s="44" t="inlineStr">
         <is>
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="G66" s="54" t="inlineStr">
+      <c r="G66" s="57" t="inlineStr">
         <is>
           <t>Coinbase ACH back to Mercury</t>
         </is>
       </c>
-      <c r="H66" s="54" t="inlineStr">
+      <c r="H66" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I66" s="54" t="inlineStr">
+      <c r="I66" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J66" s="54" t="inlineStr">
+      <c r="J66" s="57" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K66" s="54" t="inlineStr">
+      <c r="K66" s="57" t="inlineStr">
         <is>
           <t>COINBASE INC.; 6B2DA6B2; JACOB COLEY; Merchant name: COINBASE INC.</t>
         </is>
@@ -11608,55 +11630,55 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="54" t="inlineStr">
+      <c r="A67" s="57" t="inlineStr">
         <is>
           <t>2025-12-24</t>
         </is>
       </c>
-      <c r="B67" s="54" t="inlineStr">
+      <c r="B67" s="57" t="inlineStr">
         <is>
           <t>Newstar Jewelers</t>
         </is>
       </c>
-      <c r="C67" s="58" t="n">
+      <c r="C67" s="45" t="n">
         <v>-7581</v>
       </c>
-      <c r="D67" s="54" t="inlineStr">
+      <c r="D67" s="57" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E67" s="65" t="inlineStr">
+      <c r="E67" s="68" t="inlineStr">
         <is>
           <t>COGS_JEWELRY</t>
         </is>
       </c>
-      <c r="F67" s="62" t="inlineStr">
+      <c r="F67" s="44" t="inlineStr">
         <is>
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="G67" s="54" t="inlineStr">
+      <c r="G67" s="57" t="inlineStr">
         <is>
           <t>Newstar Jewelers — jewelry fabrication (3 of 3)</t>
         </is>
       </c>
-      <c r="H67" s="54" t="inlineStr">
+      <c r="H67" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I67" s="54" t="inlineStr">
+      <c r="I67" s="57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J67" s="54" t="inlineStr">
+      <c r="J67" s="57" t="inlineStr">
         <is>
           <t xml:space="preserve">Business Expense </t>
         </is>
       </c>
-      <c r="K67" s="54" t="inlineStr">
+      <c r="K67" s="57" t="inlineStr">
         <is>
           <t>From EPGC LLC via mercury.com 3 of 3; Merchant name: Newstar Jewelers</t>
         </is>

--- a/.cursor/scratch/tax_turbo_parts/Personal Income 2025 — like last year (EPGC+Art+GCM).xlsx
+++ b/.cursor/scratch/tax_turbo_parts/Personal Income 2025 — like last year (EPGC+Art+GCM).xlsx
@@ -3020,20 +3020,42 @@
           <t>Consultant Fees</t>
         </is>
       </c>
-      <c r="B69" s="5" t="n"/>
-      <c r="C69" s="5" t="n"/>
-      <c r="D69" s="5" t="n"/>
-      <c r="E69" s="5" t="n"/>
-      <c r="F69" s="5" t="n"/>
-      <c r="G69" s="5" t="n"/>
-      <c r="H69" s="5" t="n"/>
-      <c r="I69" s="5" t="n"/>
-      <c r="J69" s="12" t="n">
+      <c r="B69" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="K69" s="5" t="n"/>
-      <c r="L69" s="5" t="n"/>
-      <c r="M69" s="5" t="n"/>
+      <c r="C69" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D69" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" s="9" t="n">
+        <v>334.17</v>
+      </c>
+      <c r="I69" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" s="9" t="n">
+        <v>658.63</v>
+      </c>
+      <c r="L69" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="N69" s="5">
         <f>SUM(B69:M69)</f>
         <v/>
@@ -3195,7 +3217,7 @@
     <row r="75">
       <c r="A75" s="14" t="inlineStr">
         <is>
-          <t>2025 Mercury 2026-09-20: Art Sales = MATCHED cash only (Berk $14,000 Jan + Berk $30,000 / mosaics $105,000 Feb = $149,000). Consultant June $13,595 = David Aaron Limited LOCKED (user: consultant fee, not a sale). EOEB remainder $130,270.00 and L5 $87,396.32 still ASK — not on Consultant. Koziol/Ariadne $150,000 LOCKED pass-through — not P&amp;L. Coinbase is Investments, not this tab. Newstar $23,581 is Art Sales COGS, not operating expense. 2024 leftover supplies/furniture/consultant-fee numbers on this 2025 block were zeroed. GCM 1099 is personal. Not tax advice.</t>
+          <t>2025 Mercury 2026-09-20: Art Sales = MATCHED cash only (Berk $14,000 Jan + Berk $30,000 / mosaics $105,000 Feb = $149,000). Consultant June $13,595 = David Aaron Limited LOCKED (user: consultant fee, not a sale). Consultant Fees July $334.17 + October $658.63 = Wise expertise write-ups LOCKED ($992.80). EOEB remainder $130,270.00 and L5 $87,396.32 still ASK — not on Consultant income. Koziol/Ariadne $150,000 LOCKED pass-through — not P&amp;L. Coinbase is Investments, not this tab. Newstar $23,581 is Art Sales COGS, not operating expense. Dec Wise $565.75 reimbursed — not on Consultant Fees. GCM 1099 is personal. Not tax advice.</t>
         </is>
       </c>
     </row>
@@ -7487,7 +7509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -7498,7 +7520,7 @@
     <row r="1">
       <c r="A1" s="41" t="inlineStr">
         <is>
-          <t>ASK — remaining Mercury 8291 questions. Q6 David Aaron consultant fee and Q8 Koziol/Ariadne pass-through LOCKED 2026-09-20. Not tax advice.</t>
+          <t>ASK — remaining Mercury 8291 questions. Q6 consultant, Q7 Wise expertise write-ups, Q8 pass-through LOCKED 2026-09-20. Not tax advice.</t>
         </is>
       </c>
     </row>
@@ -7588,14 +7610,14 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="62" t="inlineStr">
-        <is>
-          <t>7. Wise $334.17 (7/9) and $658.63 (10/30)</t>
-        </is>
-      </c>
-      <c r="B10" s="63" t="inlineStr">
-        <is>
-          <t>Who / what? Dec $565.75 was reimbursed by EOEB (locked net $0). These two were not.</t>
+      <c r="A10" s="64" t="inlineStr">
+        <is>
+          <t>7. Wise $334.17 (7/9) and $658.63 (10/30) — LOCKED expertise write-ups</t>
+        </is>
+      </c>
+      <c r="B10" s="65" t="inlineStr">
+        <is>
+          <t>CONFIRMED 2026-09-20: business expenses (expertise write-ups). Booked EPGC Consultant Fees July $334.17 + October $658.63 = $992.80. Not COGS. Distinct from Dec Wise $565.75 reimbursed by EOEB (still not P&amp;L).</t>
         </is>
       </c>
     </row>
@@ -7748,6 +7770,18 @@
       <c r="B24" s="44" t="inlineStr">
         <is>
           <t>$150,000 IN 10/20 + $150,000 OUT 10/21 LOCKED pass-through — not P&amp;L</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="44" t="inlineStr">
+        <is>
+          <t>Wise expertise write-ups</t>
+        </is>
+      </c>
+      <c r="B25" s="44" t="inlineStr">
+        <is>
+          <t>$334.17 (7/9) + $658.63 (10/30) = $992.80 → EPGC Consultant Fees expense. Dec $565.75 still reimbursed / not P&amp;L.</t>
         </is>
       </c>
     </row>
@@ -7782,7 +7816,7 @@
     <row r="1">
       <c r="A1" s="66" t="inlineStr">
         <is>
-          <t>Mercury Checking 8291 — EPGC LLC (Choice Financial) 2025. 64 unique cash transactions. Coinbase ACH = investment. Newstar = jewelry COGS on intaglios/gems/scarabs. BoA 9922 draws and Koziol/Ariadne $150k are LOCKED not-P&amp;L (pass-through / owner transfer). David Aaron $13,595 is LOCKED EPGC Consultant (June). Not tax advice.</t>
+          <t>Mercury Checking 8291 — EPGC LLC (Choice Financial) 2025. 64 unique cash transactions. Coinbase ACH = investment. Newstar = jewelry COGS on intaglios/gems/scarabs. BoA 9922 draws and Koziol/Ariadne $150k are LOCKED not-P&amp;L (pass-through / owner transfer). David Aaron $13,595 is LOCKED EPGC Consultant (June). Wise $334.17 + $658.63 are LOCKED EPGC Consultant Fees (expertise write-ups). Not tax advice.</t>
         </is>
       </c>
     </row>
@@ -9240,7 +9274,7 @@
           <t>Wise Inc</t>
         </is>
       </c>
-      <c r="C27" s="70" t="n">
+      <c r="C27" s="45" t="n">
         <v>-334.17</v>
       </c>
       <c r="D27" s="57" t="inlineStr">
@@ -9248,19 +9282,19 @@
           <t>OUT</t>
         </is>
       </c>
-      <c r="E27" s="71" t="inlineStr">
-        <is>
-          <t>ASK</t>
-        </is>
-      </c>
-      <c r="F27" s="71" t="inlineStr">
-        <is>
-          <t>ASK</t>
+      <c r="E27" s="69" t="inlineStr">
+        <is>
+          <t>EPGC_EXPENSE</t>
+        </is>
+      </c>
+      <c r="F27" s="44" t="inlineStr">
+        <is>
+          <t>LOCKED</t>
         </is>
       </c>
       <c r="G27" s="57" t="inlineStr">
         <is>
-          <t>Wise — vendor / COGS / other</t>
+          <t>Wise — expertise write-ups (Consultant Fees)</t>
         </is>
       </c>
       <c r="H27" s="57" t="inlineStr">
@@ -9285,7 +9319,7 @@
       </c>
       <c r="L27" s="14" t="inlineStr">
         <is>
-          <t>International payment from EPGC. Not reimbursed. COGS, advisory cost, or personal?</t>
+          <t>User 2026-09-20: business expense (expertise write-ups). Hits EPGC Consultant Fees July $334.17. Not COGS, not reimbursed. Distinct from Dec Wise $565.75 (EOEB reimburse).</t>
         </is>
       </c>
     </row>
@@ -10860,7 +10894,7 @@
           <t>Wise Inc</t>
         </is>
       </c>
-      <c r="C54" s="70" t="n">
+      <c r="C54" s="45" t="n">
         <v>-658.63</v>
       </c>
       <c r="D54" s="57" t="inlineStr">
@@ -10868,19 +10902,19 @@
           <t>OUT</t>
         </is>
       </c>
-      <c r="E54" s="71" t="inlineStr">
-        <is>
-          <t>ASK</t>
-        </is>
-      </c>
-      <c r="F54" s="71" t="inlineStr">
-        <is>
-          <t>ASK</t>
+      <c r="E54" s="69" t="inlineStr">
+        <is>
+          <t>EPGC_EXPENSE</t>
+        </is>
+      </c>
+      <c r="F54" s="44" t="inlineStr">
+        <is>
+          <t>LOCKED</t>
         </is>
       </c>
       <c r="G54" s="57" t="inlineStr">
         <is>
-          <t>Wise — vendor / COGS / other</t>
+          <t>Wise — expertise write-ups (Consultant Fees)</t>
         </is>
       </c>
       <c r="H54" s="57" t="inlineStr">
@@ -10905,7 +10939,7 @@
       </c>
       <c r="L54" s="14" t="inlineStr">
         <is>
-          <t>International payment from EPGC. Not reimbursed. COGS, advisory cost, or personal?</t>
+          <t>User 2026-09-20: business expense (expertise write-ups). Hits EPGC Consultant Fees October $658.63. Not COGS, not reimbursed. Distinct from Dec Wise $565.75 (EOEB reimburse).</t>
         </is>
       </c>
     </row>

--- a/.cursor/scratch/tax_turbo_parts/Personal Income 2025 — like last year (EPGC+Art+GCM).xlsx
+++ b/.cursor/scratch/tax_turbo_parts/Personal Income 2025 — like last year (EPGC+Art+GCM).xlsx
@@ -175,7 +175,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -273,6 +273,7 @@
     <xf numFmtId="164" fontId="10" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="8" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -2401,7 +2402,7 @@
         <v>14000</v>
       </c>
       <c r="C53" s="9" t="n">
-        <v>135000</v>
+        <v>136000</v>
       </c>
       <c r="D53" s="10" t="n">
         <v>0</v>
@@ -3217,7 +3218,7 @@
     <row r="75">
       <c r="A75" s="14" t="inlineStr">
         <is>
-          <t>2025 Mercury 2026-09-20: Art Sales = MATCHED cash only (Berk $14,000 Jan + Berk $30,000 / mosaics $105,000 Feb = $149,000). Consultant June $13,595 = David Aaron Limited LOCKED (user: consultant fee, not a sale). Consultant Fees July $334.17 + October $658.63 = Wise expertise write-ups LOCKED ($992.80). EOEB remainder $130,270.00 and L5 $87,396.32 still ASK — not on Consultant income. Koziol/Ariadne $150,000 LOCKED pass-through — not P&amp;L. Coinbase is Investments, not this tab. Newstar $23,581 is Art Sales COGS, not operating expense. Dec Wise $565.75 reimbursed — not on Consultant Fees. GCM 1099 is personal. Not tax advice.</t>
+          <t>2025 Mercury 2026-09-20: Art Sales = MATCHED/LOCKED cash (Berk $14,000 Jan + Berk $30,000 / mosaics $105,000 / Aquinas books $1,000 Feb = $150,000). Consultant June $13,595 = David Aaron Limited LOCKED (user: consultant fee, not a sale). Consultant Fees July $334.17 + October $658.63 = Wise expertise write-ups LOCKED ($992.80). EOEB remainder $130,270.00 and L5 $87,396.32 still ASK — not on Consultant income. Koziol/Ariadne $150,000 LOCKED pass-through — not P&amp;L. Coinbase is Investments, not this tab. Newstar $23,581 is Art Sales COGS, not operating expense. Dec Wise $565.75 reimbursed — not on Consultant Fees. Aquinas books Cost TBD — cash on Art Sales, not in I8. GCM 1099 is personal. Not tax advice.</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N132"/>
+  <dimension ref="A1:N135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="47.86" customWidth="1" min="1" max="1"/>
@@ -5928,7 +5929,7 @@
     <row r="78">
       <c r="A78" s="39" t="inlineStr">
         <is>
-          <t>Mercury 8291 MATCHED: Berk $14,000 (1/10 seals) + $30,000 (2/7 lots). EOEB $105,000 (2/21 mosaics). Fortuna $13,000 (1/8 seals Cost). Plutus $50,000 of mosaics $90,000 Cost — $40,000 of Cost not on 8291 (ASK). Newstar $23,581 is jewelry fabrication COGS, parked below — not in sold-lot Cost (Berk gem/scarab lots already sold in February). David Aaron $13,595 (6/24) is LOCKED consultant fee — not a sale (EPGC Consultant June). Not tax advice.</t>
+          <t>Mercury 8291 MATCHED: Berk $14,000 (1/10 seals) + $30,000 (2/7 lots). EOEB $105,000 (2/21 mosaics). Fortuna $13,000 (1/8 seals Cost). Plutus $50,000 of mosaics $90,000 Cost — $40,000 of Cost not on 8291 (ASK). Newstar $23,581 is jewelry fabrication COGS, parked below — not in sold-lot Cost (Berk gem/scarab lots already sold in February). David Aaron $13,595 (6/24) is LOCKED consultant fee — not a sale (EPGC Consultant June). Aquinas Hobor $1,000 (2/4) is LOCKED books sold — EPGC Art Sales February; Cost TBD (not in I8). Not tax advice.</t>
         </is>
       </c>
     </row>
@@ -6779,6 +6780,48 @@
       </c>
       <c r="C132" s="42" t="n">
         <v>85000</v>
+      </c>
+    </row>
+    <row r="133"/>
+    <row r="134">
+      <c r="A134" s="43" t="inlineStr">
+        <is>
+          <t>2025 Mercury 8291 — Books sold to Aquinas Hobor (LOCKED)</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="44" t="inlineStr">
+        <is>
+          <t>Books sold to Aquinas Hobor (titles TBD)</t>
+        </is>
+      </c>
+      <c r="B135" s="44" t="inlineStr">
+        <is>
+          <t>Aquinas Hobor</t>
+        </is>
+      </c>
+      <c r="C135" s="44" t="n"/>
+      <c r="D135" s="44" t="n"/>
+      <c r="E135" s="44" t="inlineStr">
+        <is>
+          <t>Aquinas Hobor</t>
+        </is>
+      </c>
+      <c r="F135" s="45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G135" s="51" t="n">
+        <v>45692</v>
+      </c>
+      <c r="H135" s="44">
+        <f>IF(C135="","",F135-C135)</f>
+        <v/>
+      </c>
+      <c r="I135" s="44" t="inlineStr">
+        <is>
+          <t>LOCKED 2026-09-20: books sold to Aquinas. $1,000 cash on EPGC Art Sales February. Cost / titles TBD — not in Income I8 until Cost. Distinct from 2022 Saharan bracelets. Not tax advice.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -6805,15 +6848,15 @@
   <sheetData>
     <row r="1"/>
     <row r="2">
-      <c r="A2" s="51" t="inlineStr">
+      <c r="A2" s="52" t="inlineStr">
         <is>
           <t>GCM Boards 2022</t>
         </is>
       </c>
-      <c r="B2" s="52" t="n"/>
-      <c r="C2" s="52" t="n"/>
-      <c r="D2" s="52" t="n"/>
-      <c r="E2" s="52" t="n"/>
+      <c r="B2" s="53" t="n"/>
+      <c r="C2" s="53" t="n"/>
+      <c r="D2" s="53" t="n"/>
+      <c r="E2" s="53" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -6916,15 +6959,15 @@
     </row>
     <row r="8"/>
     <row r="9">
-      <c r="A9" s="51" t="inlineStr">
+      <c r="A9" s="52" t="inlineStr">
         <is>
           <t>GCM Boards 2023</t>
         </is>
       </c>
-      <c r="B9" s="52" t="n"/>
-      <c r="C9" s="52" t="n"/>
-      <c r="D9" s="52" t="n"/>
-      <c r="E9" s="52" t="n"/>
+      <c r="B9" s="53" t="n"/>
+      <c r="C9" s="53" t="n"/>
+      <c r="D9" s="53" t="n"/>
+      <c r="E9" s="53" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -6965,10 +7008,10 @@
       <c r="C11" s="5" t="n">
         <v>3675</v>
       </c>
-      <c r="D11" s="53" t="n">
+      <c r="D11" s="54" t="n">
         <v>3675</v>
       </c>
-      <c r="E11" s="53" t="n">
+      <c r="E11" s="54" t="n">
         <v>3675</v>
       </c>
     </row>
@@ -7010,15 +7053,15 @@
     </row>
     <row r="14"/>
     <row r="15">
-      <c r="A15" s="51" t="inlineStr">
+      <c r="A15" s="52" t="inlineStr">
         <is>
           <t>GCM Boards 2024</t>
         </is>
       </c>
-      <c r="B15" s="52" t="n"/>
-      <c r="C15" s="52" t="n"/>
-      <c r="D15" s="52" t="n"/>
-      <c r="E15" s="52" t="n"/>
+      <c r="B15" s="53" t="n"/>
+      <c r="C15" s="53" t="n"/>
+      <c r="D15" s="53" t="n"/>
+      <c r="E15" s="53" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -7059,10 +7102,10 @@
       <c r="C17" s="5" t="n">
         <v>4050</v>
       </c>
-      <c r="D17" s="53" t="n">
+      <c r="D17" s="54" t="n">
         <v>4050</v>
       </c>
-      <c r="E17" s="53" t="n">
+      <c r="E17" s="54" t="n">
         <v>4050</v>
       </c>
     </row>
@@ -7104,11 +7147,11 @@
     </row>
     <row r="20">
       <c r="A20" s="22" t="n"/>
-      <c r="B20" s="54" t="n"/>
+      <c r="B20" s="55" t="n"/>
     </row>
     <row r="21"/>
     <row r="22">
-      <c r="A22" s="55" t="inlineStr">
+      <c r="A22" s="56" t="inlineStr">
         <is>
           <t>GCM Boards 2025</t>
         </is>
@@ -7147,16 +7190,16 @@
           <t>GCM Board</t>
         </is>
       </c>
-      <c r="B24" s="56" t="n">
+      <c r="B24" s="57" t="n">
         <v>4100</v>
       </c>
-      <c r="C24" s="56" t="n">
+      <c r="C24" s="57" t="n">
         <v>9200</v>
       </c>
-      <c r="D24" s="56" t="n">
+      <c r="D24" s="57" t="n">
         <v>4100</v>
       </c>
-      <c r="E24" s="56" t="n">
+      <c r="E24" s="57" t="n">
         <v>4100</v>
       </c>
     </row>
@@ -7270,80 +7313,80 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="55" t="inlineStr">
+      <c r="A5" s="56" t="inlineStr">
         <is>
           <t>Coinbase (ACH from Mercury 8291)</t>
         </is>
       </c>
-      <c r="B5" s="57" t="inlineStr">
+      <c r="B5" s="58" t="inlineStr">
         <is>
           <t>Investment transfers — not EPGC Art Sales, not advisory. Distinct from Coinbase 6108 card.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="58" t="inlineStr"/>
-      <c r="B6" s="58" t="inlineStr">
+      <c r="A6" s="59" t="inlineStr"/>
+      <c r="B6" s="59" t="inlineStr">
         <is>
           <t>JAN</t>
         </is>
       </c>
-      <c r="C6" s="58" t="inlineStr">
+      <c r="C6" s="59" t="inlineStr">
         <is>
           <t>FEB</t>
         </is>
       </c>
-      <c r="D6" s="58" t="inlineStr">
+      <c r="D6" s="59" t="inlineStr">
         <is>
           <t>MAR</t>
         </is>
       </c>
-      <c r="E6" s="58" t="inlineStr">
+      <c r="E6" s="59" t="inlineStr">
         <is>
           <t>APR</t>
         </is>
       </c>
-      <c r="F6" s="58" t="inlineStr">
+      <c r="F6" s="59" t="inlineStr">
         <is>
           <t>MAY</t>
         </is>
       </c>
-      <c r="G6" s="58" t="inlineStr">
+      <c r="G6" s="59" t="inlineStr">
         <is>
           <t>JUN</t>
         </is>
       </c>
-      <c r="H6" s="58" t="inlineStr">
+      <c r="H6" s="59" t="inlineStr">
         <is>
           <t>JUL</t>
         </is>
       </c>
-      <c r="I6" s="58" t="inlineStr">
+      <c r="I6" s="59" t="inlineStr">
         <is>
           <t>AUG</t>
         </is>
       </c>
-      <c r="J6" s="58" t="inlineStr">
+      <c r="J6" s="59" t="inlineStr">
         <is>
           <t>SEP</t>
         </is>
       </c>
-      <c r="K6" s="58" t="inlineStr">
+      <c r="K6" s="59" t="inlineStr">
         <is>
           <t>OCT</t>
         </is>
       </c>
-      <c r="L6" s="58" t="inlineStr">
+      <c r="L6" s="59" t="inlineStr">
         <is>
           <t>NOV</t>
         </is>
       </c>
-      <c r="M6" s="58" t="inlineStr">
+      <c r="M6" s="59" t="inlineStr">
         <is>
           <t>DEC</t>
         </is>
       </c>
-      <c r="N6" s="58" t="inlineStr">
+      <c r="N6" s="59" t="inlineStr">
         <is>
           <t>2025 NET</t>
         </is>
@@ -7379,19 +7422,19 @@
       <c r="I7" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="J7" s="59" t="n">
+      <c r="J7" s="60" t="n">
         <v>-9000</v>
       </c>
-      <c r="K7" s="59" t="n">
+      <c r="K7" s="60" t="n">
         <v>-10000</v>
       </c>
-      <c r="L7" s="59" t="n">
+      <c r="L7" s="60" t="n">
         <v>-35000</v>
       </c>
-      <c r="M7" s="59" t="n">
+      <c r="M7" s="60" t="n">
         <v>-5000</v>
       </c>
-      <c r="N7" s="60">
+      <c r="N7" s="61">
         <f>SUM(B7:M7)</f>
         <v/>
       </c>
@@ -7435,10 +7478,10 @@
       <c r="L8" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="M8" s="59" t="n">
+      <c r="M8" s="60" t="n">
         <v>8000</v>
       </c>
-      <c r="N8" s="60">
+      <c r="N8" s="61">
         <f>SUM(B8:M8)</f>
         <v/>
       </c>
@@ -7485,14 +7528,14 @@
       <c r="M9" s="45" t="n">
         <v>3000</v>
       </c>
-      <c r="N9" s="60">
+      <c r="N9" s="61">
         <f>SUM(B9:M9)</f>
         <v/>
       </c>
     </row>
     <row r="10"/>
     <row r="11">
-      <c r="A11" s="61" t="inlineStr">
+      <c r="A11" s="62" t="inlineStr">
         <is>
           <t>2025: funded $59,000.00 / returned $8,000.00 / net $-51,000.00 off the EPGC operating account. Not income, not an expense. Not tax advice.</t>
         </is>
@@ -7509,7 +7552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -7520,138 +7563,138 @@
     <row r="1">
       <c r="A1" s="41" t="inlineStr">
         <is>
-          <t>ASK — remaining Mercury 8291 questions. Q6 consultant, Q7 Wise expertise write-ups, Q8 pass-through LOCKED 2026-09-20. Not tax advice.</t>
+          <t>ASK — remaining Mercury 8291 questions. Q6 consultant, Q7 Wise expertise write-ups, Q8 pass-through, Q9 Aquinas books LOCKED 2026-09-20. Not tax advice.</t>
         </is>
       </c>
     </row>
     <row r="2"/>
     <row r="3">
-      <c r="A3" s="58" t="inlineStr">
+      <c r="A3" s="59" t="inlineStr">
         <is>
           <t>Question</t>
         </is>
       </c>
-      <c r="B3" s="58" t="inlineStr">
+      <c r="B3" s="59" t="inlineStr">
         <is>
           <t>What I need</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="62" t="inlineStr">
+      <c r="A4" s="63" t="inlineStr">
         <is>
           <t>1. EOEB LLC remainder after mosaics</t>
         </is>
       </c>
-      <c r="B4" s="63" t="inlineStr">
+      <c r="B4" s="64" t="inlineStr">
         <is>
           <t>$130,270.00 of EOEB IN is not the $105,000 mosaics sale and not the $565.75 Wise reimbursement. Invoice / MAKE A PAYMENT pattern. Book as art advisory (EPGC Consultant) or as more art sales? Jan 16 $1,000 might be the Canosan horse (sold to Erdal $1,000 on Art Sales) — yes/no?</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="62" t="inlineStr">
+      <c r="A5" s="63" t="inlineStr">
         <is>
           <t>2. L5 (all seven invoices)</t>
         </is>
       </c>
-      <c r="B5" s="63" t="inlineStr">
+      <c r="B5" s="64" t="inlineStr">
         <is>
           <t>$87,396.32. Same Auto-Routing Request or Invoice Payment pattern as EOEB. Advisory fees, art sales, or mixed? The 7/15 $50,000 lands the same week as Aysel $50k and Fortuna $45k.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="62" t="inlineStr">
+      <c r="A6" s="63" t="inlineStr">
         <is>
           <t>3. Fortuna / Erdal Dere OUT after seals</t>
         </is>
       </c>
-      <c r="B6" s="63" t="inlineStr">
+      <c r="B6" s="64" t="inlineStr">
         <is>
           <t>$85,000.00 after the 1/8 $13,000 seals COGS (5/9 $20k, 7/21 $45k, 8/15 $20k). Inventory purchases (object names) or something else?</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="62" t="inlineStr">
+      <c r="A7" s="63" t="inlineStr">
         <is>
           <t>4. Erdal Dere IN</t>
         </is>
       </c>
-      <c r="B7" s="63" t="inlineStr">
+      <c r="B7" s="64" t="inlineStr">
         <is>
           <t>$57,000.00 (7/24 $26k, 10/9 $25k, 11/7 $6k ‘FORTUNA PAYMENT’). Sales to Erdal, refunds of Fortuna purchases, or other?</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="62" t="inlineStr">
+      <c r="A8" s="63" t="inlineStr">
         <is>
           <t>5. Aysel Dere $50,000 IN (7/18)</t>
         </is>
       </c>
-      <c r="B8" s="63" t="inlineStr">
+      <c r="B8" s="64" t="inlineStr">
         <is>
           <t>Sale, related-party transfer, or part of the mid-July Fortuna/L5 cluster?</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="64" t="inlineStr">
+      <c r="A9" s="65" t="inlineStr">
         <is>
           <t>6. David Aaron Limited $13,595 IN (6/24) — LOCKED consultant fee</t>
         </is>
       </c>
-      <c r="B9" s="65" t="inlineStr">
+      <c r="B9" s="66" t="inlineStr">
         <is>
           <t>CONFIRMED 2026-09-20: consultant fee, not a sale. Booked EPGC Consultant June $13,595 (peach). Not Art Sales. Not Income I8.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="64" t="inlineStr">
+      <c r="A10" s="65" t="inlineStr">
         <is>
           <t>7. Wise $334.17 (7/9) and $658.63 (10/30) — LOCKED expertise write-ups</t>
         </is>
       </c>
-      <c r="B10" s="65" t="inlineStr">
+      <c r="B10" s="66" t="inlineStr">
         <is>
           <t>CONFIRMED 2026-09-20: business expenses (expertise write-ups). Booked EPGC Consultant Fees July $334.17 + October $658.63 = $992.80. Not COGS. Distinct from Dec Wise $565.75 reimbursed by EOEB (still not P&amp;L).</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="64" t="inlineStr">
+      <c r="A11" s="65" t="inlineStr">
         <is>
           <t>8. Jack Koziol &amp; Tracy Hoffman $150,000 IN (10/20) / Ariadne Demirjian $150,000 OUT (10/21) — LOCKED pass-through</t>
         </is>
       </c>
-      <c r="B11" s="65" t="inlineStr">
+      <c r="B11" s="66" t="inlineStr">
         <is>
           <t>CONFIRMED 2026-09-20: pass-through, not P&amp;L. Not a sale, not a purchase, not COGS, not Consultant.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="62" t="inlineStr">
-        <is>
-          <t>9. Aquinas Hobor $1,000 IN (2/4)</t>
-        </is>
-      </c>
-      <c r="B12" s="63" t="inlineStr">
-        <is>
-          <t>Sale, leftover, or other? Aquinas bought Saharan bracelets in 2022.</t>
+      <c r="A12" s="65" t="inlineStr">
+        <is>
+          <t>9. Aquinas Hobor $1,000 IN (2/4) — LOCKED books sold</t>
+        </is>
+      </c>
+      <c r="B12" s="66" t="inlineStr">
+        <is>
+          <t>CONFIRMED 2026-09-20: books sold to Aquinas. Booked EPGC Art Sales February $1,000 (peach). Cost / titles TBD — not in Income I8 until Cost. Distinct from 2022 Saharan bracelets.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="62" t="inlineStr">
+      <c r="A13" s="63" t="inlineStr">
         <is>
           <t>10. Mosaics Cost $90,000 vs Mercury $50,000</t>
         </is>
       </c>
-      <c r="B13" s="63" t="inlineStr">
+      <c r="B13" s="64" t="inlineStr">
         <is>
           <t>Plutus &amp; Mnemosyne paid $50,000 in February. Where is the other $40,000 of Cost (other account / 2024 / still owed)?</t>
         </is>
@@ -7659,7 +7702,7 @@
     </row>
     <row r="14"/>
     <row r="15">
-      <c r="A15" s="58" t="inlineStr">
+      <c r="A15" s="59" t="inlineStr">
         <is>
           <t>LOCKED / MATCHED this pass (do not recast without saying so)</t>
         </is>
@@ -7782,6 +7825,18 @@
       <c r="B25" s="44" t="inlineStr">
         <is>
           <t>$334.17 (7/9) + $658.63 (10/30) = $992.80 → EPGC Consultant Fees expense. Dec $565.75 still reimbursed / not P&amp;L.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="44" t="inlineStr">
+        <is>
+          <t>Aquinas Hobor books</t>
+        </is>
+      </c>
+      <c r="B26" s="44" t="inlineStr">
+        <is>
+          <t>$1,000 IN 2/4 LOCKED books sold → EPGC Art Sales February. Cost / titles TBD (not in I8 until Cost).</t>
         </is>
       </c>
     </row>
@@ -7814,82 +7869,82 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="66" t="inlineStr">
-        <is>
-          <t>Mercury Checking 8291 — EPGC LLC (Choice Financial) 2025. 64 unique cash transactions. Coinbase ACH = investment. Newstar = jewelry COGS on intaglios/gems/scarabs. BoA 9922 draws and Koziol/Ariadne $150k are LOCKED not-P&amp;L (pass-through / owner transfer). David Aaron $13,595 is LOCKED EPGC Consultant (June). Wise $334.17 + $658.63 are LOCKED EPGC Consultant Fees (expertise write-ups). Not tax advice.</t>
+      <c r="A1" s="67" t="inlineStr">
+        <is>
+          <t>Mercury Checking 8291 — EPGC LLC (Choice Financial) 2025. 64 unique cash transactions. Coinbase ACH = investment. Newstar = jewelry COGS on intaglios/gems/scarabs. BoA 9922 draws and Koziol/Ariadne $150k are LOCKED not-P&amp;L (pass-through / owner transfer). David Aaron $13,595 is LOCKED EPGC Consultant (June). Wise $334.17 + $658.63 are LOCKED EPGC Consultant Fees (expertise write-ups). Aquinas Hobor $1,000 (2/4) is LOCKED books sold (EPGC Art Sales February; Cost TBD). Not tax advice.</t>
         </is>
       </c>
     </row>
     <row r="2"/>
     <row r="3">
-      <c r="A3" s="67" t="inlineStr">
+      <c r="A3" s="68" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B3" s="67" t="inlineStr">
+      <c r="B3" s="68" t="inlineStr">
         <is>
           <t>Counterparty</t>
         </is>
       </c>
-      <c r="C3" s="67" t="inlineStr">
+      <c r="C3" s="68" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="D3" s="67" t="inlineStr">
+      <c r="D3" s="68" t="inlineStr">
         <is>
           <t>Direction</t>
         </is>
       </c>
-      <c r="E3" s="67" t="inlineStr">
+      <c r="E3" s="68" t="inlineStr">
         <is>
           <t>Bucket</t>
         </is>
       </c>
-      <c r="F3" s="67" t="inlineStr">
+      <c r="F3" s="68" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G3" s="67" t="inlineStr">
+      <c r="G3" s="68" t="inlineStr">
         <is>
           <t>Deal / object</t>
         </is>
       </c>
-      <c r="H3" s="67" t="inlineStr">
+      <c r="H3" s="68" t="inlineStr">
         <is>
           <t>Hits EPGC Art Sales?</t>
         </is>
       </c>
-      <c r="I3" s="67" t="inlineStr">
+      <c r="I3" s="68" t="inlineStr">
         <is>
           <t>Hits EPGC Consultant?</t>
         </is>
       </c>
-      <c r="J3" s="67" t="inlineStr">
+      <c r="J3" s="68" t="inlineStr">
         <is>
           <t>Monarch category</t>
         </is>
       </c>
-      <c r="K3" s="67" t="inlineStr">
+      <c r="K3" s="68" t="inlineStr">
         <is>
           <t>Original statement</t>
         </is>
       </c>
-      <c r="L3" s="67" t="inlineStr">
+      <c r="L3" s="68" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="57" t="inlineStr">
+      <c r="A4" s="58" t="inlineStr">
         <is>
           <t>2025-01-08</t>
         </is>
       </c>
-      <c r="B4" s="57" t="inlineStr">
+      <c r="B4" s="58" t="inlineStr">
         <is>
           <t>Erdal Dere (Fortuna)</t>
         </is>
@@ -7897,12 +7952,12 @@
       <c r="C4" s="10" t="n">
         <v>-13000</v>
       </c>
-      <c r="D4" s="57" t="inlineStr">
+      <c r="D4" s="58" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E4" s="68" t="inlineStr">
+      <c r="E4" s="69" t="inlineStr">
         <is>
           <t>ART_PURCHASE</t>
         </is>
@@ -7912,27 +7967,27 @@
           <t>MATCHED</t>
         </is>
       </c>
-      <c r="G4" s="57" t="inlineStr">
+      <c r="G4" s="58" t="inlineStr">
         <is>
           <t>A Collection of Seals — COGS</t>
         </is>
       </c>
-      <c r="H4" s="57" t="inlineStr">
+      <c r="H4" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I4" s="57" t="inlineStr">
+      <c r="I4" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J4" s="57" t="inlineStr">
+      <c r="J4" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">Business Investment </t>
         </is>
       </c>
-      <c r="K4" s="57" t="inlineStr">
+      <c r="K4" s="58" t="inlineStr">
         <is>
           <t>Merchant name: Erdal Dere (Fortuna)</t>
         </is>
@@ -7944,12 +7999,12 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="57" t="inlineStr">
+      <c r="A5" s="58" t="inlineStr">
         <is>
           <t>2025-01-10</t>
         </is>
       </c>
-      <c r="B5" s="57" t="inlineStr">
+      <c r="B5" s="58" t="inlineStr">
         <is>
           <t>HARLAN J BERK LTD</t>
         </is>
@@ -7957,12 +8012,12 @@
       <c r="C5" s="45" t="n">
         <v>14000</v>
       </c>
-      <c r="D5" s="57" t="inlineStr">
+      <c r="D5" s="58" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E5" s="69" t="inlineStr">
+      <c r="E5" s="70" t="inlineStr">
         <is>
           <t>ART_SALE</t>
         </is>
@@ -7972,27 +8027,27 @@
           <t>MATCHED</t>
         </is>
       </c>
-      <c r="G5" s="57" t="inlineStr">
+      <c r="G5" s="58" t="inlineStr">
         <is>
           <t>A Collection of Seals — Sale Price</t>
         </is>
       </c>
-      <c r="H5" s="57" t="inlineStr">
+      <c r="H5" s="58" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="I5" s="57" t="inlineStr">
+      <c r="I5" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J5" s="57" t="inlineStr">
+      <c r="J5" s="58" t="inlineStr">
         <is>
           <t>Business Income</t>
         </is>
       </c>
-      <c r="K5" s="57" t="inlineStr">
+      <c r="K5" s="58" t="inlineStr">
         <is>
           <t>Incoming Wire; Merchant name: HARLAN J BERK LTD</t>
         </is>
@@ -8004,55 +8059,55 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="57" t="inlineStr">
+      <c r="A6" s="58" t="inlineStr">
         <is>
           <t>2025-01-16</t>
         </is>
       </c>
-      <c r="B6" s="57" t="inlineStr">
+      <c r="B6" s="58" t="inlineStr">
         <is>
           <t>EOEB LLC</t>
         </is>
       </c>
-      <c r="C6" s="70" t="n">
+      <c r="C6" s="71" t="n">
         <v>1000</v>
       </c>
-      <c r="D6" s="57" t="inlineStr">
+      <c r="D6" s="58" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E6" s="71" t="inlineStr">
+      <c r="E6" s="72" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="F6" s="71" t="inlineStr">
+      <c r="F6" s="72" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G6" s="57" t="inlineStr">
+      <c r="G6" s="58" t="inlineStr">
         <is>
           <t>EOEB $1,000 — Canosan horse vs advisory</t>
         </is>
       </c>
-      <c r="H6" s="57" t="inlineStr">
+      <c r="H6" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I6" s="57" t="inlineStr">
+      <c r="I6" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J6" s="57" t="inlineStr">
+      <c r="J6" s="58" t="inlineStr">
         <is>
           <t>Business Income</t>
         </is>
       </c>
-      <c r="K6" s="57" t="inlineStr">
+      <c r="K6" s="58" t="inlineStr">
         <is>
           <t>Incoming Wire; MAKE A PAYMENT; Merchant name: EOEB LLC</t>
         </is>
@@ -8064,12 +8119,12 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="57" t="inlineStr">
+      <c r="A7" s="58" t="inlineStr">
         <is>
           <t>2025-02-04</t>
         </is>
       </c>
-      <c r="B7" s="57" t="inlineStr">
+      <c r="B7" s="58" t="inlineStr">
         <is>
           <t>Bank of America - Checking ••9922</t>
         </is>
@@ -8077,12 +8132,12 @@
       <c r="C7" s="10" t="n">
         <v>-25000</v>
       </c>
-      <c r="D7" s="57" t="inlineStr">
+      <c r="D7" s="58" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E7" s="72" t="inlineStr">
+      <c r="E7" s="73" t="inlineStr">
         <is>
           <t>TRANSFER</t>
         </is>
@@ -8092,27 +8147,27 @@
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="G7" s="57" t="inlineStr">
+      <c r="G7" s="58" t="inlineStr">
         <is>
           <t>Owner transfer to BoA 9922</t>
         </is>
       </c>
-      <c r="H7" s="57" t="inlineStr">
+      <c r="H7" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I7" s="57" t="inlineStr">
+      <c r="I7" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J7" s="57" t="inlineStr">
+      <c r="J7" s="58" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K7" s="57" t="inlineStr">
+      <c r="K7" s="58" t="inlineStr">
         <is>
           <t>Transfer from Mercury to another bank account; Merchant name: Bank of America - Checking ••9922</t>
         </is>
@@ -8124,72 +8179,72 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="57" t="inlineStr">
+      <c r="A8" s="58" t="inlineStr">
         <is>
           <t>2025-02-04</t>
         </is>
       </c>
-      <c r="B8" s="57" t="inlineStr">
+      <c r="B8" s="58" t="inlineStr">
         <is>
           <t>AQUINAS HOBOR</t>
         </is>
       </c>
-      <c r="C8" s="70" t="n">
+      <c r="C8" s="45" t="n">
         <v>1000</v>
       </c>
-      <c r="D8" s="57" t="inlineStr">
+      <c r="D8" s="58" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E8" s="71" t="inlineStr">
-        <is>
-          <t>ASK</t>
-        </is>
-      </c>
-      <c r="F8" s="71" t="inlineStr">
-        <is>
-          <t>ASK</t>
-        </is>
-      </c>
-      <c r="G8" s="57" t="inlineStr">
-        <is>
-          <t>Aquinas Hobor $1,000</t>
-        </is>
-      </c>
-      <c r="H8" s="57" t="inlineStr">
+      <c r="E8" s="70" t="inlineStr">
+        <is>
+          <t>ART_SALE</t>
+        </is>
+      </c>
+      <c r="F8" s="44" t="inlineStr">
+        <is>
+          <t>LOCKED</t>
+        </is>
+      </c>
+      <c r="G8" s="58" t="inlineStr">
+        <is>
+          <t>Books sold to Aquinas Hobor — Sale Price</t>
+        </is>
+      </c>
+      <c r="H8" s="58" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I8" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I8" s="57" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J8" s="57" t="inlineStr">
+      <c r="J8" s="58" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K8" s="57" t="inlineStr">
+      <c r="K8" s="58" t="inlineStr">
         <is>
           <t>AQUINAS HOBOR; SENDER; 770699534; Merchant name: AQUINAS HOBOR</t>
         </is>
       </c>
       <c r="L8" s="14" t="inlineStr">
         <is>
-          <t>Prior-year buyer (Saharan bracelets 2022). 2025 sale, leftover, or something else?</t>
+          <t>User 2026-09-20: books sold to Aquinas. Hits EPGC Art Sales February $1,000. Cost / titles TBD (not in I8 net until Cost). Distinct from 2022 Saharan bracelets sale.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="57" t="inlineStr">
+      <c r="A9" s="58" t="inlineStr">
         <is>
           <t>2025-02-07</t>
         </is>
       </c>
-      <c r="B9" s="57" t="inlineStr">
+      <c r="B9" s="58" t="inlineStr">
         <is>
           <t>HARLAN J BERK LTD</t>
         </is>
@@ -8197,12 +8252,12 @@
       <c r="C9" s="45" t="n">
         <v>30000</v>
       </c>
-      <c r="D9" s="57" t="inlineStr">
+      <c r="D9" s="58" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E9" s="69" t="inlineStr">
+      <c r="E9" s="70" t="inlineStr">
         <is>
           <t>ART_SALE</t>
         </is>
@@ -8212,27 +8267,27 @@
           <t>MATCHED</t>
         </is>
       </c>
-      <c r="G9" s="57" t="inlineStr">
+      <c r="G9" s="58" t="inlineStr">
         <is>
           <t>Berk lots lump Sale Price $30,000</t>
         </is>
       </c>
-      <c r="H9" s="57" t="inlineStr">
+      <c r="H9" s="58" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="I9" s="57" t="inlineStr">
+      <c r="I9" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J9" s="57" t="inlineStr">
+      <c r="J9" s="58" t="inlineStr">
         <is>
           <t>Business Income</t>
         </is>
       </c>
-      <c r="K9" s="57" t="inlineStr">
+      <c r="K9" s="58" t="inlineStr">
         <is>
           <t>Incoming Wire; PER ARB; Merchant name: HARLAN J BERK LTD</t>
         </is>
@@ -8244,12 +8299,12 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="57" t="inlineStr">
+      <c r="A10" s="58" t="inlineStr">
         <is>
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="B10" s="57" t="inlineStr">
+      <c r="B10" s="58" t="inlineStr">
         <is>
           <t>Jamal M Rifai</t>
         </is>
@@ -8257,12 +8312,12 @@
       <c r="C10" s="10" t="n">
         <v>-10</v>
       </c>
-      <c r="D10" s="57" t="inlineStr">
+      <c r="D10" s="58" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E10" s="72" t="inlineStr">
+      <c r="E10" s="73" t="inlineStr">
         <is>
           <t>TEST</t>
         </is>
@@ -8272,27 +8327,27 @@
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="G10" s="57" t="inlineStr">
+      <c r="G10" s="58" t="inlineStr">
         <is>
           <t>$10 test wire to Jamal M. Rifai</t>
         </is>
       </c>
-      <c r="H10" s="57" t="inlineStr">
+      <c r="H10" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I10" s="57" t="inlineStr">
+      <c r="I10" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J10" s="57" t="inlineStr">
+      <c r="J10" s="58" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K10" s="57" t="inlineStr">
+      <c r="K10" s="58" t="inlineStr">
         <is>
           <t>Merchant name: Jamal M Rifai</t>
         </is>
@@ -8304,12 +8359,12 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="57" t="inlineStr">
+      <c r="A11" s="58" t="inlineStr">
         <is>
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="B11" s="57" t="inlineStr">
+      <c r="B11" s="58" t="inlineStr">
         <is>
           <t>DDA/066196221</t>
         </is>
@@ -8317,12 +8372,12 @@
       <c r="C11" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="D11" s="57" t="inlineStr">
+      <c r="D11" s="58" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E11" s="72" t="inlineStr">
+      <c r="E11" s="73" t="inlineStr">
         <is>
           <t>TEST</t>
         </is>
@@ -8332,27 +8387,27 @@
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="G11" s="57" t="inlineStr">
+      <c r="G11" s="58" t="inlineStr">
         <is>
           <t>$10 test wire in</t>
         </is>
       </c>
-      <c r="H11" s="57" t="inlineStr">
+      <c r="H11" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I11" s="57" t="inlineStr">
+      <c r="I11" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J11" s="57" t="inlineStr">
+      <c r="J11" s="58" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K11" s="57" t="inlineStr">
+      <c r="K11" s="58" t="inlineStr">
         <is>
           <t>Incoming Wire; Merchant name: DDA/066196221</t>
         </is>
@@ -8364,12 +8419,12 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="57" t="inlineStr">
+      <c r="A12" s="58" t="inlineStr">
         <is>
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="B12" s="57" t="inlineStr">
+      <c r="B12" s="58" t="inlineStr">
         <is>
           <t>EOEB LLC</t>
         </is>
@@ -8377,12 +8432,12 @@
       <c r="C12" s="45" t="n">
         <v>105000</v>
       </c>
-      <c r="D12" s="57" t="inlineStr">
+      <c r="D12" s="58" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E12" s="69" t="inlineStr">
+      <c r="E12" s="70" t="inlineStr">
         <is>
           <t>ART_SALE</t>
         </is>
@@ -8392,27 +8447,27 @@
           <t>MATCHED</t>
         </is>
       </c>
-      <c r="G12" s="57" t="inlineStr">
+      <c r="G12" s="58" t="inlineStr">
         <is>
           <t>Three Ancient Mosaics — Sale Price</t>
         </is>
       </c>
-      <c r="H12" s="57" t="inlineStr">
+      <c r="H12" s="58" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="I12" s="57" t="inlineStr">
+      <c r="I12" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J12" s="57" t="inlineStr">
+      <c r="J12" s="58" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K12" s="57" t="inlineStr">
+      <c r="K12" s="58" t="inlineStr">
         <is>
           <t>Incoming Wire; MAKE A PAYMENT; Merchant name: EOEB LLC</t>
         </is>
@@ -8424,12 +8479,12 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="57" t="inlineStr">
+      <c r="A13" s="58" t="inlineStr">
         <is>
           <t>2025-02-24</t>
         </is>
       </c>
-      <c r="B13" s="57" t="inlineStr">
+      <c r="B13" s="58" t="inlineStr">
         <is>
           <t>Bank of America - Checking ••9922</t>
         </is>
@@ -8437,12 +8492,12 @@
       <c r="C13" s="10" t="n">
         <v>-90000</v>
       </c>
-      <c r="D13" s="57" t="inlineStr">
+      <c r="D13" s="58" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E13" s="72" t="inlineStr">
+      <c r="E13" s="73" t="inlineStr">
         <is>
           <t>TRANSFER</t>
         </is>
@@ -8452,27 +8507,27 @@
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="G13" s="57" t="inlineStr">
+      <c r="G13" s="58" t="inlineStr">
         <is>
           <t>Owner transfer to BoA 9922</t>
         </is>
       </c>
-      <c r="H13" s="57" t="inlineStr">
+      <c r="H13" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I13" s="57" t="inlineStr">
+      <c r="I13" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J13" s="57" t="inlineStr">
+      <c r="J13" s="58" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K13" s="57" t="inlineStr">
+      <c r="K13" s="58" t="inlineStr">
         <is>
           <t>Transfer from Mercury to another bank account; Merchant name: Bank of America - Checking ••9922</t>
         </is>
@@ -8484,12 +8539,12 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="57" t="inlineStr">
+      <c r="A14" s="58" t="inlineStr">
         <is>
           <t>2025-02-24</t>
         </is>
       </c>
-      <c r="B14" s="57" t="inlineStr">
+      <c r="B14" s="58" t="inlineStr">
         <is>
           <t>Jamal M Rifai</t>
         </is>
@@ -8497,12 +8552,12 @@
       <c r="C14" s="10" t="n">
         <v>-10</v>
       </c>
-      <c r="D14" s="57" t="inlineStr">
+      <c r="D14" s="58" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E14" s="72" t="inlineStr">
+      <c r="E14" s="73" t="inlineStr">
         <is>
           <t>TEST</t>
         </is>
@@ -8512,27 +8567,27 @@
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="G14" s="57" t="inlineStr">
+      <c r="G14" s="58" t="inlineStr">
         <is>
           <t>$10 test (Jamal or Plutus)</t>
         </is>
       </c>
-      <c r="H14" s="57" t="inlineStr">
+      <c r="H14" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I14" s="57" t="inlineStr">
+      <c r="I14" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J14" s="57" t="inlineStr">
+      <c r="J14" s="58" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K14" s="57" t="inlineStr">
+      <c r="K14" s="58" t="inlineStr">
         <is>
           <t>Merchant name: Jamal M Rifai</t>
         </is>
@@ -8544,12 +8599,12 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="57" t="inlineStr">
+      <c r="A15" s="58" t="inlineStr">
         <is>
           <t>2025-02-24</t>
         </is>
       </c>
-      <c r="B15" s="57" t="inlineStr">
+      <c r="B15" s="58" t="inlineStr">
         <is>
           <t>Plutus &amp; Mnemosyne, LLC</t>
         </is>
@@ -8557,12 +8612,12 @@
       <c r="C15" s="10" t="n">
         <v>-10</v>
       </c>
-      <c r="D15" s="57" t="inlineStr">
+      <c r="D15" s="58" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E15" s="72" t="inlineStr">
+      <c r="E15" s="73" t="inlineStr">
         <is>
           <t>TEST</t>
         </is>
@@ -8572,27 +8627,27 @@
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="G15" s="57" t="inlineStr">
+      <c r="G15" s="58" t="inlineStr">
         <is>
           <t>$10 test (Jamal or Plutus)</t>
         </is>
       </c>
-      <c r="H15" s="57" t="inlineStr">
+      <c r="H15" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I15" s="57" t="inlineStr">
+      <c r="I15" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J15" s="57" t="inlineStr">
+      <c r="J15" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">Business Investment </t>
         </is>
       </c>
-      <c r="K15" s="57" t="inlineStr">
+      <c r="K15" s="58" t="inlineStr">
         <is>
           <t>Merchant name: Plutus &amp; Mnemosyne, LLC</t>
         </is>
@@ -8604,12 +8659,12 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="57" t="inlineStr">
+      <c r="A16" s="58" t="inlineStr">
         <is>
           <t>2025-02-24</t>
         </is>
       </c>
-      <c r="B16" s="57" t="inlineStr">
+      <c r="B16" s="58" t="inlineStr">
         <is>
           <t>EPGC LLC</t>
         </is>
@@ -8617,12 +8672,12 @@
       <c r="C16" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="D16" s="57" t="inlineStr">
+      <c r="D16" s="58" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E16" s="72" t="inlineStr">
+      <c r="E16" s="73" t="inlineStr">
         <is>
           <t>TEST</t>
         </is>
@@ -8632,27 +8687,27 @@
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="G16" s="57" t="inlineStr">
+      <c r="G16" s="58" t="inlineStr">
         <is>
           <t>$10 test wire EPGC</t>
         </is>
       </c>
-      <c r="H16" s="57" t="inlineStr">
+      <c r="H16" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I16" s="57" t="inlineStr">
+      <c r="I16" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J16" s="57" t="inlineStr">
+      <c r="J16" s="58" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K16" s="57" t="inlineStr">
+      <c r="K16" s="58" t="inlineStr">
         <is>
           <t>Incoming Wire; Merchant name: EPGC LLC</t>
         </is>
@@ -8664,12 +8719,12 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="57" t="inlineStr">
+      <c r="A17" s="58" t="inlineStr">
         <is>
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="B17" s="57" t="inlineStr">
+      <c r="B17" s="58" t="inlineStr">
         <is>
           <t>Plutus &amp; Mnemosyne, LLC</t>
         </is>
@@ -8677,12 +8732,12 @@
       <c r="C17" s="10" t="n">
         <v>-49990</v>
       </c>
-      <c r="D17" s="57" t="inlineStr">
+      <c r="D17" s="58" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E17" s="68" t="inlineStr">
+      <c r="E17" s="69" t="inlineStr">
         <is>
           <t>ART_PURCHASE</t>
         </is>
@@ -8692,27 +8747,27 @@
           <t>MATCHED</t>
         </is>
       </c>
-      <c r="G17" s="57" t="inlineStr">
+      <c r="G17" s="58" t="inlineStr">
         <is>
           <t>Three Ancient Mosaics — partial COGS</t>
         </is>
       </c>
-      <c r="H17" s="57" t="inlineStr">
+      <c r="H17" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I17" s="57" t="inlineStr">
+      <c r="I17" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J17" s="57" t="inlineStr">
+      <c r="J17" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">Business Investment </t>
         </is>
       </c>
-      <c r="K17" s="57" t="inlineStr">
+      <c r="K17" s="58" t="inlineStr">
         <is>
           <t>Merchant name: Plutus &amp; Mnemosyne, LLC</t>
         </is>
@@ -8724,55 +8779,55 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="57" t="inlineStr">
+      <c r="A18" s="58" t="inlineStr">
         <is>
           <t>2025-03-10</t>
         </is>
       </c>
-      <c r="B18" s="57" t="inlineStr">
+      <c r="B18" s="58" t="inlineStr">
         <is>
           <t>EOEB LLC</t>
         </is>
       </c>
-      <c r="C18" s="70" t="n">
+      <c r="C18" s="71" t="n">
         <v>14000</v>
       </c>
-      <c r="D18" s="57" t="inlineStr">
+      <c r="D18" s="58" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E18" s="71" t="inlineStr">
+      <c r="E18" s="72" t="inlineStr">
         <is>
           <t>ADVISORY</t>
         </is>
       </c>
-      <c r="F18" s="71" t="inlineStr">
+      <c r="F18" s="72" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G18" s="57" t="inlineStr">
+      <c r="G18" s="58" t="inlineStr">
         <is>
           <t>EOEB — sale vs art advisory</t>
         </is>
       </c>
-      <c r="H18" s="57" t="inlineStr">
+      <c r="H18" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I18" s="57" t="inlineStr">
+      <c r="I18" s="58" t="inlineStr">
         <is>
           <t>no — ASK first</t>
         </is>
       </c>
-      <c r="J18" s="57" t="inlineStr">
+      <c r="J18" s="58" t="inlineStr">
         <is>
           <t>Business Income</t>
         </is>
       </c>
-      <c r="K18" s="57" t="inlineStr">
+      <c r="K18" s="58" t="inlineStr">
         <is>
           <t>Incoming Wire; MAKE A PAYMENT; Merchant name: EOEB LLC</t>
         </is>
@@ -8784,55 +8839,55 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="57" t="inlineStr">
+      <c r="A19" s="58" t="inlineStr">
         <is>
           <t>2025-05-01</t>
         </is>
       </c>
-      <c r="B19" s="57" t="inlineStr">
+      <c r="B19" s="58" t="inlineStr">
         <is>
           <t>EOEB LLC</t>
         </is>
       </c>
-      <c r="C19" s="70" t="n">
+      <c r="C19" s="71" t="n">
         <v>21000</v>
       </c>
-      <c r="D19" s="57" t="inlineStr">
+      <c r="D19" s="58" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E19" s="71" t="inlineStr">
+      <c r="E19" s="72" t="inlineStr">
         <is>
           <t>ADVISORY</t>
         </is>
       </c>
-      <c r="F19" s="71" t="inlineStr">
+      <c r="F19" s="72" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G19" s="57" t="inlineStr">
+      <c r="G19" s="58" t="inlineStr">
         <is>
           <t>EOEB — sale vs art advisory</t>
         </is>
       </c>
-      <c r="H19" s="57" t="inlineStr">
+      <c r="H19" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I19" s="57" t="inlineStr">
+      <c r="I19" s="58" t="inlineStr">
         <is>
           <t>no — ASK first</t>
         </is>
       </c>
-      <c r="J19" s="57" t="inlineStr">
+      <c r="J19" s="58" t="inlineStr">
         <is>
           <t>Business Income</t>
         </is>
       </c>
-      <c r="K19" s="57" t="inlineStr">
+      <c r="K19" s="58" t="inlineStr">
         <is>
           <t>Incoming Wire; MAKE A PAYMENT; Merchant name: EOEB LLC</t>
         </is>
@@ -8844,55 +8899,55 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="57" t="inlineStr">
+      <c r="A20" s="58" t="inlineStr">
         <is>
           <t>2025-05-09</t>
         </is>
       </c>
-      <c r="B20" s="57" t="inlineStr">
+      <c r="B20" s="58" t="inlineStr">
         <is>
           <t>Erdal Dere (Fortuna)</t>
         </is>
       </c>
-      <c r="C20" s="70" t="n">
+      <c r="C20" s="71" t="n">
         <v>-20000</v>
       </c>
-      <c r="D20" s="57" t="inlineStr">
+      <c r="D20" s="58" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E20" s="68" t="inlineStr">
+      <c r="E20" s="69" t="inlineStr">
         <is>
           <t>ART_PURCHASE</t>
         </is>
       </c>
-      <c r="F20" s="71" t="inlineStr">
+      <c r="F20" s="72" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G20" s="57" t="inlineStr">
+      <c r="G20" s="58" t="inlineStr">
         <is>
           <t>Fortuna / Erdal — inventory vs other</t>
         </is>
       </c>
-      <c r="H20" s="57" t="inlineStr">
+      <c r="H20" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I20" s="57" t="inlineStr">
+      <c r="I20" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J20" s="57" t="inlineStr">
+      <c r="J20" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">Business Investment </t>
         </is>
       </c>
-      <c r="K20" s="57" t="inlineStr">
+      <c r="K20" s="58" t="inlineStr">
         <is>
           <t>Merchant name: Erdal Dere (Fortuna)</t>
         </is>
@@ -8904,55 +8959,55 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="57" t="inlineStr">
+      <c r="A21" s="58" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="B21" s="57" t="inlineStr">
+      <c r="B21" s="58" t="inlineStr">
         <is>
           <t>EOEB LLC</t>
         </is>
       </c>
-      <c r="C21" s="70" t="n">
+      <c r="C21" s="71" t="n">
         <v>16200</v>
       </c>
-      <c r="D21" s="57" t="inlineStr">
+      <c r="D21" s="58" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E21" s="71" t="inlineStr">
+      <c r="E21" s="72" t="inlineStr">
         <is>
           <t>ADVISORY</t>
         </is>
       </c>
-      <c r="F21" s="71" t="inlineStr">
+      <c r="F21" s="72" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G21" s="57" t="inlineStr">
+      <c r="G21" s="58" t="inlineStr">
         <is>
           <t>EOEB — sale vs art advisory</t>
         </is>
       </c>
-      <c r="H21" s="57" t="inlineStr">
+      <c r="H21" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I21" s="57" t="inlineStr">
+      <c r="I21" s="58" t="inlineStr">
         <is>
           <t>no — ASK first</t>
         </is>
       </c>
-      <c r="J21" s="57" t="inlineStr">
+      <c r="J21" s="58" t="inlineStr">
         <is>
           <t>Business Income</t>
         </is>
       </c>
-      <c r="K21" s="57" t="inlineStr">
+      <c r="K21" s="58" t="inlineStr">
         <is>
           <t>Incoming Wire; MAKE A PAYMENT; Merchant name: EOEB LLC</t>
         </is>
@@ -8964,55 +9019,55 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="57" t="inlineStr">
+      <c r="A22" s="58" t="inlineStr">
         <is>
           <t>2025-06-12</t>
         </is>
       </c>
-      <c r="B22" s="57" t="inlineStr">
+      <c r="B22" s="58" t="inlineStr">
         <is>
           <t>EOEB LLC</t>
         </is>
       </c>
-      <c r="C22" s="70" t="n">
+      <c r="C22" s="71" t="n">
         <v>3300</v>
       </c>
-      <c r="D22" s="57" t="inlineStr">
+      <c r="D22" s="58" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E22" s="71" t="inlineStr">
+      <c r="E22" s="72" t="inlineStr">
         <is>
           <t>ADVISORY</t>
         </is>
       </c>
-      <c r="F22" s="71" t="inlineStr">
+      <c r="F22" s="72" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G22" s="57" t="inlineStr">
+      <c r="G22" s="58" t="inlineStr">
         <is>
           <t>EOEB — sale vs art advisory</t>
         </is>
       </c>
-      <c r="H22" s="57" t="inlineStr">
+      <c r="H22" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I22" s="57" t="inlineStr">
+      <c r="I22" s="58" t="inlineStr">
         <is>
           <t>no — ASK first</t>
         </is>
       </c>
-      <c r="J22" s="57" t="inlineStr">
+      <c r="J22" s="58" t="inlineStr">
         <is>
           <t>Business Income</t>
         </is>
       </c>
-      <c r="K22" s="57" t="inlineStr">
+      <c r="K22" s="58" t="inlineStr">
         <is>
           <t>Incoming Wire; MAKE A PAYMENT; Merchant name: EOEB LLC</t>
         </is>
@@ -9024,55 +9079,55 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="57" t="inlineStr">
+      <c r="A23" s="58" t="inlineStr">
         <is>
           <t>2025-06-12</t>
         </is>
       </c>
-      <c r="B23" s="57" t="inlineStr">
+      <c r="B23" s="58" t="inlineStr">
         <is>
           <t>EOEB LLC</t>
         </is>
       </c>
-      <c r="C23" s="70" t="n">
+      <c r="C23" s="71" t="n">
         <v>25000</v>
       </c>
-      <c r="D23" s="57" t="inlineStr">
+      <c r="D23" s="58" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E23" s="71" t="inlineStr">
+      <c r="E23" s="72" t="inlineStr">
         <is>
           <t>ADVISORY</t>
         </is>
       </c>
-      <c r="F23" s="71" t="inlineStr">
+      <c r="F23" s="72" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G23" s="57" t="inlineStr">
+      <c r="G23" s="58" t="inlineStr">
         <is>
           <t>EOEB — sale vs art advisory</t>
         </is>
       </c>
-      <c r="H23" s="57" t="inlineStr">
+      <c r="H23" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I23" s="57" t="inlineStr">
+      <c r="I23" s="58" t="inlineStr">
         <is>
           <t>no — ASK first</t>
         </is>
       </c>
-      <c r="J23" s="57" t="inlineStr">
+      <c r="J23" s="58" t="inlineStr">
         <is>
           <t>Business Income</t>
         </is>
       </c>
-      <c r="K23" s="57" t="inlineStr">
+      <c r="K23" s="58" t="inlineStr">
         <is>
           <t>Incoming Wire; MAKE A PAYMENT; Merchant name: EOEB LLC</t>
         </is>
@@ -9084,12 +9139,12 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="57" t="inlineStr">
+      <c r="A24" s="58" t="inlineStr">
         <is>
           <t>2025-06-24</t>
         </is>
       </c>
-      <c r="B24" s="57" t="inlineStr">
+      <c r="B24" s="58" t="inlineStr">
         <is>
           <t>DAVID AARON LIMITED</t>
         </is>
@@ -9097,7 +9152,7 @@
       <c r="C24" s="45" t="n">
         <v>13595</v>
       </c>
-      <c r="D24" s="57" t="inlineStr">
+      <c r="D24" s="58" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
@@ -9112,27 +9167,27 @@
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="G24" s="57" t="inlineStr">
+      <c r="G24" s="58" t="inlineStr">
         <is>
           <t>David Aaron Limited — consultant fee</t>
         </is>
       </c>
-      <c r="H24" s="57" t="inlineStr">
+      <c r="H24" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I24" s="57" t="inlineStr">
+      <c r="I24" s="58" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="J24" s="57" t="inlineStr">
+      <c r="J24" s="58" t="inlineStr">
         <is>
           <t>Business Income</t>
         </is>
       </c>
-      <c r="K24" s="57" t="inlineStr">
+      <c r="K24" s="58" t="inlineStr">
         <is>
           <t>Auto-Routing transfer; Merchant name: DAVID AARON LIMITED</t>
         </is>
@@ -9144,12 +9199,12 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="57" t="inlineStr">
+      <c r="A25" s="58" t="inlineStr">
         <is>
           <t>2025-07-03</t>
         </is>
       </c>
-      <c r="B25" s="57" t="inlineStr">
+      <c r="B25" s="58" t="inlineStr">
         <is>
           <t>Bank of America - Checking ••9922</t>
         </is>
@@ -9157,12 +9212,12 @@
       <c r="C25" s="10" t="n">
         <v>-40000</v>
       </c>
-      <c r="D25" s="57" t="inlineStr">
+      <c r="D25" s="58" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E25" s="72" t="inlineStr">
+      <c r="E25" s="73" t="inlineStr">
         <is>
           <t>TRANSFER</t>
         </is>
@@ -9172,27 +9227,27 @@
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="G25" s="57" t="inlineStr">
+      <c r="G25" s="58" t="inlineStr">
         <is>
           <t>Owner transfer to BoA 9922</t>
         </is>
       </c>
-      <c r="H25" s="57" t="inlineStr">
+      <c r="H25" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I25" s="57" t="inlineStr">
+      <c r="I25" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J25" s="57" t="inlineStr">
+      <c r="J25" s="58" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K25" s="57" t="inlineStr">
+      <c r="K25" s="58" t="inlineStr">
         <is>
           <t>Transfer from Mercury to another bank account; Merchant name: Bank of America - Checking ••9922</t>
         </is>
@@ -9204,55 +9259,55 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="57" t="inlineStr">
+      <c r="A26" s="58" t="inlineStr">
         <is>
           <t>2025-07-08</t>
         </is>
       </c>
-      <c r="B26" s="57" t="inlineStr">
+      <c r="B26" s="58" t="inlineStr">
         <is>
           <t>EOEB LLC</t>
         </is>
       </c>
-      <c r="C26" s="70" t="n">
+      <c r="C26" s="71" t="n">
         <v>2000</v>
       </c>
-      <c r="D26" s="57" t="inlineStr">
+      <c r="D26" s="58" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E26" s="71" t="inlineStr">
+      <c r="E26" s="72" t="inlineStr">
         <is>
           <t>ADVISORY</t>
         </is>
       </c>
-      <c r="F26" s="71" t="inlineStr">
+      <c r="F26" s="72" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G26" s="57" t="inlineStr">
+      <c r="G26" s="58" t="inlineStr">
         <is>
           <t>EOEB — sale vs art advisory</t>
         </is>
       </c>
-      <c r="H26" s="57" t="inlineStr">
+      <c r="H26" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I26" s="57" t="inlineStr">
+      <c r="I26" s="58" t="inlineStr">
         <is>
           <t>no — ASK first</t>
         </is>
       </c>
-      <c r="J26" s="57" t="inlineStr">
+      <c r="J26" s="58" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K26" s="57" t="inlineStr">
+      <c r="K26" s="58" t="inlineStr">
         <is>
           <t>Auto-Routing transfer; Merchant name: EOEB LLC</t>
         </is>
@@ -9264,12 +9319,12 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="57" t="inlineStr">
+      <c r="A27" s="58" t="inlineStr">
         <is>
           <t>2025-07-09</t>
         </is>
       </c>
-      <c r="B27" s="57" t="inlineStr">
+      <c r="B27" s="58" t="inlineStr">
         <is>
           <t>Wise Inc</t>
         </is>
@@ -9277,12 +9332,12 @@
       <c r="C27" s="45" t="n">
         <v>-334.17</v>
       </c>
-      <c r="D27" s="57" t="inlineStr">
+      <c r="D27" s="58" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E27" s="69" t="inlineStr">
+      <c r="E27" s="70" t="inlineStr">
         <is>
           <t>EPGC_EXPENSE</t>
         </is>
@@ -9292,27 +9347,27 @@
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="G27" s="57" t="inlineStr">
+      <c r="G27" s="58" t="inlineStr">
         <is>
           <t>Wise — expertise write-ups (Consultant Fees)</t>
         </is>
       </c>
-      <c r="H27" s="57" t="inlineStr">
+      <c r="H27" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I27" s="57" t="inlineStr">
+      <c r="I27" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J27" s="57" t="inlineStr">
+      <c r="J27" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">Business Expense </t>
         </is>
       </c>
-      <c r="K27" s="57" t="inlineStr">
+      <c r="K27" s="58" t="inlineStr">
         <is>
           <t>Wise Inc; WISE; EPGC LLC; Merchant name: Wise Inc</t>
         </is>
@@ -9324,55 +9379,55 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="57" t="inlineStr">
+      <c r="A28" s="58" t="inlineStr">
         <is>
           <t>2025-07-11</t>
         </is>
       </c>
-      <c r="B28" s="57" t="inlineStr">
+      <c r="B28" s="58" t="inlineStr">
         <is>
           <t>L5</t>
         </is>
       </c>
-      <c r="C28" s="70" t="n">
+      <c r="C28" s="71" t="n">
         <v>8534.790000000001</v>
       </c>
-      <c r="D28" s="57" t="inlineStr">
+      <c r="D28" s="58" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E28" s="71" t="inlineStr">
+      <c r="E28" s="72" t="inlineStr">
         <is>
           <t>ADVISORY</t>
         </is>
       </c>
-      <c r="F28" s="71" t="inlineStr">
+      <c r="F28" s="72" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G28" s="57" t="inlineStr">
+      <c r="G28" s="58" t="inlineStr">
         <is>
           <t>L5 — sale vs art advisory</t>
         </is>
       </c>
-      <c r="H28" s="57" t="inlineStr">
+      <c r="H28" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I28" s="57" t="inlineStr">
+      <c r="I28" s="58" t="inlineStr">
         <is>
           <t>no — ASK first</t>
         </is>
       </c>
-      <c r="J28" s="57" t="inlineStr">
+      <c r="J28" s="58" t="inlineStr">
         <is>
           <t>Business Income</t>
         </is>
       </c>
-      <c r="K28" s="57" t="inlineStr">
+      <c r="K28" s="58" t="inlineStr">
         <is>
           <t>Auto-Routing transfer; Merchant name: L5</t>
         </is>
@@ -9384,55 +9439,55 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="57" t="inlineStr">
+      <c r="A29" s="58" t="inlineStr">
         <is>
           <t>2025-07-15</t>
         </is>
       </c>
-      <c r="B29" s="57" t="inlineStr">
+      <c r="B29" s="58" t="inlineStr">
         <is>
           <t>L5</t>
         </is>
       </c>
-      <c r="C29" s="70" t="n">
+      <c r="C29" s="71" t="n">
         <v>2500</v>
       </c>
-      <c r="D29" s="57" t="inlineStr">
+      <c r="D29" s="58" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E29" s="71" t="inlineStr">
+      <c r="E29" s="72" t="inlineStr">
         <is>
           <t>ADVISORY</t>
         </is>
       </c>
-      <c r="F29" s="71" t="inlineStr">
+      <c r="F29" s="72" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G29" s="57" t="inlineStr">
+      <c r="G29" s="58" t="inlineStr">
         <is>
           <t>L5 — sale vs art advisory</t>
         </is>
       </c>
-      <c r="H29" s="57" t="inlineStr">
+      <c r="H29" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I29" s="57" t="inlineStr">
+      <c r="I29" s="58" t="inlineStr">
         <is>
           <t>no — ASK first</t>
         </is>
       </c>
-      <c r="J29" s="57" t="inlineStr">
+      <c r="J29" s="58" t="inlineStr">
         <is>
           <t>Business Income</t>
         </is>
       </c>
-      <c r="K29" s="57" t="inlineStr">
+      <c r="K29" s="58" t="inlineStr">
         <is>
           <t>Auto-Routing transfer; Merchant name: L5</t>
         </is>
@@ -9444,55 +9499,55 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="57" t="inlineStr">
+      <c r="A30" s="58" t="inlineStr">
         <is>
           <t>2025-07-15</t>
         </is>
       </c>
-      <c r="B30" s="57" t="inlineStr">
+      <c r="B30" s="58" t="inlineStr">
         <is>
           <t>L5</t>
         </is>
       </c>
-      <c r="C30" s="70" t="n">
+      <c r="C30" s="71" t="n">
         <v>50000</v>
       </c>
-      <c r="D30" s="57" t="inlineStr">
+      <c r="D30" s="58" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E30" s="71" t="inlineStr">
+      <c r="E30" s="72" t="inlineStr">
         <is>
           <t>ADVISORY</t>
         </is>
       </c>
-      <c r="F30" s="71" t="inlineStr">
+      <c r="F30" s="72" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G30" s="57" t="inlineStr">
+      <c r="G30" s="58" t="inlineStr">
         <is>
           <t>L5 $50,000 — sale vs art advisory vs pass-through</t>
         </is>
       </c>
-      <c r="H30" s="57" t="inlineStr">
+      <c r="H30" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I30" s="57" t="inlineStr">
+      <c r="I30" s="58" t="inlineStr">
         <is>
           <t>no — ASK first</t>
         </is>
       </c>
-      <c r="J30" s="57" t="inlineStr">
+      <c r="J30" s="58" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K30" s="57" t="inlineStr">
+      <c r="K30" s="58" t="inlineStr">
         <is>
           <t>Auto-Routing transfer; Merchant name: L5</t>
         </is>
@@ -9504,55 +9559,55 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="57" t="inlineStr">
+      <c r="A31" s="58" t="inlineStr">
         <is>
           <t>2025-07-18</t>
         </is>
       </c>
-      <c r="B31" s="57" t="inlineStr">
+      <c r="B31" s="58" t="inlineStr">
         <is>
           <t>Aysel Dere</t>
         </is>
       </c>
-      <c r="C31" s="70" t="n">
+      <c r="C31" s="71" t="n">
         <v>50000</v>
       </c>
-      <c r="D31" s="57" t="inlineStr">
+      <c r="D31" s="58" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E31" s="71" t="inlineStr">
+      <c r="E31" s="72" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="F31" s="71" t="inlineStr">
+      <c r="F31" s="72" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G31" s="57" t="inlineStr">
+      <c r="G31" s="58" t="inlineStr">
         <is>
           <t>Aysel Dere $50,000 IN</t>
         </is>
       </c>
-      <c r="H31" s="57" t="inlineStr">
+      <c r="H31" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I31" s="57" t="inlineStr">
+      <c r="I31" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J31" s="57" t="inlineStr">
+      <c r="J31" s="58" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K31" s="57" t="inlineStr">
+      <c r="K31" s="58" t="inlineStr">
         <is>
           <t>Merchant name: Aysel Dere</t>
         </is>
@@ -9564,55 +9619,55 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="57" t="inlineStr">
+      <c r="A32" s="58" t="inlineStr">
         <is>
           <t>2025-07-21</t>
         </is>
       </c>
-      <c r="B32" s="57" t="inlineStr">
+      <c r="B32" s="58" t="inlineStr">
         <is>
           <t>Erdal Dere (Fortuna)</t>
         </is>
       </c>
-      <c r="C32" s="70" t="n">
+      <c r="C32" s="71" t="n">
         <v>-45000</v>
       </c>
-      <c r="D32" s="57" t="inlineStr">
+      <c r="D32" s="58" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E32" s="68" t="inlineStr">
+      <c r="E32" s="69" t="inlineStr">
         <is>
           <t>ART_PURCHASE</t>
         </is>
       </c>
-      <c r="F32" s="71" t="inlineStr">
+      <c r="F32" s="72" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G32" s="57" t="inlineStr">
+      <c r="G32" s="58" t="inlineStr">
         <is>
           <t>Fortuna / Erdal — inventory vs other</t>
         </is>
       </c>
-      <c r="H32" s="57" t="inlineStr">
+      <c r="H32" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I32" s="57" t="inlineStr">
+      <c r="I32" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J32" s="57" t="inlineStr">
+      <c r="J32" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">Business Investment </t>
         </is>
       </c>
-      <c r="K32" s="57" t="inlineStr">
+      <c r="K32" s="58" t="inlineStr">
         <is>
           <t>Merchant name: Erdal Dere (Fortuna)</t>
         </is>
@@ -9624,55 +9679,55 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="57" t="inlineStr">
+      <c r="A33" s="58" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="B33" s="57" t="inlineStr">
+      <c r="B33" s="58" t="inlineStr">
         <is>
           <t>ERDAL DERE</t>
         </is>
       </c>
-      <c r="C33" s="70" t="n">
+      <c r="C33" s="71" t="n">
         <v>26000</v>
       </c>
-      <c r="D33" s="57" t="inlineStr">
+      <c r="D33" s="58" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E33" s="69" t="inlineStr">
+      <c r="E33" s="70" t="inlineStr">
         <is>
           <t>ART_SALE</t>
         </is>
       </c>
-      <c r="F33" s="71" t="inlineStr">
+      <c r="F33" s="72" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G33" s="57" t="inlineStr">
+      <c r="G33" s="58" t="inlineStr">
         <is>
           <t>Erdal Dere $26,000 IN — sale vs other</t>
         </is>
       </c>
-      <c r="H33" s="57" t="inlineStr">
+      <c r="H33" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I33" s="57" t="inlineStr">
+      <c r="I33" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J33" s="57" t="inlineStr">
+      <c r="J33" s="58" t="inlineStr">
         <is>
           <t>Business Income</t>
         </is>
       </c>
-      <c r="K33" s="57" t="inlineStr">
+      <c r="K33" s="58" t="inlineStr">
         <is>
           <t>Incoming Wire; Merchant name: ERDAL DERE</t>
         </is>
@@ -9684,12 +9739,12 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="57" t="inlineStr">
+      <c r="A34" s="58" t="inlineStr">
         <is>
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="B34" s="57" t="inlineStr">
+      <c r="B34" s="58" t="inlineStr">
         <is>
           <t>Bank of America - Checking ••9922</t>
         </is>
@@ -9697,12 +9752,12 @@
       <c r="C34" s="10" t="n">
         <v>-60000</v>
       </c>
-      <c r="D34" s="57" t="inlineStr">
+      <c r="D34" s="58" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E34" s="72" t="inlineStr">
+      <c r="E34" s="73" t="inlineStr">
         <is>
           <t>TRANSFER</t>
         </is>
@@ -9712,27 +9767,27 @@
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="G34" s="57" t="inlineStr">
+      <c r="G34" s="58" t="inlineStr">
         <is>
           <t>Owner transfer to BoA 9922</t>
         </is>
       </c>
-      <c r="H34" s="57" t="inlineStr">
+      <c r="H34" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I34" s="57" t="inlineStr">
+      <c r="I34" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J34" s="57" t="inlineStr">
+      <c r="J34" s="58" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K34" s="57" t="inlineStr">
+      <c r="K34" s="58" t="inlineStr">
         <is>
           <t>Transfer from Mercury to another bank account; Merchant name: Bank of America - Checking ••9922</t>
         </is>
@@ -9744,55 +9799,55 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="57" t="inlineStr">
+      <c r="A35" s="58" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="B35" s="57" t="inlineStr">
+      <c r="B35" s="58" t="inlineStr">
         <is>
           <t>Erdal Dere (Fortuna)</t>
         </is>
       </c>
-      <c r="C35" s="70" t="n">
+      <c r="C35" s="71" t="n">
         <v>-20000</v>
       </c>
-      <c r="D35" s="57" t="inlineStr">
+      <c r="D35" s="58" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E35" s="68" t="inlineStr">
+      <c r="E35" s="69" t="inlineStr">
         <is>
           <t>ART_PURCHASE</t>
         </is>
       </c>
-      <c r="F35" s="71" t="inlineStr">
+      <c r="F35" s="72" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G35" s="57" t="inlineStr">
+      <c r="G35" s="58" t="inlineStr">
         <is>
           <t>Fortuna / Erdal — inventory vs other</t>
         </is>
       </c>
-      <c r="H35" s="57" t="inlineStr">
+      <c r="H35" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I35" s="57" t="inlineStr">
+      <c r="I35" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J35" s="57" t="inlineStr">
+      <c r="J35" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">Business Investment </t>
         </is>
       </c>
-      <c r="K35" s="57" t="inlineStr">
+      <c r="K35" s="58" t="inlineStr">
         <is>
           <t>Merchant name: Erdal Dere (Fortuna)</t>
         </is>
@@ -9804,55 +9859,55 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="57" t="inlineStr">
+      <c r="A36" s="58" t="inlineStr">
         <is>
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="B36" s="57" t="inlineStr">
+      <c r="B36" s="58" t="inlineStr">
         <is>
           <t>EOEB LLC</t>
         </is>
       </c>
-      <c r="C36" s="70" t="n">
+      <c r="C36" s="71" t="n">
         <v>10000</v>
       </c>
-      <c r="D36" s="57" t="inlineStr">
+      <c r="D36" s="58" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E36" s="71" t="inlineStr">
+      <c r="E36" s="72" t="inlineStr">
         <is>
           <t>ADVISORY</t>
         </is>
       </c>
-      <c r="F36" s="71" t="inlineStr">
+      <c r="F36" s="72" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G36" s="57" t="inlineStr">
+      <c r="G36" s="58" t="inlineStr">
         <is>
           <t>EOEB — sale vs art advisory</t>
         </is>
       </c>
-      <c r="H36" s="57" t="inlineStr">
+      <c r="H36" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I36" s="57" t="inlineStr">
+      <c r="I36" s="58" t="inlineStr">
         <is>
           <t>no — ASK first</t>
         </is>
       </c>
-      <c r="J36" s="57" t="inlineStr">
+      <c r="J36" s="58" t="inlineStr">
         <is>
           <t>Business Income</t>
         </is>
       </c>
-      <c r="K36" s="57" t="inlineStr">
+      <c r="K36" s="58" t="inlineStr">
         <is>
           <t>Auto-Routing transfer; Merchant name: EOEB LLC</t>
         </is>
@@ -9864,55 +9919,55 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="57" t="inlineStr">
+      <c r="A37" s="58" t="inlineStr">
         <is>
           <t>2025-09-02</t>
         </is>
       </c>
-      <c r="B37" s="57" t="inlineStr">
+      <c r="B37" s="58" t="inlineStr">
         <is>
           <t>L5</t>
         </is>
       </c>
-      <c r="C37" s="70" t="n">
+      <c r="C37" s="71" t="n">
         <v>5042</v>
       </c>
-      <c r="D37" s="57" t="inlineStr">
+      <c r="D37" s="58" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E37" s="71" t="inlineStr">
+      <c r="E37" s="72" t="inlineStr">
         <is>
           <t>ADVISORY</t>
         </is>
       </c>
-      <c r="F37" s="71" t="inlineStr">
+      <c r="F37" s="72" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G37" s="57" t="inlineStr">
+      <c r="G37" s="58" t="inlineStr">
         <is>
           <t>L5 — sale vs art advisory</t>
         </is>
       </c>
-      <c r="H37" s="57" t="inlineStr">
+      <c r="H37" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I37" s="57" t="inlineStr">
+      <c r="I37" s="58" t="inlineStr">
         <is>
           <t>no — ASK first</t>
         </is>
       </c>
-      <c r="J37" s="57" t="inlineStr">
+      <c r="J37" s="58" t="inlineStr">
         <is>
           <t>Business Income</t>
         </is>
       </c>
-      <c r="K37" s="57" t="inlineStr">
+      <c r="K37" s="58" t="inlineStr">
         <is>
           <t>Auto-Routing transfer; Merchant name: L5</t>
         </is>
@@ -9924,12 +9979,12 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="57" t="inlineStr">
+      <c r="A38" s="58" t="inlineStr">
         <is>
           <t>2025-09-04</t>
         </is>
       </c>
-      <c r="B38" s="57" t="inlineStr">
+      <c r="B38" s="58" t="inlineStr">
         <is>
           <t>COINBASE INC.</t>
         </is>
@@ -9937,12 +9992,12 @@
       <c r="C38" s="45" t="n">
         <v>-3000</v>
       </c>
-      <c r="D38" s="57" t="inlineStr">
+      <c r="D38" s="58" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E38" s="73" t="inlineStr">
+      <c r="E38" s="74" t="inlineStr">
         <is>
           <t>INVESTMENT</t>
         </is>
@@ -9952,27 +10007,27 @@
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="G38" s="57" t="inlineStr">
+      <c r="G38" s="58" t="inlineStr">
         <is>
           <t>Coinbase ACH funding</t>
         </is>
       </c>
-      <c r="H38" s="57" t="inlineStr">
+      <c r="H38" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I38" s="57" t="inlineStr">
+      <c r="I38" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J38" s="57" t="inlineStr">
+      <c r="J38" s="58" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K38" s="57" t="inlineStr">
+      <c r="K38" s="58" t="inlineStr">
         <is>
           <t>COINBASE INC.; 2A0875F9; JACOB COLEY; Merchant name: COINBASE INC.</t>
         </is>
@@ -9984,55 +10039,55 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="57" t="inlineStr">
+      <c r="A39" s="58" t="inlineStr">
         <is>
           <t>2025-09-19</t>
         </is>
       </c>
-      <c r="B39" s="57" t="inlineStr">
+      <c r="B39" s="58" t="inlineStr">
         <is>
           <t>EOEB LLC</t>
         </is>
       </c>
-      <c r="C39" s="70" t="n">
+      <c r="C39" s="71" t="n">
         <v>5000</v>
       </c>
-      <c r="D39" s="57" t="inlineStr">
+      <c r="D39" s="58" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E39" s="71" t="inlineStr">
+      <c r="E39" s="72" t="inlineStr">
         <is>
           <t>ADVISORY</t>
         </is>
       </c>
-      <c r="F39" s="71" t="inlineStr">
+      <c r="F39" s="72" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G39" s="57" t="inlineStr">
+      <c r="G39" s="58" t="inlineStr">
         <is>
           <t>EOEB — sale vs art advisory</t>
         </is>
       </c>
-      <c r="H39" s="57" t="inlineStr">
+      <c r="H39" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I39" s="57" t="inlineStr">
+      <c r="I39" s="58" t="inlineStr">
         <is>
           <t>no — ASK first</t>
         </is>
       </c>
-      <c r="J39" s="57" t="inlineStr">
+      <c r="J39" s="58" t="inlineStr">
         <is>
           <t>Business Income</t>
         </is>
       </c>
-      <c r="K39" s="57" t="inlineStr">
+      <c r="K39" s="58" t="inlineStr">
         <is>
           <t>Auto-Routing transfer; Merchant name: EOEB LLC</t>
         </is>
@@ -10044,55 +10099,55 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="57" t="inlineStr">
+      <c r="A40" s="58" t="inlineStr">
         <is>
           <t>2025-09-23</t>
         </is>
       </c>
-      <c r="B40" s="57" t="inlineStr">
+      <c r="B40" s="58" t="inlineStr">
         <is>
           <t>L5</t>
         </is>
       </c>
-      <c r="C40" s="70" t="n">
+      <c r="C40" s="71" t="n">
         <v>9119.27</v>
       </c>
-      <c r="D40" s="57" t="inlineStr">
+      <c r="D40" s="58" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E40" s="71" t="inlineStr">
+      <c r="E40" s="72" t="inlineStr">
         <is>
           <t>ADVISORY</t>
         </is>
       </c>
-      <c r="F40" s="71" t="inlineStr">
+      <c r="F40" s="72" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G40" s="57" t="inlineStr">
+      <c r="G40" s="58" t="inlineStr">
         <is>
           <t>L5 — sale vs art advisory</t>
         </is>
       </c>
-      <c r="H40" s="57" t="inlineStr">
+      <c r="H40" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I40" s="57" t="inlineStr">
+      <c r="I40" s="58" t="inlineStr">
         <is>
           <t>no — ASK first</t>
         </is>
       </c>
-      <c r="J40" s="57" t="inlineStr">
+      <c r="J40" s="58" t="inlineStr">
         <is>
           <t>Business Income</t>
         </is>
       </c>
-      <c r="K40" s="57" t="inlineStr">
+      <c r="K40" s="58" t="inlineStr">
         <is>
           <t>Auto-Routing transfer; Merchant name: L5</t>
         </is>
@@ -10104,12 +10159,12 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="57" t="inlineStr">
+      <c r="A41" s="58" t="inlineStr">
         <is>
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="B41" s="57" t="inlineStr">
+      <c r="B41" s="58" t="inlineStr">
         <is>
           <t>Bank of America - Checking ••9922</t>
         </is>
@@ -10117,12 +10172,12 @@
       <c r="C41" s="10" t="n">
         <v>-40000</v>
       </c>
-      <c r="D41" s="57" t="inlineStr">
+      <c r="D41" s="58" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E41" s="72" t="inlineStr">
+      <c r="E41" s="73" t="inlineStr">
         <is>
           <t>TRANSFER</t>
         </is>
@@ -10132,27 +10187,27 @@
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="G41" s="57" t="inlineStr">
+      <c r="G41" s="58" t="inlineStr">
         <is>
           <t>Owner transfer to BoA 9922</t>
         </is>
       </c>
-      <c r="H41" s="57" t="inlineStr">
+      <c r="H41" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I41" s="57" t="inlineStr">
+      <c r="I41" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J41" s="57" t="inlineStr">
+      <c r="J41" s="58" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K41" s="57" t="inlineStr">
+      <c r="K41" s="58" t="inlineStr">
         <is>
           <t>Transfer from Mercury to another bank account; Merchant name: Bank of America - Checking ••9922</t>
         </is>
@@ -10164,55 +10219,55 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="57" t="inlineStr">
+      <c r="A42" s="58" t="inlineStr">
         <is>
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="B42" s="57" t="inlineStr">
+      <c r="B42" s="58" t="inlineStr">
         <is>
           <t>EOEB LLC</t>
         </is>
       </c>
-      <c r="C42" s="70" t="n">
+      <c r="C42" s="71" t="n">
         <v>3100</v>
       </c>
-      <c r="D42" s="57" t="inlineStr">
+      <c r="D42" s="58" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E42" s="71" t="inlineStr">
+      <c r="E42" s="72" t="inlineStr">
         <is>
           <t>ADVISORY</t>
         </is>
       </c>
-      <c r="F42" s="71" t="inlineStr">
+      <c r="F42" s="72" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G42" s="57" t="inlineStr">
+      <c r="G42" s="58" t="inlineStr">
         <is>
           <t>EOEB — sale vs art advisory</t>
         </is>
       </c>
-      <c r="H42" s="57" t="inlineStr">
+      <c r="H42" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I42" s="57" t="inlineStr">
+      <c r="I42" s="58" t="inlineStr">
         <is>
           <t>no — ASK first</t>
         </is>
       </c>
-      <c r="J42" s="57" t="inlineStr">
+      <c r="J42" s="58" t="inlineStr">
         <is>
           <t>Business Income</t>
         </is>
       </c>
-      <c r="K42" s="57" t="inlineStr">
+      <c r="K42" s="58" t="inlineStr">
         <is>
           <t>Auto-Routing transfer; Merchant name: EOEB LLC</t>
         </is>
@@ -10224,12 +10279,12 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="57" t="inlineStr">
+      <c r="A43" s="58" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="B43" s="57" t="inlineStr">
+      <c r="B43" s="58" t="inlineStr">
         <is>
           <t>COINBASE INC.</t>
         </is>
@@ -10237,12 +10292,12 @@
       <c r="C43" s="45" t="n">
         <v>-6000</v>
       </c>
-      <c r="D43" s="57" t="inlineStr">
+      <c r="D43" s="58" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E43" s="73" t="inlineStr">
+      <c r="E43" s="74" t="inlineStr">
         <is>
           <t>INVESTMENT</t>
         </is>
@@ -10252,27 +10307,27 @@
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="G43" s="57" t="inlineStr">
+      <c r="G43" s="58" t="inlineStr">
         <is>
           <t>Coinbase ACH funding</t>
         </is>
       </c>
-      <c r="H43" s="57" t="inlineStr">
+      <c r="H43" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I43" s="57" t="inlineStr">
+      <c r="I43" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J43" s="57" t="inlineStr">
+      <c r="J43" s="58" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K43" s="57" t="inlineStr">
+      <c r="K43" s="58" t="inlineStr">
         <is>
           <t>COINBASE INC.; 27B17286; JACOB COLEY; Merchant name: COINBASE INC.</t>
         </is>
@@ -10284,12 +10339,12 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="57" t="inlineStr">
+      <c r="A44" s="58" t="inlineStr">
         <is>
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="B44" s="57" t="inlineStr">
+      <c r="B44" s="58" t="inlineStr">
         <is>
           <t>COINBASE INC.</t>
         </is>
@@ -10297,12 +10352,12 @@
       <c r="C44" s="45" t="n">
         <v>-10000</v>
       </c>
-      <c r="D44" s="57" t="inlineStr">
+      <c r="D44" s="58" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E44" s="73" t="inlineStr">
+      <c r="E44" s="74" t="inlineStr">
         <is>
           <t>INVESTMENT</t>
         </is>
@@ -10312,27 +10367,27 @@
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="G44" s="57" t="inlineStr">
+      <c r="G44" s="58" t="inlineStr">
         <is>
           <t>Coinbase ACH funding</t>
         </is>
       </c>
-      <c r="H44" s="57" t="inlineStr">
+      <c r="H44" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I44" s="57" t="inlineStr">
+      <c r="I44" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J44" s="57" t="inlineStr">
+      <c r="J44" s="58" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K44" s="57" t="inlineStr">
+      <c r="K44" s="58" t="inlineStr">
         <is>
           <t>COINBASE INC.; E2C52DA9; JACOB COLEY; Merchant name: COINBASE INC.</t>
         </is>
@@ -10344,55 +10399,55 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="57" t="inlineStr">
+      <c r="A45" s="58" t="inlineStr">
         <is>
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="B45" s="57" t="inlineStr">
+      <c r="B45" s="58" t="inlineStr">
         <is>
           <t>EOEB LLC</t>
         </is>
       </c>
-      <c r="C45" s="70" t="n">
+      <c r="C45" s="71" t="n">
         <v>10000</v>
       </c>
-      <c r="D45" s="57" t="inlineStr">
+      <c r="D45" s="58" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E45" s="71" t="inlineStr">
+      <c r="E45" s="72" t="inlineStr">
         <is>
           <t>ADVISORY</t>
         </is>
       </c>
-      <c r="F45" s="71" t="inlineStr">
+      <c r="F45" s="72" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G45" s="57" t="inlineStr">
+      <c r="G45" s="58" t="inlineStr">
         <is>
           <t>EOEB — sale vs art advisory</t>
         </is>
       </c>
-      <c r="H45" s="57" t="inlineStr">
+      <c r="H45" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I45" s="57" t="inlineStr">
+      <c r="I45" s="58" t="inlineStr">
         <is>
           <t>no — ASK first</t>
         </is>
       </c>
-      <c r="J45" s="57" t="inlineStr">
+      <c r="J45" s="58" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K45" s="57" t="inlineStr">
+      <c r="K45" s="58" t="inlineStr">
         <is>
           <t>Auto-Routing transfer; Merchant name: EOEB LLC</t>
         </is>
@@ -10404,12 +10459,12 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="57" t="inlineStr">
+      <c r="A46" s="58" t="inlineStr">
         <is>
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="B46" s="57" t="inlineStr">
+      <c r="B46" s="58" t="inlineStr">
         <is>
           <t>Bank of America - Checking ••9922</t>
         </is>
@@ -10417,12 +10472,12 @@
       <c r="C46" s="10" t="n">
         <v>-6172</v>
       </c>
-      <c r="D46" s="57" t="inlineStr">
+      <c r="D46" s="58" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E46" s="72" t="inlineStr">
+      <c r="E46" s="73" t="inlineStr">
         <is>
           <t>TRANSFER</t>
         </is>
@@ -10432,27 +10487,27 @@
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="G46" s="57" t="inlineStr">
+      <c r="G46" s="58" t="inlineStr">
         <is>
           <t>Owner transfer to BoA 9922</t>
         </is>
       </c>
-      <c r="H46" s="57" t="inlineStr">
+      <c r="H46" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I46" s="57" t="inlineStr">
+      <c r="I46" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J46" s="57" t="inlineStr">
+      <c r="J46" s="58" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K46" s="57" t="inlineStr">
+      <c r="K46" s="58" t="inlineStr">
         <is>
           <t>Transfer from Mercury to another bank account; Merchant name: Bank of America - Checking ••9922</t>
         </is>
@@ -10464,55 +10519,55 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="57" t="inlineStr">
+      <c r="A47" s="58" t="inlineStr">
         <is>
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="B47" s="57" t="inlineStr">
+      <c r="B47" s="58" t="inlineStr">
         <is>
           <t>ERDAL DERE</t>
         </is>
       </c>
-      <c r="C47" s="70" t="n">
+      <c r="C47" s="71" t="n">
         <v>25000</v>
       </c>
-      <c r="D47" s="57" t="inlineStr">
+      <c r="D47" s="58" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E47" s="69" t="inlineStr">
+      <c r="E47" s="70" t="inlineStr">
         <is>
           <t>ART_SALE</t>
         </is>
       </c>
-      <c r="F47" s="71" t="inlineStr">
+      <c r="F47" s="72" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G47" s="57" t="inlineStr">
+      <c r="G47" s="58" t="inlineStr">
         <is>
           <t>Erdal Dere $25,000 IN — sale vs other</t>
         </is>
       </c>
-      <c r="H47" s="57" t="inlineStr">
+      <c r="H47" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I47" s="57" t="inlineStr">
+      <c r="I47" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J47" s="57" t="inlineStr">
+      <c r="J47" s="58" t="inlineStr">
         <is>
           <t>Business Income</t>
         </is>
       </c>
-      <c r="K47" s="57" t="inlineStr">
+      <c r="K47" s="58" t="inlineStr">
         <is>
           <t>Incoming Wire; Merchant name: ERDAL DERE</t>
         </is>
@@ -10524,12 +10579,12 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="57" t="inlineStr">
+      <c r="A48" s="58" t="inlineStr">
         <is>
           <t>2025-10-14</t>
         </is>
       </c>
-      <c r="B48" s="57" t="inlineStr">
+      <c r="B48" s="58" t="inlineStr">
         <is>
           <t>Newstar Jewelers</t>
         </is>
@@ -10537,12 +10592,12 @@
       <c r="C48" s="45" t="n">
         <v>-8000</v>
       </c>
-      <c r="D48" s="57" t="inlineStr">
+      <c r="D48" s="58" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E48" s="68" t="inlineStr">
+      <c r="E48" s="69" t="inlineStr">
         <is>
           <t>COGS_JEWELRY</t>
         </is>
@@ -10552,27 +10607,27 @@
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="G48" s="57" t="inlineStr">
+      <c r="G48" s="58" t="inlineStr">
         <is>
           <t>Newstar Jewelers — jewelry fabrication</t>
         </is>
       </c>
-      <c r="H48" s="57" t="inlineStr">
+      <c r="H48" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I48" s="57" t="inlineStr">
+      <c r="I48" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J48" s="57" t="inlineStr">
+      <c r="J48" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">Business Expense </t>
         </is>
       </c>
-      <c r="K48" s="57" t="inlineStr">
+      <c r="K48" s="58" t="inlineStr">
         <is>
           <t>Merchant name: Newstar Jewelers</t>
         </is>
@@ -10584,55 +10639,55 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="57" t="inlineStr">
+      <c r="A49" s="58" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="B49" s="57" t="inlineStr">
+      <c r="B49" s="58" t="inlineStr">
         <is>
           <t>EOEB LLC</t>
         </is>
       </c>
-      <c r="C49" s="70" t="n">
+      <c r="C49" s="71" t="n">
         <v>16000</v>
       </c>
-      <c r="D49" s="57" t="inlineStr">
+      <c r="D49" s="58" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E49" s="71" t="inlineStr">
+      <c r="E49" s="72" t="inlineStr">
         <is>
           <t>ADVISORY</t>
         </is>
       </c>
-      <c r="F49" s="71" t="inlineStr">
+      <c r="F49" s="72" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G49" s="57" t="inlineStr">
+      <c r="G49" s="58" t="inlineStr">
         <is>
           <t>EOEB — sale vs art advisory</t>
         </is>
       </c>
-      <c r="H49" s="57" t="inlineStr">
+      <c r="H49" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I49" s="57" t="inlineStr">
+      <c r="I49" s="58" t="inlineStr">
         <is>
           <t>no — ASK first</t>
         </is>
       </c>
-      <c r="J49" s="57" t="inlineStr">
+      <c r="J49" s="58" t="inlineStr">
         <is>
           <t>Business Income</t>
         </is>
       </c>
-      <c r="K49" s="57" t="inlineStr">
+      <c r="K49" s="58" t="inlineStr">
         <is>
           <t>Auto-Routing transfer; Merchant name: EOEB LLC</t>
         </is>
@@ -10644,12 +10699,12 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="57" t="inlineStr">
+      <c r="A50" s="58" t="inlineStr">
         <is>
           <t>2025-10-20</t>
         </is>
       </c>
-      <c r="B50" s="57" t="inlineStr">
+      <c r="B50" s="58" t="inlineStr">
         <is>
           <t>JACK EDWARD KOZIOL &amp; TRACY HOFFMAN</t>
         </is>
@@ -10657,12 +10712,12 @@
       <c r="C50" s="10" t="n">
         <v>150000</v>
       </c>
-      <c r="D50" s="57" t="inlineStr">
+      <c r="D50" s="58" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E50" s="73" t="inlineStr">
+      <c r="E50" s="74" t="inlineStr">
         <is>
           <t>PASS_THROUGH</t>
         </is>
@@ -10672,27 +10727,27 @@
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="G50" s="57" t="inlineStr">
+      <c r="G50" s="58" t="inlineStr">
         <is>
           <t>Jack Koziol &amp; Tracy Hoffman $150,000 IN</t>
         </is>
       </c>
-      <c r="H50" s="57" t="inlineStr">
+      <c r="H50" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I50" s="57" t="inlineStr">
+      <c r="I50" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J50" s="57" t="inlineStr">
+      <c r="J50" s="58" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K50" s="57" t="inlineStr">
+      <c r="K50" s="58" t="inlineStr">
         <is>
           <t>Incoming Wire; /BNF/Per your request; Merchant name: JACK EDWARD KOZIOL &amp; TRACY HOFFMAN</t>
         </is>
@@ -10704,12 +10759,12 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="57" t="inlineStr">
+      <c r="A51" s="58" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="B51" s="57" t="inlineStr">
+      <c r="B51" s="58" t="inlineStr">
         <is>
           <t>Ariadne Demirjian LLC</t>
         </is>
@@ -10717,12 +10772,12 @@
       <c r="C51" s="10" t="n">
         <v>-150000</v>
       </c>
-      <c r="D51" s="57" t="inlineStr">
+      <c r="D51" s="58" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E51" s="73" t="inlineStr">
+      <c r="E51" s="74" t="inlineStr">
         <is>
           <t>PASS_THROUGH</t>
         </is>
@@ -10732,27 +10787,27 @@
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="G51" s="57" t="inlineStr">
+      <c r="G51" s="58" t="inlineStr">
         <is>
           <t>Ariadne Demirjian LLC $150,000 OUT</t>
         </is>
       </c>
-      <c r="H51" s="57" t="inlineStr">
+      <c r="H51" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I51" s="57" t="inlineStr">
+      <c r="I51" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J51" s="57" t="inlineStr">
+      <c r="J51" s="58" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K51" s="57" t="inlineStr">
+      <c r="K51" s="58" t="inlineStr">
         <is>
           <t>Merchant name: Ariadne Demirjian LLC</t>
         </is>
@@ -10764,55 +10819,55 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="57" t="inlineStr">
+      <c r="A52" s="58" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="B52" s="57" t="inlineStr">
+      <c r="B52" s="58" t="inlineStr">
         <is>
           <t>L5</t>
         </is>
       </c>
-      <c r="C52" s="70" t="n">
+      <c r="C52" s="71" t="n">
         <v>7500</v>
       </c>
-      <c r="D52" s="57" t="inlineStr">
+      <c r="D52" s="58" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E52" s="71" t="inlineStr">
+      <c r="E52" s="72" t="inlineStr">
         <is>
           <t>ADVISORY</t>
         </is>
       </c>
-      <c r="F52" s="71" t="inlineStr">
+      <c r="F52" s="72" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G52" s="57" t="inlineStr">
+      <c r="G52" s="58" t="inlineStr">
         <is>
           <t>L5 — sale vs art advisory</t>
         </is>
       </c>
-      <c r="H52" s="57" t="inlineStr">
+      <c r="H52" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I52" s="57" t="inlineStr">
+      <c r="I52" s="58" t="inlineStr">
         <is>
           <t>no — ASK first</t>
         </is>
       </c>
-      <c r="J52" s="57" t="inlineStr">
+      <c r="J52" s="58" t="inlineStr">
         <is>
           <t>Business Income</t>
         </is>
       </c>
-      <c r="K52" s="57" t="inlineStr">
+      <c r="K52" s="58" t="inlineStr">
         <is>
           <t>Auto-Routing transfer; Merchant name: L5</t>
         </is>
@@ -10824,55 +10879,55 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="57" t="inlineStr">
+      <c r="A53" s="58" t="inlineStr">
         <is>
           <t>2025-10-24</t>
         </is>
       </c>
-      <c r="B53" s="57" t="inlineStr">
+      <c r="B53" s="58" t="inlineStr">
         <is>
           <t>EOEB LLC</t>
         </is>
       </c>
-      <c r="C53" s="70" t="n">
+      <c r="C53" s="71" t="n">
         <v>1500</v>
       </c>
-      <c r="D53" s="57" t="inlineStr">
+      <c r="D53" s="58" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E53" s="71" t="inlineStr">
+      <c r="E53" s="72" t="inlineStr">
         <is>
           <t>ADVISORY</t>
         </is>
       </c>
-      <c r="F53" s="71" t="inlineStr">
+      <c r="F53" s="72" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G53" s="57" t="inlineStr">
+      <c r="G53" s="58" t="inlineStr">
         <is>
           <t>EOEB — sale vs art advisory</t>
         </is>
       </c>
-      <c r="H53" s="57" t="inlineStr">
+      <c r="H53" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I53" s="57" t="inlineStr">
+      <c r="I53" s="58" t="inlineStr">
         <is>
           <t>no — ASK first</t>
         </is>
       </c>
-      <c r="J53" s="57" t="inlineStr">
+      <c r="J53" s="58" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K53" s="57" t="inlineStr">
+      <c r="K53" s="58" t="inlineStr">
         <is>
           <t>Auto-Routing transfer; Merchant name: EOEB LLC</t>
         </is>
@@ -10884,12 +10939,12 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="57" t="inlineStr">
+      <c r="A54" s="58" t="inlineStr">
         <is>
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="B54" s="57" t="inlineStr">
+      <c r="B54" s="58" t="inlineStr">
         <is>
           <t>Wise Inc</t>
         </is>
@@ -10897,12 +10952,12 @@
       <c r="C54" s="45" t="n">
         <v>-658.63</v>
       </c>
-      <c r="D54" s="57" t="inlineStr">
+      <c r="D54" s="58" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E54" s="69" t="inlineStr">
+      <c r="E54" s="70" t="inlineStr">
         <is>
           <t>EPGC_EXPENSE</t>
         </is>
@@ -10912,27 +10967,27 @@
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="G54" s="57" t="inlineStr">
+      <c r="G54" s="58" t="inlineStr">
         <is>
           <t>Wise — expertise write-ups (Consultant Fees)</t>
         </is>
       </c>
-      <c r="H54" s="57" t="inlineStr">
+      <c r="H54" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I54" s="57" t="inlineStr">
+      <c r="I54" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J54" s="57" t="inlineStr">
+      <c r="J54" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">Business Expense </t>
         </is>
       </c>
-      <c r="K54" s="57" t="inlineStr">
+      <c r="K54" s="58" t="inlineStr">
         <is>
           <t>Wise Inc; WISE; EPGC LLC; Merchant name: Wise Inc</t>
         </is>
@@ -10944,55 +10999,55 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="57" t="inlineStr">
+      <c r="A55" s="58" t="inlineStr">
         <is>
           <t>2025-10-31</t>
         </is>
       </c>
-      <c r="B55" s="57" t="inlineStr">
+      <c r="B55" s="58" t="inlineStr">
         <is>
           <t>EOEB LLC</t>
         </is>
       </c>
-      <c r="C55" s="70" t="n">
+      <c r="C55" s="71" t="n">
         <v>2170</v>
       </c>
-      <c r="D55" s="57" t="inlineStr">
+      <c r="D55" s="58" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E55" s="71" t="inlineStr">
+      <c r="E55" s="72" t="inlineStr">
         <is>
           <t>ADVISORY</t>
         </is>
       </c>
-      <c r="F55" s="71" t="inlineStr">
+      <c r="F55" s="72" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G55" s="57" t="inlineStr">
+      <c r="G55" s="58" t="inlineStr">
         <is>
           <t>EOEB — sale vs art advisory</t>
         </is>
       </c>
-      <c r="H55" s="57" t="inlineStr">
+      <c r="H55" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I55" s="57" t="inlineStr">
+      <c r="I55" s="58" t="inlineStr">
         <is>
           <t>no — ASK first</t>
         </is>
       </c>
-      <c r="J55" s="57" t="inlineStr">
+      <c r="J55" s="58" t="inlineStr">
         <is>
           <t>Business Income</t>
         </is>
       </c>
-      <c r="K55" s="57" t="inlineStr">
+      <c r="K55" s="58" t="inlineStr">
         <is>
           <t>Auto-Routing transfer; Merchant name: EOEB LLC</t>
         </is>
@@ -11004,12 +11059,12 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="57" t="inlineStr">
+      <c r="A56" s="58" t="inlineStr">
         <is>
           <t>2025-11-06</t>
         </is>
       </c>
-      <c r="B56" s="57" t="inlineStr">
+      <c r="B56" s="58" t="inlineStr">
         <is>
           <t>COINBASE INC.</t>
         </is>
@@ -11017,12 +11072,12 @@
       <c r="C56" s="45" t="n">
         <v>-10000</v>
       </c>
-      <c r="D56" s="57" t="inlineStr">
+      <c r="D56" s="58" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E56" s="73" t="inlineStr">
+      <c r="E56" s="74" t="inlineStr">
         <is>
           <t>INVESTMENT</t>
         </is>
@@ -11032,27 +11087,27 @@
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="G56" s="57" t="inlineStr">
+      <c r="G56" s="58" t="inlineStr">
         <is>
           <t>Coinbase ACH funding</t>
         </is>
       </c>
-      <c r="H56" s="57" t="inlineStr">
+      <c r="H56" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I56" s="57" t="inlineStr">
+      <c r="I56" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J56" s="57" t="inlineStr">
+      <c r="J56" s="58" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K56" s="57" t="inlineStr">
+      <c r="K56" s="58" t="inlineStr">
         <is>
           <t>COINBASE INC.; 450310C7; JACOB COLEY; Merchant name: COINBASE INC.</t>
         </is>
@@ -11064,55 +11119,55 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="57" t="inlineStr">
+      <c r="A57" s="58" t="inlineStr">
         <is>
           <t>2025-11-07</t>
         </is>
       </c>
-      <c r="B57" s="57" t="inlineStr">
+      <c r="B57" s="58" t="inlineStr">
         <is>
           <t>ERDAL DERE</t>
         </is>
       </c>
-      <c r="C57" s="70" t="n">
+      <c r="C57" s="71" t="n">
         <v>6000</v>
       </c>
-      <c r="D57" s="57" t="inlineStr">
+      <c r="D57" s="58" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E57" s="69" t="inlineStr">
+      <c r="E57" s="70" t="inlineStr">
         <is>
           <t>ART_SALE</t>
         </is>
       </c>
-      <c r="F57" s="71" t="inlineStr">
+      <c r="F57" s="72" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G57" s="57" t="inlineStr">
+      <c r="G57" s="58" t="inlineStr">
         <is>
           <t>Erdal Dere Fortuna PAYMENT $6,000 IN</t>
         </is>
       </c>
-      <c r="H57" s="57" t="inlineStr">
+      <c r="H57" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I57" s="57" t="inlineStr">
+      <c r="I57" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J57" s="57" t="inlineStr">
+      <c r="J57" s="58" t="inlineStr">
         <is>
           <t>Business Income</t>
         </is>
       </c>
-      <c r="K57" s="57" t="inlineStr">
+      <c r="K57" s="58" t="inlineStr">
         <is>
           <t>Incoming Wire; ERDAL DERE FORTUNA PAYMENT; Merchant name: ERDAL DERE</t>
         </is>
@@ -11124,12 +11179,12 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="57" t="inlineStr">
+      <c r="A58" s="58" t="inlineStr">
         <is>
           <t>2025-11-12</t>
         </is>
       </c>
-      <c r="B58" s="57" t="inlineStr">
+      <c r="B58" s="58" t="inlineStr">
         <is>
           <t>Newstar Jewelers</t>
         </is>
@@ -11137,12 +11192,12 @@
       <c r="C58" s="45" t="n">
         <v>-8000</v>
       </c>
-      <c r="D58" s="57" t="inlineStr">
+      <c r="D58" s="58" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E58" s="68" t="inlineStr">
+      <c r="E58" s="69" t="inlineStr">
         <is>
           <t>COGS_JEWELRY</t>
         </is>
@@ -11152,27 +11207,27 @@
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="G58" s="57" t="inlineStr">
+      <c r="G58" s="58" t="inlineStr">
         <is>
           <t>Newstar Jewelers — jewelry fabrication</t>
         </is>
       </c>
-      <c r="H58" s="57" t="inlineStr">
+      <c r="H58" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I58" s="57" t="inlineStr">
+      <c r="I58" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J58" s="57" t="inlineStr">
+      <c r="J58" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">Business Expense </t>
         </is>
       </c>
-      <c r="K58" s="57" t="inlineStr">
+      <c r="K58" s="58" t="inlineStr">
         <is>
           <t>Merchant name: Newstar Jewelers</t>
         </is>
@@ -11184,12 +11239,12 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="57" t="inlineStr">
+      <c r="A59" s="58" t="inlineStr">
         <is>
           <t>2025-11-14</t>
         </is>
       </c>
-      <c r="B59" s="57" t="inlineStr">
+      <c r="B59" s="58" t="inlineStr">
         <is>
           <t>COINBASE INC.</t>
         </is>
@@ -11197,12 +11252,12 @@
       <c r="C59" s="45" t="n">
         <v>-10000</v>
       </c>
-      <c r="D59" s="57" t="inlineStr">
+      <c r="D59" s="58" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E59" s="73" t="inlineStr">
+      <c r="E59" s="74" t="inlineStr">
         <is>
           <t>INVESTMENT</t>
         </is>
@@ -11212,27 +11267,27 @@
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="G59" s="57" t="inlineStr">
+      <c r="G59" s="58" t="inlineStr">
         <is>
           <t>Coinbase ACH funding</t>
         </is>
       </c>
-      <c r="H59" s="57" t="inlineStr">
+      <c r="H59" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I59" s="57" t="inlineStr">
+      <c r="I59" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J59" s="57" t="inlineStr">
+      <c r="J59" s="58" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K59" s="57" t="inlineStr">
+      <c r="K59" s="58" t="inlineStr">
         <is>
           <t>COINBASE INC.; 8DF808EA; JACOB COLEY; Merchant name: COINBASE INC.</t>
         </is>
@@ -11244,12 +11299,12 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="57" t="inlineStr">
+      <c r="A60" s="58" t="inlineStr">
         <is>
           <t>2025-11-17</t>
         </is>
       </c>
-      <c r="B60" s="57" t="inlineStr">
+      <c r="B60" s="58" t="inlineStr">
         <is>
           <t>COINBASE INC.</t>
         </is>
@@ -11257,12 +11312,12 @@
       <c r="C60" s="45" t="n">
         <v>-10000</v>
       </c>
-      <c r="D60" s="57" t="inlineStr">
+      <c r="D60" s="58" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E60" s="73" t="inlineStr">
+      <c r="E60" s="74" t="inlineStr">
         <is>
           <t>INVESTMENT</t>
         </is>
@@ -11272,27 +11327,27 @@
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="G60" s="57" t="inlineStr">
+      <c r="G60" s="58" t="inlineStr">
         <is>
           <t>Coinbase ACH funding</t>
         </is>
       </c>
-      <c r="H60" s="57" t="inlineStr">
+      <c r="H60" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I60" s="57" t="inlineStr">
+      <c r="I60" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J60" s="57" t="inlineStr">
+      <c r="J60" s="58" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K60" s="57" t="inlineStr">
+      <c r="K60" s="58" t="inlineStr">
         <is>
           <t>COINBASE INC.; 6651A007; JACOB COLEY; Merchant name: COINBASE INC.</t>
         </is>
@@ -11304,12 +11359,12 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="57" t="inlineStr">
+      <c r="A61" s="58" t="inlineStr">
         <is>
           <t>2025-11-24</t>
         </is>
       </c>
-      <c r="B61" s="57" t="inlineStr">
+      <c r="B61" s="58" t="inlineStr">
         <is>
           <t>COINBASE INC.</t>
         </is>
@@ -11317,12 +11372,12 @@
       <c r="C61" s="45" t="n">
         <v>-5000</v>
       </c>
-      <c r="D61" s="57" t="inlineStr">
+      <c r="D61" s="58" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E61" s="73" t="inlineStr">
+      <c r="E61" s="74" t="inlineStr">
         <is>
           <t>INVESTMENT</t>
         </is>
@@ -11332,27 +11387,27 @@
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="G61" s="57" t="inlineStr">
+      <c r="G61" s="58" t="inlineStr">
         <is>
           <t>Coinbase ACH funding</t>
         </is>
       </c>
-      <c r="H61" s="57" t="inlineStr">
+      <c r="H61" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I61" s="57" t="inlineStr">
+      <c r="I61" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J61" s="57" t="inlineStr">
+      <c r="J61" s="58" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K61" s="57" t="inlineStr">
+      <c r="K61" s="58" t="inlineStr">
         <is>
           <t>COINBASE INC.; D5957FFE; JACOB COLEY; Merchant name: COINBASE INC.</t>
         </is>
@@ -11364,12 +11419,12 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="57" t="inlineStr">
+      <c r="A62" s="58" t="inlineStr">
         <is>
           <t>2025-12-02</t>
         </is>
       </c>
-      <c r="B62" s="57" t="inlineStr">
+      <c r="B62" s="58" t="inlineStr">
         <is>
           <t>Wise Inc</t>
         </is>
@@ -11377,12 +11432,12 @@
       <c r="C62" s="10" t="n">
         <v>-565.75</v>
       </c>
-      <c r="D62" s="57" t="inlineStr">
+      <c r="D62" s="58" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E62" s="72" t="inlineStr">
+      <c r="E62" s="73" t="inlineStr">
         <is>
           <t>REIMBURSE</t>
         </is>
@@ -11392,27 +11447,27 @@
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="G62" s="57" t="inlineStr">
+      <c r="G62" s="58" t="inlineStr">
         <is>
           <t>Wise $565.75 reimbursed by EOEB</t>
         </is>
       </c>
-      <c r="H62" s="57" t="inlineStr">
+      <c r="H62" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I62" s="57" t="inlineStr">
+      <c r="I62" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J62" s="57" t="inlineStr">
+      <c r="J62" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">Business Expense </t>
         </is>
       </c>
-      <c r="K62" s="57" t="inlineStr">
+      <c r="K62" s="58" t="inlineStr">
         <is>
           <t>Wise Inc; WISE; EPGC LLC; Merchant name: Wise Inc</t>
         </is>
@@ -11424,12 +11479,12 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="57" t="inlineStr">
+      <c r="A63" s="58" t="inlineStr">
         <is>
           <t>2025-12-02</t>
         </is>
       </c>
-      <c r="B63" s="57" t="inlineStr">
+      <c r="B63" s="58" t="inlineStr">
         <is>
           <t>EOEB LLC</t>
         </is>
@@ -11437,12 +11492,12 @@
       <c r="C63" s="10" t="n">
         <v>565.75</v>
       </c>
-      <c r="D63" s="57" t="inlineStr">
+      <c r="D63" s="58" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E63" s="72" t="inlineStr">
+      <c r="E63" s="73" t="inlineStr">
         <is>
           <t>REIMBURSE</t>
         </is>
@@ -11452,27 +11507,27 @@
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="G63" s="57" t="inlineStr">
+      <c r="G63" s="58" t="inlineStr">
         <is>
           <t>EOEB reimburses Wise $565.75</t>
         </is>
       </c>
-      <c r="H63" s="57" t="inlineStr">
+      <c r="H63" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I63" s="57" t="inlineStr">
+      <c r="I63" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J63" s="57" t="inlineStr">
+      <c r="J63" s="58" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K63" s="57" t="inlineStr">
+      <c r="K63" s="58" t="inlineStr">
         <is>
           <t>Auto-Routing transfer; Merchant name: EOEB LLC</t>
         </is>
@@ -11484,55 +11539,55 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="57" t="inlineStr">
+      <c r="A64" s="58" t="inlineStr">
         <is>
           <t>2025-12-04</t>
         </is>
       </c>
-      <c r="B64" s="57" t="inlineStr">
+      <c r="B64" s="58" t="inlineStr">
         <is>
           <t>L5</t>
         </is>
       </c>
-      <c r="C64" s="70" t="n">
+      <c r="C64" s="71" t="n">
         <v>4700.26</v>
       </c>
-      <c r="D64" s="57" t="inlineStr">
+      <c r="D64" s="58" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E64" s="71" t="inlineStr">
+      <c r="E64" s="72" t="inlineStr">
         <is>
           <t>ADVISORY</t>
         </is>
       </c>
-      <c r="F64" s="71" t="inlineStr">
+      <c r="F64" s="72" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G64" s="57" t="inlineStr">
+      <c r="G64" s="58" t="inlineStr">
         <is>
           <t>L5 — sale vs art advisory</t>
         </is>
       </c>
-      <c r="H64" s="57" t="inlineStr">
+      <c r="H64" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I64" s="57" t="inlineStr">
+      <c r="I64" s="58" t="inlineStr">
         <is>
           <t>no — ASK first</t>
         </is>
       </c>
-      <c r="J64" s="57" t="inlineStr">
+      <c r="J64" s="58" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K64" s="57" t="inlineStr">
+      <c r="K64" s="58" t="inlineStr">
         <is>
           <t>Auto-Routing transfer; Merchant name: L5</t>
         </is>
@@ -11544,12 +11599,12 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="57" t="inlineStr">
+      <c r="A65" s="58" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="B65" s="57" t="inlineStr">
+      <c r="B65" s="58" t="inlineStr">
         <is>
           <t>COINBASE INC.</t>
         </is>
@@ -11557,12 +11612,12 @@
       <c r="C65" s="45" t="n">
         <v>-5000</v>
       </c>
-      <c r="D65" s="57" t="inlineStr">
+      <c r="D65" s="58" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E65" s="73" t="inlineStr">
+      <c r="E65" s="74" t="inlineStr">
         <is>
           <t>INVESTMENT</t>
         </is>
@@ -11572,27 +11627,27 @@
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="G65" s="57" t="inlineStr">
+      <c r="G65" s="58" t="inlineStr">
         <is>
           <t>Coinbase ACH funding</t>
         </is>
       </c>
-      <c r="H65" s="57" t="inlineStr">
+      <c r="H65" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I65" s="57" t="inlineStr">
+      <c r="I65" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J65" s="57" t="inlineStr">
+      <c r="J65" s="58" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K65" s="57" t="inlineStr">
+      <c r="K65" s="58" t="inlineStr">
         <is>
           <t>COINBASE INC.; DFF8E6A8; JACOB COLEY; Merchant name: COINBASE INC.</t>
         </is>
@@ -11604,12 +11659,12 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="57" t="inlineStr">
+      <c r="A66" s="58" t="inlineStr">
         <is>
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="B66" s="57" t="inlineStr">
+      <c r="B66" s="58" t="inlineStr">
         <is>
           <t>COINBASE INC.</t>
         </is>
@@ -11617,12 +11672,12 @@
       <c r="C66" s="45" t="n">
         <v>8000</v>
       </c>
-      <c r="D66" s="57" t="inlineStr">
+      <c r="D66" s="58" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E66" s="73" t="inlineStr">
+      <c r="E66" s="74" t="inlineStr">
         <is>
           <t>INVESTMENT</t>
         </is>
@@ -11632,27 +11687,27 @@
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="G66" s="57" t="inlineStr">
+      <c r="G66" s="58" t="inlineStr">
         <is>
           <t>Coinbase ACH back to Mercury</t>
         </is>
       </c>
-      <c r="H66" s="57" t="inlineStr">
+      <c r="H66" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I66" s="57" t="inlineStr">
+      <c r="I66" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J66" s="57" t="inlineStr">
+      <c r="J66" s="58" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K66" s="57" t="inlineStr">
+      <c r="K66" s="58" t="inlineStr">
         <is>
           <t>COINBASE INC.; 6B2DA6B2; JACOB COLEY; Merchant name: COINBASE INC.</t>
         </is>
@@ -11664,12 +11719,12 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="57" t="inlineStr">
+      <c r="A67" s="58" t="inlineStr">
         <is>
           <t>2025-12-24</t>
         </is>
       </c>
-      <c r="B67" s="57" t="inlineStr">
+      <c r="B67" s="58" t="inlineStr">
         <is>
           <t>Newstar Jewelers</t>
         </is>
@@ -11677,12 +11732,12 @@
       <c r="C67" s="45" t="n">
         <v>-7581</v>
       </c>
-      <c r="D67" s="57" t="inlineStr">
+      <c r="D67" s="58" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E67" s="68" t="inlineStr">
+      <c r="E67" s="69" t="inlineStr">
         <is>
           <t>COGS_JEWELRY</t>
         </is>
@@ -11692,27 +11747,27 @@
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="G67" s="57" t="inlineStr">
+      <c r="G67" s="58" t="inlineStr">
         <is>
           <t>Newstar Jewelers — jewelry fabrication (3 of 3)</t>
         </is>
       </c>
-      <c r="H67" s="57" t="inlineStr">
+      <c r="H67" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I67" s="57" t="inlineStr">
+      <c r="I67" s="58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J67" s="57" t="inlineStr">
+      <c r="J67" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">Business Expense </t>
         </is>
       </c>
-      <c r="K67" s="57" t="inlineStr">
+      <c r="K67" s="58" t="inlineStr">
         <is>
           <t>From EPGC LLC via mercury.com 3 of 3; Merchant name: Newstar Jewelers</t>
         </is>

--- a/.cursor/scratch/tax_turbo_parts/Personal Income 2025 — like last year (EPGC+Art+GCM).xlsx
+++ b/.cursor/scratch/tax_turbo_parts/Personal Income 2025 — like last year (EPGC+Art+GCM).xlsx
@@ -175,7 +175,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -257,6 +257,18 @@
     <xf numFmtId="164" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="8" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -264,16 +276,12 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="10" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="10" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="8" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -282,7 +290,6 @@
     <xf numFmtId="168" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="10" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="8" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -290,9 +297,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -310,7 +314,6 @@
     <xf numFmtId="0" fontId="8" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="8" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -3218,7 +3221,7 @@
     <row r="75">
       <c r="A75" s="14" t="inlineStr">
         <is>
-          <t>2025 Mercury 2026-09-20: Art Sales = MATCHED/LOCKED cash (Berk $14,000 Jan + Berk $30,000 / mosaics $105,000 / Aquinas books $1,000 Feb = $150,000). Consultant June $13,595 = David Aaron Limited LOCKED (user: consultant fee, not a sale). Consultant Fees July $334.17 + October $658.63 = Wise expertise write-ups LOCKED ($992.80). EOEB remainder $130,270.00 and L5 $87,396.32 still ASK — not on Consultant income. Koziol/Ariadne $150,000 LOCKED pass-through — not P&amp;L. Coinbase is Investments, not this tab. Newstar $23,581 is Art Sales COGS, not operating expense. Dec Wise $565.75 reimbursed — not on Consultant Fees. Aquinas books Cost TBD — cash on Art Sales, not in I8. GCM 1099 is personal. Not tax advice.</t>
+          <t>2025 Mercury 2026-09-20: Art Sales = MATCHED/LOCKED cash (Berk $14,000 Jan + Berk $30,000 / mosaics $105,000 / Aquinas books $1,000 Feb = $150,000). Consultant June $13,595 = David Aaron Limited LOCKED (user: consultant fee, not a sale). Consultant Fees July $334.17 + October $658.63 = Wise expertise write-ups LOCKED ($992.80). EOEB remainder $130,270.00 and L5 $87,396.32 MIXED PATTERN CONFIRMED (art sales + advisory/consultant) — invoice-level split still ASK; not dumped onto Consultant or Art Sales. Koziol/Ariadne $150,000 LOCKED pass-through — not P&amp;L. Coinbase is Investments, not this tab. Newstar $23,581 is Art Sales COGS, not operating expense. Dec Wise $565.75 reimbursed — not on Consultant Fees. Aquinas books Cost TBD — cash on Art Sales, not in I8. GCM 1099 is personal. Not tax advice.</t>
         </is>
       </c>
     </row>
@@ -3234,7 +3237,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N135"/>
+  <dimension ref="A1:N134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="47.86" customWidth="1" min="1" max="1"/>
@@ -5909,82 +5912,85 @@
       <c r="I76" s="16" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="18" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B77" s="15" t="n"/>
-      <c r="C77" s="29" t="n"/>
-      <c r="D77" s="28" t="n"/>
-      <c r="E77" s="28" t="n"/>
-      <c r="F77" s="29" t="n"/>
-      <c r="G77" s="28" t="n"/>
-      <c r="H77" s="29">
-        <f>SUM(H51:H75)</f>
-        <v/>
-      </c>
-      <c r="I77" s="16" t="n"/>
+      <c r="A77" s="39" t="inlineStr">
+        <is>
+          <t>Books (titles TBD)</t>
+        </is>
+      </c>
+      <c r="B77" s="40" t="inlineStr">
+        <is>
+          <t>Cost TBD</t>
+        </is>
+      </c>
+      <c r="C77" s="41" t="n"/>
+      <c r="E77" s="39" t="inlineStr">
+        <is>
+          <t>Aquinas Hobor</t>
+        </is>
+      </c>
+      <c r="F77" s="42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G77" s="43" t="n">
+        <v>45692</v>
+      </c>
+      <c r="H77" s="44">
+        <f>IF(OR(F77="",C77=""),"",F77-C77)</f>
+        <v/>
+      </c>
+      <c r="I77" s="45" t="inlineStr">
+        <is>
+          <t>LOCKED 2026-09-20: book SALE $1,000 on Mercury 8291. Cost TBD — not in Income I8 yet (same as Sale 6428). Titles TBD. Not tax advice.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
-      <c r="A78" s="39" t="inlineStr">
+      <c r="A78" s="46" t="inlineStr">
         <is>
           <t>Mercury 8291 MATCHED: Berk $14,000 (1/10 seals) + $30,000 (2/7 lots). EOEB $105,000 (2/21 mosaics). Fortuna $13,000 (1/8 seals Cost). Plutus $50,000 of mosaics $90,000 Cost — $40,000 of Cost not on 8291 (ASK). Newstar $23,581 is jewelry fabrication COGS, parked below — not in sold-lot Cost (Berk gem/scarab lots already sold in February). David Aaron $13,595 (6/24) is LOCKED consultant fee — not a sale (EPGC Consultant June). Aquinas Hobor $1,000 (2/4) is LOCKED books sold — EPGC Art Sales February; Cost TBD (not in I8). Not tax advice.</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+      <c r="A79" s="47" t="inlineStr">
+        <is>
+          <t>Mercury 8291 MATCHED: Berk $14,000 (1/10 seals) + $30,000 (2/7 lots). EOEB $105,000 (2/21 mosaics). Fortuna $13,000 (1/8 seals Cost). Plutus $50,000 of mosaics $90,000 Cost — $40,000 of Cost not on 8291 (ASK). Newstar $23,581 is jewelry fabrication COGS, parked below — not in sold-lot Cost (Berk gem/scarab lots already sold in February). David Aaron $13,595 (6/24) is LOCKED consultant fee — not a sale (EPGC Consultant June). Aquinas Hobor $1,000 (2/4) is LOCKED books sold — EPGC Art Sales February; Cost TBD (not in I8). Not tax advice.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>Art Purchases/Inventory</t>
         </is>
       </c>
-      <c r="B79" s="15" t="n"/>
-      <c r="C79" s="5" t="n"/>
-      <c r="D79" s="22" t="n"/>
-      <c r="E79" s="40" t="n"/>
-      <c r="F79" s="5" t="n"/>
-      <c r="G79" s="22" t="n"/>
-      <c r="H79" s="40" t="n"/>
-      <c r="I79" s="16" t="n"/>
-      <c r="J79" s="40" t="n"/>
-      <c r="K79" s="40" t="n"/>
-      <c r="L79" s="40" t="n"/>
-      <c r="M79" s="40" t="n"/>
-      <c r="N79" s="40" t="n"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="4" t="inlineStr">
-        <is>
-          <t>30 Paleothic and Neolithic Stone Tools</t>
-        </is>
-      </c>
-      <c r="B80" s="31" t="inlineStr">
-        <is>
-          <t>Holestein</t>
-        </is>
-      </c>
-      <c r="C80" s="5" t="n">
-        <v>4000</v>
-      </c>
-      <c r="E80" s="16" t="n"/>
+      <c r="B80" s="15" t="n"/>
+      <c r="C80" s="5" t="n"/>
+      <c r="D80" s="22" t="n"/>
+      <c r="E80" s="48" t="n"/>
+      <c r="F80" s="5" t="n"/>
+      <c r="G80" s="22" t="n"/>
+      <c r="H80" s="48" t="n"/>
+      <c r="I80" s="16" t="n"/>
+      <c r="J80" s="48" t="n"/>
+      <c r="K80" s="48" t="n"/>
+      <c r="L80" s="48" t="n"/>
+      <c r="M80" s="48" t="n"/>
+      <c r="N80" s="48" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>A Tairona Figure</t>
+          <t>30 Paleothic and Neolithic Stone Tools</t>
         </is>
       </c>
       <c r="B81" s="31" t="inlineStr">
         <is>
-          <t>Live Auctioneers</t>
+          <t>Holestein</t>
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="D81" s="22" t="n">
-        <v>45119</v>
+        <v>4000</v>
       </c>
       <c r="E81" s="16" t="n"/>
     </row>
@@ -6000,7 +6006,7 @@
         </is>
       </c>
       <c r="C82" s="5" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="D82" s="22" t="n">
         <v>45119</v>
@@ -6010,26 +6016,26 @@
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>A Pair of Greek Bronze Greeves</t>
+          <t>A Tairona Figure</t>
         </is>
       </c>
       <c r="B83" s="31" t="inlineStr">
         <is>
-          <t>ebay</t>
+          <t>Live Auctioneers</t>
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="D83" s="22" t="n">
-        <v>45145</v>
+        <v>45119</v>
       </c>
       <c r="E83" s="16" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>An Illyrian Bronze Helmet</t>
+          <t>A Pair of Greek Bronze Greeves</t>
         </is>
       </c>
       <c r="B84" s="31" t="inlineStr">
@@ -6038,58 +6044,57 @@
         </is>
       </c>
       <c r="C84" s="5" t="n">
-        <v>551.25</v>
+        <v>200</v>
       </c>
       <c r="D84" s="22" t="n">
-        <v>45114</v>
+        <v>45145</v>
       </c>
       <c r="E84" s="16" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>An Egyptian Faience Ibis</t>
-        </is>
-      </c>
-      <c r="B85" s="15" t="inlineStr">
-        <is>
-          <t>Hindman</t>
+          <t>An Illyrian Bronze Helmet</t>
+        </is>
+      </c>
+      <c r="B85" s="31" t="inlineStr">
+        <is>
+          <t>ebay</t>
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>375</v>
+        <v>551.25</v>
       </c>
       <c r="D85" s="22" t="n">
-        <v>44343</v>
-      </c>
-      <c r="E85" s="22" t="n"/>
-      <c r="F85" s="5" t="n"/>
-      <c r="I85" s="16" t="n"/>
+        <v>45114</v>
+      </c>
+      <c r="E85" s="16" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>African Stone Bracelet Upper Volta River 1 0f 4</t>
+          <t>An Egyptian Faience Ibis</t>
         </is>
       </c>
       <c r="B86" s="15" t="inlineStr">
         <is>
-          <t>Live Auctioneers</t>
+          <t>Hindman</t>
         </is>
       </c>
       <c r="C86" s="5" t="n">
-        <v>293</v>
+        <v>375</v>
       </c>
       <c r="D86" s="22" t="n">
-        <v>44548</v>
-      </c>
+        <v>44343</v>
+      </c>
+      <c r="E86" s="22" t="n"/>
       <c r="F86" s="5" t="n"/>
       <c r="I86" s="16" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>African Stone Bracelet Upper Volta River 2 0f 4</t>
+          <t>African Stone Bracelet Upper Volta River 1 0f 4</t>
         </is>
       </c>
       <c r="B87" s="15" t="inlineStr">
@@ -6109,7 +6114,7 @@
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>African Stone Bracelet Upper Volta River 4 0f 4</t>
+          <t>African Stone Bracelet Upper Volta River 2 0f 4</t>
         </is>
       </c>
       <c r="B88" s="15" t="inlineStr">
@@ -6129,19 +6134,19 @@
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>A Saharan Stone Discoidal</t>
+          <t>African Stone Bracelet Upper Volta River 4 0f 4</t>
         </is>
       </c>
       <c r="B89" s="15" t="inlineStr">
         <is>
-          <t>Pace African Art</t>
+          <t>Live Auctioneers</t>
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>1000</v>
+        <v>293</v>
       </c>
       <c r="D89" s="22" t="n">
-        <v>44562</v>
+        <v>44548</v>
       </c>
       <c r="F89" s="5" t="n"/>
       <c r="I89" s="16" t="n"/>
@@ -6149,16 +6154,19 @@
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>Carved Ostrish Egg</t>
+          <t>A Saharan Stone Discoidal</t>
         </is>
       </c>
       <c r="B90" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Etsy </t>
+          <t>Pace African Art</t>
         </is>
       </c>
       <c r="C90" s="5" t="n">
-        <v>90</v>
+        <v>1000</v>
+      </c>
+      <c r="D90" s="22" t="n">
+        <v>44562</v>
       </c>
       <c r="F90" s="5" t="n"/>
       <c r="I90" s="16" t="n"/>
@@ -6166,16 +6174,16 @@
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>Carved Goose Egg</t>
+          <t>Carved Ostrish Egg</t>
         </is>
       </c>
       <c r="B91" s="15" t="inlineStr">
         <is>
-          <t>Etsy</t>
+          <t xml:space="preserve">Etsy </t>
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="F91" s="5" t="n"/>
       <c r="I91" s="16" t="n"/>
@@ -6192,7 +6200,7 @@
         </is>
       </c>
       <c r="C92" s="5" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F92" s="5" t="n"/>
       <c r="I92" s="16" t="n"/>
@@ -6200,31 +6208,29 @@
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>Quimbaya Figure (Gift)</t>
+          <t>Carved Goose Egg</t>
         </is>
       </c>
       <c r="B93" s="15" t="inlineStr">
         <is>
-          <t>Jeffrey Norris</t>
+          <t>Etsy</t>
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="D93" s="22" t="n">
-        <v>45079</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="F93" s="5" t="n"/>
       <c r="I93" s="16" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>A Saharan Stone Discoidal (Gift)</t>
+          <t>Quimbaya Figure (Gift)</t>
         </is>
       </c>
       <c r="B94" s="15" t="inlineStr">
         <is>
-          <t>Aquinas Hobor</t>
+          <t>Jeffrey Norris</t>
         </is>
       </c>
       <c r="C94" s="5" t="n">
@@ -6238,7 +6244,7 @@
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>A Saharan Stone Discoidal</t>
+          <t>A Saharan Stone Discoidal (Gift)</t>
         </is>
       </c>
       <c r="B95" s="15" t="inlineStr">
@@ -6246,31 +6252,30 @@
           <t>Aquinas Hobor</t>
         </is>
       </c>
-      <c r="C95" s="26" t="n">
-        <v>500</v>
+      <c r="C95" s="5" t="n">
+        <v>10</v>
       </c>
       <c r="D95" s="22" t="n">
         <v>45079</v>
       </c>
-      <c r="F95" s="5" t="n"/>
       <c r="I95" s="16" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>Two Songye and Bozo Vessels</t>
+          <t>A Saharan Stone Discoidal</t>
         </is>
       </c>
       <c r="B96" s="15" t="inlineStr">
         <is>
-          <t>Hindman</t>
+          <t>Aquinas Hobor</t>
         </is>
       </c>
       <c r="C96" s="26" t="n">
-        <v>138.91</v>
+        <v>500</v>
       </c>
       <c r="D96" s="22" t="n">
-        <v>45211</v>
+        <v>45079</v>
       </c>
       <c r="F96" s="5" t="n"/>
       <c r="I96" s="16" t="n"/>
@@ -6278,19 +6283,19 @@
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sword 9th Century </t>
+          <t>Two Songye and Bozo Vessels</t>
         </is>
       </c>
       <c r="B97" s="15" t="inlineStr">
         <is>
-          <t>Zevantiques</t>
+          <t>Hindman</t>
         </is>
       </c>
       <c r="C97" s="26" t="n">
-        <v>3000</v>
+        <v>138.91</v>
       </c>
       <c r="D97" s="22" t="n">
-        <v>45311</v>
+        <v>45211</v>
       </c>
       <c r="F97" s="5" t="n"/>
       <c r="I97" s="16" t="n"/>
@@ -6298,19 +6303,19 @@
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>A Roman Marble Plaque with Insciption</t>
+          <t xml:space="preserve">Sword 9th Century </t>
         </is>
       </c>
       <c r="B98" s="15" t="inlineStr">
         <is>
-          <t>ebay</t>
+          <t>Zevantiques</t>
         </is>
       </c>
       <c r="C98" s="26" t="n">
-        <v>1331.41</v>
+        <v>3000</v>
       </c>
       <c r="D98" s="22" t="n">
-        <v>45546</v>
+        <v>45311</v>
       </c>
       <c r="F98" s="5" t="n"/>
       <c r="I98" s="16" t="n"/>
@@ -6318,7 +6323,7 @@
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>Erotic Intaglio Finger Ring</t>
+          <t>A Roman Marble Plaque with Insciption</t>
         </is>
       </c>
       <c r="B99" s="15" t="inlineStr">
@@ -6327,73 +6332,82 @@
         </is>
       </c>
       <c r="C99" s="26" t="n">
-        <v>205.07</v>
+        <v>1331.41</v>
       </c>
       <c r="D99" s="22" t="n">
-        <v>45446</v>
+        <v>45546</v>
       </c>
       <c r="F99" s="5" t="n"/>
       <c r="I99" s="16" t="n"/>
     </row>
     <row r="100">
-      <c r="B100" s="15" t="n"/>
-      <c r="C100" s="26" t="n"/>
-      <c r="D100" s="22" t="n"/>
+      <c r="A100" s="4" t="inlineStr">
+        <is>
+          <t>Erotic Intaglio Finger Ring</t>
+        </is>
+      </c>
+      <c r="B100" s="15" t="inlineStr">
+        <is>
+          <t>ebay</t>
+        </is>
+      </c>
+      <c r="C100" s="26" t="n">
+        <v>205.07</v>
+      </c>
+      <c r="D100" s="22" t="n">
+        <v>45446</v>
+      </c>
       <c r="F100" s="5" t="n"/>
       <c r="I100" s="16" t="n"/>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
       <c r="B101" s="15" t="n"/>
-      <c r="C101" s="7" t="n"/>
+      <c r="C101" s="26" t="n"/>
+      <c r="D101" s="22" t="n"/>
       <c r="F101" s="5" t="n"/>
       <c r="I101" s="16" t="n"/>
     </row>
     <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="B102" s="15" t="n"/>
-      <c r="C102" s="5" t="n"/>
+      <c r="C102" s="7" t="n"/>
       <c r="F102" s="5" t="n"/>
       <c r="I102" s="16" t="n"/>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="inlineStr">
-        <is>
-          <t>Office/Business Inventory</t>
-        </is>
-      </c>
       <c r="B103" s="15" t="n"/>
       <c r="C103" s="5" t="n"/>
-      <c r="D103" s="40" t="n"/>
-      <c r="E103" s="40" t="n"/>
       <c r="F103" s="5" t="n"/>
-      <c r="G103" s="40" t="n"/>
-      <c r="H103" s="40" t="n"/>
       <c r="I103" s="16" t="n"/>
-      <c r="J103" s="40" t="n"/>
-      <c r="K103" s="40" t="n"/>
-      <c r="L103" s="40" t="n"/>
-      <c r="M103" s="40" t="n"/>
-      <c r="N103" s="40" t="n"/>
     </row>
     <row r="104">
-      <c r="A104" s="4" t="inlineStr">
-        <is>
-          <t>Sofa</t>
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>Office/Business Inventory</t>
         </is>
       </c>
       <c r="B104" s="15" t="n"/>
       <c r="C104" s="5" t="n"/>
+      <c r="D104" s="48" t="n"/>
+      <c r="E104" s="48" t="n"/>
       <c r="F104" s="5" t="n"/>
+      <c r="G104" s="48" t="n"/>
+      <c r="H104" s="48" t="n"/>
       <c r="I104" s="16" t="n"/>
+      <c r="J104" s="48" t="n"/>
+      <c r="K104" s="48" t="n"/>
+      <c r="L104" s="48" t="n"/>
+      <c r="M104" s="48" t="n"/>
+      <c r="N104" s="48" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>Space Heater</t>
+          <t>Sofa</t>
         </is>
       </c>
       <c r="B105" s="15" t="n"/>
@@ -6404,7 +6418,7 @@
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>Shelving</t>
+          <t>Space Heater</t>
         </is>
       </c>
       <c r="B106" s="15" t="n"/>
@@ -6415,7 +6429,7 @@
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>Storage Bins</t>
+          <t>Shelving</t>
         </is>
       </c>
       <c r="B107" s="15" t="n"/>
@@ -6426,7 +6440,7 @@
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>Table</t>
+          <t>Storage Bins</t>
         </is>
       </c>
       <c r="B108" s="15" t="n"/>
@@ -6437,7 +6451,7 @@
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>Computer</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="B109" s="15" t="n"/>
@@ -6448,7 +6462,7 @@
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>Art Library</t>
+          <t>Computer</t>
         </is>
       </c>
       <c r="B110" s="15" t="n"/>
@@ -6459,7 +6473,7 @@
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>Standing Desk</t>
+          <t>Art Library</t>
         </is>
       </c>
       <c r="B111" s="15" t="n"/>
@@ -6468,46 +6482,37 @@
       <c r="I111" s="16" t="n"/>
     </row>
     <row r="112">
+      <c r="A112" s="4" t="inlineStr">
+        <is>
+          <t>Standing Desk</t>
+        </is>
+      </c>
       <c r="B112" s="15" t="n"/>
       <c r="C112" s="5" t="n"/>
       <c r="F112" s="5" t="n"/>
       <c r="I112" s="16" t="n"/>
     </row>
     <row r="113">
-      <c r="A113" s="41" t="inlineStr">
-        <is>
-          <t>2025 CC inventory (not in Cost total until object is named)</t>
-        </is>
-      </c>
       <c r="B113" s="15" t="n"/>
       <c r="C113" s="5" t="n"/>
       <c r="F113" s="5" t="n"/>
       <c r="I113" s="16" t="n"/>
     </row>
     <row r="114">
-      <c r="A114" s="32" t="inlineStr">
-        <is>
-          <t>Los Angeles Modern Auctions (inventory purchase)</t>
-        </is>
-      </c>
-      <c r="B114" s="32" t="inlineStr">
-        <is>
-          <t>Sapphire 5423</t>
-        </is>
-      </c>
-      <c r="C114" s="42" t="n">
-        <v>6821.06</v>
-      </c>
-      <c r="D114" s="32" t="inlineStr">
-        <is>
-          <t>2025-07-24</t>
-        </is>
-      </c>
+      <c r="A114" s="49" t="inlineStr">
+        <is>
+          <t>2025 CC inventory (not in Cost total until object is named)</t>
+        </is>
+      </c>
+      <c r="B114" s="15" t="n"/>
+      <c r="C114" s="5" t="n"/>
+      <c r="F114" s="5" t="n"/>
+      <c r="I114" s="16" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="32" t="inlineStr">
         <is>
-          <t>Hindman LLC (inventory purchase)</t>
+          <t>Los Angeles Modern Auctions (inventory purchase)</t>
         </is>
       </c>
       <c r="B115" s="32" t="inlineStr">
@@ -6515,12 +6520,12 @@
           <t>Sapphire 5423</t>
         </is>
       </c>
-      <c r="C115" s="42" t="n">
-        <v>282.24</v>
+      <c r="C115" s="50" t="n">
+        <v>6821.06</v>
       </c>
       <c r="D115" s="32" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-07-24</t>
         </is>
       </c>
     </row>
@@ -6535,295 +6540,274 @@
           <t>Sapphire 5423</t>
         </is>
       </c>
-      <c r="C116" s="42" t="n">
-        <v>403.51</v>
+      <c r="C116" s="50" t="n">
+        <v>282.24</v>
       </c>
       <c r="D116" s="32" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-04-03</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="32" t="inlineStr">
         <is>
+          <t>Hindman LLC (inventory purchase)</t>
+        </is>
+      </c>
+      <c r="B117" s="32" t="inlineStr">
+        <is>
+          <t>Sapphire 5423</t>
+        </is>
+      </c>
+      <c r="C117" s="50" t="n">
+        <v>403.51</v>
+      </c>
+      <c r="D117" s="32" t="inlineStr">
+        <is>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="32" t="inlineStr">
+        <is>
           <t>The Great Frame Up (inventory framing)</t>
         </is>
       </c>
-      <c r="B117" s="32" t="inlineStr">
+      <c r="B118" s="32" t="inlineStr">
         <is>
           <t>Sapphire 5423</t>
         </is>
       </c>
-      <c r="C117" s="42" t="n">
+      <c r="C118" s="50" t="n">
         <v>536.41</v>
       </c>
-      <c r="D117" s="32" t="inlineStr">
+      <c r="D118" s="32" t="inlineStr">
         <is>
           <t>2025-02-16</t>
         </is>
       </c>
     </row>
-    <row r="118"/>
-    <row r="119">
-      <c r="A119" s="43" t="inlineStr">
+    <row r="119"/>
+    <row r="120">
+      <c r="A120" s="51" t="inlineStr">
         <is>
           <t>2025 Mercury 8291 — David Aaron Limited is LOCKED consultant fee (not Art Sales)</t>
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="44" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="39" t="inlineStr">
         <is>
           <t>NOT a 2025 art sale — David Aaron Limited consultant fee (EPGC Consultant June)</t>
         </is>
       </c>
-      <c r="B120" s="44" t="inlineStr">
+      <c r="B121" s="39" t="inlineStr">
         <is>
           <t>David Aaron Limited</t>
         </is>
       </c>
-      <c r="C120" s="44" t="n"/>
-      <c r="D120" s="44" t="n"/>
-      <c r="E120" s="44" t="n"/>
-      <c r="F120" s="45" t="n"/>
-      <c r="G120" s="46" t="n"/>
-      <c r="H120" s="46" t="n"/>
-      <c r="I120" s="44" t="inlineStr">
+      <c r="C121" s="39" t="n"/>
+      <c r="D121" s="39" t="n"/>
+      <c r="E121" s="39" t="n"/>
+      <c r="F121" s="42" t="n"/>
+      <c r="G121" s="52" t="n"/>
+      <c r="H121" s="52" t="n"/>
+      <c r="I121" s="39" t="inlineStr">
         <is>
           <t>LOCKED 2026-09-20: consultant fee, not a sale. $13,595 is on EPGC Consultant June. Not tax advice.</t>
         </is>
       </c>
     </row>
-    <row r="121"/>
-    <row r="122">
-      <c r="A122" s="43" t="inlineStr">
+    <row r="122"/>
+    <row r="123">
+      <c r="A123" s="51" t="inlineStr">
         <is>
           <t>2025 Mercury COGS — Newstar Jewelers (LOCKED jewelry fabrication)</t>
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="47" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="53" t="inlineStr">
         <is>
           <t>Newstar Jewelers — jewelry from intaglios / engraved gems / scarabs</t>
         </is>
       </c>
-      <c r="B123" s="47" t="inlineStr">
+      <c r="B124" s="53" t="inlineStr">
         <is>
           <t>Mercury 8291</t>
         </is>
       </c>
-      <c r="C123" s="48" t="n">
+      <c r="C124" s="54" t="n">
         <v>8000</v>
       </c>
-      <c r="D123" s="47" t="inlineStr">
+      <c r="D124" s="53" t="inlineStr">
         <is>
           <t>2025-10-14</t>
         </is>
       </c>
-      <c r="I123" s="32" t="inlineStr">
+      <c r="I124" s="32" t="inlineStr">
         <is>
           <t>LOCKED COGS fabrication. Not in sold-lot Cost total (Feb Berk lots already sold). Identify which gems/intaglios/scarabs.</t>
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="47" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="53" t="inlineStr">
         <is>
           <t>Newstar Jewelers — jewelry from intaglios / engraved gems / scarabs</t>
         </is>
       </c>
-      <c r="B124" s="47" t="inlineStr">
+      <c r="B125" s="53" t="inlineStr">
         <is>
           <t>Mercury 8291</t>
         </is>
       </c>
-      <c r="C124" s="48" t="n">
+      <c r="C125" s="54" t="n">
         <v>8000</v>
       </c>
-      <c r="D124" s="47" t="inlineStr">
+      <c r="D125" s="53" t="inlineStr">
         <is>
           <t>2025-11-12</t>
         </is>
       </c>
-      <c r="I124" s="32" t="inlineStr">
+      <c r="I125" s="32" t="inlineStr">
         <is>
           <t>LOCKED COGS fabrication. Not in sold-lot Cost total (Feb Berk lots already sold). Identify which gems/intaglios/scarabs.</t>
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="47" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="53" t="inlineStr">
         <is>
           <t>Newstar Jewelers — jewelry from intaglios / engraved gems / scarabs (3 of 3)</t>
         </is>
       </c>
-      <c r="B125" s="47" t="inlineStr">
+      <c r="B126" s="53" t="inlineStr">
         <is>
           <t>Mercury 8291</t>
         </is>
       </c>
-      <c r="C125" s="48" t="n">
+      <c r="C126" s="54" t="n">
         <v>7581</v>
       </c>
-      <c r="D125" s="47" t="inlineStr">
+      <c r="D126" s="53" t="inlineStr">
         <is>
           <t>2025-12-24</t>
         </is>
       </c>
-      <c r="I125" s="32" t="inlineStr">
+      <c r="I126" s="32" t="inlineStr">
         <is>
           <t>LOCKED COGS fabrication. Not in sold-lot Cost total (Feb Berk lots already sold). Identify which gems/intaglios/scarabs.</t>
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="32" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="32" t="inlineStr">
         <is>
           <t>Newstar 2025 total</t>
         </is>
       </c>
-      <c r="C126" s="48">
+      <c r="C127" s="54">
         <f>SUM(C123:C125)</f>
         <v/>
       </c>
     </row>
-    <row r="127"/>
-    <row r="128">
-      <c r="A128" s="49" t="inlineStr">
+    <row r="128"/>
+    <row r="129">
+      <c r="A129" s="55" t="inlineStr">
         <is>
           <t>2025 Mercury ASK — Fortuna inventory remaining (not in Cost total until object is named)</t>
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="50" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="41" t="inlineStr">
         <is>
           <t>Fortuna / Erdal Dere — object TBD</t>
         </is>
       </c>
-      <c r="B129" s="50" t="inlineStr">
+      <c r="B130" s="41" t="inlineStr">
         <is>
           <t>Mercury 8291</t>
         </is>
       </c>
-      <c r="C129" s="42" t="n">
+      <c r="C130" s="50" t="n">
         <v>20000</v>
       </c>
-      <c r="D129" s="50" t="inlineStr">
+      <c r="D130" s="41" t="inlineStr">
         <is>
           <t>2025-05-09</t>
         </is>
       </c>
-      <c r="I129" s="32" t="inlineStr">
+      <c r="I130" s="32" t="inlineStr">
         <is>
           <t>ASK: inventory purchase vs other. Do not add to sold Cost until named (avoid double count).</t>
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="50" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="41" t="inlineStr">
         <is>
           <t>Fortuna / Erdal Dere — object TBD</t>
         </is>
       </c>
-      <c r="B130" s="50" t="inlineStr">
+      <c r="B131" s="41" t="inlineStr">
         <is>
           <t>Mercury 8291</t>
         </is>
       </c>
-      <c r="C130" s="42" t="n">
+      <c r="C131" s="50" t="n">
         <v>45000</v>
       </c>
-      <c r="D130" s="50" t="inlineStr">
+      <c r="D131" s="41" t="inlineStr">
         <is>
           <t>2025-07-21</t>
         </is>
       </c>
-      <c r="I130" s="32" t="inlineStr">
+      <c r="I131" s="32" t="inlineStr">
         <is>
           <t>ASK: inventory purchase vs other. Do not add to sold Cost until named (avoid double count).</t>
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="50" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="41" t="inlineStr">
         <is>
           <t>Fortuna / Erdal Dere — object TBD</t>
         </is>
       </c>
-      <c r="B131" s="50" t="inlineStr">
+      <c r="B132" s="41" t="inlineStr">
         <is>
           <t>Mercury 8291</t>
         </is>
       </c>
-      <c r="C131" s="42" t="n">
+      <c r="C132" s="50" t="n">
         <v>20000</v>
       </c>
-      <c r="D131" s="50" t="inlineStr">
+      <c r="D132" s="41" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="I131" s="32" t="inlineStr">
+      <c r="I132" s="32" t="inlineStr">
         <is>
           <t>ASK: inventory purchase vs other. Do not add to sold Cost until named (avoid double count).</t>
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="32" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="32" t="inlineStr">
         <is>
           <t>Fortuna remaining 2025 (excl. seals $13,000 already on row 73)</t>
         </is>
       </c>
-      <c r="C132" s="42" t="n">
+      <c r="C133" s="50" t="n">
         <v>85000</v>
       </c>
     </row>
-    <row r="133"/>
-    <row r="134">
-      <c r="A134" s="43" t="inlineStr">
-        <is>
-          <t>2025 Mercury 8291 — Books sold to Aquinas Hobor (LOCKED)</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="44" t="inlineStr">
-        <is>
-          <t>Books sold to Aquinas Hobor (titles TBD)</t>
-        </is>
-      </c>
-      <c r="B135" s="44" t="inlineStr">
-        <is>
-          <t>Aquinas Hobor</t>
-        </is>
-      </c>
-      <c r="C135" s="44" t="n"/>
-      <c r="D135" s="44" t="n"/>
-      <c r="E135" s="44" t="inlineStr">
-        <is>
-          <t>Aquinas Hobor</t>
-        </is>
-      </c>
-      <c r="F135" s="45" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G135" s="51" t="n">
-        <v>45692</v>
-      </c>
-      <c r="H135" s="44">
-        <f>IF(C135="","",F135-C135)</f>
-        <v/>
-      </c>
-      <c r="I135" s="44" t="inlineStr">
-        <is>
-          <t>LOCKED 2026-09-20: books sold to Aquinas. $1,000 cash on EPGC Art Sales February. Cost / titles TBD — not in Income I8 until Cost. Distinct from 2022 Saharan bracelets. Not tax advice.</t>
-        </is>
-      </c>
-    </row>
+    <row r="134"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6848,15 +6832,15 @@
   <sheetData>
     <row r="1"/>
     <row r="2">
-      <c r="A2" s="52" t="inlineStr">
+      <c r="A2" s="56" t="inlineStr">
         <is>
           <t>GCM Boards 2022</t>
         </is>
       </c>
-      <c r="B2" s="53" t="n"/>
-      <c r="C2" s="53" t="n"/>
-      <c r="D2" s="53" t="n"/>
-      <c r="E2" s="53" t="n"/>
+      <c r="B2" s="57" t="n"/>
+      <c r="C2" s="57" t="n"/>
+      <c r="D2" s="57" t="n"/>
+      <c r="E2" s="57" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -6959,15 +6943,15 @@
     </row>
     <row r="8"/>
     <row r="9">
-      <c r="A9" s="52" t="inlineStr">
+      <c r="A9" s="56" t="inlineStr">
         <is>
           <t>GCM Boards 2023</t>
         </is>
       </c>
-      <c r="B9" s="53" t="n"/>
-      <c r="C9" s="53" t="n"/>
-      <c r="D9" s="53" t="n"/>
-      <c r="E9" s="53" t="n"/>
+      <c r="B9" s="57" t="n"/>
+      <c r="C9" s="57" t="n"/>
+      <c r="D9" s="57" t="n"/>
+      <c r="E9" s="57" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -7008,10 +6992,10 @@
       <c r="C11" s="5" t="n">
         <v>3675</v>
       </c>
-      <c r="D11" s="54" t="n">
+      <c r="D11" s="58" t="n">
         <v>3675</v>
       </c>
-      <c r="E11" s="54" t="n">
+      <c r="E11" s="58" t="n">
         <v>3675</v>
       </c>
     </row>
@@ -7053,15 +7037,15 @@
     </row>
     <row r="14"/>
     <row r="15">
-      <c r="A15" s="52" t="inlineStr">
+      <c r="A15" s="56" t="inlineStr">
         <is>
           <t>GCM Boards 2024</t>
         </is>
       </c>
-      <c r="B15" s="53" t="n"/>
-      <c r="C15" s="53" t="n"/>
-      <c r="D15" s="53" t="n"/>
-      <c r="E15" s="53" t="n"/>
+      <c r="B15" s="57" t="n"/>
+      <c r="C15" s="57" t="n"/>
+      <c r="D15" s="57" t="n"/>
+      <c r="E15" s="57" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -7102,10 +7086,10 @@
       <c r="C17" s="5" t="n">
         <v>4050</v>
       </c>
-      <c r="D17" s="54" t="n">
+      <c r="D17" s="58" t="n">
         <v>4050</v>
       </c>
-      <c r="E17" s="54" t="n">
+      <c r="E17" s="58" t="n">
         <v>4050</v>
       </c>
     </row>
@@ -7147,11 +7131,11 @@
     </row>
     <row r="20">
       <c r="A20" s="22" t="n"/>
-      <c r="B20" s="55" t="n"/>
+      <c r="B20" s="59" t="n"/>
     </row>
     <row r="21"/>
     <row r="22">
-      <c r="A22" s="56" t="inlineStr">
+      <c r="A22" s="60" t="inlineStr">
         <is>
           <t>GCM Boards 2025</t>
         </is>
@@ -7190,16 +7174,16 @@
           <t>GCM Board</t>
         </is>
       </c>
-      <c r="B24" s="57" t="n">
+      <c r="B24" s="61" t="n">
         <v>4100</v>
       </c>
-      <c r="C24" s="57" t="n">
+      <c r="C24" s="61" t="n">
         <v>9200</v>
       </c>
-      <c r="D24" s="57" t="n">
+      <c r="D24" s="61" t="n">
         <v>4100</v>
       </c>
-      <c r="E24" s="57" t="n">
+      <c r="E24" s="61" t="n">
         <v>4100</v>
       </c>
     </row>
@@ -7313,80 +7297,80 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="56" t="inlineStr">
+      <c r="A5" s="60" t="inlineStr">
         <is>
           <t>Coinbase (ACH from Mercury 8291)</t>
         </is>
       </c>
-      <c r="B5" s="58" t="inlineStr">
+      <c r="B5" s="44" t="inlineStr">
         <is>
           <t>Investment transfers — not EPGC Art Sales, not advisory. Distinct from Coinbase 6108 card.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="59" t="inlineStr"/>
-      <c r="B6" s="59" t="inlineStr">
+      <c r="A6" s="62" t="inlineStr"/>
+      <c r="B6" s="62" t="inlineStr">
         <is>
           <t>JAN</t>
         </is>
       </c>
-      <c r="C6" s="59" t="inlineStr">
+      <c r="C6" s="62" t="inlineStr">
         <is>
           <t>FEB</t>
         </is>
       </c>
-      <c r="D6" s="59" t="inlineStr">
+      <c r="D6" s="62" t="inlineStr">
         <is>
           <t>MAR</t>
         </is>
       </c>
-      <c r="E6" s="59" t="inlineStr">
+      <c r="E6" s="62" t="inlineStr">
         <is>
           <t>APR</t>
         </is>
       </c>
-      <c r="F6" s="59" t="inlineStr">
+      <c r="F6" s="62" t="inlineStr">
         <is>
           <t>MAY</t>
         </is>
       </c>
-      <c r="G6" s="59" t="inlineStr">
+      <c r="G6" s="62" t="inlineStr">
         <is>
           <t>JUN</t>
         </is>
       </c>
-      <c r="H6" s="59" t="inlineStr">
+      <c r="H6" s="62" t="inlineStr">
         <is>
           <t>JUL</t>
         </is>
       </c>
-      <c r="I6" s="59" t="inlineStr">
+      <c r="I6" s="62" t="inlineStr">
         <is>
           <t>AUG</t>
         </is>
       </c>
-      <c r="J6" s="59" t="inlineStr">
+      <c r="J6" s="62" t="inlineStr">
         <is>
           <t>SEP</t>
         </is>
       </c>
-      <c r="K6" s="59" t="inlineStr">
+      <c r="K6" s="62" t="inlineStr">
         <is>
           <t>OCT</t>
         </is>
       </c>
-      <c r="L6" s="59" t="inlineStr">
+      <c r="L6" s="62" t="inlineStr">
         <is>
           <t>NOV</t>
         </is>
       </c>
-      <c r="M6" s="59" t="inlineStr">
+      <c r="M6" s="62" t="inlineStr">
         <is>
           <t>DEC</t>
         </is>
       </c>
-      <c r="N6" s="59" t="inlineStr">
+      <c r="N6" s="62" t="inlineStr">
         <is>
           <t>2025 NET</t>
         </is>
@@ -7422,19 +7406,19 @@
       <c r="I7" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="J7" s="60" t="n">
+      <c r="J7" s="63" t="n">
         <v>-9000</v>
       </c>
-      <c r="K7" s="60" t="n">
+      <c r="K7" s="63" t="n">
         <v>-10000</v>
       </c>
-      <c r="L7" s="60" t="n">
+      <c r="L7" s="63" t="n">
         <v>-35000</v>
       </c>
-      <c r="M7" s="60" t="n">
+      <c r="M7" s="63" t="n">
         <v>-5000</v>
       </c>
-      <c r="N7" s="61">
+      <c r="N7" s="64">
         <f>SUM(B7:M7)</f>
         <v/>
       </c>
@@ -7478,10 +7462,10 @@
       <c r="L8" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="M8" s="60" t="n">
+      <c r="M8" s="63" t="n">
         <v>8000</v>
       </c>
-      <c r="N8" s="61">
+      <c r="N8" s="64">
         <f>SUM(B8:M8)</f>
         <v/>
       </c>
@@ -7516,26 +7500,26 @@
       <c r="I9" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="J9" s="45" t="n">
+      <c r="J9" s="42" t="n">
         <v>-9000</v>
       </c>
-      <c r="K9" s="45" t="n">
+      <c r="K9" s="42" t="n">
         <v>-10000</v>
       </c>
-      <c r="L9" s="45" t="n">
+      <c r="L9" s="42" t="n">
         <v>-35000</v>
       </c>
-      <c r="M9" s="45" t="n">
+      <c r="M9" s="42" t="n">
         <v>3000</v>
       </c>
-      <c r="N9" s="61">
+      <c r="N9" s="64">
         <f>SUM(B9:M9)</f>
         <v/>
       </c>
     </row>
     <row r="10"/>
     <row r="11">
-      <c r="A11" s="62" t="inlineStr">
+      <c r="A11" s="65" t="inlineStr">
         <is>
           <t>2025: funded $59,000.00 / returned $8,000.00 / net $-51,000.00 off the EPGC operating account. Not income, not an expense. Not tax advice.</t>
         </is>
@@ -7561,140 +7545,140 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="41" t="inlineStr">
-        <is>
-          <t>ASK — remaining Mercury 8291 questions. Q6 consultant, Q7 Wise expertise write-ups, Q8 pass-through, Q9 Aquinas books LOCKED 2026-09-20. Not tax advice.</t>
+      <c r="A1" s="49" t="inlineStr">
+        <is>
+          <t>ASK — remaining Mercury 8291 questions. Q6 consultant, Q7 Wise expertise, Q8 pass-through, Q9 Aquinas books LOCKED (green). Q1/Q2 mixed pattern CONFIRMED, dollars unallocated (yellow). Not tax advice.</t>
         </is>
       </c>
     </row>
     <row r="2"/>
     <row r="3">
-      <c r="A3" s="59" t="inlineStr">
+      <c r="A3" s="62" t="inlineStr">
         <is>
           <t>Question</t>
         </is>
       </c>
-      <c r="B3" s="59" t="inlineStr">
+      <c r="B3" s="62" t="inlineStr">
         <is>
           <t>What I need</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="63" t="inlineStr">
-        <is>
-          <t>1. EOEB LLC remainder after mosaics</t>
-        </is>
-      </c>
-      <c r="B4" s="64" t="inlineStr">
-        <is>
-          <t>$130,270.00 of EOEB IN is not the $105,000 mosaics sale and not the $565.75 Wise reimbursement. Invoice / MAKE A PAYMENT pattern. Book as art advisory (EPGC Consultant) or as more art sales? Jan 16 $1,000 might be the Canosan horse (sold to Erdal $1,000 on Art Sales) — yes/no?</t>
+      <c r="A4" s="66" t="inlineStr">
+        <is>
+          <t>1. EOEB LLC remainder after mosaics — MIXED PATTERN CONFIRMED, dollars unallocated</t>
+        </is>
+      </c>
+      <c r="B4" s="45" t="inlineStr">
+        <is>
+          <t>$130,270.00 of EOEB IN is not mosaics $105,000 and not Wise reimburse $565.75. User 2026-09-20: EOEB is mixed art sales AND advisory/consultant fees. Do NOT dump this remainder onto Consultant or Art Sales. Invoice-level split still ASK. Jan 16 $1,000 Canosan-horse question STILL OPEN (Art Sales horse is to Erdal; this cash is EOEB).</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="63" t="inlineStr">
-        <is>
-          <t>2. L5 (all seven invoices)</t>
-        </is>
-      </c>
-      <c r="B5" s="64" t="inlineStr">
-        <is>
-          <t>$87,396.32. Same Auto-Routing Request or Invoice Payment pattern as EOEB. Advisory fees, art sales, or mixed? The 7/15 $50,000 lands the same week as Aysel $50k and Fortuna $45k.</t>
+      <c r="A5" s="66" t="inlineStr">
+        <is>
+          <t>2. L5 (all seven invoices) — MIXED PATTERN CONFIRMED, dollars unallocated</t>
+        </is>
+      </c>
+      <c r="B5" s="45" t="inlineStr">
+        <is>
+          <t>$87,396.32. User 2026-09-20: L5 is mixed art sales AND advisory/consultant fees. Do NOT dump onto Consultant or Art Sales. Invoice-level split still ASK. The 7/15 $50,000 still sits in the Aysel $50k / Fortuna $45k week.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="63" t="inlineStr">
+      <c r="A6" s="66" t="inlineStr">
         <is>
           <t>3. Fortuna / Erdal Dere OUT after seals</t>
         </is>
       </c>
-      <c r="B6" s="64" t="inlineStr">
+      <c r="B6" s="45" t="inlineStr">
         <is>
           <t>$85,000.00 after the 1/8 $13,000 seals COGS (5/9 $20k, 7/21 $45k, 8/15 $20k). Inventory purchases (object names) or something else?</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="63" t="inlineStr">
+      <c r="A7" s="66" t="inlineStr">
         <is>
           <t>4. Erdal Dere IN</t>
         </is>
       </c>
-      <c r="B7" s="64" t="inlineStr">
+      <c r="B7" s="45" t="inlineStr">
         <is>
           <t>$57,000.00 (7/24 $26k, 10/9 $25k, 11/7 $6k ‘FORTUNA PAYMENT’). Sales to Erdal, refunds of Fortuna purchases, or other?</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="63" t="inlineStr">
+      <c r="A8" s="66" t="inlineStr">
         <is>
           <t>5. Aysel Dere $50,000 IN (7/18)</t>
         </is>
       </c>
-      <c r="B8" s="64" t="inlineStr">
+      <c r="B8" s="45" t="inlineStr">
         <is>
           <t>Sale, related-party transfer, or part of the mid-July Fortuna/L5 cluster?</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="65" t="inlineStr">
+      <c r="A9" s="67" t="inlineStr">
         <is>
           <t>6. David Aaron Limited $13,595 IN (6/24) — LOCKED consultant fee</t>
         </is>
       </c>
-      <c r="B9" s="66" t="inlineStr">
+      <c r="B9" s="68" t="inlineStr">
         <is>
           <t>CONFIRMED 2026-09-20: consultant fee, not a sale. Booked EPGC Consultant June $13,595 (peach). Not Art Sales. Not Income I8.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="65" t="inlineStr">
+      <c r="A10" s="67" t="inlineStr">
         <is>
           <t>7. Wise $334.17 (7/9) and $658.63 (10/30) — LOCKED expertise write-ups</t>
         </is>
       </c>
-      <c r="B10" s="66" t="inlineStr">
+      <c r="B10" s="68" t="inlineStr">
         <is>
           <t>CONFIRMED 2026-09-20: business expenses (expertise write-ups). Booked EPGC Consultant Fees July $334.17 + October $658.63 = $992.80. Not COGS. Distinct from Dec Wise $565.75 reimbursed by EOEB (still not P&amp;L).</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="65" t="inlineStr">
+      <c r="A11" s="67" t="inlineStr">
         <is>
           <t>8. Jack Koziol &amp; Tracy Hoffman $150,000 IN (10/20) / Ariadne Demirjian $150,000 OUT (10/21) — LOCKED pass-through</t>
         </is>
       </c>
-      <c r="B11" s="66" t="inlineStr">
+      <c r="B11" s="68" t="inlineStr">
         <is>
           <t>CONFIRMED 2026-09-20: pass-through, not P&amp;L. Not a sale, not a purchase, not COGS, not Consultant.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="65" t="inlineStr">
-        <is>
-          <t>9. Aquinas Hobor $1,000 IN (2/4) — LOCKED books sold</t>
-        </is>
-      </c>
-      <c r="B12" s="66" t="inlineStr">
-        <is>
-          <t>CONFIRMED 2026-09-20: books sold to Aquinas. Booked EPGC Art Sales February $1,000 (peach). Cost / titles TBD — not in Income I8 until Cost. Distinct from 2022 Saharan bracelets.</t>
+      <c r="A12" s="67" t="inlineStr">
+        <is>
+          <t>9. Aquinas Hobor $1,000 IN (2/4) — LOCKED book sale</t>
+        </is>
+      </c>
+      <c r="B12" s="68" t="inlineStr">
+        <is>
+          <t>CONFIRMED 2026-09-20: book SALE. Hits EPGC Art Sales February +$1,000 (Feb $136,000; matched cash $150,000). Art Sales register: Books (titles TBD) to Aquinas Hobor, Sale Price $1,000, Sale Date 2025-02-04, Cost TBD. Not in Income I8 until Cost (same as Sale 6428).</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="63" t="inlineStr">
+      <c r="A13" s="66" t="inlineStr">
         <is>
           <t>10. Mosaics Cost $90,000 vs Mercury $50,000</t>
         </is>
       </c>
-      <c r="B13" s="64" t="inlineStr">
+      <c r="B13" s="45" t="inlineStr">
         <is>
           <t>Plutus &amp; Mnemosyne paid $50,000 in February. Where is the other $40,000 of Cost (other account / 2024 / still owed)?</t>
         </is>
@@ -7702,141 +7686,141 @@
     </row>
     <row r="14"/>
     <row r="15">
-      <c r="A15" s="59" t="inlineStr">
+      <c r="A15" s="62" t="inlineStr">
         <is>
           <t>LOCKED / MATCHED this pass (do not recast without saying so)</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="44" t="inlineStr">
+      <c r="A16" s="39" t="inlineStr">
         <is>
           <t>Coinbase ACH net</t>
         </is>
       </c>
-      <c r="B16" s="44" t="inlineStr">
+      <c r="B16" s="39" t="inlineStr">
         <is>
           <t>$-51,000.00  (OUT $-59,000.00 / IN $8,000.00) — Investments tab, not EPGC</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="44" t="inlineStr">
+      <c r="A17" s="39" t="inlineStr">
         <is>
           <t>Newstar Jewelers</t>
         </is>
       </c>
-      <c r="B17" s="44" t="inlineStr">
+      <c r="B17" s="39" t="inlineStr">
         <is>
           <t>$23,581.00 jewelry fabrication COGS (10/14 $8,000 + 11/12 $8,000 + 12/24 $7,581)</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="44" t="inlineStr">
+      <c r="A18" s="39" t="inlineStr">
         <is>
           <t>Berk sales</t>
         </is>
       </c>
-      <c r="B18" s="44" t="inlineStr">
+      <c r="B18" s="39" t="inlineStr">
         <is>
           <t>$14,000 seals (1/10) + $30,000 lots (2/7) = $44,000 Art Sales</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="44" t="inlineStr">
+      <c r="A19" s="39" t="inlineStr">
         <is>
           <t>Mosaics</t>
         </is>
       </c>
-      <c r="B19" s="44" t="inlineStr">
+      <c r="B19" s="39" t="inlineStr">
         <is>
           <t>EOEB $105,000 sale (2/21) / Plutus $50,000 of $90,000 Cost</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="44" t="inlineStr">
+      <c r="A20" s="39" t="inlineStr">
         <is>
           <t>BoA 9922 draws</t>
         </is>
       </c>
-      <c r="B20" s="44" t="inlineStr">
+      <c r="B20" s="39" t="inlineStr">
         <is>
           <t>$261,172.00 owner transfer — not P&amp;L</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="44" t="inlineStr">
+      <c r="A21" s="39" t="inlineStr">
         <is>
           <t>Wise/EOEB 12/2</t>
         </is>
       </c>
-      <c r="B21" s="44" t="inlineStr">
+      <c r="B21" s="39" t="inlineStr">
         <is>
           <t>$565.75 reimbursed — not income, not expense</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="44" t="inlineStr">
+      <c r="A22" s="39" t="inlineStr">
         <is>
           <t>$10 test wires</t>
         </is>
       </c>
-      <c r="B22" s="44" t="inlineStr">
+      <c r="B22" s="39" t="inlineStr">
         <is>
           <t>Jamal Rifai / EPGC / Plutus tests — not P&amp;L</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="44" t="inlineStr">
+      <c r="A23" s="39" t="inlineStr">
         <is>
           <t>David Aaron Limited</t>
         </is>
       </c>
-      <c r="B23" s="44" t="inlineStr">
+      <c r="B23" s="39" t="inlineStr">
         <is>
           <t>$13,595 (6/24) consultant fee → EPGC Consultant June. Not a sale.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="44" t="inlineStr">
+      <c r="A24" s="39" t="inlineStr">
         <is>
           <t>Koziol / Ariadne</t>
         </is>
       </c>
-      <c r="B24" s="44" t="inlineStr">
+      <c r="B24" s="39" t="inlineStr">
         <is>
           <t>$150,000 IN 10/20 + $150,000 OUT 10/21 LOCKED pass-through — not P&amp;L</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="44" t="inlineStr">
+      <c r="A25" s="39" t="inlineStr">
         <is>
           <t>Wise expertise write-ups</t>
         </is>
       </c>
-      <c r="B25" s="44" t="inlineStr">
+      <c r="B25" s="39" t="inlineStr">
         <is>
           <t>$334.17 (7/9) + $658.63 (10/30) = $992.80 → EPGC Consultant Fees expense. Dec $565.75 still reimbursed / not P&amp;L.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="44" t="inlineStr">
+      <c r="A26" s="39" t="inlineStr">
         <is>
           <t>Aquinas Hobor books</t>
         </is>
       </c>
-      <c r="B26" s="44" t="inlineStr">
-        <is>
-          <t>$1,000 IN 2/4 LOCKED books sold → EPGC Art Sales February. Cost / titles TBD (not in I8 until Cost).</t>
+      <c r="B26" s="39" t="inlineStr">
+        <is>
+          <t>$1,000 IN 2/4 LOCKED book sale → EPGC Art Sales February +$1,000 (Feb $136,000; matched cash $150,000). Cost / titles TBD (not in I8 until Cost, same as Sale 6428).</t>
         </is>
       </c>
     </row>
@@ -7869,7 +7853,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="67" t="inlineStr">
+      <c r="A1" s="69" t="inlineStr">
         <is>
           <t>Mercury Checking 8291 — EPGC LLC (Choice Financial) 2025. 64 unique cash transactions. Coinbase ACH = investment. Newstar = jewelry COGS on intaglios/gems/scarabs. BoA 9922 draws and Koziol/Ariadne $150k are LOCKED not-P&amp;L (pass-through / owner transfer). David Aaron $13,595 is LOCKED EPGC Consultant (June). Wise $334.17 + $658.63 are LOCKED EPGC Consultant Fees (expertise write-ups). Aquinas Hobor $1,000 (2/4) is LOCKED books sold (EPGC Art Sales February; Cost TBD). Not tax advice.</t>
         </is>
@@ -7877,74 +7861,74 @@
     </row>
     <row r="2"/>
     <row r="3">
-      <c r="A3" s="68" t="inlineStr">
+      <c r="A3" s="70" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B3" s="68" t="inlineStr">
+      <c r="B3" s="70" t="inlineStr">
         <is>
           <t>Counterparty</t>
         </is>
       </c>
-      <c r="C3" s="68" t="inlineStr">
+      <c r="C3" s="70" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="D3" s="68" t="inlineStr">
+      <c r="D3" s="70" t="inlineStr">
         <is>
           <t>Direction</t>
         </is>
       </c>
-      <c r="E3" s="68" t="inlineStr">
+      <c r="E3" s="70" t="inlineStr">
         <is>
           <t>Bucket</t>
         </is>
       </c>
-      <c r="F3" s="68" t="inlineStr">
+      <c r="F3" s="70" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G3" s="68" t="inlineStr">
+      <c r="G3" s="70" t="inlineStr">
         <is>
           <t>Deal / object</t>
         </is>
       </c>
-      <c r="H3" s="68" t="inlineStr">
+      <c r="H3" s="70" t="inlineStr">
         <is>
           <t>Hits EPGC Art Sales?</t>
         </is>
       </c>
-      <c r="I3" s="68" t="inlineStr">
+      <c r="I3" s="70" t="inlineStr">
         <is>
           <t>Hits EPGC Consultant?</t>
         </is>
       </c>
-      <c r="J3" s="68" t="inlineStr">
+      <c r="J3" s="70" t="inlineStr">
         <is>
           <t>Monarch category</t>
         </is>
       </c>
-      <c r="K3" s="68" t="inlineStr">
+      <c r="K3" s="70" t="inlineStr">
         <is>
           <t>Original statement</t>
         </is>
       </c>
-      <c r="L3" s="68" t="inlineStr">
+      <c r="L3" s="70" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="58" t="inlineStr">
+      <c r="A4" s="44" t="inlineStr">
         <is>
           <t>2025-01-08</t>
         </is>
       </c>
-      <c r="B4" s="58" t="inlineStr">
+      <c r="B4" s="44" t="inlineStr">
         <is>
           <t>Erdal Dere (Fortuna)</t>
         </is>
@@ -7952,42 +7936,42 @@
       <c r="C4" s="10" t="n">
         <v>-13000</v>
       </c>
-      <c r="D4" s="58" t="inlineStr">
+      <c r="D4" s="44" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E4" s="69" t="inlineStr">
+      <c r="E4" s="71" t="inlineStr">
         <is>
           <t>ART_PURCHASE</t>
         </is>
       </c>
-      <c r="F4" s="44" t="inlineStr">
+      <c r="F4" s="39" t="inlineStr">
         <is>
           <t>MATCHED</t>
         </is>
       </c>
-      <c r="G4" s="58" t="inlineStr">
+      <c r="G4" s="44" t="inlineStr">
         <is>
           <t>A Collection of Seals — COGS</t>
         </is>
       </c>
-      <c r="H4" s="58" t="inlineStr">
+      <c r="H4" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I4" s="58" t="inlineStr">
+      <c r="I4" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J4" s="58" t="inlineStr">
+      <c r="J4" s="44" t="inlineStr">
         <is>
           <t xml:space="preserve">Business Investment </t>
         </is>
       </c>
-      <c r="K4" s="58" t="inlineStr">
+      <c r="K4" s="44" t="inlineStr">
         <is>
           <t>Merchant name: Erdal Dere (Fortuna)</t>
         </is>
@@ -7999,55 +7983,55 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="58" t="inlineStr">
+      <c r="A5" s="44" t="inlineStr">
         <is>
           <t>2025-01-10</t>
         </is>
       </c>
-      <c r="B5" s="58" t="inlineStr">
+      <c r="B5" s="44" t="inlineStr">
         <is>
           <t>HARLAN J BERK LTD</t>
         </is>
       </c>
-      <c r="C5" s="45" t="n">
+      <c r="C5" s="42" t="n">
         <v>14000</v>
       </c>
-      <c r="D5" s="58" t="inlineStr">
+      <c r="D5" s="44" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E5" s="70" t="inlineStr">
+      <c r="E5" s="72" t="inlineStr">
         <is>
           <t>ART_SALE</t>
         </is>
       </c>
-      <c r="F5" s="44" t="inlineStr">
+      <c r="F5" s="39" t="inlineStr">
         <is>
           <t>MATCHED</t>
         </is>
       </c>
-      <c r="G5" s="58" t="inlineStr">
+      <c r="G5" s="44" t="inlineStr">
         <is>
           <t>A Collection of Seals — Sale Price</t>
         </is>
       </c>
-      <c r="H5" s="58" t="inlineStr">
+      <c r="H5" s="44" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="I5" s="58" t="inlineStr">
+      <c r="I5" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J5" s="58" t="inlineStr">
+      <c r="J5" s="44" t="inlineStr">
         <is>
           <t>Business Income</t>
         </is>
       </c>
-      <c r="K5" s="58" t="inlineStr">
+      <c r="K5" s="44" t="inlineStr">
         <is>
           <t>Incoming Wire; Merchant name: HARLAN J BERK LTD</t>
         </is>
@@ -8059,72 +8043,72 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="58" t="inlineStr">
+      <c r="A6" s="44" t="inlineStr">
         <is>
           <t>2025-01-16</t>
         </is>
       </c>
-      <c r="B6" s="58" t="inlineStr">
+      <c r="B6" s="44" t="inlineStr">
         <is>
           <t>EOEB LLC</t>
         </is>
       </c>
-      <c r="C6" s="71" t="n">
+      <c r="C6" s="73" t="n">
         <v>1000</v>
       </c>
-      <c r="D6" s="58" t="inlineStr">
+      <c r="D6" s="44" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E6" s="72" t="inlineStr">
+      <c r="E6" s="40" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="F6" s="72" t="inlineStr">
+      <c r="F6" s="40" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G6" s="58" t="inlineStr">
-        <is>
-          <t>EOEB $1,000 — Canosan horse vs advisory</t>
-        </is>
-      </c>
-      <c r="H6" s="58" t="inlineStr">
+      <c r="G6" s="44" t="inlineStr">
+        <is>
+          <t>EOEB $1,000 — Canosan horse vs advisory (STILL OPEN)</t>
+        </is>
+      </c>
+      <c r="H6" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I6" s="58" t="inlineStr">
+      <c r="I6" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J6" s="58" t="inlineStr">
+      <c r="J6" s="44" t="inlineStr">
         <is>
           <t>Business Income</t>
         </is>
       </c>
-      <c r="K6" s="58" t="inlineStr">
+      <c r="K6" s="44" t="inlineStr">
         <is>
           <t>Incoming Wire; MAKE A PAYMENT; Merchant name: EOEB LLC</t>
         </is>
       </c>
       <c r="L6" s="14" t="inlineStr">
         <is>
-          <t>Art Sales has Canosan Terracotta Horse to Erdal $1,000. This cash is EOEB, not Erdal. Sale or advisory invoice?</t>
+          <t>STILL OPEN after mixed-pattern confirm. Art Sales has Canosan Terracotta Horse to Erdal $1,000. This cash is EOEB, not Erdal. Sale of the horse, advisory invoice, or other? Not allocated.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="58" t="inlineStr">
+      <c r="A7" s="44" t="inlineStr">
         <is>
           <t>2025-02-04</t>
         </is>
       </c>
-      <c r="B7" s="58" t="inlineStr">
+      <c r="B7" s="44" t="inlineStr">
         <is>
           <t>Bank of America - Checking ••9922</t>
         </is>
@@ -8132,42 +8116,42 @@
       <c r="C7" s="10" t="n">
         <v>-25000</v>
       </c>
-      <c r="D7" s="58" t="inlineStr">
+      <c r="D7" s="44" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E7" s="73" t="inlineStr">
+      <c r="E7" s="74" t="inlineStr">
         <is>
           <t>TRANSFER</t>
         </is>
       </c>
-      <c r="F7" s="44" t="inlineStr">
+      <c r="F7" s="39" t="inlineStr">
         <is>
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="G7" s="58" t="inlineStr">
+      <c r="G7" s="44" t="inlineStr">
         <is>
           <t>Owner transfer to BoA 9922</t>
         </is>
       </c>
-      <c r="H7" s="58" t="inlineStr">
+      <c r="H7" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I7" s="58" t="inlineStr">
+      <c r="I7" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J7" s="58" t="inlineStr">
+      <c r="J7" s="44" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K7" s="58" t="inlineStr">
+      <c r="K7" s="44" t="inlineStr">
         <is>
           <t>Transfer from Mercury to another bank account; Merchant name: Bank of America - Checking ••9922</t>
         </is>
@@ -8179,115 +8163,115 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="58" t="inlineStr">
+      <c r="A8" s="44" t="inlineStr">
         <is>
           <t>2025-02-04</t>
         </is>
       </c>
-      <c r="B8" s="58" t="inlineStr">
+      <c r="B8" s="44" t="inlineStr">
         <is>
           <t>AQUINAS HOBOR</t>
         </is>
       </c>
-      <c r="C8" s="45" t="n">
+      <c r="C8" s="42" t="n">
         <v>1000</v>
       </c>
-      <c r="D8" s="58" t="inlineStr">
+      <c r="D8" s="44" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E8" s="70" t="inlineStr">
+      <c r="E8" s="72" t="inlineStr">
         <is>
           <t>ART_SALE</t>
         </is>
       </c>
-      <c r="F8" s="44" t="inlineStr">
+      <c r="F8" s="39" t="inlineStr">
         <is>
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="G8" s="58" t="inlineStr">
-        <is>
-          <t>Books sold to Aquinas Hobor — Sale Price</t>
-        </is>
-      </c>
-      <c r="H8" s="58" t="inlineStr">
+      <c r="G8" s="44" t="inlineStr">
+        <is>
+          <t>Books (titles TBD) — Sale Price</t>
+        </is>
+      </c>
+      <c r="H8" s="44" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="I8" s="58" t="inlineStr">
+      <c r="I8" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J8" s="58" t="inlineStr">
+      <c r="J8" s="44" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K8" s="58" t="inlineStr">
+      <c r="K8" s="44" t="inlineStr">
         <is>
           <t>AQUINAS HOBOR; SENDER; 770699534; Merchant name: AQUINAS HOBOR</t>
         </is>
       </c>
       <c r="L8" s="14" t="inlineStr">
         <is>
-          <t>User 2026-09-20: books sold to Aquinas. Hits EPGC Art Sales February $1,000. Cost / titles TBD (not in I8 net until Cost). Distinct from 2022 Saharan bracelets sale.</t>
+          <t>User 2026-09-20: book SALE to Aquinas Hobor. Hits EPGC Art Sales February +$1,000. Art Sales register: Books (titles TBD), Cost TBD. Not in Income I8 until Cost is known (same as Sale 6428).</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="58" t="inlineStr">
+      <c r="A9" s="44" t="inlineStr">
         <is>
           <t>2025-02-07</t>
         </is>
       </c>
-      <c r="B9" s="58" t="inlineStr">
+      <c r="B9" s="44" t="inlineStr">
         <is>
           <t>HARLAN J BERK LTD</t>
         </is>
       </c>
-      <c r="C9" s="45" t="n">
+      <c r="C9" s="42" t="n">
         <v>30000</v>
       </c>
-      <c r="D9" s="58" t="inlineStr">
+      <c r="D9" s="44" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E9" s="70" t="inlineStr">
+      <c r="E9" s="72" t="inlineStr">
         <is>
           <t>ART_SALE</t>
         </is>
       </c>
-      <c r="F9" s="44" t="inlineStr">
+      <c r="F9" s="39" t="inlineStr">
         <is>
           <t>MATCHED</t>
         </is>
       </c>
-      <c r="G9" s="58" t="inlineStr">
+      <c r="G9" s="44" t="inlineStr">
         <is>
           <t>Berk lots lump Sale Price $30,000</t>
         </is>
       </c>
-      <c r="H9" s="58" t="inlineStr">
+      <c r="H9" s="44" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="I9" s="58" t="inlineStr">
+      <c r="I9" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J9" s="58" t="inlineStr">
+      <c r="J9" s="44" t="inlineStr">
         <is>
           <t>Business Income</t>
         </is>
       </c>
-      <c r="K9" s="58" t="inlineStr">
+      <c r="K9" s="44" t="inlineStr">
         <is>
           <t>Incoming Wire; PER ARB; Merchant name: HARLAN J BERK LTD</t>
         </is>
@@ -8299,12 +8283,12 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="58" t="inlineStr">
+      <c r="A10" s="44" t="inlineStr">
         <is>
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="B10" s="58" t="inlineStr">
+      <c r="B10" s="44" t="inlineStr">
         <is>
           <t>Jamal M Rifai</t>
         </is>
@@ -8312,42 +8296,42 @@
       <c r="C10" s="10" t="n">
         <v>-10</v>
       </c>
-      <c r="D10" s="58" t="inlineStr">
+      <c r="D10" s="44" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E10" s="73" t="inlineStr">
+      <c r="E10" s="74" t="inlineStr">
         <is>
           <t>TEST</t>
         </is>
       </c>
-      <c r="F10" s="44" t="inlineStr">
+      <c r="F10" s="39" t="inlineStr">
         <is>
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="G10" s="58" t="inlineStr">
+      <c r="G10" s="44" t="inlineStr">
         <is>
           <t>$10 test wire to Jamal M. Rifai</t>
         </is>
       </c>
-      <c r="H10" s="58" t="inlineStr">
+      <c r="H10" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I10" s="58" t="inlineStr">
+      <c r="I10" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J10" s="58" t="inlineStr">
+      <c r="J10" s="44" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K10" s="58" t="inlineStr">
+      <c r="K10" s="44" t="inlineStr">
         <is>
           <t>Merchant name: Jamal M Rifai</t>
         </is>
@@ -8359,12 +8343,12 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="58" t="inlineStr">
+      <c r="A11" s="44" t="inlineStr">
         <is>
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="B11" s="58" t="inlineStr">
+      <c r="B11" s="44" t="inlineStr">
         <is>
           <t>DDA/066196221</t>
         </is>
@@ -8372,42 +8356,42 @@
       <c r="C11" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="D11" s="58" t="inlineStr">
+      <c r="D11" s="44" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E11" s="73" t="inlineStr">
+      <c r="E11" s="74" t="inlineStr">
         <is>
           <t>TEST</t>
         </is>
       </c>
-      <c r="F11" s="44" t="inlineStr">
+      <c r="F11" s="39" t="inlineStr">
         <is>
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="G11" s="58" t="inlineStr">
+      <c r="G11" s="44" t="inlineStr">
         <is>
           <t>$10 test wire in</t>
         </is>
       </c>
-      <c r="H11" s="58" t="inlineStr">
+      <c r="H11" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I11" s="58" t="inlineStr">
+      <c r="I11" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J11" s="58" t="inlineStr">
+      <c r="J11" s="44" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K11" s="58" t="inlineStr">
+      <c r="K11" s="44" t="inlineStr">
         <is>
           <t>Incoming Wire; Merchant name: DDA/066196221</t>
         </is>
@@ -8419,55 +8403,55 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="58" t="inlineStr">
+      <c r="A12" s="44" t="inlineStr">
         <is>
           <t>2025-02-21</t>
         </is>
       </c>
-      <c r="B12" s="58" t="inlineStr">
+      <c r="B12" s="44" t="inlineStr">
         <is>
           <t>EOEB LLC</t>
         </is>
       </c>
-      <c r="C12" s="45" t="n">
+      <c r="C12" s="42" t="n">
         <v>105000</v>
       </c>
-      <c r="D12" s="58" t="inlineStr">
+      <c r="D12" s="44" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E12" s="70" t="inlineStr">
+      <c r="E12" s="72" t="inlineStr">
         <is>
           <t>ART_SALE</t>
         </is>
       </c>
-      <c r="F12" s="44" t="inlineStr">
+      <c r="F12" s="39" t="inlineStr">
         <is>
           <t>MATCHED</t>
         </is>
       </c>
-      <c r="G12" s="58" t="inlineStr">
+      <c r="G12" s="44" t="inlineStr">
         <is>
           <t>Three Ancient Mosaics — Sale Price</t>
         </is>
       </c>
-      <c r="H12" s="58" t="inlineStr">
+      <c r="H12" s="44" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="I12" s="58" t="inlineStr">
+      <c r="I12" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J12" s="58" t="inlineStr">
+      <c r="J12" s="44" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K12" s="58" t="inlineStr">
+      <c r="K12" s="44" t="inlineStr">
         <is>
           <t>Incoming Wire; MAKE A PAYMENT; Merchant name: EOEB LLC</t>
         </is>
@@ -8479,12 +8463,12 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="58" t="inlineStr">
+      <c r="A13" s="44" t="inlineStr">
         <is>
           <t>2025-02-24</t>
         </is>
       </c>
-      <c r="B13" s="58" t="inlineStr">
+      <c r="B13" s="44" t="inlineStr">
         <is>
           <t>Bank of America - Checking ••9922</t>
         </is>
@@ -8492,42 +8476,42 @@
       <c r="C13" s="10" t="n">
         <v>-90000</v>
       </c>
-      <c r="D13" s="58" t="inlineStr">
+      <c r="D13" s="44" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E13" s="73" t="inlineStr">
+      <c r="E13" s="74" t="inlineStr">
         <is>
           <t>TRANSFER</t>
         </is>
       </c>
-      <c r="F13" s="44" t="inlineStr">
+      <c r="F13" s="39" t="inlineStr">
         <is>
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="G13" s="58" t="inlineStr">
+      <c r="G13" s="44" t="inlineStr">
         <is>
           <t>Owner transfer to BoA 9922</t>
         </is>
       </c>
-      <c r="H13" s="58" t="inlineStr">
+      <c r="H13" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I13" s="58" t="inlineStr">
+      <c r="I13" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J13" s="58" t="inlineStr">
+      <c r="J13" s="44" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K13" s="58" t="inlineStr">
+      <c r="K13" s="44" t="inlineStr">
         <is>
           <t>Transfer from Mercury to another bank account; Merchant name: Bank of America - Checking ••9922</t>
         </is>
@@ -8539,12 +8523,12 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="58" t="inlineStr">
+      <c r="A14" s="44" t="inlineStr">
         <is>
           <t>2025-02-24</t>
         </is>
       </c>
-      <c r="B14" s="58" t="inlineStr">
+      <c r="B14" s="44" t="inlineStr">
         <is>
           <t>Jamal M Rifai</t>
         </is>
@@ -8552,42 +8536,42 @@
       <c r="C14" s="10" t="n">
         <v>-10</v>
       </c>
-      <c r="D14" s="58" t="inlineStr">
+      <c r="D14" s="44" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E14" s="73" t="inlineStr">
+      <c r="E14" s="74" t="inlineStr">
         <is>
           <t>TEST</t>
         </is>
       </c>
-      <c r="F14" s="44" t="inlineStr">
+      <c r="F14" s="39" t="inlineStr">
         <is>
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="G14" s="58" t="inlineStr">
+      <c r="G14" s="44" t="inlineStr">
         <is>
           <t>$10 test (Jamal or Plutus)</t>
         </is>
       </c>
-      <c r="H14" s="58" t="inlineStr">
+      <c r="H14" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I14" s="58" t="inlineStr">
+      <c r="I14" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J14" s="58" t="inlineStr">
+      <c r="J14" s="44" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K14" s="58" t="inlineStr">
+      <c r="K14" s="44" t="inlineStr">
         <is>
           <t>Merchant name: Jamal M Rifai</t>
         </is>
@@ -8599,12 +8583,12 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="58" t="inlineStr">
+      <c r="A15" s="44" t="inlineStr">
         <is>
           <t>2025-02-24</t>
         </is>
       </c>
-      <c r="B15" s="58" t="inlineStr">
+      <c r="B15" s="44" t="inlineStr">
         <is>
           <t>Plutus &amp; Mnemosyne, LLC</t>
         </is>
@@ -8612,42 +8596,42 @@
       <c r="C15" s="10" t="n">
         <v>-10</v>
       </c>
-      <c r="D15" s="58" t="inlineStr">
+      <c r="D15" s="44" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E15" s="73" t="inlineStr">
+      <c r="E15" s="74" t="inlineStr">
         <is>
           <t>TEST</t>
         </is>
       </c>
-      <c r="F15" s="44" t="inlineStr">
+      <c r="F15" s="39" t="inlineStr">
         <is>
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="G15" s="58" t="inlineStr">
+      <c r="G15" s="44" t="inlineStr">
         <is>
           <t>$10 test (Jamal or Plutus)</t>
         </is>
       </c>
-      <c r="H15" s="58" t="inlineStr">
+      <c r="H15" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I15" s="58" t="inlineStr">
+      <c r="I15" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J15" s="58" t="inlineStr">
+      <c r="J15" s="44" t="inlineStr">
         <is>
           <t xml:space="preserve">Business Investment </t>
         </is>
       </c>
-      <c r="K15" s="58" t="inlineStr">
+      <c r="K15" s="44" t="inlineStr">
         <is>
           <t>Merchant name: Plutus &amp; Mnemosyne, LLC</t>
         </is>
@@ -8659,12 +8643,12 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="58" t="inlineStr">
+      <c r="A16" s="44" t="inlineStr">
         <is>
           <t>2025-02-24</t>
         </is>
       </c>
-      <c r="B16" s="58" t="inlineStr">
+      <c r="B16" s="44" t="inlineStr">
         <is>
           <t>EPGC LLC</t>
         </is>
@@ -8672,42 +8656,42 @@
       <c r="C16" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="D16" s="58" t="inlineStr">
+      <c r="D16" s="44" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E16" s="73" t="inlineStr">
+      <c r="E16" s="74" t="inlineStr">
         <is>
           <t>TEST</t>
         </is>
       </c>
-      <c r="F16" s="44" t="inlineStr">
+      <c r="F16" s="39" t="inlineStr">
         <is>
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="G16" s="58" t="inlineStr">
+      <c r="G16" s="44" t="inlineStr">
         <is>
           <t>$10 test wire EPGC</t>
         </is>
       </c>
-      <c r="H16" s="58" t="inlineStr">
+      <c r="H16" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I16" s="58" t="inlineStr">
+      <c r="I16" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J16" s="58" t="inlineStr">
+      <c r="J16" s="44" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K16" s="58" t="inlineStr">
+      <c r="K16" s="44" t="inlineStr">
         <is>
           <t>Incoming Wire; Merchant name: EPGC LLC</t>
         </is>
@@ -8719,12 +8703,12 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="58" t="inlineStr">
+      <c r="A17" s="44" t="inlineStr">
         <is>
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="B17" s="58" t="inlineStr">
+      <c r="B17" s="44" t="inlineStr">
         <is>
           <t>Plutus &amp; Mnemosyne, LLC</t>
         </is>
@@ -8732,42 +8716,42 @@
       <c r="C17" s="10" t="n">
         <v>-49990</v>
       </c>
-      <c r="D17" s="58" t="inlineStr">
+      <c r="D17" s="44" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E17" s="69" t="inlineStr">
+      <c r="E17" s="71" t="inlineStr">
         <is>
           <t>ART_PURCHASE</t>
         </is>
       </c>
-      <c r="F17" s="44" t="inlineStr">
+      <c r="F17" s="39" t="inlineStr">
         <is>
           <t>MATCHED</t>
         </is>
       </c>
-      <c r="G17" s="58" t="inlineStr">
+      <c r="G17" s="44" t="inlineStr">
         <is>
           <t>Three Ancient Mosaics — partial COGS</t>
         </is>
       </c>
-      <c r="H17" s="58" t="inlineStr">
+      <c r="H17" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I17" s="58" t="inlineStr">
+      <c r="I17" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J17" s="58" t="inlineStr">
+      <c r="J17" s="44" t="inlineStr">
         <is>
           <t xml:space="preserve">Business Investment </t>
         </is>
       </c>
-      <c r="K17" s="58" t="inlineStr">
+      <c r="K17" s="44" t="inlineStr">
         <is>
           <t>Merchant name: Plutus &amp; Mnemosyne, LLC</t>
         </is>
@@ -8779,175 +8763,175 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="58" t="inlineStr">
+      <c r="A18" s="44" t="inlineStr">
         <is>
           <t>2025-03-10</t>
         </is>
       </c>
-      <c r="B18" s="58" t="inlineStr">
+      <c r="B18" s="44" t="inlineStr">
         <is>
           <t>EOEB LLC</t>
         </is>
       </c>
-      <c r="C18" s="71" t="n">
+      <c r="C18" s="73" t="n">
         <v>14000</v>
       </c>
-      <c r="D18" s="58" t="inlineStr">
+      <c r="D18" s="44" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E18" s="72" t="inlineStr">
+      <c r="E18" s="40" t="inlineStr">
         <is>
           <t>ADVISORY</t>
         </is>
       </c>
-      <c r="F18" s="72" t="inlineStr">
+      <c r="F18" s="40" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G18" s="58" t="inlineStr">
-        <is>
-          <t>EOEB — sale vs art advisory</t>
-        </is>
-      </c>
-      <c r="H18" s="58" t="inlineStr">
+      <c r="G18" s="44" t="inlineStr">
+        <is>
+          <t>EOEB — mixed unallocated (sale vs advisory)</t>
+        </is>
+      </c>
+      <c r="H18" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I18" s="58" t="inlineStr">
+      <c r="I18" s="44" t="inlineStr">
         <is>
           <t>no — ASK first</t>
         </is>
       </c>
-      <c r="J18" s="58" t="inlineStr">
+      <c r="J18" s="44" t="inlineStr">
         <is>
           <t>Business Income</t>
         </is>
       </c>
-      <c r="K18" s="58" t="inlineStr">
+      <c r="K18" s="44" t="inlineStr">
         <is>
           <t>Incoming Wire; MAKE A PAYMENT; Merchant name: EOEB LLC</t>
         </is>
       </c>
       <c r="L18" s="14" t="inlineStr">
         <is>
-          <t>Invoice / MAKE A PAYMENT. Not matched to an Art Sales object. Proposed advisory (Consultant) until you say otherwise.</t>
+          <t>User 2026-09-20: EOEB LLC mixed art sales AND advisory/consultant fees. Pattern confirmed; this invoice still unallocated. Do NOT dump EOEB remainder $130,270 onto Consultant or Art Sales. Invoice-level split still ASK.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="58" t="inlineStr">
+      <c r="A19" s="44" t="inlineStr">
         <is>
           <t>2025-05-01</t>
         </is>
       </c>
-      <c r="B19" s="58" t="inlineStr">
+      <c r="B19" s="44" t="inlineStr">
         <is>
           <t>EOEB LLC</t>
         </is>
       </c>
-      <c r="C19" s="71" t="n">
+      <c r="C19" s="73" t="n">
         <v>21000</v>
       </c>
-      <c r="D19" s="58" t="inlineStr">
+      <c r="D19" s="44" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E19" s="72" t="inlineStr">
+      <c r="E19" s="40" t="inlineStr">
         <is>
           <t>ADVISORY</t>
         </is>
       </c>
-      <c r="F19" s="72" t="inlineStr">
+      <c r="F19" s="40" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G19" s="58" t="inlineStr">
-        <is>
-          <t>EOEB — sale vs art advisory</t>
-        </is>
-      </c>
-      <c r="H19" s="58" t="inlineStr">
+      <c r="G19" s="44" t="inlineStr">
+        <is>
+          <t>EOEB — mixed unallocated (sale vs advisory)</t>
+        </is>
+      </c>
+      <c r="H19" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I19" s="58" t="inlineStr">
+      <c r="I19" s="44" t="inlineStr">
         <is>
           <t>no — ASK first</t>
         </is>
       </c>
-      <c r="J19" s="58" t="inlineStr">
+      <c r="J19" s="44" t="inlineStr">
         <is>
           <t>Business Income</t>
         </is>
       </c>
-      <c r="K19" s="58" t="inlineStr">
+      <c r="K19" s="44" t="inlineStr">
         <is>
           <t>Incoming Wire; MAKE A PAYMENT; Merchant name: EOEB LLC</t>
         </is>
       </c>
       <c r="L19" s="14" t="inlineStr">
         <is>
-          <t>Invoice / MAKE A PAYMENT. Proposed advisory until confirmed.</t>
+          <t>User 2026-09-20: EOEB LLC mixed art sales AND advisory/consultant fees. Pattern confirmed; this invoice still unallocated. Do NOT dump EOEB remainder $130,270 onto Consultant or Art Sales. Invoice-level split still ASK.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="58" t="inlineStr">
+      <c r="A20" s="44" t="inlineStr">
         <is>
           <t>2025-05-09</t>
         </is>
       </c>
-      <c r="B20" s="58" t="inlineStr">
+      <c r="B20" s="44" t="inlineStr">
         <is>
           <t>Erdal Dere (Fortuna)</t>
         </is>
       </c>
-      <c r="C20" s="71" t="n">
+      <c r="C20" s="73" t="n">
         <v>-20000</v>
       </c>
-      <c r="D20" s="58" t="inlineStr">
+      <c r="D20" s="44" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E20" s="69" t="inlineStr">
+      <c r="E20" s="71" t="inlineStr">
         <is>
           <t>ART_PURCHASE</t>
         </is>
       </c>
-      <c r="F20" s="72" t="inlineStr">
+      <c r="F20" s="40" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G20" s="58" t="inlineStr">
+      <c r="G20" s="44" t="inlineStr">
         <is>
           <t>Fortuna / Erdal — inventory vs other</t>
         </is>
       </c>
-      <c r="H20" s="58" t="inlineStr">
+      <c r="H20" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I20" s="58" t="inlineStr">
+      <c r="I20" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J20" s="58" t="inlineStr">
+      <c r="J20" s="44" t="inlineStr">
         <is>
           <t xml:space="preserve">Business Investment </t>
         </is>
       </c>
-      <c r="K20" s="58" t="inlineStr">
+      <c r="K20" s="44" t="inlineStr">
         <is>
           <t>Merchant name: Erdal Dere (Fortuna)</t>
         </is>
@@ -8959,235 +8943,235 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="58" t="inlineStr">
+      <c r="A21" s="44" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="B21" s="58" t="inlineStr">
+      <c r="B21" s="44" t="inlineStr">
         <is>
           <t>EOEB LLC</t>
         </is>
       </c>
-      <c r="C21" s="71" t="n">
+      <c r="C21" s="73" t="n">
         <v>16200</v>
       </c>
-      <c r="D21" s="58" t="inlineStr">
+      <c r="D21" s="44" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E21" s="72" t="inlineStr">
+      <c r="E21" s="40" t="inlineStr">
         <is>
           <t>ADVISORY</t>
         </is>
       </c>
-      <c r="F21" s="72" t="inlineStr">
+      <c r="F21" s="40" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G21" s="58" t="inlineStr">
-        <is>
-          <t>EOEB — sale vs art advisory</t>
-        </is>
-      </c>
-      <c r="H21" s="58" t="inlineStr">
+      <c r="G21" s="44" t="inlineStr">
+        <is>
+          <t>EOEB — mixed unallocated (sale vs advisory)</t>
+        </is>
+      </c>
+      <c r="H21" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I21" s="58" t="inlineStr">
+      <c r="I21" s="44" t="inlineStr">
         <is>
           <t>no — ASK first</t>
         </is>
       </c>
-      <c r="J21" s="58" t="inlineStr">
+      <c r="J21" s="44" t="inlineStr">
         <is>
           <t>Business Income</t>
         </is>
       </c>
-      <c r="K21" s="58" t="inlineStr">
+      <c r="K21" s="44" t="inlineStr">
         <is>
           <t>Incoming Wire; MAKE A PAYMENT; Merchant name: EOEB LLC</t>
         </is>
       </c>
       <c r="L21" s="14" t="inlineStr">
         <is>
-          <t>Invoice / MAKE A PAYMENT. Proposed advisory until confirmed.</t>
+          <t>User 2026-09-20: EOEB LLC mixed art sales AND advisory/consultant fees. Pattern confirmed; this invoice still unallocated. Do NOT dump EOEB remainder $130,270 onto Consultant or Art Sales. Invoice-level split still ASK.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="58" t="inlineStr">
+      <c r="A22" s="44" t="inlineStr">
         <is>
           <t>2025-06-12</t>
         </is>
       </c>
-      <c r="B22" s="58" t="inlineStr">
+      <c r="B22" s="44" t="inlineStr">
         <is>
           <t>EOEB LLC</t>
         </is>
       </c>
-      <c r="C22" s="71" t="n">
+      <c r="C22" s="73" t="n">
         <v>3300</v>
       </c>
-      <c r="D22" s="58" t="inlineStr">
+      <c r="D22" s="44" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E22" s="72" t="inlineStr">
+      <c r="E22" s="40" t="inlineStr">
         <is>
           <t>ADVISORY</t>
         </is>
       </c>
-      <c r="F22" s="72" t="inlineStr">
+      <c r="F22" s="40" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G22" s="58" t="inlineStr">
-        <is>
-          <t>EOEB — sale vs art advisory</t>
-        </is>
-      </c>
-      <c r="H22" s="58" t="inlineStr">
+      <c r="G22" s="44" t="inlineStr">
+        <is>
+          <t>EOEB — mixed unallocated (sale vs advisory)</t>
+        </is>
+      </c>
+      <c r="H22" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I22" s="58" t="inlineStr">
+      <c r="I22" s="44" t="inlineStr">
         <is>
           <t>no — ASK first</t>
         </is>
       </c>
-      <c r="J22" s="58" t="inlineStr">
+      <c r="J22" s="44" t="inlineStr">
         <is>
           <t>Business Income</t>
         </is>
       </c>
-      <c r="K22" s="58" t="inlineStr">
+      <c r="K22" s="44" t="inlineStr">
         <is>
           <t>Incoming Wire; MAKE A PAYMENT; Merchant name: EOEB LLC</t>
         </is>
       </c>
       <c r="L22" s="14" t="inlineStr">
         <is>
-          <t>Invoice / MAKE A PAYMENT. Proposed advisory until confirmed.</t>
+          <t>User 2026-09-20: EOEB LLC mixed art sales AND advisory/consultant fees. Pattern confirmed; this invoice still unallocated. Do NOT dump EOEB remainder $130,270 onto Consultant or Art Sales. Invoice-level split still ASK.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="58" t="inlineStr">
+      <c r="A23" s="44" t="inlineStr">
         <is>
           <t>2025-06-12</t>
         </is>
       </c>
-      <c r="B23" s="58" t="inlineStr">
+      <c r="B23" s="44" t="inlineStr">
         <is>
           <t>EOEB LLC</t>
         </is>
       </c>
-      <c r="C23" s="71" t="n">
+      <c r="C23" s="73" t="n">
         <v>25000</v>
       </c>
-      <c r="D23" s="58" t="inlineStr">
+      <c r="D23" s="44" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E23" s="72" t="inlineStr">
+      <c r="E23" s="40" t="inlineStr">
         <is>
           <t>ADVISORY</t>
         </is>
       </c>
-      <c r="F23" s="72" t="inlineStr">
+      <c r="F23" s="40" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G23" s="58" t="inlineStr">
-        <is>
-          <t>EOEB — sale vs art advisory</t>
-        </is>
-      </c>
-      <c r="H23" s="58" t="inlineStr">
+      <c r="G23" s="44" t="inlineStr">
+        <is>
+          <t>EOEB — mixed unallocated (sale vs advisory)</t>
+        </is>
+      </c>
+      <c r="H23" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I23" s="58" t="inlineStr">
+      <c r="I23" s="44" t="inlineStr">
         <is>
           <t>no — ASK first</t>
         </is>
       </c>
-      <c r="J23" s="58" t="inlineStr">
+      <c r="J23" s="44" t="inlineStr">
         <is>
           <t>Business Income</t>
         </is>
       </c>
-      <c r="K23" s="58" t="inlineStr">
+      <c r="K23" s="44" t="inlineStr">
         <is>
           <t>Incoming Wire; MAKE A PAYMENT; Merchant name: EOEB LLC</t>
         </is>
       </c>
       <c r="L23" s="14" t="inlineStr">
         <is>
-          <t>Invoice / MAKE A PAYMENT. Proposed advisory until confirmed.</t>
+          <t>User 2026-09-20: EOEB LLC mixed art sales AND advisory/consultant fees. Pattern confirmed; this invoice still unallocated. Do NOT dump EOEB remainder $130,270 onto Consultant or Art Sales. Invoice-level split still ASK.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="58" t="inlineStr">
+      <c r="A24" s="44" t="inlineStr">
         <is>
           <t>2025-06-24</t>
         </is>
       </c>
-      <c r="B24" s="58" t="inlineStr">
+      <c r="B24" s="44" t="inlineStr">
         <is>
           <t>DAVID AARON LIMITED</t>
         </is>
       </c>
-      <c r="C24" s="45" t="n">
+      <c r="C24" s="42" t="n">
         <v>13595</v>
       </c>
-      <c r="D24" s="58" t="inlineStr">
+      <c r="D24" s="44" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E24" s="44" t="inlineStr">
+      <c r="E24" s="39" t="inlineStr">
         <is>
           <t>ADVISORY</t>
         </is>
       </c>
-      <c r="F24" s="44" t="inlineStr">
+      <c r="F24" s="39" t="inlineStr">
         <is>
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="G24" s="58" t="inlineStr">
+      <c r="G24" s="44" t="inlineStr">
         <is>
           <t>David Aaron Limited — consultant fee</t>
         </is>
       </c>
-      <c r="H24" s="58" t="inlineStr">
+      <c r="H24" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I24" s="58" t="inlineStr">
+      <c r="I24" s="44" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="J24" s="58" t="inlineStr">
+      <c r="J24" s="44" t="inlineStr">
         <is>
           <t>Business Income</t>
         </is>
       </c>
-      <c r="K24" s="58" t="inlineStr">
+      <c r="K24" s="44" t="inlineStr">
         <is>
           <t>Auto-Routing transfer; Merchant name: DAVID AARON LIMITED</t>
         </is>
@@ -9199,12 +9183,12 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="58" t="inlineStr">
+      <c r="A25" s="44" t="inlineStr">
         <is>
           <t>2025-07-03</t>
         </is>
       </c>
-      <c r="B25" s="58" t="inlineStr">
+      <c r="B25" s="44" t="inlineStr">
         <is>
           <t>Bank of America - Checking ••9922</t>
         </is>
@@ -9212,42 +9196,42 @@
       <c r="C25" s="10" t="n">
         <v>-40000</v>
       </c>
-      <c r="D25" s="58" t="inlineStr">
+      <c r="D25" s="44" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E25" s="73" t="inlineStr">
+      <c r="E25" s="74" t="inlineStr">
         <is>
           <t>TRANSFER</t>
         </is>
       </c>
-      <c r="F25" s="44" t="inlineStr">
+      <c r="F25" s="39" t="inlineStr">
         <is>
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="G25" s="58" t="inlineStr">
+      <c r="G25" s="44" t="inlineStr">
         <is>
           <t>Owner transfer to BoA 9922</t>
         </is>
       </c>
-      <c r="H25" s="58" t="inlineStr">
+      <c r="H25" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I25" s="58" t="inlineStr">
+      <c r="I25" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J25" s="58" t="inlineStr">
+      <c r="J25" s="44" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K25" s="58" t="inlineStr">
+      <c r="K25" s="44" t="inlineStr">
         <is>
           <t>Transfer from Mercury to another bank account; Merchant name: Bank of America - Checking ••9922</t>
         </is>
@@ -9259,115 +9243,115 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="58" t="inlineStr">
+      <c r="A26" s="44" t="inlineStr">
         <is>
           <t>2025-07-08</t>
         </is>
       </c>
-      <c r="B26" s="58" t="inlineStr">
+      <c r="B26" s="44" t="inlineStr">
         <is>
           <t>EOEB LLC</t>
         </is>
       </c>
-      <c r="C26" s="71" t="n">
+      <c r="C26" s="73" t="n">
         <v>2000</v>
       </c>
-      <c r="D26" s="58" t="inlineStr">
+      <c r="D26" s="44" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E26" s="72" t="inlineStr">
+      <c r="E26" s="40" t="inlineStr">
         <is>
           <t>ADVISORY</t>
         </is>
       </c>
-      <c r="F26" s="72" t="inlineStr">
+      <c r="F26" s="40" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G26" s="58" t="inlineStr">
-        <is>
-          <t>EOEB — sale vs art advisory</t>
-        </is>
-      </c>
-      <c r="H26" s="58" t="inlineStr">
+      <c r="G26" s="44" t="inlineStr">
+        <is>
+          <t>EOEB — mixed unallocated (sale vs advisory)</t>
+        </is>
+      </c>
+      <c r="H26" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I26" s="58" t="inlineStr">
+      <c r="I26" s="44" t="inlineStr">
         <is>
           <t>no — ASK first</t>
         </is>
       </c>
-      <c r="J26" s="58" t="inlineStr">
+      <c r="J26" s="44" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K26" s="58" t="inlineStr">
+      <c r="K26" s="44" t="inlineStr">
         <is>
           <t>Auto-Routing transfer; Merchant name: EOEB LLC</t>
         </is>
       </c>
       <c r="L26" s="14" t="inlineStr">
         <is>
-          <t>Auto-Routing Request or Invoice Payment. Proposed advisory until confirmed.</t>
+          <t>User 2026-09-20: EOEB LLC mixed art sales AND advisory/consultant fees. Pattern confirmed; this invoice still unallocated. Do NOT dump EOEB remainder $130,270 onto Consultant or Art Sales. Invoice-level split still ASK.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="58" t="inlineStr">
+      <c r="A27" s="44" t="inlineStr">
         <is>
           <t>2025-07-09</t>
         </is>
       </c>
-      <c r="B27" s="58" t="inlineStr">
+      <c r="B27" s="44" t="inlineStr">
         <is>
           <t>Wise Inc</t>
         </is>
       </c>
-      <c r="C27" s="45" t="n">
+      <c r="C27" s="42" t="n">
         <v>-334.17</v>
       </c>
-      <c r="D27" s="58" t="inlineStr">
+      <c r="D27" s="44" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E27" s="70" t="inlineStr">
+      <c r="E27" s="72" t="inlineStr">
         <is>
           <t>EPGC_EXPENSE</t>
         </is>
       </c>
-      <c r="F27" s="44" t="inlineStr">
+      <c r="F27" s="39" t="inlineStr">
         <is>
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="G27" s="58" t="inlineStr">
+      <c r="G27" s="44" t="inlineStr">
         <is>
           <t>Wise — expertise write-ups (Consultant Fees)</t>
         </is>
       </c>
-      <c r="H27" s="58" t="inlineStr">
+      <c r="H27" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I27" s="58" t="inlineStr">
+      <c r="I27" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J27" s="58" t="inlineStr">
+      <c r="J27" s="44" t="inlineStr">
         <is>
           <t xml:space="preserve">Business Expense </t>
         </is>
       </c>
-      <c r="K27" s="58" t="inlineStr">
+      <c r="K27" s="44" t="inlineStr">
         <is>
           <t>Wise Inc; WISE; EPGC LLC; Merchant name: Wise Inc</t>
         </is>
@@ -9379,235 +9363,235 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="58" t="inlineStr">
+      <c r="A28" s="44" t="inlineStr">
         <is>
           <t>2025-07-11</t>
         </is>
       </c>
-      <c r="B28" s="58" t="inlineStr">
+      <c r="B28" s="44" t="inlineStr">
         <is>
           <t>L5</t>
         </is>
       </c>
-      <c r="C28" s="71" t="n">
+      <c r="C28" s="73" t="n">
         <v>8534.790000000001</v>
       </c>
-      <c r="D28" s="58" t="inlineStr">
+      <c r="D28" s="44" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E28" s="72" t="inlineStr">
+      <c r="E28" s="40" t="inlineStr">
         <is>
           <t>ADVISORY</t>
         </is>
       </c>
-      <c r="F28" s="72" t="inlineStr">
+      <c r="F28" s="40" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G28" s="58" t="inlineStr">
-        <is>
-          <t>L5 — sale vs art advisory</t>
-        </is>
-      </c>
-      <c r="H28" s="58" t="inlineStr">
+      <c r="G28" s="44" t="inlineStr">
+        <is>
+          <t>L5 — mixed unallocated (sale vs advisory)</t>
+        </is>
+      </c>
+      <c r="H28" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I28" s="58" t="inlineStr">
+      <c r="I28" s="44" t="inlineStr">
         <is>
           <t>no — ASK first</t>
         </is>
       </c>
-      <c r="J28" s="58" t="inlineStr">
+      <c r="J28" s="44" t="inlineStr">
         <is>
           <t>Business Income</t>
         </is>
       </c>
-      <c r="K28" s="58" t="inlineStr">
+      <c r="K28" s="44" t="inlineStr">
         <is>
           <t>Auto-Routing transfer; Merchant name: L5</t>
         </is>
       </c>
       <c r="L28" s="14" t="inlineStr">
         <is>
-          <t>Auto-Routing Request or Invoice Payment. Same invoice pattern as EOEB. Proposed advisory until confirmed.</t>
+          <t>User 2026-09-20: L5 LLC mixed art sales AND advisory/consultant fees. Pattern confirmed; this invoice still unallocated. Do NOT dump L5 remainder $87,396.32 onto Consultant or Art Sales. Invoice-level split still ASK.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="58" t="inlineStr">
+      <c r="A29" s="44" t="inlineStr">
         <is>
           <t>2025-07-15</t>
         </is>
       </c>
-      <c r="B29" s="58" t="inlineStr">
+      <c r="B29" s="44" t="inlineStr">
         <is>
           <t>L5</t>
         </is>
       </c>
-      <c r="C29" s="71" t="n">
+      <c r="C29" s="73" t="n">
         <v>2500</v>
       </c>
-      <c r="D29" s="58" t="inlineStr">
+      <c r="D29" s="44" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E29" s="72" t="inlineStr">
+      <c r="E29" s="40" t="inlineStr">
         <is>
           <t>ADVISORY</t>
         </is>
       </c>
-      <c r="F29" s="72" t="inlineStr">
+      <c r="F29" s="40" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G29" s="58" t="inlineStr">
-        <is>
-          <t>L5 — sale vs art advisory</t>
-        </is>
-      </c>
-      <c r="H29" s="58" t="inlineStr">
+      <c r="G29" s="44" t="inlineStr">
+        <is>
+          <t>L5 — mixed unallocated (sale vs advisory)</t>
+        </is>
+      </c>
+      <c r="H29" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I29" s="58" t="inlineStr">
+      <c r="I29" s="44" t="inlineStr">
         <is>
           <t>no — ASK first</t>
         </is>
       </c>
-      <c r="J29" s="58" t="inlineStr">
+      <c r="J29" s="44" t="inlineStr">
         <is>
           <t>Business Income</t>
         </is>
       </c>
-      <c r="K29" s="58" t="inlineStr">
+      <c r="K29" s="44" t="inlineStr">
         <is>
           <t>Auto-Routing transfer; Merchant name: L5</t>
         </is>
       </c>
       <c r="L29" s="14" t="inlineStr">
         <is>
-          <t>Auto-Routing Request or Invoice Payment. Proposed advisory until confirmed.</t>
+          <t>User 2026-09-20: L5 LLC mixed art sales AND advisory/consultant fees. Pattern confirmed; this invoice still unallocated. Do NOT dump L5 remainder $87,396.32 onto Consultant or Art Sales. Invoice-level split still ASK.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="58" t="inlineStr">
+      <c r="A30" s="44" t="inlineStr">
         <is>
           <t>2025-07-15</t>
         </is>
       </c>
-      <c r="B30" s="58" t="inlineStr">
+      <c r="B30" s="44" t="inlineStr">
         <is>
           <t>L5</t>
         </is>
       </c>
-      <c r="C30" s="71" t="n">
+      <c r="C30" s="73" t="n">
         <v>50000</v>
       </c>
-      <c r="D30" s="58" t="inlineStr">
+      <c r="D30" s="44" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E30" s="72" t="inlineStr">
+      <c r="E30" s="40" t="inlineStr">
         <is>
           <t>ADVISORY</t>
         </is>
       </c>
-      <c r="F30" s="72" t="inlineStr">
+      <c r="F30" s="40" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G30" s="58" t="inlineStr">
-        <is>
-          <t>L5 $50,000 — sale vs art advisory vs pass-through</t>
-        </is>
-      </c>
-      <c r="H30" s="58" t="inlineStr">
+      <c r="G30" s="44" t="inlineStr">
+        <is>
+          <t>L5 $50,000 — mixed unallocated (sale vs advisory)</t>
+        </is>
+      </c>
+      <c r="H30" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I30" s="58" t="inlineStr">
+      <c r="I30" s="44" t="inlineStr">
         <is>
           <t>no — ASK first</t>
         </is>
       </c>
-      <c r="J30" s="58" t="inlineStr">
+      <c r="J30" s="44" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K30" s="58" t="inlineStr">
+      <c r="K30" s="44" t="inlineStr">
         <is>
           <t>Auto-Routing transfer; Merchant name: L5</t>
         </is>
       </c>
       <c r="L30" s="14" t="inlineStr">
         <is>
-          <t>Largest L5 invoice. Sale of an object, advisory, or pass-through? Same week as Aysel $50k IN and Fortuna $45k OUT.</t>
+          <t>User 2026-09-20: L5 LLC mixed art sales AND advisory/consultant fees. Pattern confirmed; this invoice still unallocated. Do NOT dump L5 remainder $87,396.32 onto Consultant or Art Sales. Invoice-level split still ASK. Same week as Aysel $50k IN and Fortuna $45k OUT.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="58" t="inlineStr">
+      <c r="A31" s="44" t="inlineStr">
         <is>
           <t>2025-07-18</t>
         </is>
       </c>
-      <c r="B31" s="58" t="inlineStr">
+      <c r="B31" s="44" t="inlineStr">
         <is>
           <t>Aysel Dere</t>
         </is>
       </c>
-      <c r="C31" s="71" t="n">
+      <c r="C31" s="73" t="n">
         <v>50000</v>
       </c>
-      <c r="D31" s="58" t="inlineStr">
+      <c r="D31" s="44" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E31" s="72" t="inlineStr">
+      <c r="E31" s="40" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="F31" s="72" t="inlineStr">
+      <c r="F31" s="40" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G31" s="58" t="inlineStr">
+      <c r="G31" s="44" t="inlineStr">
         <is>
           <t>Aysel Dere $50,000 IN</t>
         </is>
       </c>
-      <c r="H31" s="58" t="inlineStr">
+      <c r="H31" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I31" s="58" t="inlineStr">
+      <c r="I31" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J31" s="58" t="inlineStr">
+      <c r="J31" s="44" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K31" s="58" t="inlineStr">
+      <c r="K31" s="44" t="inlineStr">
         <is>
           <t>Merchant name: Aysel Dere</t>
         </is>
@@ -9619,55 +9603,55 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="58" t="inlineStr">
+      <c r="A32" s="44" t="inlineStr">
         <is>
           <t>2025-07-21</t>
         </is>
       </c>
-      <c r="B32" s="58" t="inlineStr">
+      <c r="B32" s="44" t="inlineStr">
         <is>
           <t>Erdal Dere (Fortuna)</t>
         </is>
       </c>
-      <c r="C32" s="71" t="n">
+      <c r="C32" s="73" t="n">
         <v>-45000</v>
       </c>
-      <c r="D32" s="58" t="inlineStr">
+      <c r="D32" s="44" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E32" s="69" t="inlineStr">
+      <c r="E32" s="71" t="inlineStr">
         <is>
           <t>ART_PURCHASE</t>
         </is>
       </c>
-      <c r="F32" s="72" t="inlineStr">
+      <c r="F32" s="40" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G32" s="58" t="inlineStr">
+      <c r="G32" s="44" t="inlineStr">
         <is>
           <t>Fortuna / Erdal — inventory vs other</t>
         </is>
       </c>
-      <c r="H32" s="58" t="inlineStr">
+      <c r="H32" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I32" s="58" t="inlineStr">
+      <c r="I32" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J32" s="58" t="inlineStr">
+      <c r="J32" s="44" t="inlineStr">
         <is>
           <t xml:space="preserve">Business Investment </t>
         </is>
       </c>
-      <c r="K32" s="58" t="inlineStr">
+      <c r="K32" s="44" t="inlineStr">
         <is>
           <t>Merchant name: Erdal Dere (Fortuna)</t>
         </is>
@@ -9679,55 +9663,55 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="58" t="inlineStr">
+      <c r="A33" s="44" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="B33" s="58" t="inlineStr">
+      <c r="B33" s="44" t="inlineStr">
         <is>
           <t>ERDAL DERE</t>
         </is>
       </c>
-      <c r="C33" s="71" t="n">
+      <c r="C33" s="73" t="n">
         <v>26000</v>
       </c>
-      <c r="D33" s="58" t="inlineStr">
+      <c r="D33" s="44" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E33" s="70" t="inlineStr">
+      <c r="E33" s="72" t="inlineStr">
         <is>
           <t>ART_SALE</t>
         </is>
       </c>
-      <c r="F33" s="72" t="inlineStr">
+      <c r="F33" s="40" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G33" s="58" t="inlineStr">
+      <c r="G33" s="44" t="inlineStr">
         <is>
           <t>Erdal Dere $26,000 IN — sale vs other</t>
         </is>
       </c>
-      <c r="H33" s="58" t="inlineStr">
+      <c r="H33" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I33" s="58" t="inlineStr">
+      <c r="I33" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J33" s="58" t="inlineStr">
+      <c r="J33" s="44" t="inlineStr">
         <is>
           <t>Business Income</t>
         </is>
       </c>
-      <c r="K33" s="58" t="inlineStr">
+      <c r="K33" s="44" t="inlineStr">
         <is>
           <t>Incoming Wire; Merchant name: ERDAL DERE</t>
         </is>
@@ -9739,12 +9723,12 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="58" t="inlineStr">
+      <c r="A34" s="44" t="inlineStr">
         <is>
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="B34" s="58" t="inlineStr">
+      <c r="B34" s="44" t="inlineStr">
         <is>
           <t>Bank of America - Checking ••9922</t>
         </is>
@@ -9752,42 +9736,42 @@
       <c r="C34" s="10" t="n">
         <v>-60000</v>
       </c>
-      <c r="D34" s="58" t="inlineStr">
+      <c r="D34" s="44" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E34" s="73" t="inlineStr">
+      <c r="E34" s="74" t="inlineStr">
         <is>
           <t>TRANSFER</t>
         </is>
       </c>
-      <c r="F34" s="44" t="inlineStr">
+      <c r="F34" s="39" t="inlineStr">
         <is>
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="G34" s="58" t="inlineStr">
+      <c r="G34" s="44" t="inlineStr">
         <is>
           <t>Owner transfer to BoA 9922</t>
         </is>
       </c>
-      <c r="H34" s="58" t="inlineStr">
+      <c r="H34" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I34" s="58" t="inlineStr">
+      <c r="I34" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J34" s="58" t="inlineStr">
+      <c r="J34" s="44" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K34" s="58" t="inlineStr">
+      <c r="K34" s="44" t="inlineStr">
         <is>
           <t>Transfer from Mercury to another bank account; Merchant name: Bank of America - Checking ••9922</t>
         </is>
@@ -9799,55 +9783,55 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="58" t="inlineStr">
+      <c r="A35" s="44" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="B35" s="58" t="inlineStr">
+      <c r="B35" s="44" t="inlineStr">
         <is>
           <t>Erdal Dere (Fortuna)</t>
         </is>
       </c>
-      <c r="C35" s="71" t="n">
+      <c r="C35" s="73" t="n">
         <v>-20000</v>
       </c>
-      <c r="D35" s="58" t="inlineStr">
+      <c r="D35" s="44" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E35" s="69" t="inlineStr">
+      <c r="E35" s="71" t="inlineStr">
         <is>
           <t>ART_PURCHASE</t>
         </is>
       </c>
-      <c r="F35" s="72" t="inlineStr">
+      <c r="F35" s="40" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G35" s="58" t="inlineStr">
+      <c r="G35" s="44" t="inlineStr">
         <is>
           <t>Fortuna / Erdal — inventory vs other</t>
         </is>
       </c>
-      <c r="H35" s="58" t="inlineStr">
+      <c r="H35" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I35" s="58" t="inlineStr">
+      <c r="I35" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J35" s="58" t="inlineStr">
+      <c r="J35" s="44" t="inlineStr">
         <is>
           <t xml:space="preserve">Business Investment </t>
         </is>
       </c>
-      <c r="K35" s="58" t="inlineStr">
+      <c r="K35" s="44" t="inlineStr">
         <is>
           <t>Merchant name: Erdal Dere (Fortuna)</t>
         </is>
@@ -9859,175 +9843,175 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="58" t="inlineStr">
+      <c r="A36" s="44" t="inlineStr">
         <is>
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="B36" s="58" t="inlineStr">
+      <c r="B36" s="44" t="inlineStr">
         <is>
           <t>EOEB LLC</t>
         </is>
       </c>
-      <c r="C36" s="71" t="n">
+      <c r="C36" s="73" t="n">
         <v>10000</v>
       </c>
-      <c r="D36" s="58" t="inlineStr">
+      <c r="D36" s="44" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E36" s="72" t="inlineStr">
+      <c r="E36" s="40" t="inlineStr">
         <is>
           <t>ADVISORY</t>
         </is>
       </c>
-      <c r="F36" s="72" t="inlineStr">
+      <c r="F36" s="40" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G36" s="58" t="inlineStr">
-        <is>
-          <t>EOEB — sale vs art advisory</t>
-        </is>
-      </c>
-      <c r="H36" s="58" t="inlineStr">
+      <c r="G36" s="44" t="inlineStr">
+        <is>
+          <t>EOEB — mixed unallocated (sale vs advisory)</t>
+        </is>
+      </c>
+      <c r="H36" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I36" s="58" t="inlineStr">
+      <c r="I36" s="44" t="inlineStr">
         <is>
           <t>no — ASK first</t>
         </is>
       </c>
-      <c r="J36" s="58" t="inlineStr">
+      <c r="J36" s="44" t="inlineStr">
         <is>
           <t>Business Income</t>
         </is>
       </c>
-      <c r="K36" s="58" t="inlineStr">
+      <c r="K36" s="44" t="inlineStr">
         <is>
           <t>Auto-Routing transfer; Merchant name: EOEB LLC</t>
         </is>
       </c>
       <c r="L36" s="14" t="inlineStr">
         <is>
-          <t>Auto-Routing. Proposed advisory until confirmed.</t>
+          <t>User 2026-09-20: EOEB LLC mixed art sales AND advisory/consultant fees. Pattern confirmed; this invoice still unallocated. Do NOT dump EOEB remainder $130,270 onto Consultant or Art Sales. Invoice-level split still ASK.</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="58" t="inlineStr">
+      <c r="A37" s="44" t="inlineStr">
         <is>
           <t>2025-09-02</t>
         </is>
       </c>
-      <c r="B37" s="58" t="inlineStr">
+      <c r="B37" s="44" t="inlineStr">
         <is>
           <t>L5</t>
         </is>
       </c>
-      <c r="C37" s="71" t="n">
+      <c r="C37" s="73" t="n">
         <v>5042</v>
       </c>
-      <c r="D37" s="58" t="inlineStr">
+      <c r="D37" s="44" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E37" s="72" t="inlineStr">
+      <c r="E37" s="40" t="inlineStr">
         <is>
           <t>ADVISORY</t>
         </is>
       </c>
-      <c r="F37" s="72" t="inlineStr">
+      <c r="F37" s="40" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G37" s="58" t="inlineStr">
-        <is>
-          <t>L5 — sale vs art advisory</t>
-        </is>
-      </c>
-      <c r="H37" s="58" t="inlineStr">
+      <c r="G37" s="44" t="inlineStr">
+        <is>
+          <t>L5 — mixed unallocated (sale vs advisory)</t>
+        </is>
+      </c>
+      <c r="H37" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I37" s="58" t="inlineStr">
+      <c r="I37" s="44" t="inlineStr">
         <is>
           <t>no — ASK first</t>
         </is>
       </c>
-      <c r="J37" s="58" t="inlineStr">
+      <c r="J37" s="44" t="inlineStr">
         <is>
           <t>Business Income</t>
         </is>
       </c>
-      <c r="K37" s="58" t="inlineStr">
+      <c r="K37" s="44" t="inlineStr">
         <is>
           <t>Auto-Routing transfer; Merchant name: L5</t>
         </is>
       </c>
       <c r="L37" s="14" t="inlineStr">
         <is>
-          <t>Auto-Routing. Proposed advisory until confirmed.</t>
+          <t>User 2026-09-20: L5 LLC mixed art sales AND advisory/consultant fees. Pattern confirmed; this invoice still unallocated. Do NOT dump L5 remainder $87,396.32 onto Consultant or Art Sales. Invoice-level split still ASK.</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="58" t="inlineStr">
+      <c r="A38" s="44" t="inlineStr">
         <is>
           <t>2025-09-04</t>
         </is>
       </c>
-      <c r="B38" s="58" t="inlineStr">
+      <c r="B38" s="44" t="inlineStr">
         <is>
           <t>COINBASE INC.</t>
         </is>
       </c>
-      <c r="C38" s="45" t="n">
+      <c r="C38" s="42" t="n">
         <v>-3000</v>
       </c>
-      <c r="D38" s="58" t="inlineStr">
+      <c r="D38" s="44" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E38" s="74" t="inlineStr">
+      <c r="E38" s="75" t="inlineStr">
         <is>
           <t>INVESTMENT</t>
         </is>
       </c>
-      <c r="F38" s="44" t="inlineStr">
+      <c r="F38" s="39" t="inlineStr">
         <is>
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="G38" s="58" t="inlineStr">
+      <c r="G38" s="44" t="inlineStr">
         <is>
           <t>Coinbase ACH funding</t>
         </is>
       </c>
-      <c r="H38" s="58" t="inlineStr">
+      <c r="H38" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I38" s="58" t="inlineStr">
+      <c r="I38" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J38" s="58" t="inlineStr">
+      <c r="J38" s="44" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K38" s="58" t="inlineStr">
+      <c r="K38" s="44" t="inlineStr">
         <is>
           <t>COINBASE INC.; 2A0875F9; JACOB COLEY; Merchant name: COINBASE INC.</t>
         </is>
@@ -10039,132 +10023,132 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="58" t="inlineStr">
+      <c r="A39" s="44" t="inlineStr">
         <is>
           <t>2025-09-19</t>
         </is>
       </c>
-      <c r="B39" s="58" t="inlineStr">
+      <c r="B39" s="44" t="inlineStr">
         <is>
           <t>EOEB LLC</t>
         </is>
       </c>
-      <c r="C39" s="71" t="n">
+      <c r="C39" s="73" t="n">
         <v>5000</v>
       </c>
-      <c r="D39" s="58" t="inlineStr">
+      <c r="D39" s="44" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E39" s="72" t="inlineStr">
+      <c r="E39" s="40" t="inlineStr">
         <is>
           <t>ADVISORY</t>
         </is>
       </c>
-      <c r="F39" s="72" t="inlineStr">
+      <c r="F39" s="40" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G39" s="58" t="inlineStr">
-        <is>
-          <t>EOEB — sale vs art advisory</t>
-        </is>
-      </c>
-      <c r="H39" s="58" t="inlineStr">
+      <c r="G39" s="44" t="inlineStr">
+        <is>
+          <t>EOEB — mixed unallocated (sale vs advisory)</t>
+        </is>
+      </c>
+      <c r="H39" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I39" s="58" t="inlineStr">
+      <c r="I39" s="44" t="inlineStr">
         <is>
           <t>no — ASK first</t>
         </is>
       </c>
-      <c r="J39" s="58" t="inlineStr">
+      <c r="J39" s="44" t="inlineStr">
         <is>
           <t>Business Income</t>
         </is>
       </c>
-      <c r="K39" s="58" t="inlineStr">
+      <c r="K39" s="44" t="inlineStr">
         <is>
           <t>Auto-Routing transfer; Merchant name: EOEB LLC</t>
         </is>
       </c>
       <c r="L39" s="14" t="inlineStr">
         <is>
-          <t>Auto-Routing. Proposed advisory until confirmed.</t>
+          <t>User 2026-09-20: EOEB LLC mixed art sales AND advisory/consultant fees. Pattern confirmed; this invoice still unallocated. Do NOT dump EOEB remainder $130,270 onto Consultant or Art Sales. Invoice-level split still ASK.</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="58" t="inlineStr">
+      <c r="A40" s="44" t="inlineStr">
         <is>
           <t>2025-09-23</t>
         </is>
       </c>
-      <c r="B40" s="58" t="inlineStr">
+      <c r="B40" s="44" t="inlineStr">
         <is>
           <t>L5</t>
         </is>
       </c>
-      <c r="C40" s="71" t="n">
+      <c r="C40" s="73" t="n">
         <v>9119.27</v>
       </c>
-      <c r="D40" s="58" t="inlineStr">
+      <c r="D40" s="44" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E40" s="72" t="inlineStr">
+      <c r="E40" s="40" t="inlineStr">
         <is>
           <t>ADVISORY</t>
         </is>
       </c>
-      <c r="F40" s="72" t="inlineStr">
+      <c r="F40" s="40" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G40" s="58" t="inlineStr">
-        <is>
-          <t>L5 — sale vs art advisory</t>
-        </is>
-      </c>
-      <c r="H40" s="58" t="inlineStr">
+      <c r="G40" s="44" t="inlineStr">
+        <is>
+          <t>L5 — mixed unallocated (sale vs advisory)</t>
+        </is>
+      </c>
+      <c r="H40" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I40" s="58" t="inlineStr">
+      <c r="I40" s="44" t="inlineStr">
         <is>
           <t>no — ASK first</t>
         </is>
       </c>
-      <c r="J40" s="58" t="inlineStr">
+      <c r="J40" s="44" t="inlineStr">
         <is>
           <t>Business Income</t>
         </is>
       </c>
-      <c r="K40" s="58" t="inlineStr">
+      <c r="K40" s="44" t="inlineStr">
         <is>
           <t>Auto-Routing transfer; Merchant name: L5</t>
         </is>
       </c>
       <c r="L40" s="14" t="inlineStr">
         <is>
-          <t>Auto-Routing. Proposed advisory until confirmed.</t>
+          <t>User 2026-09-20: L5 LLC mixed art sales AND advisory/consultant fees. Pattern confirmed; this invoice still unallocated. Do NOT dump L5 remainder $87,396.32 onto Consultant or Art Sales. Invoice-level split still ASK.</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="58" t="inlineStr">
+      <c r="A41" s="44" t="inlineStr">
         <is>
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="B41" s="58" t="inlineStr">
+      <c r="B41" s="44" t="inlineStr">
         <is>
           <t>Bank of America - Checking ••9922</t>
         </is>
@@ -10172,42 +10156,42 @@
       <c r="C41" s="10" t="n">
         <v>-40000</v>
       </c>
-      <c r="D41" s="58" t="inlineStr">
+      <c r="D41" s="44" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E41" s="73" t="inlineStr">
+      <c r="E41" s="74" t="inlineStr">
         <is>
           <t>TRANSFER</t>
         </is>
       </c>
-      <c r="F41" s="44" t="inlineStr">
+      <c r="F41" s="39" t="inlineStr">
         <is>
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="G41" s="58" t="inlineStr">
+      <c r="G41" s="44" t="inlineStr">
         <is>
           <t>Owner transfer to BoA 9922</t>
         </is>
       </c>
-      <c r="H41" s="58" t="inlineStr">
+      <c r="H41" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I41" s="58" t="inlineStr">
+      <c r="I41" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J41" s="58" t="inlineStr">
+      <c r="J41" s="44" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K41" s="58" t="inlineStr">
+      <c r="K41" s="44" t="inlineStr">
         <is>
           <t>Transfer from Mercury to another bank account; Merchant name: Bank of America - Checking ••9922</t>
         </is>
@@ -10219,115 +10203,115 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="58" t="inlineStr">
+      <c r="A42" s="44" t="inlineStr">
         <is>
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="B42" s="58" t="inlineStr">
+      <c r="B42" s="44" t="inlineStr">
         <is>
           <t>EOEB LLC</t>
         </is>
       </c>
-      <c r="C42" s="71" t="n">
+      <c r="C42" s="73" t="n">
         <v>3100</v>
       </c>
-      <c r="D42" s="58" t="inlineStr">
+      <c r="D42" s="44" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E42" s="72" t="inlineStr">
+      <c r="E42" s="40" t="inlineStr">
         <is>
           <t>ADVISORY</t>
         </is>
       </c>
-      <c r="F42" s="72" t="inlineStr">
+      <c r="F42" s="40" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G42" s="58" t="inlineStr">
-        <is>
-          <t>EOEB — sale vs art advisory</t>
-        </is>
-      </c>
-      <c r="H42" s="58" t="inlineStr">
+      <c r="G42" s="44" t="inlineStr">
+        <is>
+          <t>EOEB — mixed unallocated (sale vs advisory)</t>
+        </is>
+      </c>
+      <c r="H42" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I42" s="58" t="inlineStr">
+      <c r="I42" s="44" t="inlineStr">
         <is>
           <t>no — ASK first</t>
         </is>
       </c>
-      <c r="J42" s="58" t="inlineStr">
+      <c r="J42" s="44" t="inlineStr">
         <is>
           <t>Business Income</t>
         </is>
       </c>
-      <c r="K42" s="58" t="inlineStr">
+      <c r="K42" s="44" t="inlineStr">
         <is>
           <t>Auto-Routing transfer; Merchant name: EOEB LLC</t>
         </is>
       </c>
       <c r="L42" s="14" t="inlineStr">
         <is>
-          <t>Auto-Routing. Proposed advisory until confirmed.</t>
+          <t>User 2026-09-20: EOEB LLC mixed art sales AND advisory/consultant fees. Pattern confirmed; this invoice still unallocated. Do NOT dump EOEB remainder $130,270 onto Consultant or Art Sales. Invoice-level split still ASK.</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="58" t="inlineStr">
+      <c r="A43" s="44" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="B43" s="58" t="inlineStr">
+      <c r="B43" s="44" t="inlineStr">
         <is>
           <t>COINBASE INC.</t>
         </is>
       </c>
-      <c r="C43" s="45" t="n">
+      <c r="C43" s="42" t="n">
         <v>-6000</v>
       </c>
-      <c r="D43" s="58" t="inlineStr">
+      <c r="D43" s="44" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E43" s="74" t="inlineStr">
+      <c r="E43" s="75" t="inlineStr">
         <is>
           <t>INVESTMENT</t>
         </is>
       </c>
-      <c r="F43" s="44" t="inlineStr">
+      <c r="F43" s="39" t="inlineStr">
         <is>
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="G43" s="58" t="inlineStr">
+      <c r="G43" s="44" t="inlineStr">
         <is>
           <t>Coinbase ACH funding</t>
         </is>
       </c>
-      <c r="H43" s="58" t="inlineStr">
+      <c r="H43" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I43" s="58" t="inlineStr">
+      <c r="I43" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J43" s="58" t="inlineStr">
+      <c r="J43" s="44" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K43" s="58" t="inlineStr">
+      <c r="K43" s="44" t="inlineStr">
         <is>
           <t>COINBASE INC.; 27B17286; JACOB COLEY; Merchant name: COINBASE INC.</t>
         </is>
@@ -10339,55 +10323,55 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="58" t="inlineStr">
+      <c r="A44" s="44" t="inlineStr">
         <is>
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="B44" s="58" t="inlineStr">
+      <c r="B44" s="44" t="inlineStr">
         <is>
           <t>COINBASE INC.</t>
         </is>
       </c>
-      <c r="C44" s="45" t="n">
+      <c r="C44" s="42" t="n">
         <v>-10000</v>
       </c>
-      <c r="D44" s="58" t="inlineStr">
+      <c r="D44" s="44" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E44" s="74" t="inlineStr">
+      <c r="E44" s="75" t="inlineStr">
         <is>
           <t>INVESTMENT</t>
         </is>
       </c>
-      <c r="F44" s="44" t="inlineStr">
+      <c r="F44" s="39" t="inlineStr">
         <is>
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="G44" s="58" t="inlineStr">
+      <c r="G44" s="44" t="inlineStr">
         <is>
           <t>Coinbase ACH funding</t>
         </is>
       </c>
-      <c r="H44" s="58" t="inlineStr">
+      <c r="H44" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I44" s="58" t="inlineStr">
+      <c r="I44" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J44" s="58" t="inlineStr">
+      <c r="J44" s="44" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K44" s="58" t="inlineStr">
+      <c r="K44" s="44" t="inlineStr">
         <is>
           <t>COINBASE INC.; E2C52DA9; JACOB COLEY; Merchant name: COINBASE INC.</t>
         </is>
@@ -10399,72 +10383,72 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="58" t="inlineStr">
+      <c r="A45" s="44" t="inlineStr">
         <is>
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="B45" s="58" t="inlineStr">
+      <c r="B45" s="44" t="inlineStr">
         <is>
           <t>EOEB LLC</t>
         </is>
       </c>
-      <c r="C45" s="71" t="n">
+      <c r="C45" s="73" t="n">
         <v>10000</v>
       </c>
-      <c r="D45" s="58" t="inlineStr">
+      <c r="D45" s="44" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E45" s="72" t="inlineStr">
+      <c r="E45" s="40" t="inlineStr">
         <is>
           <t>ADVISORY</t>
         </is>
       </c>
-      <c r="F45" s="72" t="inlineStr">
+      <c r="F45" s="40" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G45" s="58" t="inlineStr">
-        <is>
-          <t>EOEB — sale vs art advisory</t>
-        </is>
-      </c>
-      <c r="H45" s="58" t="inlineStr">
+      <c r="G45" s="44" t="inlineStr">
+        <is>
+          <t>EOEB — mixed unallocated (sale vs advisory)</t>
+        </is>
+      </c>
+      <c r="H45" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I45" s="58" t="inlineStr">
+      <c r="I45" s="44" t="inlineStr">
         <is>
           <t>no — ASK first</t>
         </is>
       </c>
-      <c r="J45" s="58" t="inlineStr">
+      <c r="J45" s="44" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K45" s="58" t="inlineStr">
+      <c r="K45" s="44" t="inlineStr">
         <is>
           <t>Auto-Routing transfer; Merchant name: EOEB LLC</t>
         </is>
       </c>
       <c r="L45" s="14" t="inlineStr">
         <is>
-          <t>Auto-Routing. Proposed advisory until confirmed.</t>
+          <t>User 2026-09-20: EOEB LLC mixed art sales AND advisory/consultant fees. Pattern confirmed; this invoice still unallocated. Do NOT dump EOEB remainder $130,270 onto Consultant or Art Sales. Invoice-level split still ASK.</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="58" t="inlineStr">
+      <c r="A46" s="44" t="inlineStr">
         <is>
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="B46" s="58" t="inlineStr">
+      <c r="B46" s="44" t="inlineStr">
         <is>
           <t>Bank of America - Checking ••9922</t>
         </is>
@@ -10472,42 +10456,42 @@
       <c r="C46" s="10" t="n">
         <v>-6172</v>
       </c>
-      <c r="D46" s="58" t="inlineStr">
+      <c r="D46" s="44" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E46" s="73" t="inlineStr">
+      <c r="E46" s="74" t="inlineStr">
         <is>
           <t>TRANSFER</t>
         </is>
       </c>
-      <c r="F46" s="44" t="inlineStr">
+      <c r="F46" s="39" t="inlineStr">
         <is>
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="G46" s="58" t="inlineStr">
+      <c r="G46" s="44" t="inlineStr">
         <is>
           <t>Owner transfer to BoA 9922</t>
         </is>
       </c>
-      <c r="H46" s="58" t="inlineStr">
+      <c r="H46" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I46" s="58" t="inlineStr">
+      <c r="I46" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J46" s="58" t="inlineStr">
+      <c r="J46" s="44" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K46" s="58" t="inlineStr">
+      <c r="K46" s="44" t="inlineStr">
         <is>
           <t>Transfer from Mercury to another bank account; Merchant name: Bank of America - Checking ••9922</t>
         </is>
@@ -10519,55 +10503,55 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="58" t="inlineStr">
+      <c r="A47" s="44" t="inlineStr">
         <is>
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="B47" s="58" t="inlineStr">
+      <c r="B47" s="44" t="inlineStr">
         <is>
           <t>ERDAL DERE</t>
         </is>
       </c>
-      <c r="C47" s="71" t="n">
+      <c r="C47" s="73" t="n">
         <v>25000</v>
       </c>
-      <c r="D47" s="58" t="inlineStr">
+      <c r="D47" s="44" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E47" s="70" t="inlineStr">
+      <c r="E47" s="72" t="inlineStr">
         <is>
           <t>ART_SALE</t>
         </is>
       </c>
-      <c r="F47" s="72" t="inlineStr">
+      <c r="F47" s="40" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G47" s="58" t="inlineStr">
+      <c r="G47" s="44" t="inlineStr">
         <is>
           <t>Erdal Dere $25,000 IN — sale vs other</t>
         </is>
       </c>
-      <c r="H47" s="58" t="inlineStr">
+      <c r="H47" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I47" s="58" t="inlineStr">
+      <c r="I47" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J47" s="58" t="inlineStr">
+      <c r="J47" s="44" t="inlineStr">
         <is>
           <t>Business Income</t>
         </is>
       </c>
-      <c r="K47" s="58" t="inlineStr">
+      <c r="K47" s="44" t="inlineStr">
         <is>
           <t>Incoming Wire; Merchant name: ERDAL DERE</t>
         </is>
@@ -10579,55 +10563,55 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="58" t="inlineStr">
+      <c r="A48" s="44" t="inlineStr">
         <is>
           <t>2025-10-14</t>
         </is>
       </c>
-      <c r="B48" s="58" t="inlineStr">
+      <c r="B48" s="44" t="inlineStr">
         <is>
           <t>Newstar Jewelers</t>
         </is>
       </c>
-      <c r="C48" s="45" t="n">
+      <c r="C48" s="42" t="n">
         <v>-8000</v>
       </c>
-      <c r="D48" s="58" t="inlineStr">
+      <c r="D48" s="44" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E48" s="69" t="inlineStr">
+      <c r="E48" s="71" t="inlineStr">
         <is>
           <t>COGS_JEWELRY</t>
         </is>
       </c>
-      <c r="F48" s="44" t="inlineStr">
+      <c r="F48" s="39" t="inlineStr">
         <is>
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="G48" s="58" t="inlineStr">
+      <c r="G48" s="44" t="inlineStr">
         <is>
           <t>Newstar Jewelers — jewelry fabrication</t>
         </is>
       </c>
-      <c r="H48" s="58" t="inlineStr">
+      <c r="H48" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I48" s="58" t="inlineStr">
+      <c r="I48" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J48" s="58" t="inlineStr">
+      <c r="J48" s="44" t="inlineStr">
         <is>
           <t xml:space="preserve">Business Expense </t>
         </is>
       </c>
-      <c r="K48" s="58" t="inlineStr">
+      <c r="K48" s="44" t="inlineStr">
         <is>
           <t>Merchant name: Newstar Jewelers</t>
         </is>
@@ -10639,72 +10623,72 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="58" t="inlineStr">
+      <c r="A49" s="44" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="B49" s="58" t="inlineStr">
+      <c r="B49" s="44" t="inlineStr">
         <is>
           <t>EOEB LLC</t>
         </is>
       </c>
-      <c r="C49" s="71" t="n">
+      <c r="C49" s="73" t="n">
         <v>16000</v>
       </c>
-      <c r="D49" s="58" t="inlineStr">
+      <c r="D49" s="44" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E49" s="72" t="inlineStr">
+      <c r="E49" s="40" t="inlineStr">
         <is>
           <t>ADVISORY</t>
         </is>
       </c>
-      <c r="F49" s="72" t="inlineStr">
+      <c r="F49" s="40" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G49" s="58" t="inlineStr">
-        <is>
-          <t>EOEB — sale vs art advisory</t>
-        </is>
-      </c>
-      <c r="H49" s="58" t="inlineStr">
+      <c r="G49" s="44" t="inlineStr">
+        <is>
+          <t>EOEB — mixed unallocated (sale vs advisory)</t>
+        </is>
+      </c>
+      <c r="H49" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I49" s="58" t="inlineStr">
+      <c r="I49" s="44" t="inlineStr">
         <is>
           <t>no — ASK first</t>
         </is>
       </c>
-      <c r="J49" s="58" t="inlineStr">
+      <c r="J49" s="44" t="inlineStr">
         <is>
           <t>Business Income</t>
         </is>
       </c>
-      <c r="K49" s="58" t="inlineStr">
+      <c r="K49" s="44" t="inlineStr">
         <is>
           <t>Auto-Routing transfer; Merchant name: EOEB LLC</t>
         </is>
       </c>
       <c r="L49" s="14" t="inlineStr">
         <is>
-          <t>Auto-Routing. Proposed advisory until confirmed.</t>
+          <t>User 2026-09-20: EOEB LLC mixed art sales AND advisory/consultant fees. Pattern confirmed; this invoice still unallocated. Do NOT dump EOEB remainder $130,270 onto Consultant or Art Sales. Invoice-level split still ASK.</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="58" t="inlineStr">
+      <c r="A50" s="44" t="inlineStr">
         <is>
           <t>2025-10-20</t>
         </is>
       </c>
-      <c r="B50" s="58" t="inlineStr">
+      <c r="B50" s="44" t="inlineStr">
         <is>
           <t>JACK EDWARD KOZIOL &amp; TRACY HOFFMAN</t>
         </is>
@@ -10712,42 +10696,42 @@
       <c r="C50" s="10" t="n">
         <v>150000</v>
       </c>
-      <c r="D50" s="58" t="inlineStr">
+      <c r="D50" s="44" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E50" s="74" t="inlineStr">
+      <c r="E50" s="75" t="inlineStr">
         <is>
           <t>PASS_THROUGH</t>
         </is>
       </c>
-      <c r="F50" s="44" t="inlineStr">
+      <c r="F50" s="39" t="inlineStr">
         <is>
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="G50" s="58" t="inlineStr">
+      <c r="G50" s="44" t="inlineStr">
         <is>
           <t>Jack Koziol &amp; Tracy Hoffman $150,000 IN</t>
         </is>
       </c>
-      <c r="H50" s="58" t="inlineStr">
+      <c r="H50" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I50" s="58" t="inlineStr">
+      <c r="I50" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J50" s="58" t="inlineStr">
+      <c r="J50" s="44" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K50" s="58" t="inlineStr">
+      <c r="K50" s="44" t="inlineStr">
         <is>
           <t>Incoming Wire; /BNF/Per your request; Merchant name: JACK EDWARD KOZIOL &amp; TRACY HOFFMAN</t>
         </is>
@@ -10759,12 +10743,12 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="58" t="inlineStr">
+      <c r="A51" s="44" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="B51" s="58" t="inlineStr">
+      <c r="B51" s="44" t="inlineStr">
         <is>
           <t>Ariadne Demirjian LLC</t>
         </is>
@@ -10772,42 +10756,42 @@
       <c r="C51" s="10" t="n">
         <v>-150000</v>
       </c>
-      <c r="D51" s="58" t="inlineStr">
+      <c r="D51" s="44" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E51" s="74" t="inlineStr">
+      <c r="E51" s="75" t="inlineStr">
         <is>
           <t>PASS_THROUGH</t>
         </is>
       </c>
-      <c r="F51" s="44" t="inlineStr">
+      <c r="F51" s="39" t="inlineStr">
         <is>
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="G51" s="58" t="inlineStr">
+      <c r="G51" s="44" t="inlineStr">
         <is>
           <t>Ariadne Demirjian LLC $150,000 OUT</t>
         </is>
       </c>
-      <c r="H51" s="58" t="inlineStr">
+      <c r="H51" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I51" s="58" t="inlineStr">
+      <c r="I51" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J51" s="58" t="inlineStr">
+      <c r="J51" s="44" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K51" s="58" t="inlineStr">
+      <c r="K51" s="44" t="inlineStr">
         <is>
           <t>Merchant name: Ariadne Demirjian LLC</t>
         </is>
@@ -10819,175 +10803,175 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="58" t="inlineStr">
+      <c r="A52" s="44" t="inlineStr">
         <is>
           <t>2025-10-21</t>
         </is>
       </c>
-      <c r="B52" s="58" t="inlineStr">
+      <c r="B52" s="44" t="inlineStr">
         <is>
           <t>L5</t>
         </is>
       </c>
-      <c r="C52" s="71" t="n">
+      <c r="C52" s="73" t="n">
         <v>7500</v>
       </c>
-      <c r="D52" s="58" t="inlineStr">
+      <c r="D52" s="44" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E52" s="72" t="inlineStr">
+      <c r="E52" s="40" t="inlineStr">
         <is>
           <t>ADVISORY</t>
         </is>
       </c>
-      <c r="F52" s="72" t="inlineStr">
+      <c r="F52" s="40" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G52" s="58" t="inlineStr">
-        <is>
-          <t>L5 — sale vs art advisory</t>
-        </is>
-      </c>
-      <c r="H52" s="58" t="inlineStr">
+      <c r="G52" s="44" t="inlineStr">
+        <is>
+          <t>L5 — mixed unallocated (sale vs advisory)</t>
+        </is>
+      </c>
+      <c r="H52" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I52" s="58" t="inlineStr">
+      <c r="I52" s="44" t="inlineStr">
         <is>
           <t>no — ASK first</t>
         </is>
       </c>
-      <c r="J52" s="58" t="inlineStr">
+      <c r="J52" s="44" t="inlineStr">
         <is>
           <t>Business Income</t>
         </is>
       </c>
-      <c r="K52" s="58" t="inlineStr">
+      <c r="K52" s="44" t="inlineStr">
         <is>
           <t>Auto-Routing transfer; Merchant name: L5</t>
         </is>
       </c>
       <c r="L52" s="14" t="inlineStr">
         <is>
-          <t>Auto-Routing. Proposed advisory until confirmed.</t>
+          <t>User 2026-09-20: L5 LLC mixed art sales AND advisory/consultant fees. Pattern confirmed; this invoice still unallocated. Do NOT dump L5 remainder $87,396.32 onto Consultant or Art Sales. Invoice-level split still ASK.</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="58" t="inlineStr">
+      <c r="A53" s="44" t="inlineStr">
         <is>
           <t>2025-10-24</t>
         </is>
       </c>
-      <c r="B53" s="58" t="inlineStr">
+      <c r="B53" s="44" t="inlineStr">
         <is>
           <t>EOEB LLC</t>
         </is>
       </c>
-      <c r="C53" s="71" t="n">
+      <c r="C53" s="73" t="n">
         <v>1500</v>
       </c>
-      <c r="D53" s="58" t="inlineStr">
+      <c r="D53" s="44" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E53" s="72" t="inlineStr">
+      <c r="E53" s="40" t="inlineStr">
         <is>
           <t>ADVISORY</t>
         </is>
       </c>
-      <c r="F53" s="72" t="inlineStr">
+      <c r="F53" s="40" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G53" s="58" t="inlineStr">
-        <is>
-          <t>EOEB — sale vs art advisory</t>
-        </is>
-      </c>
-      <c r="H53" s="58" t="inlineStr">
+      <c r="G53" s="44" t="inlineStr">
+        <is>
+          <t>EOEB — mixed unallocated (sale vs advisory)</t>
+        </is>
+      </c>
+      <c r="H53" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I53" s="58" t="inlineStr">
+      <c r="I53" s="44" t="inlineStr">
         <is>
           <t>no — ASK first</t>
         </is>
       </c>
-      <c r="J53" s="58" t="inlineStr">
+      <c r="J53" s="44" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K53" s="58" t="inlineStr">
+      <c r="K53" s="44" t="inlineStr">
         <is>
           <t>Auto-Routing transfer; Merchant name: EOEB LLC</t>
         </is>
       </c>
       <c r="L53" s="14" t="inlineStr">
         <is>
-          <t>Auto-Routing. Proposed advisory until confirmed.</t>
+          <t>User 2026-09-20: EOEB LLC mixed art sales AND advisory/consultant fees. Pattern confirmed; this invoice still unallocated. Do NOT dump EOEB remainder $130,270 onto Consultant or Art Sales. Invoice-level split still ASK.</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="58" t="inlineStr">
+      <c r="A54" s="44" t="inlineStr">
         <is>
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="B54" s="58" t="inlineStr">
+      <c r="B54" s="44" t="inlineStr">
         <is>
           <t>Wise Inc</t>
         </is>
       </c>
-      <c r="C54" s="45" t="n">
+      <c r="C54" s="42" t="n">
         <v>-658.63</v>
       </c>
-      <c r="D54" s="58" t="inlineStr">
+      <c r="D54" s="44" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E54" s="70" t="inlineStr">
+      <c r="E54" s="72" t="inlineStr">
         <is>
           <t>EPGC_EXPENSE</t>
         </is>
       </c>
-      <c r="F54" s="44" t="inlineStr">
+      <c r="F54" s="39" t="inlineStr">
         <is>
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="G54" s="58" t="inlineStr">
+      <c r="G54" s="44" t="inlineStr">
         <is>
           <t>Wise — expertise write-ups (Consultant Fees)</t>
         </is>
       </c>
-      <c r="H54" s="58" t="inlineStr">
+      <c r="H54" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I54" s="58" t="inlineStr">
+      <c r="I54" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J54" s="58" t="inlineStr">
+      <c r="J54" s="44" t="inlineStr">
         <is>
           <t xml:space="preserve">Business Expense </t>
         </is>
       </c>
-      <c r="K54" s="58" t="inlineStr">
+      <c r="K54" s="44" t="inlineStr">
         <is>
           <t>Wise Inc; WISE; EPGC LLC; Merchant name: Wise Inc</t>
         </is>
@@ -10999,115 +10983,115 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="58" t="inlineStr">
+      <c r="A55" s="44" t="inlineStr">
         <is>
           <t>2025-10-31</t>
         </is>
       </c>
-      <c r="B55" s="58" t="inlineStr">
+      <c r="B55" s="44" t="inlineStr">
         <is>
           <t>EOEB LLC</t>
         </is>
       </c>
-      <c r="C55" s="71" t="n">
+      <c r="C55" s="73" t="n">
         <v>2170</v>
       </c>
-      <c r="D55" s="58" t="inlineStr">
+      <c r="D55" s="44" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E55" s="72" t="inlineStr">
+      <c r="E55" s="40" t="inlineStr">
         <is>
           <t>ADVISORY</t>
         </is>
       </c>
-      <c r="F55" s="72" t="inlineStr">
+      <c r="F55" s="40" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G55" s="58" t="inlineStr">
-        <is>
-          <t>EOEB — sale vs art advisory</t>
-        </is>
-      </c>
-      <c r="H55" s="58" t="inlineStr">
+      <c r="G55" s="44" t="inlineStr">
+        <is>
+          <t>EOEB — mixed unallocated (sale vs advisory)</t>
+        </is>
+      </c>
+      <c r="H55" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I55" s="58" t="inlineStr">
+      <c r="I55" s="44" t="inlineStr">
         <is>
           <t>no — ASK first</t>
         </is>
       </c>
-      <c r="J55" s="58" t="inlineStr">
+      <c r="J55" s="44" t="inlineStr">
         <is>
           <t>Business Income</t>
         </is>
       </c>
-      <c r="K55" s="58" t="inlineStr">
+      <c r="K55" s="44" t="inlineStr">
         <is>
           <t>Auto-Routing transfer; Merchant name: EOEB LLC</t>
         </is>
       </c>
       <c r="L55" s="14" t="inlineStr">
         <is>
-          <t>Auto-Routing. Proposed advisory until confirmed.</t>
+          <t>User 2026-09-20: EOEB LLC mixed art sales AND advisory/consultant fees. Pattern confirmed; this invoice still unallocated. Do NOT dump EOEB remainder $130,270 onto Consultant or Art Sales. Invoice-level split still ASK.</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="58" t="inlineStr">
+      <c r="A56" s="44" t="inlineStr">
         <is>
           <t>2025-11-06</t>
         </is>
       </c>
-      <c r="B56" s="58" t="inlineStr">
+      <c r="B56" s="44" t="inlineStr">
         <is>
           <t>COINBASE INC.</t>
         </is>
       </c>
-      <c r="C56" s="45" t="n">
+      <c r="C56" s="42" t="n">
         <v>-10000</v>
       </c>
-      <c r="D56" s="58" t="inlineStr">
+      <c r="D56" s="44" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E56" s="74" t="inlineStr">
+      <c r="E56" s="75" t="inlineStr">
         <is>
           <t>INVESTMENT</t>
         </is>
       </c>
-      <c r="F56" s="44" t="inlineStr">
+      <c r="F56" s="39" t="inlineStr">
         <is>
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="G56" s="58" t="inlineStr">
+      <c r="G56" s="44" t="inlineStr">
         <is>
           <t>Coinbase ACH funding</t>
         </is>
       </c>
-      <c r="H56" s="58" t="inlineStr">
+      <c r="H56" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I56" s="58" t="inlineStr">
+      <c r="I56" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J56" s="58" t="inlineStr">
+      <c r="J56" s="44" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K56" s="58" t="inlineStr">
+      <c r="K56" s="44" t="inlineStr">
         <is>
           <t>COINBASE INC.; 450310C7; JACOB COLEY; Merchant name: COINBASE INC.</t>
         </is>
@@ -11119,55 +11103,55 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="58" t="inlineStr">
+      <c r="A57" s="44" t="inlineStr">
         <is>
           <t>2025-11-07</t>
         </is>
       </c>
-      <c r="B57" s="58" t="inlineStr">
+      <c r="B57" s="44" t="inlineStr">
         <is>
           <t>ERDAL DERE</t>
         </is>
       </c>
-      <c r="C57" s="71" t="n">
+      <c r="C57" s="73" t="n">
         <v>6000</v>
       </c>
-      <c r="D57" s="58" t="inlineStr">
+      <c r="D57" s="44" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E57" s="70" t="inlineStr">
+      <c r="E57" s="72" t="inlineStr">
         <is>
           <t>ART_SALE</t>
         </is>
       </c>
-      <c r="F57" s="72" t="inlineStr">
+      <c r="F57" s="40" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G57" s="58" t="inlineStr">
+      <c r="G57" s="44" t="inlineStr">
         <is>
           <t>Erdal Dere Fortuna PAYMENT $6,000 IN</t>
         </is>
       </c>
-      <c r="H57" s="58" t="inlineStr">
+      <c r="H57" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I57" s="58" t="inlineStr">
+      <c r="I57" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J57" s="58" t="inlineStr">
+      <c r="J57" s="44" t="inlineStr">
         <is>
           <t>Business Income</t>
         </is>
       </c>
-      <c r="K57" s="58" t="inlineStr">
+      <c r="K57" s="44" t="inlineStr">
         <is>
           <t>Incoming Wire; ERDAL DERE FORTUNA PAYMENT; Merchant name: ERDAL DERE</t>
         </is>
@@ -11179,55 +11163,55 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="58" t="inlineStr">
+      <c r="A58" s="44" t="inlineStr">
         <is>
           <t>2025-11-12</t>
         </is>
       </c>
-      <c r="B58" s="58" t="inlineStr">
+      <c r="B58" s="44" t="inlineStr">
         <is>
           <t>Newstar Jewelers</t>
         </is>
       </c>
-      <c r="C58" s="45" t="n">
+      <c r="C58" s="42" t="n">
         <v>-8000</v>
       </c>
-      <c r="D58" s="58" t="inlineStr">
+      <c r="D58" s="44" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E58" s="69" t="inlineStr">
+      <c r="E58" s="71" t="inlineStr">
         <is>
           <t>COGS_JEWELRY</t>
         </is>
       </c>
-      <c r="F58" s="44" t="inlineStr">
+      <c r="F58" s="39" t="inlineStr">
         <is>
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="G58" s="58" t="inlineStr">
+      <c r="G58" s="44" t="inlineStr">
         <is>
           <t>Newstar Jewelers — jewelry fabrication</t>
         </is>
       </c>
-      <c r="H58" s="58" t="inlineStr">
+      <c r="H58" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I58" s="58" t="inlineStr">
+      <c r="I58" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J58" s="58" t="inlineStr">
+      <c r="J58" s="44" t="inlineStr">
         <is>
           <t xml:space="preserve">Business Expense </t>
         </is>
       </c>
-      <c r="K58" s="58" t="inlineStr">
+      <c r="K58" s="44" t="inlineStr">
         <is>
           <t>Merchant name: Newstar Jewelers</t>
         </is>
@@ -11239,55 +11223,55 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="58" t="inlineStr">
+      <c r="A59" s="44" t="inlineStr">
         <is>
           <t>2025-11-14</t>
         </is>
       </c>
-      <c r="B59" s="58" t="inlineStr">
+      <c r="B59" s="44" t="inlineStr">
         <is>
           <t>COINBASE INC.</t>
         </is>
       </c>
-      <c r="C59" s="45" t="n">
+      <c r="C59" s="42" t="n">
         <v>-10000</v>
       </c>
-      <c r="D59" s="58" t="inlineStr">
+      <c r="D59" s="44" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E59" s="74" t="inlineStr">
+      <c r="E59" s="75" t="inlineStr">
         <is>
           <t>INVESTMENT</t>
         </is>
       </c>
-      <c r="F59" s="44" t="inlineStr">
+      <c r="F59" s="39" t="inlineStr">
         <is>
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="G59" s="58" t="inlineStr">
+      <c r="G59" s="44" t="inlineStr">
         <is>
           <t>Coinbase ACH funding</t>
         </is>
       </c>
-      <c r="H59" s="58" t="inlineStr">
+      <c r="H59" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I59" s="58" t="inlineStr">
+      <c r="I59" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J59" s="58" t="inlineStr">
+      <c r="J59" s="44" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K59" s="58" t="inlineStr">
+      <c r="K59" s="44" t="inlineStr">
         <is>
           <t>COINBASE INC.; 8DF808EA; JACOB COLEY; Merchant name: COINBASE INC.</t>
         </is>
@@ -11299,55 +11283,55 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="58" t="inlineStr">
+      <c r="A60" s="44" t="inlineStr">
         <is>
           <t>2025-11-17</t>
         </is>
       </c>
-      <c r="B60" s="58" t="inlineStr">
+      <c r="B60" s="44" t="inlineStr">
         <is>
           <t>COINBASE INC.</t>
         </is>
       </c>
-      <c r="C60" s="45" t="n">
+      <c r="C60" s="42" t="n">
         <v>-10000</v>
       </c>
-      <c r="D60" s="58" t="inlineStr">
+      <c r="D60" s="44" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E60" s="74" t="inlineStr">
+      <c r="E60" s="75" t="inlineStr">
         <is>
           <t>INVESTMENT</t>
         </is>
       </c>
-      <c r="F60" s="44" t="inlineStr">
+      <c r="F60" s="39" t="inlineStr">
         <is>
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="G60" s="58" t="inlineStr">
+      <c r="G60" s="44" t="inlineStr">
         <is>
           <t>Coinbase ACH funding</t>
         </is>
       </c>
-      <c r="H60" s="58" t="inlineStr">
+      <c r="H60" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I60" s="58" t="inlineStr">
+      <c r="I60" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J60" s="58" t="inlineStr">
+      <c r="J60" s="44" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K60" s="58" t="inlineStr">
+      <c r="K60" s="44" t="inlineStr">
         <is>
           <t>COINBASE INC.; 6651A007; JACOB COLEY; Merchant name: COINBASE INC.</t>
         </is>
@@ -11359,55 +11343,55 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="58" t="inlineStr">
+      <c r="A61" s="44" t="inlineStr">
         <is>
           <t>2025-11-24</t>
         </is>
       </c>
-      <c r="B61" s="58" t="inlineStr">
+      <c r="B61" s="44" t="inlineStr">
         <is>
           <t>COINBASE INC.</t>
         </is>
       </c>
-      <c r="C61" s="45" t="n">
+      <c r="C61" s="42" t="n">
         <v>-5000</v>
       </c>
-      <c r="D61" s="58" t="inlineStr">
+      <c r="D61" s="44" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E61" s="74" t="inlineStr">
+      <c r="E61" s="75" t="inlineStr">
         <is>
           <t>INVESTMENT</t>
         </is>
       </c>
-      <c r="F61" s="44" t="inlineStr">
+      <c r="F61" s="39" t="inlineStr">
         <is>
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="G61" s="58" t="inlineStr">
+      <c r="G61" s="44" t="inlineStr">
         <is>
           <t>Coinbase ACH funding</t>
         </is>
       </c>
-      <c r="H61" s="58" t="inlineStr">
+      <c r="H61" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I61" s="58" t="inlineStr">
+      <c r="I61" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J61" s="58" t="inlineStr">
+      <c r="J61" s="44" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K61" s="58" t="inlineStr">
+      <c r="K61" s="44" t="inlineStr">
         <is>
           <t>COINBASE INC.; D5957FFE; JACOB COLEY; Merchant name: COINBASE INC.</t>
         </is>
@@ -11419,12 +11403,12 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="58" t="inlineStr">
+      <c r="A62" s="44" t="inlineStr">
         <is>
           <t>2025-12-02</t>
         </is>
       </c>
-      <c r="B62" s="58" t="inlineStr">
+      <c r="B62" s="44" t="inlineStr">
         <is>
           <t>Wise Inc</t>
         </is>
@@ -11432,42 +11416,42 @@
       <c r="C62" s="10" t="n">
         <v>-565.75</v>
       </c>
-      <c r="D62" s="58" t="inlineStr">
+      <c r="D62" s="44" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E62" s="73" t="inlineStr">
+      <c r="E62" s="74" t="inlineStr">
         <is>
           <t>REIMBURSE</t>
         </is>
       </c>
-      <c r="F62" s="44" t="inlineStr">
+      <c r="F62" s="39" t="inlineStr">
         <is>
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="G62" s="58" t="inlineStr">
+      <c r="G62" s="44" t="inlineStr">
         <is>
           <t>Wise $565.75 reimbursed by EOEB</t>
         </is>
       </c>
-      <c r="H62" s="58" t="inlineStr">
+      <c r="H62" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I62" s="58" t="inlineStr">
+      <c r="I62" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J62" s="58" t="inlineStr">
+      <c r="J62" s="44" t="inlineStr">
         <is>
           <t xml:space="preserve">Business Expense </t>
         </is>
       </c>
-      <c r="K62" s="58" t="inlineStr">
+      <c r="K62" s="44" t="inlineStr">
         <is>
           <t>Wise Inc; WISE; EPGC LLC; Merchant name: Wise Inc</t>
         </is>
@@ -11479,12 +11463,12 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="58" t="inlineStr">
+      <c r="A63" s="44" t="inlineStr">
         <is>
           <t>2025-12-02</t>
         </is>
       </c>
-      <c r="B63" s="58" t="inlineStr">
+      <c r="B63" s="44" t="inlineStr">
         <is>
           <t>EOEB LLC</t>
         </is>
@@ -11492,42 +11476,42 @@
       <c r="C63" s="10" t="n">
         <v>565.75</v>
       </c>
-      <c r="D63" s="58" t="inlineStr">
+      <c r="D63" s="44" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E63" s="73" t="inlineStr">
+      <c r="E63" s="74" t="inlineStr">
         <is>
           <t>REIMBURSE</t>
         </is>
       </c>
-      <c r="F63" s="44" t="inlineStr">
+      <c r="F63" s="39" t="inlineStr">
         <is>
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="G63" s="58" t="inlineStr">
+      <c r="G63" s="44" t="inlineStr">
         <is>
           <t>EOEB reimburses Wise $565.75</t>
         </is>
       </c>
-      <c r="H63" s="58" t="inlineStr">
+      <c r="H63" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I63" s="58" t="inlineStr">
+      <c r="I63" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J63" s="58" t="inlineStr">
+      <c r="J63" s="44" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K63" s="58" t="inlineStr">
+      <c r="K63" s="44" t="inlineStr">
         <is>
           <t>Auto-Routing transfer; Merchant name: EOEB LLC</t>
         </is>
@@ -11539,115 +11523,115 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="58" t="inlineStr">
+      <c r="A64" s="44" t="inlineStr">
         <is>
           <t>2025-12-04</t>
         </is>
       </c>
-      <c r="B64" s="58" t="inlineStr">
+      <c r="B64" s="44" t="inlineStr">
         <is>
           <t>L5</t>
         </is>
       </c>
-      <c r="C64" s="71" t="n">
+      <c r="C64" s="73" t="n">
         <v>4700.26</v>
       </c>
-      <c r="D64" s="58" t="inlineStr">
+      <c r="D64" s="44" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E64" s="72" t="inlineStr">
+      <c r="E64" s="40" t="inlineStr">
         <is>
           <t>ADVISORY</t>
         </is>
       </c>
-      <c r="F64" s="72" t="inlineStr">
+      <c r="F64" s="40" t="inlineStr">
         <is>
           <t>ASK</t>
         </is>
       </c>
-      <c r="G64" s="58" t="inlineStr">
-        <is>
-          <t>L5 — sale vs art advisory</t>
-        </is>
-      </c>
-      <c r="H64" s="58" t="inlineStr">
+      <c r="G64" s="44" t="inlineStr">
+        <is>
+          <t>L5 — mixed unallocated (sale vs advisory)</t>
+        </is>
+      </c>
+      <c r="H64" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I64" s="58" t="inlineStr">
+      <c r="I64" s="44" t="inlineStr">
         <is>
           <t>no — ASK first</t>
         </is>
       </c>
-      <c r="J64" s="58" t="inlineStr">
+      <c r="J64" s="44" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K64" s="58" t="inlineStr">
+      <c r="K64" s="44" t="inlineStr">
         <is>
           <t>Auto-Routing transfer; Merchant name: L5</t>
         </is>
       </c>
       <c r="L64" s="14" t="inlineStr">
         <is>
-          <t>Auto-Routing. Proposed advisory until confirmed.</t>
+          <t>User 2026-09-20: L5 LLC mixed art sales AND advisory/consultant fees. Pattern confirmed; this invoice still unallocated. Do NOT dump L5 remainder $87,396.32 onto Consultant or Art Sales. Invoice-level split still ASK.</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="58" t="inlineStr">
+      <c r="A65" s="44" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="B65" s="58" t="inlineStr">
+      <c r="B65" s="44" t="inlineStr">
         <is>
           <t>COINBASE INC.</t>
         </is>
       </c>
-      <c r="C65" s="45" t="n">
+      <c r="C65" s="42" t="n">
         <v>-5000</v>
       </c>
-      <c r="D65" s="58" t="inlineStr">
+      <c r="D65" s="44" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E65" s="74" t="inlineStr">
+      <c r="E65" s="75" t="inlineStr">
         <is>
           <t>INVESTMENT</t>
         </is>
       </c>
-      <c r="F65" s="44" t="inlineStr">
+      <c r="F65" s="39" t="inlineStr">
         <is>
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="G65" s="58" t="inlineStr">
+      <c r="G65" s="44" t="inlineStr">
         <is>
           <t>Coinbase ACH funding</t>
         </is>
       </c>
-      <c r="H65" s="58" t="inlineStr">
+      <c r="H65" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I65" s="58" t="inlineStr">
+      <c r="I65" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J65" s="58" t="inlineStr">
+      <c r="J65" s="44" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K65" s="58" t="inlineStr">
+      <c r="K65" s="44" t="inlineStr">
         <is>
           <t>COINBASE INC.; DFF8E6A8; JACOB COLEY; Merchant name: COINBASE INC.</t>
         </is>
@@ -11659,55 +11643,55 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="58" t="inlineStr">
+      <c r="A66" s="44" t="inlineStr">
         <is>
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="B66" s="58" t="inlineStr">
+      <c r="B66" s="44" t="inlineStr">
         <is>
           <t>COINBASE INC.</t>
         </is>
       </c>
-      <c r="C66" s="45" t="n">
+      <c r="C66" s="42" t="n">
         <v>8000</v>
       </c>
-      <c r="D66" s="58" t="inlineStr">
+      <c r="D66" s="44" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E66" s="74" t="inlineStr">
+      <c r="E66" s="75" t="inlineStr">
         <is>
           <t>INVESTMENT</t>
         </is>
       </c>
-      <c r="F66" s="44" t="inlineStr">
+      <c r="F66" s="39" t="inlineStr">
         <is>
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="G66" s="58" t="inlineStr">
+      <c r="G66" s="44" t="inlineStr">
         <is>
           <t>Coinbase ACH back to Mercury</t>
         </is>
       </c>
-      <c r="H66" s="58" t="inlineStr">
+      <c r="H66" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I66" s="58" t="inlineStr">
+      <c r="I66" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J66" s="58" t="inlineStr">
+      <c r="J66" s="44" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="K66" s="58" t="inlineStr">
+      <c r="K66" s="44" t="inlineStr">
         <is>
           <t>COINBASE INC.; 6B2DA6B2; JACOB COLEY; Merchant name: COINBASE INC.</t>
         </is>
@@ -11719,55 +11703,55 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="58" t="inlineStr">
+      <c r="A67" s="44" t="inlineStr">
         <is>
           <t>2025-12-24</t>
         </is>
       </c>
-      <c r="B67" s="58" t="inlineStr">
+      <c r="B67" s="44" t="inlineStr">
         <is>
           <t>Newstar Jewelers</t>
         </is>
       </c>
-      <c r="C67" s="45" t="n">
+      <c r="C67" s="42" t="n">
         <v>-7581</v>
       </c>
-      <c r="D67" s="58" t="inlineStr">
+      <c r="D67" s="44" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="E67" s="69" t="inlineStr">
+      <c r="E67" s="71" t="inlineStr">
         <is>
           <t>COGS_JEWELRY</t>
         </is>
       </c>
-      <c r="F67" s="44" t="inlineStr">
+      <c r="F67" s="39" t="inlineStr">
         <is>
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="G67" s="58" t="inlineStr">
+      <c r="G67" s="44" t="inlineStr">
         <is>
           <t>Newstar Jewelers — jewelry fabrication (3 of 3)</t>
         </is>
       </c>
-      <c r="H67" s="58" t="inlineStr">
+      <c r="H67" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="I67" s="58" t="inlineStr">
+      <c r="I67" s="44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="J67" s="58" t="inlineStr">
+      <c r="J67" s="44" t="inlineStr">
         <is>
           <t xml:space="preserve">Business Expense </t>
         </is>
       </c>
-      <c r="K67" s="58" t="inlineStr">
+      <c r="K67" s="44" t="inlineStr">
         <is>
           <t>From EPGC LLC via mercury.com 3 of 3; Merchant name: Newstar Jewelers</t>
         </is>

--- a/.cursor/scratch/tax_turbo_parts/Personal Income 2025 — like last year (EPGC+Art+GCM).xlsx
+++ b/.cursor/scratch/tax_turbo_parts/Personal Income 2025 — like last year (EPGC+Art+GCM).xlsx
@@ -175,7 +175,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -266,10 +266,8 @@
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -292,8 +290,13 @@
     <xf numFmtId="164" fontId="10" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="8" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -5945,16 +5948,20 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="46" t="inlineStr">
-        <is>
-          <t>Mercury 8291 MATCHED: Berk $14,000 (1/10 seals) + $30,000 (2/7 lots). EOEB $105,000 (2/21 mosaics). Fortuna $13,000 (1/8 seals Cost). Plutus $50,000 of mosaics $90,000 Cost — $40,000 of Cost not on 8291 (ASK). Newstar $23,581 is jewelry fabrication COGS, parked below — not in sold-lot Cost (Berk gem/scarab lots already sold in February). David Aaron $13,595 (6/24) is LOCKED consultant fee — not a sale (EPGC Consultant June). Aquinas Hobor $1,000 (2/4) is LOCKED books sold — EPGC Art Sales February; Cost TBD (not in I8). Not tax advice.</t>
-        </is>
+      <c r="A78" s="44" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="H78" s="46">
+        <f>SUM(H51:H75)</f>
+        <v/>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="47" t="inlineStr">
         <is>
-          <t>Mercury 8291 MATCHED: Berk $14,000 (1/10 seals) + $30,000 (2/7 lots). EOEB $105,000 (2/21 mosaics). Fortuna $13,000 (1/8 seals Cost). Plutus $50,000 of mosaics $90,000 Cost — $40,000 of Cost not on 8291 (ASK). Newstar $23,581 is jewelry fabrication COGS, parked below — not in sold-lot Cost (Berk gem/scarab lots already sold in February). David Aaron $13,595 (6/24) is LOCKED consultant fee — not a sale (EPGC Consultant June). Aquinas Hobor $1,000 (2/4) is LOCKED books sold — EPGC Art Sales February; Cost TBD (not in I8). Not tax advice.</t>
+          <t>Mercury 8291 MATCHED: Berk $14,000 (1/10 seals) + $30,000 (2/7 lots). EOEB $105,000 (2/21 mosaics). Fortuna $13,000 (1/8 seals Cost). Plutus $50,000 of mosaics $90,000 Cost — $40,000 of Cost not on 8291 (ASK). Newstar $23,581 is jewelry fabrication COGS, parked below — not in sold-lot Cost (Berk gem/scarab lots already sold in February). David Aaron $13,595 (6/24) is LOCKED consultant fee — not a sale (EPGC Consultant June). Aquinas Hobor $1,000 (2/4) is LOCKED book sale — EPGC Art Sales February; Cost TBD (not in I8). Not tax advice.</t>
         </is>
       </c>
     </row>
@@ -7418,7 +7425,7 @@
       <c r="M7" s="63" t="n">
         <v>-5000</v>
       </c>
-      <c r="N7" s="64">
+      <c r="N7" s="46">
         <f>SUM(B7:M7)</f>
         <v/>
       </c>
@@ -7465,7 +7472,7 @@
       <c r="M8" s="63" t="n">
         <v>8000</v>
       </c>
-      <c r="N8" s="64">
+      <c r="N8" s="46">
         <f>SUM(B8:M8)</f>
         <v/>
       </c>
@@ -7512,14 +7519,14 @@
       <c r="M9" s="42" t="n">
         <v>3000</v>
       </c>
-      <c r="N9" s="64">
+      <c r="N9" s="46">
         <f>SUM(B9:M9)</f>
         <v/>
       </c>
     </row>
     <row r="10"/>
     <row r="11">
-      <c r="A11" s="65" t="inlineStr">
+      <c r="A11" s="64" t="inlineStr">
         <is>
           <t>2025: funded $59,000.00 / returned $8,000.00 / net $-51,000.00 off the EPGC operating account. Not income, not an expense. Not tax advice.</t>
         </is>
@@ -7536,7 +7543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -7547,7 +7554,7 @@
     <row r="1">
       <c r="A1" s="49" t="inlineStr">
         <is>
-          <t>ASK — remaining Mercury 8291 questions. Q6 consultant, Q7 Wise expertise, Q8 pass-through, Q9 Aquinas books LOCKED (green). Q1/Q2 mixed pattern CONFIRMED, dollars unallocated (yellow). Not tax advice.</t>
+          <t>ASK — remaining Mercury 8291 questions. Q6 consultant, Q7 Wise expertise, Q8 pass-through, Q9 Aquinas books LOCKED (green). Q1/Q2 mixed pattern CONFIRMED (blue) — remainder dollars unallocated until invoice split. Not tax advice.</t>
         </is>
       </c>
     </row>
@@ -7565,31 +7572,31 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="66" t="inlineStr">
+      <c r="A4" s="65" t="inlineStr">
         <is>
           <t>1. EOEB LLC remainder after mosaics — MIXED PATTERN CONFIRMED, dollars unallocated</t>
         </is>
       </c>
-      <c r="B4" s="45" t="inlineStr">
-        <is>
-          <t>$130,270.00 of EOEB IN is not mosaics $105,000 and not Wise reimburse $565.75. User 2026-09-20: EOEB is mixed art sales AND advisory/consultant fees. Do NOT dump this remainder onto Consultant or Art Sales. Invoice-level split still ASK. Jan 16 $1,000 Canosan-horse question STILL OPEN (Art Sales horse is to Erdal; this cash is EOEB).</t>
+      <c r="B4" s="66" t="inlineStr">
+        <is>
+          <t>$130,270.00 of EOEB IN is not mosaics $105,000 and not Wise reimburse $565.75. User 2026-09-20: EOEB is mixed art sales AND advisory/consultant fees. Do NOT dump this remainder onto Consultant or Art Sales. Mark each invoice sale vs advisory: 1/16 $1,000 (Canosan-horse STILL OPEN — Art Sales horse is to Erdal, this cash is EOEB); 3/10 $14,000; 5/1 $21,000; 5/13 $16,200; 6/12 $25,000 + $3,300; 7/8 $2,000; 8/29 $10,000; 9/19 $5,000; 9/25 $3,100; 10/1 $10,000; 10/15 $16,000; 10/24 $1,500; 10/31 $2,170.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="66" t="inlineStr">
+      <c r="A5" s="65" t="inlineStr">
         <is>
           <t>2. L5 (all seven invoices) — MIXED PATTERN CONFIRMED, dollars unallocated</t>
         </is>
       </c>
-      <c r="B5" s="45" t="inlineStr">
-        <is>
-          <t>$87,396.32. User 2026-09-20: L5 is mixed art sales AND advisory/consultant fees. Do NOT dump onto Consultant or Art Sales. Invoice-level split still ASK. The 7/15 $50,000 still sits in the Aysel $50k / Fortuna $45k week.</t>
+      <c r="B5" s="66" t="inlineStr">
+        <is>
+          <t>$87,396.32. User 2026-09-20: L5 is mixed art sales AND advisory/consultant fees. Do NOT dump onto Consultant or Art Sales. Mark each invoice sale vs advisory: 7/11 $8,534.79; 7/15 $50,000 + $2,500 (same week as Aysel $50k / Fortuna $45k); 9/2 $5,042; 9/23 $9,119.27; 10/21 $7,500; 12/4 $4,700.26.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="66" t="inlineStr">
+      <c r="A6" s="67" t="inlineStr">
         <is>
           <t>3. Fortuna / Erdal Dere OUT after seals</t>
         </is>
@@ -7601,7 +7608,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="66" t="inlineStr">
+      <c r="A7" s="67" t="inlineStr">
         <is>
           <t>4. Erdal Dere IN</t>
         </is>
@@ -7613,7 +7620,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="66" t="inlineStr">
+      <c r="A8" s="67" t="inlineStr">
         <is>
           <t>5. Aysel Dere $50,000 IN (7/18)</t>
         </is>
@@ -7625,55 +7632,55 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="67" t="inlineStr">
+      <c r="A9" s="68" t="inlineStr">
         <is>
           <t>6. David Aaron Limited $13,595 IN (6/24) — LOCKED consultant fee</t>
         </is>
       </c>
-      <c r="B9" s="68" t="inlineStr">
+      <c r="B9" s="69" t="inlineStr">
         <is>
           <t>CONFIRMED 2026-09-20: consultant fee, not a sale. Booked EPGC Consultant June $13,595 (peach). Not Art Sales. Not Income I8.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="67" t="inlineStr">
+      <c r="A10" s="68" t="inlineStr">
         <is>
           <t>7. Wise $334.17 (7/9) and $658.63 (10/30) — LOCKED expertise write-ups</t>
         </is>
       </c>
-      <c r="B10" s="68" t="inlineStr">
+      <c r="B10" s="69" t="inlineStr">
         <is>
           <t>CONFIRMED 2026-09-20: business expenses (expertise write-ups). Booked EPGC Consultant Fees July $334.17 + October $658.63 = $992.80. Not COGS. Distinct from Dec Wise $565.75 reimbursed by EOEB (still not P&amp;L).</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="67" t="inlineStr">
+      <c r="A11" s="68" t="inlineStr">
         <is>
           <t>8. Jack Koziol &amp; Tracy Hoffman $150,000 IN (10/20) / Ariadne Demirjian $150,000 OUT (10/21) — LOCKED pass-through</t>
         </is>
       </c>
-      <c r="B11" s="68" t="inlineStr">
+      <c r="B11" s="69" t="inlineStr">
         <is>
           <t>CONFIRMED 2026-09-20: pass-through, not P&amp;L. Not a sale, not a purchase, not COGS, not Consultant.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="67" t="inlineStr">
+      <c r="A12" s="68" t="inlineStr">
         <is>
           <t>9. Aquinas Hobor $1,000 IN (2/4) — LOCKED book sale</t>
         </is>
       </c>
-      <c r="B12" s="68" t="inlineStr">
+      <c r="B12" s="69" t="inlineStr">
         <is>
           <t>CONFIRMED 2026-09-20: book SALE. Hits EPGC Art Sales February +$1,000 (Feb $136,000; matched cash $150,000). Art Sales register: Books (titles TBD) to Aquinas Hobor, Sale Price $1,000, Sale Date 2025-02-04, Cost TBD. Not in Income I8 until Cost (same as Sale 6428).</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="66" t="inlineStr">
+      <c r="A13" s="67" t="inlineStr">
         <is>
           <t>10. Mosaics Cost $90,000 vs Mercury $50,000</t>
         </is>
@@ -7821,6 +7828,18 @@
       <c r="B26" s="39" t="inlineStr">
         <is>
           <t>$1,000 IN 2/4 LOCKED book sale → EPGC Art Sales February +$1,000 (Feb $136,000; matched cash $150,000). Cost / titles TBD (not in I8 until Cost, same as Sale 6428).</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="39" t="inlineStr">
+        <is>
+          <t>EOEB / L5 mixed pattern</t>
+        </is>
+      </c>
+      <c r="B27" s="39" t="inlineStr">
+        <is>
+          <t>CONFIRMED mixed art sales AND advisory/consultant. Remainder $130,270 / $87,396.32 unallocated — not on P&amp;L until invoice split. Jan 16 $1,000 Canosan-horse still open.</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7872,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="69" t="inlineStr">
+      <c r="A1" s="70" t="inlineStr">
         <is>
           <t>Mercury Checking 8291 — EPGC LLC (Choice Financial) 2025. 64 unique cash transactions. Coinbase ACH = investment. Newstar = jewelry COGS on intaglios/gems/scarabs. BoA 9922 draws and Koziol/Ariadne $150k are LOCKED not-P&amp;L (pass-through / owner transfer). David Aaron $13,595 is LOCKED EPGC Consultant (June). Wise $334.17 + $658.63 are LOCKED EPGC Consultant Fees (expertise write-ups). Aquinas Hobor $1,000 (2/4) is LOCKED books sold (EPGC Art Sales February; Cost TBD). Not tax advice.</t>
         </is>
@@ -7861,62 +7880,62 @@
     </row>
     <row r="2"/>
     <row r="3">
-      <c r="A3" s="70" t="inlineStr">
+      <c r="A3" s="71" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B3" s="70" t="inlineStr">
+      <c r="B3" s="71" t="inlineStr">
         <is>
           <t>Counterparty</t>
         </is>
       </c>
-      <c r="C3" s="70" t="inlineStr">
+      <c r="C3" s="71" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="D3" s="70" t="inlineStr">
+      <c r="D3" s="71" t="inlineStr">
         <is>
           <t>Direction</t>
         </is>
       </c>
-      <c r="E3" s="70" t="inlineStr">
+      <c r="E3" s="71" t="inlineStr">
         <is>
           <t>Bucket</t>
         </is>
       </c>
-      <c r="F3" s="70" t="inlineStr">
+      <c r="F3" s="71" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G3" s="70" t="inlineStr">
+      <c r="G3" s="71" t="inlineStr">
         <is>
           <t>Deal / object</t>
         </is>
       </c>
-      <c r="H3" s="70" t="inlineStr">
+      <c r="H3" s="71" t="inlineStr">
         <is>
           <t>Hits EPGC Art Sales?</t>
         </is>
       </c>
-      <c r="I3" s="70" t="inlineStr">
+      <c r="I3" s="71" t="inlineStr">
         <is>
           <t>Hits EPGC Consultant?</t>
         </is>
       </c>
-      <c r="J3" s="70" t="inlineStr">
+      <c r="J3" s="71" t="inlineStr">
         <is>
           <t>Monarch category</t>
         </is>
       </c>
-      <c r="K3" s="70" t="inlineStr">
+      <c r="K3" s="71" t="inlineStr">
         <is>
           <t>Original statement</t>
         </is>
       </c>
-      <c r="L3" s="70" t="inlineStr">
+      <c r="L3" s="71" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -7941,7 +7960,7 @@
           <t>OUT</t>
         </is>
       </c>
-      <c r="E4" s="71" t="inlineStr">
+      <c r="E4" s="72" t="inlineStr">
         <is>
           <t>ART_PURCHASE</t>
         </is>
@@ -8001,7 +8020,7 @@
           <t>IN</t>
         </is>
       </c>
-      <c r="E5" s="72" t="inlineStr">
+      <c r="E5" s="73" t="inlineStr">
         <is>
           <t>ART_SALE</t>
         </is>
@@ -8053,7 +8072,7 @@
           <t>EOEB LLC</t>
         </is>
       </c>
-      <c r="C6" s="73" t="n">
+      <c r="C6" s="74" t="n">
         <v>1000</v>
       </c>
       <c r="D6" s="44" t="inlineStr">
@@ -8121,7 +8140,7 @@
           <t>OUT</t>
         </is>
       </c>
-      <c r="E7" s="74" t="inlineStr">
+      <c r="E7" s="75" t="inlineStr">
         <is>
           <t>TRANSFER</t>
         </is>
@@ -8181,7 +8200,7 @@
           <t>IN</t>
         </is>
       </c>
-      <c r="E8" s="72" t="inlineStr">
+      <c r="E8" s="73" t="inlineStr">
         <is>
           <t>ART_SALE</t>
         </is>
@@ -8241,7 +8260,7 @@
           <t>IN</t>
         </is>
       </c>
-      <c r="E9" s="72" t="inlineStr">
+      <c r="E9" s="73" t="inlineStr">
         <is>
           <t>ART_SALE</t>
         </is>
@@ -8301,7 +8320,7 @@
           <t>OUT</t>
         </is>
       </c>
-      <c r="E10" s="74" t="inlineStr">
+      <c r="E10" s="75" t="inlineStr">
         <is>
           <t>TEST</t>
         </is>
@@ -8361,7 +8380,7 @@
           <t>IN</t>
         </is>
       </c>
-      <c r="E11" s="74" t="inlineStr">
+      <c r="E11" s="75" t="inlineStr">
         <is>
           <t>TEST</t>
         </is>
@@ -8421,7 +8440,7 @@
           <t>IN</t>
         </is>
       </c>
-      <c r="E12" s="72" t="inlineStr">
+      <c r="E12" s="73" t="inlineStr">
         <is>
           <t>ART_SALE</t>
         </is>
@@ -8481,7 +8500,7 @@
           <t>OUT</t>
         </is>
       </c>
-      <c r="E13" s="74" t="inlineStr">
+      <c r="E13" s="75" t="inlineStr">
         <is>
           <t>TRANSFER</t>
         </is>
@@ -8541,7 +8560,7 @@
           <t>OUT</t>
         </is>
       </c>
-      <c r="E14" s="74" t="inlineStr">
+      <c r="E14" s="75" t="inlineStr">
         <is>
           <t>TEST</t>
         </is>
@@ -8601,7 +8620,7 @@
           <t>OUT</t>
         </is>
       </c>
-      <c r="E15" s="74" t="inlineStr">
+      <c r="E15" s="75" t="inlineStr">
         <is>
           <t>TEST</t>
         </is>
@@ -8661,7 +8680,7 @@
           <t>IN</t>
         </is>
       </c>
-      <c r="E16" s="74" t="inlineStr">
+      <c r="E16" s="75" t="inlineStr">
         <is>
           <t>TEST</t>
         </is>
@@ -8721,7 +8740,7 @@
           <t>OUT</t>
         </is>
       </c>
-      <c r="E17" s="71" t="inlineStr">
+      <c r="E17" s="72" t="inlineStr">
         <is>
           <t>ART_PURCHASE</t>
         </is>
@@ -8773,7 +8792,7 @@
           <t>EOEB LLC</t>
         </is>
       </c>
-      <c r="C18" s="73" t="n">
+      <c r="C18" s="74" t="n">
         <v>14000</v>
       </c>
       <c r="D18" s="44" t="inlineStr">
@@ -8833,7 +8852,7 @@
           <t>EOEB LLC</t>
         </is>
       </c>
-      <c r="C19" s="73" t="n">
+      <c r="C19" s="74" t="n">
         <v>21000</v>
       </c>
       <c r="D19" s="44" t="inlineStr">
@@ -8893,7 +8912,7 @@
           <t>Erdal Dere (Fortuna)</t>
         </is>
       </c>
-      <c r="C20" s="73" t="n">
+      <c r="C20" s="74" t="n">
         <v>-20000</v>
       </c>
       <c r="D20" s="44" t="inlineStr">
@@ -8901,7 +8920,7 @@
           <t>OUT</t>
         </is>
       </c>
-      <c r="E20" s="71" t="inlineStr">
+      <c r="E20" s="72" t="inlineStr">
         <is>
           <t>ART_PURCHASE</t>
         </is>
@@ -8953,7 +8972,7 @@
           <t>EOEB LLC</t>
         </is>
       </c>
-      <c r="C21" s="73" t="n">
+      <c r="C21" s="74" t="n">
         <v>16200</v>
       </c>
       <c r="D21" s="44" t="inlineStr">
@@ -9013,7 +9032,7 @@
           <t>EOEB LLC</t>
         </is>
       </c>
-      <c r="C22" s="73" t="n">
+      <c r="C22" s="74" t="n">
         <v>3300</v>
       </c>
       <c r="D22" s="44" t="inlineStr">
@@ -9073,7 +9092,7 @@
           <t>EOEB LLC</t>
         </is>
       </c>
-      <c r="C23" s="73" t="n">
+      <c r="C23" s="74" t="n">
         <v>25000</v>
       </c>
       <c r="D23" s="44" t="inlineStr">
@@ -9201,7 +9220,7 @@
           <t>OUT</t>
         </is>
       </c>
-      <c r="E25" s="74" t="inlineStr">
+      <c r="E25" s="75" t="inlineStr">
         <is>
           <t>TRANSFER</t>
         </is>
@@ -9253,7 +9272,7 @@
           <t>EOEB LLC</t>
         </is>
       </c>
-      <c r="C26" s="73" t="n">
+      <c r="C26" s="74" t="n">
         <v>2000</v>
       </c>
       <c r="D26" s="44" t="inlineStr">
@@ -9321,7 +9340,7 @@
           <t>OUT</t>
         </is>
       </c>
-      <c r="E27" s="72" t="inlineStr">
+      <c r="E27" s="73" t="inlineStr">
         <is>
           <t>EPGC_EXPENSE</t>
         </is>
@@ -9373,7 +9392,7 @@
           <t>L5</t>
         </is>
       </c>
-      <c r="C28" s="73" t="n">
+      <c r="C28" s="74" t="n">
         <v>8534.790000000001</v>
       </c>
       <c r="D28" s="44" t="inlineStr">
@@ -9433,7 +9452,7 @@
           <t>L5</t>
         </is>
       </c>
-      <c r="C29" s="73" t="n">
+      <c r="C29" s="74" t="n">
         <v>2500</v>
       </c>
       <c r="D29" s="44" t="inlineStr">
@@ -9493,7 +9512,7 @@
           <t>L5</t>
         </is>
       </c>
-      <c r="C30" s="73" t="n">
+      <c r="C30" s="74" t="n">
         <v>50000</v>
       </c>
       <c r="D30" s="44" t="inlineStr">
@@ -9553,7 +9572,7 @@
           <t>Aysel Dere</t>
         </is>
       </c>
-      <c r="C31" s="73" t="n">
+      <c r="C31" s="74" t="n">
         <v>50000</v>
       </c>
       <c r="D31" s="44" t="inlineStr">
@@ -9613,7 +9632,7 @@
           <t>Erdal Dere (Fortuna)</t>
         </is>
       </c>
-      <c r="C32" s="73" t="n">
+      <c r="C32" s="74" t="n">
         <v>-45000</v>
       </c>
       <c r="D32" s="44" t="inlineStr">
@@ -9621,7 +9640,7 @@
           <t>OUT</t>
         </is>
       </c>
-      <c r="E32" s="71" t="inlineStr">
+      <c r="E32" s="72" t="inlineStr">
         <is>
           <t>ART_PURCHASE</t>
         </is>
@@ -9673,7 +9692,7 @@
           <t>ERDAL DERE</t>
         </is>
       </c>
-      <c r="C33" s="73" t="n">
+      <c r="C33" s="74" t="n">
         <v>26000</v>
       </c>
       <c r="D33" s="44" t="inlineStr">
@@ -9681,7 +9700,7 @@
           <t>IN</t>
         </is>
       </c>
-      <c r="E33" s="72" t="inlineStr">
+      <c r="E33" s="73" t="inlineStr">
         <is>
           <t>ART_SALE</t>
         </is>
@@ -9741,7 +9760,7 @@
           <t>OUT</t>
         </is>
       </c>
-      <c r="E34" s="74" t="inlineStr">
+      <c r="E34" s="75" t="inlineStr">
         <is>
           <t>TRANSFER</t>
         </is>
@@ -9793,7 +9812,7 @@
           <t>Erdal Dere (Fortuna)</t>
         </is>
       </c>
-      <c r="C35" s="73" t="n">
+      <c r="C35" s="74" t="n">
         <v>-20000</v>
       </c>
       <c r="D35" s="44" t="inlineStr">
@@ -9801,7 +9820,7 @@
           <t>OUT</t>
         </is>
       </c>
-      <c r="E35" s="71" t="inlineStr">
+      <c r="E35" s="72" t="inlineStr">
         <is>
           <t>ART_PURCHASE</t>
         </is>
@@ -9853,7 +9872,7 @@
           <t>EOEB LLC</t>
         </is>
       </c>
-      <c r="C36" s="73" t="n">
+      <c r="C36" s="74" t="n">
         <v>10000</v>
       </c>
       <c r="D36" s="44" t="inlineStr">
@@ -9913,7 +9932,7 @@
           <t>L5</t>
         </is>
       </c>
-      <c r="C37" s="73" t="n">
+      <c r="C37" s="74" t="n">
         <v>5042</v>
       </c>
       <c r="D37" s="44" t="inlineStr">
@@ -9981,7 +10000,7 @@
           <t>OUT</t>
         </is>
       </c>
-      <c r="E38" s="75" t="inlineStr">
+      <c r="E38" s="76" t="inlineStr">
         <is>
           <t>INVESTMENT</t>
         </is>
@@ -10033,7 +10052,7 @@
           <t>EOEB LLC</t>
         </is>
       </c>
-      <c r="C39" s="73" t="n">
+      <c r="C39" s="74" t="n">
         <v>5000</v>
       </c>
       <c r="D39" s="44" t="inlineStr">
@@ -10093,7 +10112,7 @@
           <t>L5</t>
         </is>
       </c>
-      <c r="C40" s="73" t="n">
+      <c r="C40" s="74" t="n">
         <v>9119.27</v>
       </c>
       <c r="D40" s="44" t="inlineStr">
@@ -10161,7 +10180,7 @@
           <t>OUT</t>
         </is>
       </c>
-      <c r="E41" s="74" t="inlineStr">
+      <c r="E41" s="75" t="inlineStr">
         <is>
           <t>TRANSFER</t>
         </is>
@@ -10213,7 +10232,7 @@
           <t>EOEB LLC</t>
         </is>
       </c>
-      <c r="C42" s="73" t="n">
+      <c r="C42" s="74" t="n">
         <v>3100</v>
       </c>
       <c r="D42" s="44" t="inlineStr">
@@ -10281,7 +10300,7 @@
           <t>OUT</t>
         </is>
       </c>
-      <c r="E43" s="75" t="inlineStr">
+      <c r="E43" s="76" t="inlineStr">
         <is>
           <t>INVESTMENT</t>
         </is>
@@ -10341,7 +10360,7 @@
           <t>OUT</t>
         </is>
       </c>
-      <c r="E44" s="75" t="inlineStr">
+      <c r="E44" s="76" t="inlineStr">
         <is>
           <t>INVESTMENT</t>
         </is>
@@ -10393,7 +10412,7 @@
           <t>EOEB LLC</t>
         </is>
       </c>
-      <c r="C45" s="73" t="n">
+      <c r="C45" s="74" t="n">
         <v>10000</v>
       </c>
       <c r="D45" s="44" t="inlineStr">
@@ -10461,7 +10480,7 @@
           <t>OUT</t>
         </is>
       </c>
-      <c r="E46" s="74" t="inlineStr">
+      <c r="E46" s="75" t="inlineStr">
         <is>
           <t>TRANSFER</t>
         </is>
@@ -10513,7 +10532,7 @@
           <t>ERDAL DERE</t>
         </is>
       </c>
-      <c r="C47" s="73" t="n">
+      <c r="C47" s="74" t="n">
         <v>25000</v>
       </c>
       <c r="D47" s="44" t="inlineStr">
@@ -10521,7 +10540,7 @@
           <t>IN</t>
         </is>
       </c>
-      <c r="E47" s="72" t="inlineStr">
+      <c r="E47" s="73" t="inlineStr">
         <is>
           <t>ART_SALE</t>
         </is>
@@ -10581,7 +10600,7 @@
           <t>OUT</t>
         </is>
       </c>
-      <c r="E48" s="71" t="inlineStr">
+      <c r="E48" s="72" t="inlineStr">
         <is>
           <t>COGS_JEWELRY</t>
         </is>
@@ -10633,7 +10652,7 @@
           <t>EOEB LLC</t>
         </is>
       </c>
-      <c r="C49" s="73" t="n">
+      <c r="C49" s="74" t="n">
         <v>16000</v>
       </c>
       <c r="D49" s="44" t="inlineStr">
@@ -10701,7 +10720,7 @@
           <t>IN</t>
         </is>
       </c>
-      <c r="E50" s="75" t="inlineStr">
+      <c r="E50" s="76" t="inlineStr">
         <is>
           <t>PASS_THROUGH</t>
         </is>
@@ -10761,7 +10780,7 @@
           <t>OUT</t>
         </is>
       </c>
-      <c r="E51" s="75" t="inlineStr">
+      <c r="E51" s="76" t="inlineStr">
         <is>
           <t>PASS_THROUGH</t>
         </is>
@@ -10813,7 +10832,7 @@
           <t>L5</t>
         </is>
       </c>
-      <c r="C52" s="73" t="n">
+      <c r="C52" s="74" t="n">
         <v>7500</v>
       </c>
       <c r="D52" s="44" t="inlineStr">
@@ -10873,7 +10892,7 @@
           <t>EOEB LLC</t>
         </is>
       </c>
-      <c r="C53" s="73" t="n">
+      <c r="C53" s="74" t="n">
         <v>1500</v>
       </c>
       <c r="D53" s="44" t="inlineStr">
@@ -10941,7 +10960,7 @@
           <t>OUT</t>
         </is>
       </c>
-      <c r="E54" s="72" t="inlineStr">
+      <c r="E54" s="73" t="inlineStr">
         <is>
           <t>EPGC_EXPENSE</t>
         </is>
@@ -10993,7 +11012,7 @@
           <t>EOEB LLC</t>
         </is>
       </c>
-      <c r="C55" s="73" t="n">
+      <c r="C55" s="74" t="n">
         <v>2170</v>
       </c>
       <c r="D55" s="44" t="inlineStr">
@@ -11061,7 +11080,7 @@
           <t>OUT</t>
         </is>
       </c>
-      <c r="E56" s="75" t="inlineStr">
+      <c r="E56" s="76" t="inlineStr">
         <is>
           <t>INVESTMENT</t>
         </is>
@@ -11113,7 +11132,7 @@
           <t>ERDAL DERE</t>
         </is>
       </c>
-      <c r="C57" s="73" t="n">
+      <c r="C57" s="74" t="n">
         <v>6000</v>
       </c>
       <c r="D57" s="44" t="inlineStr">
@@ -11121,7 +11140,7 @@
           <t>IN</t>
         </is>
       </c>
-      <c r="E57" s="72" t="inlineStr">
+      <c r="E57" s="73" t="inlineStr">
         <is>
           <t>ART_SALE</t>
         </is>
@@ -11181,7 +11200,7 @@
           <t>OUT</t>
         </is>
       </c>
-      <c r="E58" s="71" t="inlineStr">
+      <c r="E58" s="72" t="inlineStr">
         <is>
           <t>COGS_JEWELRY</t>
         </is>
@@ -11241,7 +11260,7 @@
           <t>OUT</t>
         </is>
       </c>
-      <c r="E59" s="75" t="inlineStr">
+      <c r="E59" s="76" t="inlineStr">
         <is>
           <t>INVESTMENT</t>
         </is>
@@ -11301,7 +11320,7 @@
           <t>OUT</t>
         </is>
       </c>
-      <c r="E60" s="75" t="inlineStr">
+      <c r="E60" s="76" t="inlineStr">
         <is>
           <t>INVESTMENT</t>
         </is>
@@ -11361,7 +11380,7 @@
           <t>OUT</t>
         </is>
       </c>
-      <c r="E61" s="75" t="inlineStr">
+      <c r="E61" s="76" t="inlineStr">
         <is>
           <t>INVESTMENT</t>
         </is>
@@ -11421,7 +11440,7 @@
           <t>OUT</t>
         </is>
       </c>
-      <c r="E62" s="74" t="inlineStr">
+      <c r="E62" s="75" t="inlineStr">
         <is>
           <t>REIMBURSE</t>
         </is>
@@ -11481,7 +11500,7 @@
           <t>IN</t>
         </is>
       </c>
-      <c r="E63" s="74" t="inlineStr">
+      <c r="E63" s="75" t="inlineStr">
         <is>
           <t>REIMBURSE</t>
         </is>
@@ -11533,7 +11552,7 @@
           <t>L5</t>
         </is>
       </c>
-      <c r="C64" s="73" t="n">
+      <c r="C64" s="74" t="n">
         <v>4700.26</v>
       </c>
       <c r="D64" s="44" t="inlineStr">
@@ -11601,7 +11620,7 @@
           <t>OUT</t>
         </is>
       </c>
-      <c r="E65" s="75" t="inlineStr">
+      <c r="E65" s="76" t="inlineStr">
         <is>
           <t>INVESTMENT</t>
         </is>
@@ -11661,7 +11680,7 @@
           <t>IN</t>
         </is>
       </c>
-      <c r="E66" s="75" t="inlineStr">
+      <c r="E66" s="76" t="inlineStr">
         <is>
           <t>INVESTMENT</t>
         </is>
@@ -11721,7 +11740,7 @@
           <t>OUT</t>
         </is>
       </c>
-      <c r="E67" s="71" t="inlineStr">
+      <c r="E67" s="72" t="inlineStr">
         <is>
           <t>COGS_JEWELRY</t>
         </is>

--- a/.cursor/scratch/tax_turbo_parts/Personal Income 2025 — like last year (EPGC+Art+GCM).xlsx
+++ b/.cursor/scratch/tax_turbo_parts/Personal Income 2025 — like last year (EPGC+Art+GCM).xlsx
@@ -175,7 +175,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -279,7 +279,9 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="10" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -303,9 +305,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -6723,69 +6722,69 @@
     </row>
     <row r="128"/>
     <row r="129">
-      <c r="A129" s="55" t="inlineStr">
-        <is>
-          <t>2025 Mercury ASK — Fortuna inventory remaining (not in Cost total until object is named)</t>
+      <c r="A129" s="51" t="inlineStr">
+        <is>
+          <t>2025 Mercury Fortuna inventory — Venus + Roman Gold Belt LOCKED; Aug $20k unnamed ASK</t>
         </is>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="41" t="inlineStr">
-        <is>
-          <t>Fortuna / Erdal Dere — object TBD</t>
-        </is>
-      </c>
-      <c r="B130" s="41" t="inlineStr">
+      <c r="A130" s="39" t="inlineStr">
+        <is>
+          <t>Bronze head of a goddess, likely Venus — Fortuna inventory</t>
+        </is>
+      </c>
+      <c r="B130" s="39" t="inlineStr">
         <is>
           <t>Mercury 8291</t>
         </is>
       </c>
-      <c r="C130" s="50" t="n">
+      <c r="C130" s="54" t="n">
         <v>20000</v>
       </c>
-      <c r="D130" s="41" t="inlineStr">
+      <c r="D130" s="53" t="inlineStr">
         <is>
           <t>2025-05-09</t>
         </is>
       </c>
-      <c r="I130" s="32" t="inlineStr">
-        <is>
-          <t>ASK: inventory purchase vs other. Do not add to sold Cost until named (avoid double count).</t>
+      <c r="I130" s="55" t="inlineStr">
+        <is>
+          <t>LOCKED 2026-09-20 from Mercury native CSV note. Parked Cost. Not sold 2025 — not in sold-lot Cost. Not tax advice.</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="41" t="inlineStr">
-        <is>
-          <t>Fortuna / Erdal Dere — object TBD</t>
-        </is>
-      </c>
-      <c r="B131" s="41" t="inlineStr">
+      <c r="A131" s="39" t="inlineStr">
+        <is>
+          <t>Roman Gold Belt — Fortuna inventory</t>
+        </is>
+      </c>
+      <c r="B131" s="39" t="inlineStr">
         <is>
           <t>Mercury 8291</t>
         </is>
       </c>
-      <c r="C131" s="50" t="n">
+      <c r="C131" s="54" t="n">
         <v>45000</v>
       </c>
-      <c r="D131" s="41" t="inlineStr">
+      <c r="D131" s="53" t="inlineStr">
         <is>
           <t>2025-07-21</t>
         </is>
       </c>
-      <c r="I131" s="32" t="inlineStr">
-        <is>
-          <t>ASK: inventory purchase vs other. Do not add to sold Cost until named (avoid double count).</t>
+      <c r="I131" s="55" t="inlineStr">
+        <is>
+          <t>LOCKED 2026-09-20 from Mercury native CSV note. Parked Cost. Not sold 2025 — not in sold-lot Cost. Not tax advice.</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="41" t="inlineStr">
-        <is>
-          <t>Fortuna / Erdal Dere — object TBD</t>
-        </is>
-      </c>
-      <c r="B132" s="41" t="inlineStr">
+      <c r="A132" s="40" t="inlineStr">
+        <is>
+          <t>Fortuna / Erdal Dere — object still unnamed (native 8/18 = Monarch 8/15)</t>
+        </is>
+      </c>
+      <c r="B132" s="40" t="inlineStr">
         <is>
           <t>Mercury 8291</t>
         </is>
@@ -6798,20 +6797,20 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="I132" s="32" t="inlineStr">
-        <is>
-          <t>ASK: inventory purchase vs other. Do not add to sold Cost until named (avoid double count).</t>
+      <c r="I132" s="45" t="inlineStr">
+        <is>
+          <t>ASK: same $20,000 as Mercury native 2025-08-18. No object name. Do not add to sold Cost. Not a second unique txn.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="32" t="inlineStr">
         <is>
-          <t>Fortuna remaining 2025 (excl. seals $13,000 already on row 73)</t>
+          <t>Fortuna unnamed remaining 2025 (excl. seals $13,000 + Venus $20,000 + Belt $45,000)</t>
         </is>
       </c>
       <c r="C133" s="50" t="n">
-        <v>85000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="134"/>
@@ -7543,7 +7542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -7598,12 +7597,12 @@
     <row r="6">
       <c r="A6" s="67" t="inlineStr">
         <is>
-          <t>3. Fortuna / Erdal Dere OUT after seals</t>
+          <t>3. Fortuna / Erdal $20,000 Aug — object still unnamed</t>
         </is>
       </c>
       <c r="B6" s="45" t="inlineStr">
         <is>
-          <t>$85,000.00 after the 1/8 $13,000 seals COGS (5/9 $20k, 7/21 $45k, 8/15 $20k). Inventory purchases (object names) or something else?</t>
+          <t>$20,000.00. Monarch posted 8/15 = Mercury native initiated 8/18 (same cash, not a second unique txn). Native memo has no object name. Venus $20,000 (5/9) and Roman Gold Belt $45,000 (7/21) are LOCKED inventory below — not this question.</t>
         </is>
       </c>
     </row>
@@ -7622,12 +7621,12 @@
     <row r="8">
       <c r="A8" s="67" t="inlineStr">
         <is>
-          <t>5. Aysel Dere $50,000 IN (7/18)</t>
+          <t>5. Aysel Dere $50,000 — Monarch IN vs native Failed OUT</t>
         </is>
       </c>
       <c r="B8" s="45" t="inlineStr">
         <is>
-          <t>Sale, related-party transfer, or part of the mid-July Fortuna/L5 cluster?</t>
+          <t>Monarch 7/18 +$50,000 IN is in the 64. Mercury native CSV has NO Sent Aysel cash — only Failed $50,000 OUT 7/17 'Recipient account does not exist'. Is the Monarch IN a phantom of the failed send, or a real incoming the export omitted? Do not dump onto Art Sales or Consultant until confirmed.</t>
         </is>
       </c>
     </row>
@@ -7637,7 +7636,7 @@
           <t>6. David Aaron Limited $13,595 IN (6/24) — LOCKED consultant fee</t>
         </is>
       </c>
-      <c r="B9" s="69" t="inlineStr">
+      <c r="B9" s="55" t="inlineStr">
         <is>
           <t>CONFIRMED 2026-09-20: consultant fee, not a sale. Booked EPGC Consultant June $13,595 (peach). Not Art Sales. Not Income I8.</t>
         </is>
@@ -7649,7 +7648,7 @@
           <t>7. Wise $334.17 (7/9) and $658.63 (10/30) — LOCKED expertise write-ups</t>
         </is>
       </c>
-      <c r="B10" s="69" t="inlineStr">
+      <c r="B10" s="55" t="inlineStr">
         <is>
           <t>CONFIRMED 2026-09-20: business expenses (expertise write-ups). Booked EPGC Consultant Fees July $334.17 + October $658.63 = $992.80. Not COGS. Distinct from Dec Wise $565.75 reimbursed by EOEB (still not P&amp;L).</t>
         </is>
@@ -7661,7 +7660,7 @@
           <t>8. Jack Koziol &amp; Tracy Hoffman $150,000 IN (10/20) / Ariadne Demirjian $150,000 OUT (10/21) — LOCKED pass-through</t>
         </is>
       </c>
-      <c r="B11" s="69" t="inlineStr">
+      <c r="B11" s="55" t="inlineStr">
         <is>
           <t>CONFIRMED 2026-09-20: pass-through, not P&amp;L. Not a sale, not a purchase, not COGS, not Consultant.</t>
         </is>
@@ -7673,7 +7672,7 @@
           <t>9. Aquinas Hobor $1,000 IN (2/4) — LOCKED book sale</t>
         </is>
       </c>
-      <c r="B12" s="69" t="inlineStr">
+      <c r="B12" s="55" t="inlineStr">
         <is>
           <t>CONFIRMED 2026-09-20: book SALE. Hits EPGC Art Sales February +$1,000 (Feb $136,000; matched cash $150,000). Art Sales register: Books (titles TBD) to Aquinas Hobor, Sale Price $1,000, Sale Date 2025-02-04, Cost TBD. Not in Income I8 until Cost (same as Sale 6428).</t>
         </is>
@@ -7840,6 +7839,42 @@
       <c r="B27" s="39" t="inlineStr">
         <is>
           <t>CONFIRMED mixed art sales AND advisory/consultant. Remainder $130,270 / $87,396.32 unallocated — not on P&amp;L until invoice split. Jan 16 $1,000 Canosan-horse still open.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="39" t="inlineStr">
+        <is>
+          <t>Fortuna Venus inventory</t>
+        </is>
+      </c>
+      <c r="B28" s="39" t="inlineStr">
+        <is>
+          <t>$20,000 OUT 5/9 LOCKED. Mercury native note: bronze head of a goddess, likely Venus. Parked Cost — not sold 2025, not dumped onto Art Sales/Consultant.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="39" t="inlineStr">
+        <is>
+          <t>Fortuna Roman Gold Belt</t>
+        </is>
+      </c>
+      <c r="B29" s="39" t="inlineStr">
+        <is>
+          <t>$45,000 OUT 7/21 LOCKED. Mercury native note: Roman Gold Belt. Parked Cost — not sold 2025, not dumped onto Art Sales/Consultant.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="39" t="inlineStr">
+        <is>
+          <t>Native CSV 2026-09-20</t>
+        </is>
+      </c>
+      <c r="B30" s="39" t="inlineStr">
+        <is>
+          <t>epgc-llc-transactions-2025-jan-01-to-2025-dec-31.csv is account 8291, same 2025 year already classified. 0 new unique Sent cash vs the 64. Failed Aysel 7/17 and Cancelled Erdal 1/8 are not cash.</t>
         </is>
       </c>
     </row>
@@ -7872,70 +7907,70 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="70" t="inlineStr">
-        <is>
-          <t>Mercury Checking 8291 — EPGC LLC (Choice Financial) 2025. 64 unique cash transactions. Coinbase ACH = investment. Newstar = jewelry COGS on intaglios/gems/scarabs. BoA 9922 draws and Koziol/Ariadne $150k are LOCKED not-P&amp;L (pass-through / owner transfer). David Aaron $13,595 is LOCKED EPGC Consultant (June). Wise $334.17 + $658.63 are LOCKED EPGC Consultant Fees (expertise write-ups). Aquinas Hobor $1,000 (2/4) is LOCKED books sold (EPGC Art Sales February; Cost TBD). Not tax advice.</t>
+      <c r="A1" s="69" t="inlineStr">
+        <is>
+          <t>Mercury Checking 8291 — EPGC LLC (Choice Financial) 2025. 64 unique cash transactions (Monarch IDs). Native Mercury CSV 2026-09-20 is the same 8291 year — 0 new unique Sent cash. Coinbase ACH = investment. Newstar = jewelry COGS on intaglios/gems/scarabs. Fortuna Venus $20k (5/9) + Roman Gold Belt $45k (7/21) LOCKED inventory (not sold Cost). BoA 9922 draws and Koziol/Ariadne $150k are LOCKED not-P&amp;L (pass-through / owner transfer). David Aaron $13,595 is LOCKED EPGC Consultant (June). Wise $334.17 + $658.63 are LOCKED EPGC Consultant Fees (expertise write-ups). Aquinas Hobor $1,000 (2/4) is LOCKED books sold (EPGC Art Sales February; Cost TBD). Not tax advice.</t>
         </is>
       </c>
     </row>
     <row r="2"/>
     <row r="3">
-      <c r="A3" s="71" t="inlineStr">
+      <c r="A3" s="70" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B3" s="71" t="inlineStr">
+      <c r="B3" s="70" t="inlineStr">
         <is>
           <t>Counterparty</t>
         </is>
       </c>
-      <c r="C3" s="71" t="inlineStr">
+      <c r="C3" s="70" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="D3" s="71" t="inlineStr">
+      <c r="D3" s="70" t="inlineStr">
         <is>
           <t>Direction</t>
         </is>
       </c>
-      <c r="E3" s="71" t="inlineStr">
+      <c r="E3" s="70" t="inlineStr">
         <is>
           <t>Bucket</t>
         </is>
       </c>
-      <c r="F3" s="71" t="inlineStr">
+      <c r="F3" s="70" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G3" s="71" t="inlineStr">
+      <c r="G3" s="70" t="inlineStr">
         <is>
           <t>Deal / object</t>
         </is>
       </c>
-      <c r="H3" s="71" t="inlineStr">
+      <c r="H3" s="70" t="inlineStr">
         <is>
           <t>Hits EPGC Art Sales?</t>
         </is>
       </c>
-      <c r="I3" s="71" t="inlineStr">
+      <c r="I3" s="70" t="inlineStr">
         <is>
           <t>Hits EPGC Consultant?</t>
         </is>
       </c>
-      <c r="J3" s="71" t="inlineStr">
+      <c r="J3" s="70" t="inlineStr">
         <is>
           <t>Monarch category</t>
         </is>
       </c>
-      <c r="K3" s="71" t="inlineStr">
+      <c r="K3" s="70" t="inlineStr">
         <is>
           <t>Original statement</t>
         </is>
       </c>
-      <c r="L3" s="71" t="inlineStr">
+      <c r="L3" s="70" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -7960,7 +7995,7 @@
           <t>OUT</t>
         </is>
       </c>
-      <c r="E4" s="72" t="inlineStr">
+      <c r="E4" s="71" t="inlineStr">
         <is>
           <t>ART_PURCHASE</t>
         </is>
@@ -7992,12 +8027,12 @@
       </c>
       <c r="K4" s="44" t="inlineStr">
         <is>
-          <t>Merchant name: Erdal Dere (Fortuna)</t>
+          <t>Merchant name: Erdal Dere (Fortuna); Mercury native: J.K. New York Collection | Send Money transaction initiated on Mercury</t>
         </is>
       </c>
       <c r="L4" s="14" t="inlineStr">
         <is>
-          <t>Fortuna / Erdal Dere. Matches Art Sales Cost $13,000; Berk sold it 1/10 for $14,000.</t>
+          <t>Fortuna / Erdal Dere. Mercury native note: J.K. New York Collection. Matches Art Sales Cost $13,000; Berk sold it 1/10 for $14,000. Same-day Cancelled ACH to Erdal Dere (closed) is not cash.</t>
         </is>
       </c>
     </row>
@@ -8020,7 +8055,7 @@
           <t>IN</t>
         </is>
       </c>
-      <c r="E5" s="73" t="inlineStr">
+      <c r="E5" s="72" t="inlineStr">
         <is>
           <t>ART_SALE</t>
         </is>
@@ -8072,7 +8107,7 @@
           <t>EOEB LLC</t>
         </is>
       </c>
-      <c r="C6" s="74" t="n">
+      <c r="C6" s="73" t="n">
         <v>1000</v>
       </c>
       <c r="D6" s="44" t="inlineStr">
@@ -8140,7 +8175,7 @@
           <t>OUT</t>
         </is>
       </c>
-      <c r="E7" s="75" t="inlineStr">
+      <c r="E7" s="74" t="inlineStr">
         <is>
           <t>TRANSFER</t>
         </is>
@@ -8200,7 +8235,7 @@
           <t>IN</t>
         </is>
       </c>
-      <c r="E8" s="73" t="inlineStr">
+      <c r="E8" s="72" t="inlineStr">
         <is>
           <t>ART_SALE</t>
         </is>
@@ -8260,7 +8295,7 @@
           <t>IN</t>
         </is>
       </c>
-      <c r="E9" s="73" t="inlineStr">
+      <c r="E9" s="72" t="inlineStr">
         <is>
           <t>ART_SALE</t>
         </is>
@@ -8320,7 +8355,7 @@
           <t>OUT</t>
         </is>
       </c>
-      <c r="E10" s="75" t="inlineStr">
+      <c r="E10" s="74" t="inlineStr">
         <is>
           <t>TEST</t>
         </is>
@@ -8352,7 +8387,7 @@
       </c>
       <c r="K10" s="44" t="inlineStr">
         <is>
-          <t>Merchant name: Jamal M Rifai</t>
+          <t>Merchant name: Jamal M Rifai; Mercury native: via mercury.com | Send Money transaction initiated on Mercury</t>
         </is>
       </c>
       <c r="L10" s="14" t="inlineStr">
@@ -8380,7 +8415,7 @@
           <t>IN</t>
         </is>
       </c>
-      <c r="E11" s="75" t="inlineStr">
+      <c r="E11" s="74" t="inlineStr">
         <is>
           <t>TEST</t>
         </is>
@@ -8440,7 +8475,7 @@
           <t>IN</t>
         </is>
       </c>
-      <c r="E12" s="73" t="inlineStr">
+      <c r="E12" s="72" t="inlineStr">
         <is>
           <t>ART_SALE</t>
         </is>
@@ -8500,7 +8535,7 @@
           <t>OUT</t>
         </is>
       </c>
-      <c r="E13" s="75" t="inlineStr">
+      <c r="E13" s="74" t="inlineStr">
         <is>
           <t>TRANSFER</t>
         </is>
@@ -8560,7 +8595,7 @@
           <t>OUT</t>
         </is>
       </c>
-      <c r="E14" s="75" t="inlineStr">
+      <c r="E14" s="74" t="inlineStr">
         <is>
           <t>TEST</t>
         </is>
@@ -8592,7 +8627,7 @@
       </c>
       <c r="K14" s="44" t="inlineStr">
         <is>
-          <t>Merchant name: Jamal M Rifai</t>
+          <t>Merchant name: Jamal M Rifai; Mercury native: From EPGC LLC via mercury.com | Send Money transaction initiated on Mercury</t>
         </is>
       </c>
       <c r="L14" s="14" t="inlineStr">
@@ -8620,7 +8655,7 @@
           <t>OUT</t>
         </is>
       </c>
-      <c r="E15" s="75" t="inlineStr">
+      <c r="E15" s="74" t="inlineStr">
         <is>
           <t>TEST</t>
         </is>
@@ -8652,7 +8687,7 @@
       </c>
       <c r="K15" s="44" t="inlineStr">
         <is>
-          <t>Merchant name: Plutus &amp; Mnemosyne, LLC</t>
+          <t>Merchant name: Plutus &amp; Mnemosyne, LLC; Mercury native: via mercury.com | Send Money transaction initiated on Mercury</t>
         </is>
       </c>
       <c r="L15" s="14" t="inlineStr">
@@ -8680,7 +8715,7 @@
           <t>IN</t>
         </is>
       </c>
-      <c r="E16" s="75" t="inlineStr">
+      <c r="E16" s="74" t="inlineStr">
         <is>
           <t>TEST</t>
         </is>
@@ -8740,7 +8775,7 @@
           <t>OUT</t>
         </is>
       </c>
-      <c r="E17" s="72" t="inlineStr">
+      <c r="E17" s="71" t="inlineStr">
         <is>
           <t>ART_PURCHASE</t>
         </is>
@@ -8772,7 +8807,7 @@
       </c>
       <c r="K17" s="44" t="inlineStr">
         <is>
-          <t>Merchant name: Plutus &amp; Mnemosyne, LLC</t>
+          <t>Merchant name: Plutus &amp; Mnemosyne, LLC; Mercury native: From EPGC LLC via mercury.com | Send Money transaction initiated on Mercury</t>
         </is>
       </c>
       <c r="L17" s="14" t="inlineStr">
@@ -8792,7 +8827,7 @@
           <t>EOEB LLC</t>
         </is>
       </c>
-      <c r="C18" s="74" t="n">
+      <c r="C18" s="73" t="n">
         <v>14000</v>
       </c>
       <c r="D18" s="44" t="inlineStr">
@@ -8852,7 +8887,7 @@
           <t>EOEB LLC</t>
         </is>
       </c>
-      <c r="C19" s="74" t="n">
+      <c r="C19" s="73" t="n">
         <v>21000</v>
       </c>
       <c r="D19" s="44" t="inlineStr">
@@ -8912,7 +8947,7 @@
           <t>Erdal Dere (Fortuna)</t>
         </is>
       </c>
-      <c r="C20" s="74" t="n">
+      <c r="C20" s="10" t="n">
         <v>-20000</v>
       </c>
       <c r="D20" s="44" t="inlineStr">
@@ -8920,19 +8955,19 @@
           <t>OUT</t>
         </is>
       </c>
-      <c r="E20" s="72" t="inlineStr">
+      <c r="E20" s="71" t="inlineStr">
         <is>
           <t>ART_PURCHASE</t>
         </is>
       </c>
-      <c r="F20" s="40" t="inlineStr">
-        <is>
-          <t>ASK</t>
+      <c r="F20" s="39" t="inlineStr">
+        <is>
+          <t>LOCKED</t>
         </is>
       </c>
       <c r="G20" s="44" t="inlineStr">
         <is>
-          <t>Fortuna / Erdal — inventory vs other</t>
+          <t>Bronze head of a goddess, likely Venus — inventory Cost</t>
         </is>
       </c>
       <c r="H20" s="44" t="inlineStr">
@@ -8952,12 +8987,12 @@
       </c>
       <c r="K20" s="44" t="inlineStr">
         <is>
-          <t>Merchant name: Erdal Dere (Fortuna)</t>
+          <t>Merchant name: Erdal Dere (Fortuna); Mercury native: For bronze head of a goddess, likely Venus | Send Money transaction initiated on Mercury</t>
         </is>
       </c>
       <c r="L20" s="14" t="inlineStr">
         <is>
-          <t>After seals $13,000. Object name? Inventory purchase (COGS when sold) or something else?</t>
+          <t>Mercury native 2025 CSV note: 'For bronze head of a goddess, likely Venus'. Inventory purchase from Fortuna / Erdal. Not sold on 2025 Art Sales — parked Cost, not in sold-lot Cost (avoid double count). Not dumped onto Consultant or Art Sales P&amp;L.</t>
         </is>
       </c>
     </row>
@@ -8972,7 +9007,7 @@
           <t>EOEB LLC</t>
         </is>
       </c>
-      <c r="C21" s="74" t="n">
+      <c r="C21" s="73" t="n">
         <v>16200</v>
       </c>
       <c r="D21" s="44" t="inlineStr">
@@ -9032,7 +9067,7 @@
           <t>EOEB LLC</t>
         </is>
       </c>
-      <c r="C22" s="74" t="n">
+      <c r="C22" s="73" t="n">
         <v>3300</v>
       </c>
       <c r="D22" s="44" t="inlineStr">
@@ -9092,7 +9127,7 @@
           <t>EOEB LLC</t>
         </is>
       </c>
-      <c r="C23" s="74" t="n">
+      <c r="C23" s="73" t="n">
         <v>25000</v>
       </c>
       <c r="D23" s="44" t="inlineStr">
@@ -9220,7 +9255,7 @@
           <t>OUT</t>
         </is>
       </c>
-      <c r="E25" s="75" t="inlineStr">
+      <c r="E25" s="74" t="inlineStr">
         <is>
           <t>TRANSFER</t>
         </is>
@@ -9272,7 +9307,7 @@
           <t>EOEB LLC</t>
         </is>
       </c>
-      <c r="C26" s="74" t="n">
+      <c r="C26" s="73" t="n">
         <v>2000</v>
       </c>
       <c r="D26" s="44" t="inlineStr">
@@ -9340,7 +9375,7 @@
           <t>OUT</t>
         </is>
       </c>
-      <c r="E27" s="73" t="inlineStr">
+      <c r="E27" s="72" t="inlineStr">
         <is>
           <t>EPGC_EXPENSE</t>
         </is>
@@ -9392,7 +9427,7 @@
           <t>L5</t>
         </is>
       </c>
-      <c r="C28" s="74" t="n">
+      <c r="C28" s="73" t="n">
         <v>8534.790000000001</v>
       </c>
       <c r="D28" s="44" t="inlineStr">
@@ -9452,7 +9487,7 @@
           <t>L5</t>
         </is>
       </c>
-      <c r="C29" s="74" t="n">
+      <c r="C29" s="73" t="n">
         <v>2500</v>
       </c>
       <c r="D29" s="44" t="inlineStr">
@@ -9512,7 +9547,7 @@
           <t>L5</t>
         </is>
       </c>
-      <c r="C30" s="74" t="n">
+      <c r="C30" s="73" t="n">
         <v>50000</v>
       </c>
       <c r="D30" s="44" t="inlineStr">
@@ -9572,7 +9607,7 @@
           <t>Aysel Dere</t>
         </is>
       </c>
-      <c r="C31" s="74" t="n">
+      <c r="C31" s="73" t="n">
         <v>50000</v>
       </c>
       <c r="D31" s="44" t="inlineStr">
@@ -9592,7 +9627,7 @@
       </c>
       <c r="G31" s="44" t="inlineStr">
         <is>
-          <t>Aysel Dere $50,000 IN</t>
+          <t>Aysel Dere $50,000 IN on Monarch — NOT on Mercury native Sent</t>
         </is>
       </c>
       <c r="H31" s="44" t="inlineStr">
@@ -9617,7 +9652,7 @@
       </c>
       <c r="L31" s="14" t="inlineStr">
         <is>
-          <t>Same week as L5 $50k, Fortuna $45k OUT (7/21), Erdal $26k IN (7/24). Sale, family/related transfer, or inventory reverse?</t>
+          <t>Monarch 7/18 +$50,000 IN. Mercury native 2025 CSV (user upload 2026-09-20) has no Sent Aysel cash. Native has Failed $50,000 OUT 7/17 'Recipient account does not exist'. Keep on ASK — do not dump onto Art Sales or Consultant. Is the Monarch IN a phantom of the failed send?</t>
         </is>
       </c>
     </row>
@@ -9632,7 +9667,7 @@
           <t>Erdal Dere (Fortuna)</t>
         </is>
       </c>
-      <c r="C32" s="74" t="n">
+      <c r="C32" s="10" t="n">
         <v>-45000</v>
       </c>
       <c r="D32" s="44" t="inlineStr">
@@ -9640,19 +9675,19 @@
           <t>OUT</t>
         </is>
       </c>
-      <c r="E32" s="72" t="inlineStr">
+      <c r="E32" s="71" t="inlineStr">
         <is>
           <t>ART_PURCHASE</t>
         </is>
       </c>
-      <c r="F32" s="40" t="inlineStr">
-        <is>
-          <t>ASK</t>
+      <c r="F32" s="39" t="inlineStr">
+        <is>
+          <t>LOCKED</t>
         </is>
       </c>
       <c r="G32" s="44" t="inlineStr">
         <is>
-          <t>Fortuna / Erdal — inventory vs other</t>
+          <t>Roman Gold Belt — inventory Cost</t>
         </is>
       </c>
       <c r="H32" s="44" t="inlineStr">
@@ -9672,12 +9707,12 @@
       </c>
       <c r="K32" s="44" t="inlineStr">
         <is>
-          <t>Merchant name: Erdal Dere (Fortuna)</t>
+          <t>Merchant name: Erdal Dere (Fortuna); Mercury native: From EPGC LLC via mercury.com | Roman Gold Belt | Send Money transaction initiated on Mercury</t>
         </is>
       </c>
       <c r="L32" s="14" t="inlineStr">
         <is>
-          <t>Object name? Ties to Aysel $50k / Erdal $26k the same week?</t>
+          <t>Mercury native 2025 CSV note: Roman Gold Belt. Inventory purchase from Fortuna / Erdal. Not sold on 2025 Art Sales — parked Cost, not in sold-lot Cost. Same week as L5 $50k / Monarch Aysel $50k ASK / Erdal $26k IN.</t>
         </is>
       </c>
     </row>
@@ -9692,7 +9727,7 @@
           <t>ERDAL DERE</t>
         </is>
       </c>
-      <c r="C33" s="74" t="n">
+      <c r="C33" s="73" t="n">
         <v>26000</v>
       </c>
       <c r="D33" s="44" t="inlineStr">
@@ -9700,7 +9735,7 @@
           <t>IN</t>
         </is>
       </c>
-      <c r="E33" s="73" t="inlineStr">
+      <c r="E33" s="72" t="inlineStr">
         <is>
           <t>ART_SALE</t>
         </is>
@@ -9760,7 +9795,7 @@
           <t>OUT</t>
         </is>
       </c>
-      <c r="E34" s="75" t="inlineStr">
+      <c r="E34" s="74" t="inlineStr">
         <is>
           <t>TRANSFER</t>
         </is>
@@ -9812,7 +9847,7 @@
           <t>Erdal Dere (Fortuna)</t>
         </is>
       </c>
-      <c r="C35" s="74" t="n">
+      <c r="C35" s="73" t="n">
         <v>-20000</v>
       </c>
       <c r="D35" s="44" t="inlineStr">
@@ -9820,7 +9855,7 @@
           <t>OUT</t>
         </is>
       </c>
-      <c r="E35" s="72" t="inlineStr">
+      <c r="E35" s="71" t="inlineStr">
         <is>
           <t>ART_PURCHASE</t>
         </is>
@@ -9832,7 +9867,7 @@
       </c>
       <c r="G35" s="44" t="inlineStr">
         <is>
-          <t>Fortuna / Erdal — inventory vs other</t>
+          <t>Fortuna / Erdal — object still unnamed</t>
         </is>
       </c>
       <c r="H35" s="44" t="inlineStr">
@@ -9852,12 +9887,12 @@
       </c>
       <c r="K35" s="44" t="inlineStr">
         <is>
-          <t>Merchant name: Erdal Dere (Fortuna)</t>
+          <t>Merchant name: Erdal Dere (Fortuna); Mercury native: From EPGC LLC via mercury.com | Send Money transaction initiated on Mercury</t>
         </is>
       </c>
       <c r="L35" s="14" t="inlineStr">
         <is>
-          <t>Object name?</t>
+          <t>Same $20,000 OUT as Mercury native initiated 2025-08-18 / Monarch posted 2025-08-15. No object name in the native memo ('From EPGC LLC via mercury.com'). Inventory vs other? Do not add to sold Cost until named. Not a second unique txn.</t>
         </is>
       </c>
     </row>
@@ -9872,7 +9907,7 @@
           <t>EOEB LLC</t>
         </is>
       </c>
-      <c r="C36" s="74" t="n">
+      <c r="C36" s="73" t="n">
         <v>10000</v>
       </c>
       <c r="D36" s="44" t="inlineStr">
@@ -9932,7 +9967,7 @@
           <t>L5</t>
         </is>
       </c>
-      <c r="C37" s="74" t="n">
+      <c r="C37" s="73" t="n">
         <v>5042</v>
       </c>
       <c r="D37" s="44" t="inlineStr">
@@ -10000,7 +10035,7 @@
           <t>OUT</t>
         </is>
       </c>
-      <c r="E38" s="76" t="inlineStr">
+      <c r="E38" s="75" t="inlineStr">
         <is>
           <t>INVESTMENT</t>
         </is>
@@ -10052,7 +10087,7 @@
           <t>EOEB LLC</t>
         </is>
       </c>
-      <c r="C39" s="74" t="n">
+      <c r="C39" s="73" t="n">
         <v>5000</v>
       </c>
       <c r="D39" s="44" t="inlineStr">
@@ -10112,7 +10147,7 @@
           <t>L5</t>
         </is>
       </c>
-      <c r="C40" s="74" t="n">
+      <c r="C40" s="73" t="n">
         <v>9119.27</v>
       </c>
       <c r="D40" s="44" t="inlineStr">
@@ -10180,7 +10215,7 @@
           <t>OUT</t>
         </is>
       </c>
-      <c r="E41" s="75" t="inlineStr">
+      <c r="E41" s="74" t="inlineStr">
         <is>
           <t>TRANSFER</t>
         </is>
@@ -10232,7 +10267,7 @@
           <t>EOEB LLC</t>
         </is>
       </c>
-      <c r="C42" s="74" t="n">
+      <c r="C42" s="73" t="n">
         <v>3100</v>
       </c>
       <c r="D42" s="44" t="inlineStr">
@@ -10300,7 +10335,7 @@
           <t>OUT</t>
         </is>
       </c>
-      <c r="E43" s="76" t="inlineStr">
+      <c r="E43" s="75" t="inlineStr">
         <is>
           <t>INVESTMENT</t>
         </is>
@@ -10360,7 +10395,7 @@
           <t>OUT</t>
         </is>
       </c>
-      <c r="E44" s="76" t="inlineStr">
+      <c r="E44" s="75" t="inlineStr">
         <is>
           <t>INVESTMENT</t>
         </is>
@@ -10412,7 +10447,7 @@
           <t>EOEB LLC</t>
         </is>
       </c>
-      <c r="C45" s="74" t="n">
+      <c r="C45" s="73" t="n">
         <v>10000</v>
       </c>
       <c r="D45" s="44" t="inlineStr">
@@ -10480,7 +10515,7 @@
           <t>OUT</t>
         </is>
       </c>
-      <c r="E46" s="75" t="inlineStr">
+      <c r="E46" s="74" t="inlineStr">
         <is>
           <t>TRANSFER</t>
         </is>
@@ -10532,7 +10567,7 @@
           <t>ERDAL DERE</t>
         </is>
       </c>
-      <c r="C47" s="74" t="n">
+      <c r="C47" s="73" t="n">
         <v>25000</v>
       </c>
       <c r="D47" s="44" t="inlineStr">
@@ -10540,7 +10575,7 @@
           <t>IN</t>
         </is>
       </c>
-      <c r="E47" s="73" t="inlineStr">
+      <c r="E47" s="72" t="inlineStr">
         <is>
           <t>ART_SALE</t>
         </is>
@@ -10600,7 +10635,7 @@
           <t>OUT</t>
         </is>
       </c>
-      <c r="E48" s="72" t="inlineStr">
+      <c r="E48" s="71" t="inlineStr">
         <is>
           <t>COGS_JEWELRY</t>
         </is>
@@ -10632,7 +10667,7 @@
       </c>
       <c r="K48" s="44" t="inlineStr">
         <is>
-          <t>Merchant name: Newstar Jewelers</t>
+          <t>Merchant name: Newstar Jewelers; Mercury native: From EPGC LLC via mercury.com | 1 of 3 payments | Send Money transaction initiated on Mercury</t>
         </is>
       </c>
       <c r="L48" s="14" t="inlineStr">
@@ -10652,7 +10687,7 @@
           <t>EOEB LLC</t>
         </is>
       </c>
-      <c r="C49" s="74" t="n">
+      <c r="C49" s="73" t="n">
         <v>16000</v>
       </c>
       <c r="D49" s="44" t="inlineStr">
@@ -10720,7 +10755,7 @@
           <t>IN</t>
         </is>
       </c>
-      <c r="E50" s="76" t="inlineStr">
+      <c r="E50" s="75" t="inlineStr">
         <is>
           <t>PASS_THROUGH</t>
         </is>
@@ -10780,7 +10815,7 @@
           <t>OUT</t>
         </is>
       </c>
-      <c r="E51" s="76" t="inlineStr">
+      <c r="E51" s="75" t="inlineStr">
         <is>
           <t>PASS_THROUGH</t>
         </is>
@@ -10812,7 +10847,7 @@
       </c>
       <c r="K51" s="44" t="inlineStr">
         <is>
-          <t>Merchant name: Ariadne Demirjian LLC</t>
+          <t>Merchant name: Ariadne Demirjian LLC; Mercury native: via mercury.com; Vendor: Ariadne Demirjian LLC Roth 401k Account 5386-8600 | Send Money transaction initiated on Mercury</t>
         </is>
       </c>
       <c r="L51" s="14" t="inlineStr">
@@ -10832,7 +10867,7 @@
           <t>L5</t>
         </is>
       </c>
-      <c r="C52" s="74" t="n">
+      <c r="C52" s="73" t="n">
         <v>7500</v>
       </c>
       <c r="D52" s="44" t="inlineStr">
@@ -10892,7 +10927,7 @@
           <t>EOEB LLC</t>
         </is>
       </c>
-      <c r="C53" s="74" t="n">
+      <c r="C53" s="73" t="n">
         <v>1500</v>
       </c>
       <c r="D53" s="44" t="inlineStr">
@@ -10960,7 +10995,7 @@
           <t>OUT</t>
         </is>
       </c>
-      <c r="E54" s="73" t="inlineStr">
+      <c r="E54" s="72" t="inlineStr">
         <is>
           <t>EPGC_EXPENSE</t>
         </is>
@@ -11012,7 +11047,7 @@
           <t>EOEB LLC</t>
         </is>
       </c>
-      <c r="C55" s="74" t="n">
+      <c r="C55" s="73" t="n">
         <v>2170</v>
       </c>
       <c r="D55" s="44" t="inlineStr">
@@ -11080,7 +11115,7 @@
           <t>OUT</t>
         </is>
       </c>
-      <c r="E56" s="76" t="inlineStr">
+      <c r="E56" s="75" t="inlineStr">
         <is>
           <t>INVESTMENT</t>
         </is>
@@ -11132,7 +11167,7 @@
           <t>ERDAL DERE</t>
         </is>
       </c>
-      <c r="C57" s="74" t="n">
+      <c r="C57" s="73" t="n">
         <v>6000</v>
       </c>
       <c r="D57" s="44" t="inlineStr">
@@ -11140,7 +11175,7 @@
           <t>IN</t>
         </is>
       </c>
-      <c r="E57" s="73" t="inlineStr">
+      <c r="E57" s="72" t="inlineStr">
         <is>
           <t>ART_SALE</t>
         </is>
@@ -11200,7 +11235,7 @@
           <t>OUT</t>
         </is>
       </c>
-      <c r="E58" s="72" t="inlineStr">
+      <c r="E58" s="71" t="inlineStr">
         <is>
           <t>COGS_JEWELRY</t>
         </is>
@@ -11232,7 +11267,7 @@
       </c>
       <c r="K58" s="44" t="inlineStr">
         <is>
-          <t>Merchant name: Newstar Jewelers</t>
+          <t>Merchant name: Newstar Jewelers; Mercury native: From EPGC LLC via mercury.com | Send Money transaction initiated on Mercury</t>
         </is>
       </c>
       <c r="L58" s="14" t="inlineStr">
@@ -11260,7 +11295,7 @@
           <t>OUT</t>
         </is>
       </c>
-      <c r="E59" s="76" t="inlineStr">
+      <c r="E59" s="75" t="inlineStr">
         <is>
           <t>INVESTMENT</t>
         </is>
@@ -11320,7 +11355,7 @@
           <t>OUT</t>
         </is>
       </c>
-      <c r="E60" s="76" t="inlineStr">
+      <c r="E60" s="75" t="inlineStr">
         <is>
           <t>INVESTMENT</t>
         </is>
@@ -11380,7 +11415,7 @@
           <t>OUT</t>
         </is>
       </c>
-      <c r="E61" s="76" t="inlineStr">
+      <c r="E61" s="75" t="inlineStr">
         <is>
           <t>INVESTMENT</t>
         </is>
@@ -11440,7 +11475,7 @@
           <t>OUT</t>
         </is>
       </c>
-      <c r="E62" s="75" t="inlineStr">
+      <c r="E62" s="74" t="inlineStr">
         <is>
           <t>REIMBURSE</t>
         </is>
@@ -11500,7 +11535,7 @@
           <t>IN</t>
         </is>
       </c>
-      <c r="E63" s="75" t="inlineStr">
+      <c r="E63" s="74" t="inlineStr">
         <is>
           <t>REIMBURSE</t>
         </is>
@@ -11552,7 +11587,7 @@
           <t>L5</t>
         </is>
       </c>
-      <c r="C64" s="74" t="n">
+      <c r="C64" s="73" t="n">
         <v>4700.26</v>
       </c>
       <c r="D64" s="44" t="inlineStr">
@@ -11620,7 +11655,7 @@
           <t>OUT</t>
         </is>
       </c>
-      <c r="E65" s="76" t="inlineStr">
+      <c r="E65" s="75" t="inlineStr">
         <is>
           <t>INVESTMENT</t>
         </is>
@@ -11680,7 +11715,7 @@
           <t>IN</t>
         </is>
       </c>
-      <c r="E66" s="76" t="inlineStr">
+      <c r="E66" s="75" t="inlineStr">
         <is>
           <t>INVESTMENT</t>
         </is>
@@ -11740,7 +11775,7 @@
           <t>OUT</t>
         </is>
       </c>
-      <c r="E67" s="72" t="inlineStr">
+      <c r="E67" s="71" t="inlineStr">
         <is>
           <t>COGS_JEWELRY</t>
         </is>
@@ -11772,7 +11807,7 @@
       </c>
       <c r="K67" s="44" t="inlineStr">
         <is>
-          <t>From EPGC LLC via mercury.com 3 of 3; Merchant name: Newstar Jewelers</t>
+          <t>From EPGC LLC via mercury.com 3 of 3; Merchant name: Newstar Jewelers; Mercury native: From EPGC LLC via mercury.com 3 of 3 | Send Money transaction initiated on Mercury</t>
         </is>
       </c>
       <c r="L67" s="14" t="inlineStr">
